--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MPCI QC\Desktop\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746E6D7C-AAAE-44A1-911D-C63F3E38A05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F32A99-063D-4A3F-BC38-CDFB67FB1049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14697" uniqueCount="3588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14715" uniqueCount="3595">
   <si>
     <t>PDS No.</t>
   </si>
@@ -10831,6 +10831,27 @@
   </si>
   <si>
     <t>Pet 225ml Micro Round Milky White 25mm 19.5gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0437</t>
+  </si>
+  <si>
+    <t>MP0437.1</t>
+  </si>
+  <si>
+    <t>Pet 750ml Dot Sharbat Clear 28mm 46gm Bottle</t>
+  </si>
+  <si>
+    <t>Dot Sharbat</t>
+  </si>
+  <si>
+    <t>73.70 ± 1.20</t>
+  </si>
+  <si>
+    <t>269.00 ± 1.20</t>
+  </si>
+  <si>
+    <t>760.00 ± 6.00</t>
   </si>
 </sst>
 </file>
@@ -11025,6 +11046,41 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -11528,6 +11584,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -11546,48 +11609,6 @@
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -11602,30 +11623,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CF846D4E-484F-44ED-AA71-DA107E226D36}" name="Table1" displayName="Table1" ref="A1:U791" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
-  <autoFilter ref="A1:U791" xr:uid="{CF846D4E-484F-44ED-AA71-DA107E226D36}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7B4645F-B9CB-45ED-B436-FA2B491E712F}" name="Table1" displayName="Table1" ref="A1:U792" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U792" xr:uid="{C7B4645F-B9CB-45ED-B436-FA2B491E712F}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{22599428-1D8C-44D8-B54B-A850AAC4CFCC}" name="PDS No." dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{76732FCE-B14A-4A8D-B8CB-7083D32B10EC}" name="STATUS" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{D8691F8D-CE0B-4133-B4BA-1E185FC09EAB}" name="Product Code" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{FDC39E9B-7014-4CBA-B046-0EFE169BA679}" name="Old Item Code" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{AEF93A91-4197-4FFA-A16E-343B786E720B}" name="Item Code" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{DEE7CD08-06AA-45E3-BB5F-5B8E83B35ADD}" name="Item Name" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{3780E491-4FF2-429F-B070-2863DF29C828}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{CAE6F6E3-B0B7-45D2-85A9-56E2D2A14C24}" name="List of Matrix::Total Pcs" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{CD898384-D350-44C8-B419-02234645B288}" name="List of Matrix::Total Pouch Used" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{0D5C9CE1-04B0-4ABE-AB4F-4B132204ADD5}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{404197D5-0EEB-4F25-A5C3-957479426048}" name="Technical DataSheet::Product Shape" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{8B4040DD-3D10-4F88-B80F-156D0E2A5E16}" name="Corrugated Box Code" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{82CB852A-F795-4373-9477-6B7DFC4B6B57}" name="Corrugated Box Size" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{C4B4684D-1DAE-4406-A619-5891C4DC45E5}" name="Pouch Product Code" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{826C35AE-BE8B-4C96-B92B-06C391C31AF5}" name="Pouch Size" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{FEE1C17D-DAB3-4A04-BF33-8D90542086FB}" name="Tape Roll Product Code" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{C7B8CFC8-5C87-4C1A-A313-D79792CB56D9}" name="Tape Roll Size" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{CC3D7A2D-DA74-469D-ACDF-2AD87B2DF170}" name="Technical DataSheet::Body Dia Major" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{EB54B1C2-1F44-4B67-87E2-C30CF1A4760C}" name="Technical DataSheet::Total Height" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{53B02DC4-EFBF-4E52-B71F-C0626C1DD071}" name="Technical DataSheet::Weight" dataDxfId="1"/>
-    <tableColumn id="21" xr3:uid="{4B4DC961-9478-455B-AE31-8CC55EB22A91}" name="Technical DataSheet::OFC" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{DE07036F-5C88-4F2B-A42F-D6E23CDFB773}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{77FCC7D3-5611-4B54-89C7-19908EC40970}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{8505469F-FAF9-4E71-B502-0A737D9E766B}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{C381169D-2361-4A52-8EAA-80CD07723169}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{77B6E929-972B-46F7-9292-D8B8590C829B}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{4B2583FC-4BA4-489B-8BE3-23209ABA2EA7}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{BB540808-FBC5-4FF6-9FC4-755269447142}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{61F77916-9C19-4CC6-A54B-CA4B7870B582}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{63650A7B-5EDD-41FE-B3FE-DA3FB8ECC7ED}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{03481BF2-EFC8-4B2C-8C4D-C0D523E4C785}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{068AEA08-659E-490E-86A8-9B52039EA404}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{8D635DBF-EA2F-4468-9B86-6D563825FB42}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{C123D33E-B73E-408F-B885-3F4D4B80B498}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{9C65CCAF-8852-41BB-9AAE-6E60D7D63D39}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{8CD001FF-8A53-4D7D-9A38-34C9532259A0}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{1FFB8C65-AFF6-486C-8B34-37A2A87FD6C6}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{F7E42296-C5FB-4BEC-932B-1CBD63F6AD59}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{F2FDF24D-A50F-40E4-BE74-0EB1C808C581}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{D9A293CC-7DAD-4ADE-8C2D-37009B344782}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{648E86F2-4CB2-4813-ACCE-F3B7391C10D1}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{E45A7D77-E41C-4C07-AD6C-C828ADC39611}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11928,7 +11949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U791"/>
+  <dimension ref="A1:U792"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -61061,68 +61082,129 @@
       </c>
     </row>
     <row r="791" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A791" s="9">
+      <c r="A791" s="4">
         <v>790</v>
       </c>
-      <c r="B791" s="10"/>
-      <c r="C791" s="11" t="s">
+      <c r="B791" s="5"/>
+      <c r="C791" s="6" t="s">
         <v>2866</v>
       </c>
-      <c r="D791" s="10"/>
-      <c r="E791" s="11" t="s">
+      <c r="D791" s="5"/>
+      <c r="E791" s="6" t="s">
         <v>3586</v>
       </c>
-      <c r="F791" s="11" t="s">
+      <c r="F791" s="6" t="s">
         <v>3587</v>
       </c>
-      <c r="G791" s="11" t="s">
+      <c r="G791" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H791" s="11" t="s">
+      <c r="H791" s="6" t="s">
         <v>882</v>
       </c>
-      <c r="I791" s="11" t="s">
+      <c r="I791" s="6" t="s">
         <v>146</v>
       </c>
       <c r="J791" s="13" t="s">
         <v>420</v>
       </c>
-      <c r="K791" s="11" t="s">
+      <c r="K791" s="6" t="s">
         <v>1844</v>
       </c>
-      <c r="L791" s="11" t="s">
+      <c r="L791" s="6" t="s">
         <v>690</v>
       </c>
-      <c r="M791" s="11" t="s">
+      <c r="M791" s="6" t="s">
         <v>691</v>
       </c>
-      <c r="N791" s="11" t="s">
+      <c r="N791" s="6" t="s">
         <v>764</v>
       </c>
-      <c r="O791" s="11" t="s">
+      <c r="O791" s="6" t="s">
         <v>765</v>
       </c>
-      <c r="P791" s="11" t="s">
+      <c r="P791" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="Q791" s="11" t="s">
+      <c r="Q791" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="R791" s="11" t="s">
+      <c r="R791" s="6" t="s">
         <v>2444</v>
       </c>
-      <c r="S791" s="11" t="s">
+      <c r="S791" s="6" t="s">
         <v>2445</v>
       </c>
-      <c r="T791" s="11" t="s">
+      <c r="T791" s="6" t="s">
         <v>2098</v>
       </c>
-      <c r="U791" s="12" t="s">
+      <c r="U791" s="7" t="s">
         <v>2869</v>
       </c>
     </row>
+    <row r="792" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A792" s="9">
+        <v>791</v>
+      </c>
+      <c r="B792" s="10"/>
+      <c r="C792" s="11" t="s">
+        <v>3588</v>
+      </c>
+      <c r="D792" s="10"/>
+      <c r="E792" s="11" t="s">
+        <v>3589</v>
+      </c>
+      <c r="F792" s="11" t="s">
+        <v>3590</v>
+      </c>
+      <c r="G792" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H792" s="11" t="s">
+        <v>780</v>
+      </c>
+      <c r="I792" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="J792" s="13" t="s">
+        <v>781</v>
+      </c>
+      <c r="K792" s="11" t="s">
+        <v>3591</v>
+      </c>
+      <c r="L792" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="M792" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="N792" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="O792" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="P792" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q792" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="R792" s="11" t="s">
+        <v>3592</v>
+      </c>
+      <c r="S792" s="11" t="s">
+        <v>3593</v>
+      </c>
+      <c r="T792" s="11" t="s">
+        <v>2526</v>
+      </c>
+      <c r="U792" s="12" t="s">
+        <v>3594</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="yFGcRxW8voEqw+tYdaTErjyVnQ89n8eaWLgrlI+1HBSSFgCWyD8bqL9qudhFNGSTdsOrynNzz2CgSy88zjzeTw==" saltValue="GHCk5qiltSZnAIJB7YyM0Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="R6fVvvaP3NLaqCAeoFTDtwd3/iDFnfn+Kk6N77xN523r3cNXiKUc8wA9+5h9a6P5p07jLi8JWyiHC/08ANHMJw==" saltValue="i1U8K8ba9FfbNTASM8MmLA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MPCI QC\Desktop\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F32A99-063D-4A3F-BC38-CDFB67FB1049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68542EE2-EDEB-44CF-9903-1FF0EBA78747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11623,30 +11623,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7B4645F-B9CB-45ED-B436-FA2B491E712F}" name="Table1" displayName="Table1" ref="A1:U792" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U792" xr:uid="{C7B4645F-B9CB-45ED-B436-FA2B491E712F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C014C06-7C16-4A12-8056-F74D2781492F}" name="Table1" displayName="Table1" ref="A1:U792" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U792" xr:uid="{1C014C06-7C16-4A12-8056-F74D2781492F}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{DE07036F-5C88-4F2B-A42F-D6E23CDFB773}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{77FCC7D3-5611-4B54-89C7-19908EC40970}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{8505469F-FAF9-4E71-B502-0A737D9E766B}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{C381169D-2361-4A52-8EAA-80CD07723169}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{77B6E929-972B-46F7-9292-D8B8590C829B}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{4B2583FC-4BA4-489B-8BE3-23209ABA2EA7}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{BB540808-FBC5-4FF6-9FC4-755269447142}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{61F77916-9C19-4CC6-A54B-CA4B7870B582}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{63650A7B-5EDD-41FE-B3FE-DA3FB8ECC7ED}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{03481BF2-EFC8-4B2C-8C4D-C0D523E4C785}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{068AEA08-659E-490E-86A8-9B52039EA404}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{8D635DBF-EA2F-4468-9B86-6D563825FB42}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{C123D33E-B73E-408F-B885-3F4D4B80B498}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{9C65CCAF-8852-41BB-9AAE-6E60D7D63D39}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{8CD001FF-8A53-4D7D-9A38-34C9532259A0}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{1FFB8C65-AFF6-486C-8B34-37A2A87FD6C6}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{F7E42296-C5FB-4BEC-932B-1CBD63F6AD59}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{F2FDF24D-A50F-40E4-BE74-0EB1C808C581}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{D9A293CC-7DAD-4ADE-8C2D-37009B344782}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{648E86F2-4CB2-4813-ACCE-F3B7391C10D1}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{E45A7D77-E41C-4C07-AD6C-C828ADC39611}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{720303F6-9817-407D-AA46-D77D7176313D}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{894F809F-C3E1-4540-A0E2-7777A7DCE590}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{8F0BE019-AACE-4DF3-BA9D-FB53B48B54E8}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{CCF4D828-C096-479C-BD66-3394EAA8835F}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{BEF1B900-D6A0-48F6-AA0F-F1D20B5F9181}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{67FA6BC4-8311-4ECE-A2A7-74702A62D275}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{EBA483B9-B9C9-40B6-AAA6-BEAE8839B678}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{4B0C185E-C25F-425A-B3E8-AA0D090C9D03}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{FE71F7BF-55D5-4DD0-B350-407D7B96E855}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{DDD07F13-E4D6-4F0C-B552-192F6BFBF4A4}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{6969D908-721A-44F7-BF53-A3832E99B9BE}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{DF661A87-855A-4BA3-9853-4C671AC15C33}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{174A85C8-8ECD-46BF-A26E-50FF9EDB9D39}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{6D4EE746-FF45-4482-A18E-6804DB38993A}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{197D9713-29C1-4D2D-A1D7-8B426E84C75D}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{ACFD8984-377A-4248-937C-ECF16B6780B9}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{5CAC9ED2-B017-495E-8E2E-CF20295B2645}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{05F65D0A-8BB8-4003-B253-32762673A4FB}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{AC474C82-B828-4A5C-A28D-3740C5D2B60A}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{A2C1E8FF-2F53-462B-940F-0ADC20515A47}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{89B6AC35-6978-4739-9EA9-41A7EC0404E7}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -61204,7 +61204,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="R6fVvvaP3NLaqCAeoFTDtwd3/iDFnfn+Kk6N77xN523r3cNXiKUc8wA9+5h9a6P5p07jLi8JWyiHC/08ANHMJw==" saltValue="i1U8K8ba9FfbNTASM8MmLA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="FVERNGBirHbxRaE/RWhSHlW8e3wdlGhuInXX1PXlCCpSv8TqEaBewIordylryt1Br0wmg7RDI+KF22uACzRt3g==" saltValue="OPS85BtO3E/rA3Yj4FYyJA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MPCI QC\Desktop\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68542EE2-EDEB-44CF-9903-1FF0EBA78747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0C0F62-7E10-4E34-B753-635F18D23985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14715" uniqueCount="3595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14733" uniqueCount="3603">
   <si>
     <t>PDS No.</t>
   </si>
@@ -10852,6 +10852,31 @@
   </si>
   <si>
     <t>760.00 ± 6.00</t>
+  </si>
+  <si>
+    <t>MP0434</t>
+  </si>
+  <si>
+    <t>MP0434.1</t>
+  </si>
+  <si>
+    <t>Pet 250ml Decagon Clear 24mm 23gm Bottle</t>
+  </si>
+  <si>
+    <t>10 Pcs x 4 Rows = 40 Pcs
+09 Pcs x 4 Rows = 36 Pcs</t>
+  </si>
+  <si>
+    <t>Decagon</t>
+  </si>
+  <si>
+    <t>51.60 ± 1.00</t>
+  </si>
+  <si>
+    <t>169.00 ± 1.20</t>
+  </si>
+  <si>
+    <t>275.00 ± 5.00</t>
   </si>
 </sst>
 </file>
@@ -11623,30 +11648,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C014C06-7C16-4A12-8056-F74D2781492F}" name="Table1" displayName="Table1" ref="A1:U792" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U792" xr:uid="{1C014C06-7C16-4A12-8056-F74D2781492F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F6D7203B-24EA-42EF-B9A8-CDB5FDB69781}" name="Table1" displayName="Table1" ref="A1:U793" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U793" xr:uid="{F6D7203B-24EA-42EF-B9A8-CDB5FDB69781}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{720303F6-9817-407D-AA46-D77D7176313D}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{894F809F-C3E1-4540-A0E2-7777A7DCE590}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{8F0BE019-AACE-4DF3-BA9D-FB53B48B54E8}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{CCF4D828-C096-479C-BD66-3394EAA8835F}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{BEF1B900-D6A0-48F6-AA0F-F1D20B5F9181}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{67FA6BC4-8311-4ECE-A2A7-74702A62D275}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{EBA483B9-B9C9-40B6-AAA6-BEAE8839B678}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{4B0C185E-C25F-425A-B3E8-AA0D090C9D03}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{FE71F7BF-55D5-4DD0-B350-407D7B96E855}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{DDD07F13-E4D6-4F0C-B552-192F6BFBF4A4}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{6969D908-721A-44F7-BF53-A3832E99B9BE}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{DF661A87-855A-4BA3-9853-4C671AC15C33}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{174A85C8-8ECD-46BF-A26E-50FF9EDB9D39}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{6D4EE746-FF45-4482-A18E-6804DB38993A}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{197D9713-29C1-4D2D-A1D7-8B426E84C75D}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{ACFD8984-377A-4248-937C-ECF16B6780B9}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{5CAC9ED2-B017-495E-8E2E-CF20295B2645}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{05F65D0A-8BB8-4003-B253-32762673A4FB}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{AC474C82-B828-4A5C-A28D-3740C5D2B60A}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{A2C1E8FF-2F53-462B-940F-0ADC20515A47}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{89B6AC35-6978-4739-9EA9-41A7EC0404E7}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{FE9A8E96-C805-4A87-B451-9E27E9E7501C}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{8A6BC545-FDAE-4F23-9E7F-224820D1AF54}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{AD681837-C341-4E02-BFBD-85E9440A6DE5}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{25B3489E-8EC9-462D-8BB7-D208610B23E4}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{7F4870AC-6DA2-4537-AD01-CF1F8DC4C5C7}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{2BE9DA89-3121-4068-AF1D-C308B142B942}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{8655773A-2E19-48D0-8F3E-91428C8BFD3F}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{6EFC5148-8894-4241-BAF9-47068FAE3815}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{6E791BC2-0322-4368-B9B1-8506C638B93A}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{7E91910E-8A58-495F-BD2B-0C31EA4534B6}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{B95921D9-C45E-4EEE-A51E-4D4A50F6FD3B}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{BDB86633-8E20-4C44-922E-7925E93355E1}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{EF0B604E-B293-4D30-ACE5-8D5E6DEBF111}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{E2ABBF44-49EE-4545-98A7-A4E902B35D19}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{3BDE09C7-AFF4-46BE-AC87-697459960D24}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{1C645D31-8493-4B55-BB78-0811EF6D039F}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{59E44D55-0CAD-42B5-9134-39A005ED0A09}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{E5095F04-1A1C-4F8A-8EB8-71E15D125464}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{588B18C9-35D9-4AFC-A82E-811ABC9D826E}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{5F2FD527-C334-4967-86CA-0A1EE403A4CF}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{F7158A67-C146-4D66-899E-0FA279D7BF36}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11949,7 +11974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U792"/>
+  <dimension ref="A1:U793"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -61143,68 +61168,129 @@
       </c>
     </row>
     <row r="792" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A792" s="9">
+      <c r="A792" s="4">
         <v>791</v>
       </c>
-      <c r="B792" s="10"/>
-      <c r="C792" s="11" t="s">
+      <c r="B792" s="5"/>
+      <c r="C792" s="6" t="s">
         <v>3588</v>
       </c>
-      <c r="D792" s="10"/>
-      <c r="E792" s="11" t="s">
+      <c r="D792" s="5"/>
+      <c r="E792" s="6" t="s">
         <v>3589</v>
       </c>
-      <c r="F792" s="11" t="s">
+      <c r="F792" s="6" t="s">
         <v>3590</v>
       </c>
-      <c r="G792" s="11" t="s">
+      <c r="G792" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H792" s="11" t="s">
+      <c r="H792" s="6" t="s">
         <v>780</v>
       </c>
-      <c r="I792" s="11" t="s">
+      <c r="I792" s="6" t="s">
         <v>269</v>
       </c>
       <c r="J792" s="13" t="s">
         <v>781</v>
       </c>
-      <c r="K792" s="11" t="s">
+      <c r="K792" s="6" t="s">
         <v>3591</v>
       </c>
-      <c r="L792" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="M792" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="N792" s="11" t="s">
+      <c r="L792" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M792" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N792" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="O792" s="11" t="s">
+      <c r="O792" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="P792" s="11" t="s">
+      <c r="P792" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="Q792" s="11" t="s">
+      <c r="Q792" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="R792" s="11" t="s">
+      <c r="R792" s="6" t="s">
         <v>3592</v>
       </c>
-      <c r="S792" s="11" t="s">
+      <c r="S792" s="6" t="s">
         <v>3593</v>
       </c>
-      <c r="T792" s="11" t="s">
+      <c r="T792" s="6" t="s">
         <v>2526</v>
       </c>
-      <c r="U792" s="12" t="s">
+      <c r="U792" s="7" t="s">
         <v>3594</v>
       </c>
     </row>
+    <row r="793" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A793" s="9">
+        <v>792</v>
+      </c>
+      <c r="B793" s="10"/>
+      <c r="C793" s="11" t="s">
+        <v>3595</v>
+      </c>
+      <c r="D793" s="10"/>
+      <c r="E793" s="11" t="s">
+        <v>3596</v>
+      </c>
+      <c r="F793" s="11" t="s">
+        <v>3597</v>
+      </c>
+      <c r="G793" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H793" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="I793" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="J793" s="13" t="s">
+        <v>3598</v>
+      </c>
+      <c r="K793" s="11" t="s">
+        <v>3599</v>
+      </c>
+      <c r="L793" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="M793" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="N793" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="O793" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="P793" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q793" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R793" s="11" t="s">
+        <v>3600</v>
+      </c>
+      <c r="S793" s="11" t="s">
+        <v>3601</v>
+      </c>
+      <c r="T793" s="11" t="s">
+        <v>868</v>
+      </c>
+      <c r="U793" s="12" t="s">
+        <v>3602</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="FVERNGBirHbxRaE/RWhSHlW8e3wdlGhuInXX1PXlCCpSv8TqEaBewIordylryt1Br0wmg7RDI+KF22uACzRt3g==" saltValue="OPS85BtO3E/rA3Yj4FYyJA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Ge6++hMYP7pwt2mdjBd3RJ78wNeXbR/saqePKUTOGNlI+2o0f1bJkveBd17PJ2zkKhO7Y5MwzIlg0e1xLKq8Eg==" saltValue="7q+IJGvxvjDhQGcjRLHGPA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MPCI QC\Desktop\FG &amp; RMPM LIST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F57C96-2411-473A-939A-BC3BC3431F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A53606-20C4-409C-A80E-728AD3007DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14757" uniqueCount="3605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14852" uniqueCount="3616">
   <si>
     <t>PDS No.</t>
   </si>
@@ -10883,6 +10883,39 @@
   </si>
   <si>
     <t>Pet 2.1 lt. Hajmola Clear 83mm 36gm Jar rPET100 Dabur Box</t>
+  </si>
+  <si>
+    <t>MP0102.10</t>
+  </si>
+  <si>
+    <t>Pet 2.1 lt. Hajmola Amber 83mm 36gm Jar rPET100 Dabur Box</t>
+  </si>
+  <si>
+    <t>MP0445</t>
+  </si>
+  <si>
+    <t>MP0445.1</t>
+  </si>
+  <si>
+    <t>Pet 500ml Round Clear 25mm 28.5gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0338.5</t>
+  </si>
+  <si>
+    <t>Pet 300ml BIO Clear 24mm 23gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0369.2</t>
+  </si>
+  <si>
+    <t>Pet 300ml Nutra Clear 24mm 23gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0369.3</t>
+  </si>
+  <si>
+    <t>Pet 300ml Nutra Milky White 24mm 23gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -11654,30 +11687,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{637F7BBE-5D8D-49E4-A723-8C516C095E8D}" name="Table1" displayName="Table1" ref="A1:U794" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U794" xr:uid="{637F7BBE-5D8D-49E4-A723-8C516C095E8D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A29765D1-DBA7-47DB-A561-3196CF9317DF}" name="Table1" displayName="Table1" ref="A1:U799" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U799" xr:uid="{A29765D1-DBA7-47DB-A561-3196CF9317DF}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{4798E198-EFF4-43EA-AE15-27714EDF5785}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{EEEB8304-845B-4316-BD17-A81E72065985}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{559131D5-9AE0-4C32-8B62-7A05FF85D2F1}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{E18FCBC1-952F-40F0-A6E1-CE0B9A4B5BF3}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{1DB59EA5-D1E3-4ABA-A6DE-279B7AEB2EC6}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{DF3DD3E8-88D3-4F3F-B5F1-93F4291907A9}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{204C88D5-D032-40AD-AFAF-A1FCF05B0250}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{BFAA5D66-8B13-4061-A532-4DE856BB5C59}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{D58A7AD9-6320-44C3-AC46-FAD43D14432F}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{0AB87B31-9141-404F-B988-096DA08494D6}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{E956DEB0-B012-4E5D-8761-8485B0FE5001}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{A4EA7FCA-FCBD-4DA7-A55F-7E1BE487DAD8}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{11FE4817-47EE-4589-8742-01FD6B8E7BB7}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{D2E972BB-844F-4A34-9185-592CF715FB69}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{5817482F-DC7C-4356-9773-49D9A543E57A}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{92697489-5D30-412F-88AD-341A3B326DB8}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{BDB28D0B-F70C-4288-8B67-9598C174CF6A}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{61671B19-5A6C-4AAB-858D-F54CAC0153D1}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{1DF1884E-211E-4BF2-BCB2-54035AFFBDED}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{98218941-8009-4798-B57B-AFE4DDE1CEC8}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{0F45F79F-EF58-45FD-81AC-3E998323A47B}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{03A9E97D-6517-4692-9E9B-2197FF7EBA0F}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{7B530726-937A-47AC-93FA-BFA31096E04B}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{B7B5020F-3CCE-4C91-ABF4-6736554F53BF}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{C04F0C1D-6369-492A-A860-65665B74AD7F}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{2B1233D4-13E5-4390-BC4F-8B3638A70A7F}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{EBDE50C7-13DC-4B54-B017-EC003905DA4E}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{260D1DE9-A397-491A-ACBF-7D6588553219}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{0C00318E-4CAE-42C8-BC20-4FF124B45C1F}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{34D3ED6F-5422-4B72-ACDB-6C7595ED15C9}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{DA9A7BB9-F953-4667-B9AB-423769EC1287}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{DF22A0E9-A134-4770-A7DF-77B3E8FA990F}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{2B34BF5F-88D5-4989-BBE3-2E18540D3795}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{6A1F594F-FF8F-4535-AC41-D4A2A9D901EE}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{092B0BD4-447A-4885-80A6-30149C2C71CE}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{3B2DCB8E-8DA1-4412-BE8C-E5E50247AF65}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{4B9D3963-D9EE-486F-9291-CB58DDE27261}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{7BB40F64-6633-4EF5-9863-AA91E05183D2}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{41F7E59B-CABE-47C4-8B4D-A0EDEEACE42F}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{671331AC-7DAF-41B2-A331-C7577550B756}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{7C01FC80-E9F4-446B-8C5B-4028004EB872}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{653F3171-4A2E-4D94-A566-CA2CCD0FF8AF}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11980,7 +12013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U794"/>
+  <dimension ref="A1:U799"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -42021,7 +42054,9 @@
       <c r="A478" s="4">
         <v>477</v>
       </c>
-      <c r="B478" s="5"/>
+      <c r="B478" s="6" t="s">
+        <v>325</v>
+      </c>
       <c r="C478" s="6" t="s">
         <v>2270</v>
       </c>
@@ -42084,7 +42119,9 @@
       <c r="A479" s="4">
         <v>478</v>
       </c>
-      <c r="B479" s="5"/>
+      <c r="B479" s="6" t="s">
+        <v>325</v>
+      </c>
       <c r="C479" s="6" t="s">
         <v>2270</v>
       </c>
@@ -42147,7 +42184,9 @@
       <c r="A480" s="4">
         <v>479</v>
       </c>
-      <c r="B480" s="5"/>
+      <c r="B480" s="6" t="s">
+        <v>325</v>
+      </c>
       <c r="C480" s="6" t="s">
         <v>2270</v>
       </c>
@@ -48703,7 +48742,9 @@
       <c r="A586" s="4">
         <v>585</v>
       </c>
-      <c r="B586" s="5"/>
+      <c r="B586" s="6" t="s">
+        <v>325</v>
+      </c>
       <c r="C586" s="6" t="s">
         <v>2270</v>
       </c>
@@ -59296,7 +59337,9 @@
       <c r="A761" s="4">
         <v>760</v>
       </c>
-      <c r="B761" s="5"/>
+      <c r="B761" s="6" t="s">
+        <v>325</v>
+      </c>
       <c r="C761" s="6" t="s">
         <v>2270</v>
       </c>
@@ -61308,68 +61351,373 @@
       </c>
     </row>
     <row r="794" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A794" s="9">
+      <c r="A794" s="4">
         <v>793</v>
       </c>
-      <c r="B794" s="10"/>
-      <c r="C794" s="11" t="s">
+      <c r="B794" s="5"/>
+      <c r="C794" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="D794" s="10"/>
-      <c r="E794" s="11" t="s">
+      <c r="D794" s="5"/>
+      <c r="E794" s="6" t="s">
         <v>3603</v>
       </c>
-      <c r="F794" s="11" t="s">
+      <c r="F794" s="6" t="s">
         <v>3604</v>
       </c>
-      <c r="G794" s="11" t="s">
+      <c r="G794" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H794" s="11" t="s">
+      <c r="H794" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="I794" s="11" t="s">
+      <c r="I794" s="6" t="s">
         <v>331</v>
       </c>
       <c r="J794" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="K794" s="11" t="s">
+      <c r="K794" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="L794" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="M794" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="N794" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="O794" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="P794" s="11" t="s">
+      <c r="L794" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M794" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N794" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="O794" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="P794" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="Q794" s="11" t="s">
+      <c r="Q794" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="R794" s="11" t="s">
+      <c r="R794" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="S794" s="11" t="s">
+      <c r="S794" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="T794" s="11" t="s">
+      <c r="T794" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="U794" s="12" t="s">
+      <c r="U794" s="7" t="s">
         <v>336</v>
       </c>
     </row>
+    <row r="795" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A795" s="4">
+        <v>794</v>
+      </c>
+      <c r="B795" s="5"/>
+      <c r="C795" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="D795" s="5"/>
+      <c r="E795" s="6" t="s">
+        <v>3605</v>
+      </c>
+      <c r="F795" s="6" t="s">
+        <v>3606</v>
+      </c>
+      <c r="G795" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H795" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="I795" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="J795" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="K795" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="L795" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M795" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N795" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="O795" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="P795" s="6" t="s">
+        <v>1784</v>
+      </c>
+      <c r="Q795" s="6" t="s">
+        <v>1785</v>
+      </c>
+      <c r="R795" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="S795" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="T795" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="U795" s="7" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="796" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A796" s="4">
+        <v>795</v>
+      </c>
+      <c r="B796" s="5"/>
+      <c r="C796" s="6" t="s">
+        <v>3607</v>
+      </c>
+      <c r="D796" s="5"/>
+      <c r="E796" s="6" t="s">
+        <v>3608</v>
+      </c>
+      <c r="F796" s="6" t="s">
+        <v>3609</v>
+      </c>
+      <c r="G796" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H796" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I796" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J796" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="K796" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L796" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="M796" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="N796" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="O796" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="P796" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q796" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R796" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="S796" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="T796" s="6" t="s">
+        <v>1910</v>
+      </c>
+      <c r="U796" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="797" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A797" s="4">
+        <v>796</v>
+      </c>
+      <c r="B797" s="5"/>
+      <c r="C797" s="6" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D797" s="5"/>
+      <c r="E797" s="6" t="s">
+        <v>3610</v>
+      </c>
+      <c r="F797" s="6" t="s">
+        <v>3611</v>
+      </c>
+      <c r="G797" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H797" s="6" t="s">
+        <v>2242</v>
+      </c>
+      <c r="I797" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J797" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="K797" s="6" t="s">
+        <v>2315</v>
+      </c>
+      <c r="L797" s="6" t="s">
+        <v>865</v>
+      </c>
+      <c r="M797" s="6" t="s">
+        <v>866</v>
+      </c>
+      <c r="N797" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="O797" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="P797" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q797" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R797" s="6" t="s">
+        <v>2244</v>
+      </c>
+      <c r="S797" s="6" t="s">
+        <v>2245</v>
+      </c>
+      <c r="T797" s="6" t="s">
+        <v>2316</v>
+      </c>
+      <c r="U797" s="7" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="798" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A798" s="4">
+        <v>797</v>
+      </c>
+      <c r="B798" s="5"/>
+      <c r="C798" s="6" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D798" s="5"/>
+      <c r="E798" s="6" t="s">
+        <v>3612</v>
+      </c>
+      <c r="F798" s="6" t="s">
+        <v>3613</v>
+      </c>
+      <c r="G798" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H798" s="6" t="s">
+        <v>2306</v>
+      </c>
+      <c r="I798" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J798" s="13" t="s">
+        <v>3322</v>
+      </c>
+      <c r="K798" s="6" t="s">
+        <v>3323</v>
+      </c>
+      <c r="L798" s="6" t="s">
+        <v>690</v>
+      </c>
+      <c r="M798" s="6" t="s">
+        <v>691</v>
+      </c>
+      <c r="N798" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="O798" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P798" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q798" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R798" s="6" t="s">
+        <v>3324</v>
+      </c>
+      <c r="S798" s="6" t="s">
+        <v>3325</v>
+      </c>
+      <c r="T798" s="6" t="s">
+        <v>2316</v>
+      </c>
+      <c r="U798" s="7" t="s">
+        <v>3326</v>
+      </c>
+    </row>
+    <row r="799" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A799" s="9">
+        <v>798</v>
+      </c>
+      <c r="B799" s="10"/>
+      <c r="C799" s="11" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D799" s="10"/>
+      <c r="E799" s="11" t="s">
+        <v>3614</v>
+      </c>
+      <c r="F799" s="11" t="s">
+        <v>3615</v>
+      </c>
+      <c r="G799" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H799" s="11" t="s">
+        <v>2306</v>
+      </c>
+      <c r="I799" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="J799" s="13" t="s">
+        <v>3322</v>
+      </c>
+      <c r="K799" s="11" t="s">
+        <v>3323</v>
+      </c>
+      <c r="L799" s="11" t="s">
+        <v>690</v>
+      </c>
+      <c r="M799" s="11" t="s">
+        <v>691</v>
+      </c>
+      <c r="N799" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="O799" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="P799" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q799" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R799" s="11" t="s">
+        <v>3324</v>
+      </c>
+      <c r="S799" s="11" t="s">
+        <v>3325</v>
+      </c>
+      <c r="T799" s="11" t="s">
+        <v>2316</v>
+      </c>
+      <c r="U799" s="12" t="s">
+        <v>3326</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Kh3pyZ0IodQdlHybo3SKG3m6HgKhjkBgqxozLKdCaemSHW+e5xt5c1hjYotaOGR5GfOS1IwaSYKgT/H2ZlNw3Q==" saltValue="TtXkhwN7naYn5qy3emkErA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="XQvuswH9/KFBvy5VzTI2F4D/J8CSFVpqT6+pu/2o6/yHX/n7kU7X4diAUavZh4CrXRAS0B1picY5JPxzp+9hSQ==" saltValue="cNQbOgaEBUEZ/g0pd3/srw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A53606-20C4-409C-A80E-728AD3007DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2416EC7A-CD70-4980-83E3-8229B2C954C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14852" uniqueCount="3616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14978" uniqueCount="3636">
   <si>
     <t>PDS No.</t>
   </si>
@@ -6862,13 +6862,13 @@
     <t>Pet 200ml Round Milky White 24mm 20gm CR16.5 Bottle</t>
   </si>
   <si>
-    <t>MP0332</t>
+    <t>MP0332REV00</t>
   </si>
   <si>
     <t>MP5189</t>
   </si>
   <si>
-    <t>MP0332.1</t>
+    <t>MP0332REV00.1</t>
   </si>
   <si>
     <t>Pet 200ml Avon Milky White 24mm 20gm Bottle</t>
@@ -6886,7 +6886,7 @@
     <t>MP5190</t>
   </si>
   <si>
-    <t>MP0332.2</t>
+    <t>MP0332REV00.2</t>
   </si>
   <si>
     <t>Pet 200ml Avon Clear 24mm 20gm Bottle</t>
@@ -6895,7 +6895,7 @@
     <t>MP5202</t>
   </si>
   <si>
-    <t>MP0332.3</t>
+    <t>MP0332REV00.3</t>
   </si>
   <si>
     <t>Pet 200ml Avon Black 24mm 20gm Bottle</t>
@@ -8394,7 +8394,7 @@
     <t>Pet 100ml Kesh King Clear Short Neck 19mm 12.5gm Bottle</t>
   </si>
   <si>
-    <t>MP0332.4</t>
+    <t>MP0332REV00.4</t>
   </si>
   <si>
     <t>Pet 200ml Avon Amber 24mm 20gm Bottle</t>
@@ -10548,7 +10548,7 @@
     <t>Pet 100ml Classic Dark Milky Long Neck 19mm 12.5gm Bottle</t>
   </si>
   <si>
-    <t>MP0332.5</t>
+    <t>MP0332REV00.5</t>
   </si>
   <si>
     <t>Pet 200ml Avon Yellow 24mm 20gm Bottle</t>
@@ -10916,6 +10916,66 @@
   </si>
   <si>
     <t>Pet 300ml Nutra Milky White 24mm 23gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0332</t>
+  </si>
+  <si>
+    <t>MP0332.1</t>
+  </si>
+  <si>
+    <t>Pet 200ml N Avon Milky White 24mm 20gm Bottle</t>
+  </si>
+  <si>
+    <t>N AVON</t>
+  </si>
+  <si>
+    <t>47.10 ± 0.80</t>
+  </si>
+  <si>
+    <t>221.00 ± 4.00</t>
+  </si>
+  <si>
+    <t>MP0332.2</t>
+  </si>
+  <si>
+    <t>Pet 200ml N Avon Clear 24mm 20gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0332.3</t>
+  </si>
+  <si>
+    <t>Pet 200ml N Avon Black 24mm 20gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0332.4</t>
+  </si>
+  <si>
+    <t>Pet 200ml N Avon Amber 24mm 20gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0332.5</t>
+  </si>
+  <si>
+    <t>Pet 200ml N Avon Yellow 24mm 20gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0449</t>
+  </si>
+  <si>
+    <t>MP0449.1</t>
+  </si>
+  <si>
+    <t>Pet 50ml Oval Clear 25mm 10gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0448</t>
+  </si>
+  <si>
+    <t>MP0448.1</t>
+  </si>
+  <si>
+    <t>Pet 60ml Round Amber 25mm 8gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -11687,30 +11747,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A29765D1-DBA7-47DB-A561-3196CF9317DF}" name="Table1" displayName="Table1" ref="A1:U799" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U799" xr:uid="{A29765D1-DBA7-47DB-A561-3196CF9317DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3A9BDB5-849A-4735-8650-1ABC4D358834}" name="Table1" displayName="Table1" ref="A1:U806" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U806" xr:uid="{A3A9BDB5-849A-4735-8650-1ABC4D358834}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{03A9E97D-6517-4692-9E9B-2197FF7EBA0F}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{7B530726-937A-47AC-93FA-BFA31096E04B}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{B7B5020F-3CCE-4C91-ABF4-6736554F53BF}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{C04F0C1D-6369-492A-A860-65665B74AD7F}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{2B1233D4-13E5-4390-BC4F-8B3638A70A7F}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{EBDE50C7-13DC-4B54-B017-EC003905DA4E}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{260D1DE9-A397-491A-ACBF-7D6588553219}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{0C00318E-4CAE-42C8-BC20-4FF124B45C1F}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{34D3ED6F-5422-4B72-ACDB-6C7595ED15C9}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{DA9A7BB9-F953-4667-B9AB-423769EC1287}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{DF22A0E9-A134-4770-A7DF-77B3E8FA990F}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{2B34BF5F-88D5-4989-BBE3-2E18540D3795}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{6A1F594F-FF8F-4535-AC41-D4A2A9D901EE}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{092B0BD4-447A-4885-80A6-30149C2C71CE}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{3B2DCB8E-8DA1-4412-BE8C-E5E50247AF65}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{4B9D3963-D9EE-486F-9291-CB58DDE27261}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{7BB40F64-6633-4EF5-9863-AA91E05183D2}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{41F7E59B-CABE-47C4-8B4D-A0EDEEACE42F}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{671331AC-7DAF-41B2-A331-C7577550B756}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{7C01FC80-E9F4-446B-8C5B-4028004EB872}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{653F3171-4A2E-4D94-A566-CA2CCD0FF8AF}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{69CE5DE0-535A-4C2E-8FEC-C0C492F0BAD6}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{E19E830C-480E-4913-82EE-BD37B03F5233}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{EEC7A765-DECF-4143-ACFF-AF28FCCA9CDC}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{925EDFE4-701D-4A0C-86E4-574DAC0C71A3}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{F1D630C2-9922-4F62-9AD1-78633B31B5F9}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{A41F70BE-CC9F-43FB-A9CC-8596BE913A0A}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{7EDE2211-6E49-4E09-AF74-3212FFFA1D8B}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{FB1A6F27-C439-49AA-BF52-D81E9AE3C2DE}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{0492DC07-5BFD-427D-B165-06312C81D62A}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{4C91D29E-627D-41E5-8E45-BB871A06C7C1}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{C8E3F044-3C1F-4B35-9F77-70A0EA5B0337}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{F95F58F7-917C-4E75-9006-8F6E1E2C4A86}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{A968510A-BC05-4106-BE7C-7538ACEC4BBA}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{D2796D85-73CE-4C6C-8A4D-0B85C010BED5}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{B83B6BCD-60A5-41D8-8C98-8C7AC1AEE8AD}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{A18DA0D4-7B7D-48B4-9D89-1F0039BB2C13}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{856923D1-2B34-4B89-B204-10AB06AF7179}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{53FFAD16-D3B0-4641-9120-1004E97AC78F}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{7FD3A826-DA3D-47A5-B2F2-86332CC5ECC9}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{EA5412EE-503F-4BED-9F99-6CE7039C4FEE}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{3545492F-7FD7-4000-9389-BD5A0AFB8BEB}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12013,14 +12073,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U799"/>
+  <dimension ref="A1:U806"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="60.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="39.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
@@ -61656,68 +61716,495 @@
       </c>
     </row>
     <row r="799" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A799" s="9">
+      <c r="A799" s="4">
         <v>798</v>
       </c>
-      <c r="B799" s="10"/>
-      <c r="C799" s="11" t="s">
+      <c r="B799" s="5"/>
+      <c r="C799" s="6" t="s">
         <v>3319</v>
       </c>
-      <c r="D799" s="10"/>
-      <c r="E799" s="11" t="s">
+      <c r="D799" s="5"/>
+      <c r="E799" s="6" t="s">
         <v>3614</v>
       </c>
-      <c r="F799" s="11" t="s">
+      <c r="F799" s="6" t="s">
         <v>3615</v>
       </c>
-      <c r="G799" s="11" t="s">
+      <c r="G799" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H799" s="11" t="s">
+      <c r="H799" s="6" t="s">
         <v>2306</v>
       </c>
-      <c r="I799" s="11" t="s">
+      <c r="I799" s="6" t="s">
         <v>146</v>
       </c>
       <c r="J799" s="13" t="s">
         <v>3322</v>
       </c>
-      <c r="K799" s="11" t="s">
+      <c r="K799" s="6" t="s">
         <v>3323</v>
       </c>
-      <c r="L799" s="11" t="s">
+      <c r="L799" s="6" t="s">
         <v>690</v>
       </c>
-      <c r="M799" s="11" t="s">
+      <c r="M799" s="6" t="s">
         <v>691</v>
       </c>
-      <c r="N799" s="11" t="s">
+      <c r="N799" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="O799" s="11" t="s">
+      <c r="O799" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="P799" s="11" t="s">
+      <c r="P799" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="Q799" s="11" t="s">
+      <c r="Q799" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="R799" s="11" t="s">
+      <c r="R799" s="6" t="s">
         <v>3324</v>
       </c>
-      <c r="S799" s="11" t="s">
+      <c r="S799" s="6" t="s">
         <v>3325</v>
       </c>
-      <c r="T799" s="11" t="s">
+      <c r="T799" s="6" t="s">
         <v>2316</v>
       </c>
-      <c r="U799" s="12" t="s">
+      <c r="U799" s="7" t="s">
         <v>3326</v>
       </c>
     </row>
+    <row r="800" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A800" s="4">
+        <v>799</v>
+      </c>
+      <c r="B800" s="5"/>
+      <c r="C800" s="6" t="s">
+        <v>3616</v>
+      </c>
+      <c r="D800" s="5"/>
+      <c r="E800" s="6" t="s">
+        <v>3617</v>
+      </c>
+      <c r="F800" s="6" t="s">
+        <v>3618</v>
+      </c>
+      <c r="G800" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H800" s="6" t="s">
+        <v>2287</v>
+      </c>
+      <c r="I800" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="J800" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="K800" s="6" t="s">
+        <v>3619</v>
+      </c>
+      <c r="L800" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M800" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N800" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="O800" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="P800" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q800" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R800" s="6" t="s">
+        <v>3620</v>
+      </c>
+      <c r="S800" s="6" t="s">
+        <v>2275</v>
+      </c>
+      <c r="T800" s="6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="U800" s="7" t="s">
+        <v>3621</v>
+      </c>
+    </row>
+    <row r="801" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A801" s="4">
+        <v>800</v>
+      </c>
+      <c r="B801" s="5"/>
+      <c r="C801" s="6" t="s">
+        <v>3616</v>
+      </c>
+      <c r="D801" s="5"/>
+      <c r="E801" s="6" t="s">
+        <v>3622</v>
+      </c>
+      <c r="F801" s="6" t="s">
+        <v>3623</v>
+      </c>
+      <c r="G801" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H801" s="6" t="s">
+        <v>2287</v>
+      </c>
+      <c r="I801" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="J801" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="K801" s="6" t="s">
+        <v>3619</v>
+      </c>
+      <c r="L801" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M801" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N801" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="O801" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="P801" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q801" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R801" s="6" t="s">
+        <v>3620</v>
+      </c>
+      <c r="S801" s="6" t="s">
+        <v>2275</v>
+      </c>
+      <c r="T801" s="6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="U801" s="7" t="s">
+        <v>3621</v>
+      </c>
+    </row>
+    <row r="802" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A802" s="4">
+        <v>801</v>
+      </c>
+      <c r="B802" s="5"/>
+      <c r="C802" s="6" t="s">
+        <v>3616</v>
+      </c>
+      <c r="D802" s="5"/>
+      <c r="E802" s="6" t="s">
+        <v>3624</v>
+      </c>
+      <c r="F802" s="6" t="s">
+        <v>3625</v>
+      </c>
+      <c r="G802" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H802" s="6" t="s">
+        <v>2287</v>
+      </c>
+      <c r="I802" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="J802" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="K802" s="6" t="s">
+        <v>3619</v>
+      </c>
+      <c r="L802" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M802" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N802" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="O802" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="P802" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q802" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R802" s="6" t="s">
+        <v>3620</v>
+      </c>
+      <c r="S802" s="6" t="s">
+        <v>2275</v>
+      </c>
+      <c r="T802" s="6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="U802" s="7" t="s">
+        <v>3621</v>
+      </c>
+    </row>
+    <row r="803" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A803" s="4">
+        <v>802</v>
+      </c>
+      <c r="B803" s="5"/>
+      <c r="C803" s="6" t="s">
+        <v>3616</v>
+      </c>
+      <c r="D803" s="5"/>
+      <c r="E803" s="6" t="s">
+        <v>3626</v>
+      </c>
+      <c r="F803" s="6" t="s">
+        <v>3627</v>
+      </c>
+      <c r="G803" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H803" s="6" t="s">
+        <v>2287</v>
+      </c>
+      <c r="I803" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="J803" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="K803" s="6" t="s">
+        <v>3619</v>
+      </c>
+      <c r="L803" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M803" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N803" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="O803" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="P803" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q803" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R803" s="6" t="s">
+        <v>3620</v>
+      </c>
+      <c r="S803" s="6" t="s">
+        <v>2275</v>
+      </c>
+      <c r="T803" s="6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="U803" s="7" t="s">
+        <v>3621</v>
+      </c>
+    </row>
+    <row r="804" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A804" s="4">
+        <v>803</v>
+      </c>
+      <c r="B804" s="5"/>
+      <c r="C804" s="6" t="s">
+        <v>3616</v>
+      </c>
+      <c r="D804" s="5"/>
+      <c r="E804" s="6" t="s">
+        <v>3628</v>
+      </c>
+      <c r="F804" s="6" t="s">
+        <v>3629</v>
+      </c>
+      <c r="G804" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H804" s="6" t="s">
+        <v>2287</v>
+      </c>
+      <c r="I804" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="J804" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="K804" s="6" t="s">
+        <v>3619</v>
+      </c>
+      <c r="L804" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M804" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N804" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="O804" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="P804" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q804" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R804" s="6" t="s">
+        <v>3620</v>
+      </c>
+      <c r="S804" s="6" t="s">
+        <v>2275</v>
+      </c>
+      <c r="T804" s="6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="U804" s="7" t="s">
+        <v>3621</v>
+      </c>
+    </row>
+    <row r="805" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A805" s="4">
+        <v>804</v>
+      </c>
+      <c r="B805" s="5"/>
+      <c r="C805" s="6" t="s">
+        <v>3630</v>
+      </c>
+      <c r="D805" s="5"/>
+      <c r="E805" s="6" t="s">
+        <v>3631</v>
+      </c>
+      <c r="F805" s="6" t="s">
+        <v>3632</v>
+      </c>
+      <c r="G805" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H805" s="6" t="s">
+        <v>2296</v>
+      </c>
+      <c r="I805" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J805" s="13" t="s">
+        <v>2297</v>
+      </c>
+      <c r="K805" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="L805" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M805" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N805" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O805" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P805" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q805" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R805" s="6" t="s">
+        <v>2298</v>
+      </c>
+      <c r="S805" s="6" t="s">
+        <v>2299</v>
+      </c>
+      <c r="T805" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="U805" s="7" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="806" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A806" s="9">
+        <v>805</v>
+      </c>
+      <c r="B806" s="10"/>
+      <c r="C806" s="11" t="s">
+        <v>3633</v>
+      </c>
+      <c r="D806" s="10"/>
+      <c r="E806" s="11" t="s">
+        <v>3634</v>
+      </c>
+      <c r="F806" s="11" t="s">
+        <v>3635</v>
+      </c>
+      <c r="G806" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H806" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I806" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="J806" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="K806" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="L806" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="M806" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="N806" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O806" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="P806" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q806" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R806" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="S806" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="T806" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="U806" s="12" t="s">
+        <v>389</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="XQvuswH9/KFBvy5VzTI2F4D/J8CSFVpqT6+pu/2o6/yHX/n7kU7X4diAUavZh4CrXRAS0B1picY5JPxzp+9hSQ==" saltValue="cNQbOgaEBUEZ/g0pd3/srw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="VhLgCngJMiRW8QF3T/2YwF7B2jflRV9LNmbSWXkTo2yiZH22btpk8lDVh5X/4xjL8MyX3EAD53hcLpfYaJ+uzQ==" saltValue="5Dw36BW3x0KzOe5AXguZSw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2416EC7A-CD70-4980-83E3-8229B2C954C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E306A68E-78E3-48D6-8225-5C397D585D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14978" uniqueCount="3636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14996" uniqueCount="3638">
   <si>
     <t>PDS No.</t>
   </si>
@@ -10976,6 +10976,12 @@
   </si>
   <si>
     <t>Pet 60ml Round Amber 25mm 8gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0382.2</t>
+  </si>
+  <si>
+    <t>Pet 250ml Ellipse Milky White 24mm 23gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -11747,30 +11753,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3A9BDB5-849A-4735-8650-1ABC4D358834}" name="Table1" displayName="Table1" ref="A1:U806" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U806" xr:uid="{A3A9BDB5-849A-4735-8650-1ABC4D358834}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ABBA5036-D419-4C71-9AC2-124AABB16776}" name="Table1" displayName="Table1" ref="A1:U807" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U807" xr:uid="{ABBA5036-D419-4C71-9AC2-124AABB16776}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{69CE5DE0-535A-4C2E-8FEC-C0C492F0BAD6}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{E19E830C-480E-4913-82EE-BD37B03F5233}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{EEC7A765-DECF-4143-ACFF-AF28FCCA9CDC}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{925EDFE4-701D-4A0C-86E4-574DAC0C71A3}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{F1D630C2-9922-4F62-9AD1-78633B31B5F9}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{A41F70BE-CC9F-43FB-A9CC-8596BE913A0A}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{7EDE2211-6E49-4E09-AF74-3212FFFA1D8B}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{FB1A6F27-C439-49AA-BF52-D81E9AE3C2DE}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{0492DC07-5BFD-427D-B165-06312C81D62A}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{4C91D29E-627D-41E5-8E45-BB871A06C7C1}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{C8E3F044-3C1F-4B35-9F77-70A0EA5B0337}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{F95F58F7-917C-4E75-9006-8F6E1E2C4A86}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{A968510A-BC05-4106-BE7C-7538ACEC4BBA}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{D2796D85-73CE-4C6C-8A4D-0B85C010BED5}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{B83B6BCD-60A5-41D8-8C98-8C7AC1AEE8AD}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{A18DA0D4-7B7D-48B4-9D89-1F0039BB2C13}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{856923D1-2B34-4B89-B204-10AB06AF7179}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{53FFAD16-D3B0-4641-9120-1004E97AC78F}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{7FD3A826-DA3D-47A5-B2F2-86332CC5ECC9}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{EA5412EE-503F-4BED-9F99-6CE7039C4FEE}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{3545492F-7FD7-4000-9389-BD5A0AFB8BEB}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{D03BC132-B53C-49B9-8AFA-577DE88B41C2}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{CF5B499E-1B18-4B4C-B97B-E9DC0BEC65D5}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{5CD0EC99-EBB2-406A-B191-FDEBDF815073}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{69E10667-69ED-45F8-81C1-6FC7ACDFBE65}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{6224F04D-5C00-40A2-BC9D-AA0268B2673D}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{F316351A-4420-4C06-AEE9-20A2EA289E70}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{6537F8A2-AE7D-4C97-891A-044E9E71C0DC}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{AC81384E-D8DD-47C5-9113-8CA91C0EACD0}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{C8DC3D75-6B33-4E9C-A8DC-86B0DE6C8DCE}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{01D52676-CD14-4B66-9EF1-857CFAD22C28}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{76A00F05-07E9-4B75-AFEB-5C9A4EAFF0F2}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{C85A14FB-ECF0-4E42-B47A-70DD6CA2A713}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{96824955-BBC9-4801-AA73-5BEF64D5E54C}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{48FED2C4-A444-47D2-9692-4E3C7D8D3AC8}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{D704356A-395B-474C-A209-DD9FC878334C}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{23F98EE4-0219-42C7-8EF1-FB96A768612B}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{C2466E4A-4006-4F97-8162-BF085E439F14}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{6C70697C-9A0D-4D1A-8CE7-6D41BB8232C3}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{5E755C35-2CD5-4A60-ADC8-6B1D607A5D97}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{D8BF8ACC-0A76-4D2A-8526-3BE1BF68FAD6}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{A44A770E-28C8-4B14-B262-EDBC594E1E32}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12073,7 +12079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U806"/>
+  <dimension ref="A1:U807"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -62143,68 +62149,129 @@
       </c>
     </row>
     <row r="806" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A806" s="9">
+      <c r="A806" s="4">
         <v>805</v>
       </c>
-      <c r="B806" s="10"/>
-      <c r="C806" s="11" t="s">
+      <c r="B806" s="5"/>
+      <c r="C806" s="6" t="s">
         <v>3633</v>
       </c>
-      <c r="D806" s="10"/>
-      <c r="E806" s="11" t="s">
+      <c r="D806" s="5"/>
+      <c r="E806" s="6" t="s">
         <v>3634</v>
       </c>
-      <c r="F806" s="11" t="s">
+      <c r="F806" s="6" t="s">
         <v>3635</v>
       </c>
-      <c r="G806" s="11" t="s">
+      <c r="G806" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H806" s="11" t="s">
+      <c r="H806" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I806" s="11" t="s">
+      <c r="I806" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J806" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="K806" s="11" t="s">
+      <c r="K806" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="L806" s="11" t="s">
+      <c r="L806" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="M806" s="11" t="s">
+      <c r="M806" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="N806" s="11" t="s">
+      <c r="N806" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O806" s="11" t="s">
+      <c r="O806" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="P806" s="11" t="s">
+      <c r="P806" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="Q806" s="11" t="s">
+      <c r="Q806" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="R806" s="11" t="s">
+      <c r="R806" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="S806" s="11" t="s">
+      <c r="S806" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="T806" s="11" t="s">
+      <c r="T806" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="U806" s="12" t="s">
+      <c r="U806" s="7" t="s">
         <v>389</v>
       </c>
     </row>
+    <row r="807" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A807" s="9">
+        <v>806</v>
+      </c>
+      <c r="B807" s="10"/>
+      <c r="C807" s="11" t="s">
+        <v>2892</v>
+      </c>
+      <c r="D807" s="10"/>
+      <c r="E807" s="11" t="s">
+        <v>3636</v>
+      </c>
+      <c r="F807" s="11" t="s">
+        <v>3637</v>
+      </c>
+      <c r="G807" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H807" s="11" t="s">
+        <v>2895</v>
+      </c>
+      <c r="I807" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="J807" s="13" t="s">
+        <v>2896</v>
+      </c>
+      <c r="K807" s="11" t="s">
+        <v>2897</v>
+      </c>
+      <c r="L807" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="M807" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="N807" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="O807" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="P807" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q807" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R807" s="11" t="s">
+        <v>2898</v>
+      </c>
+      <c r="S807" s="11" t="s">
+        <v>2899</v>
+      </c>
+      <c r="T807" s="11" t="s">
+        <v>2900</v>
+      </c>
+      <c r="U807" s="12" t="s">
+        <v>2901</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="VhLgCngJMiRW8QF3T/2YwF7B2jflRV9LNmbSWXkTo2yiZH22btpk8lDVh5X/4xjL8MyX3EAD53hcLpfYaJ+uzQ==" saltValue="5Dw36BW3x0KzOe5AXguZSw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="aaTwfIMB/OYhYE6ySk0BDkN2Hx8W3tUVmTo1OhpQw7QdXdNoE+8nPbzJoFkWHiveOkP5I5V+c/aFjxxMehnYUg==" saltValue="XwNltVOLYRw7D/OObFAzKg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B49C3C9-6878-4C9C-9816-0EC8DB60A274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8214975D-8352-4344-90FF-B2913E81E928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15075" uniqueCount="3655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15072" uniqueCount="3655">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11804,30 +11804,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{560F57B4-69FC-460F-838B-941C53B83465}" name="Table1" displayName="Table1" ref="A1:U812" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U812" xr:uid="{560F57B4-69FC-460F-838B-941C53B83465}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{678045F8-23DD-4863-8225-10DE1B56C25E}" name="Table1" displayName="Table1" ref="A1:U812" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U812" xr:uid="{678045F8-23DD-4863-8225-10DE1B56C25E}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{6F77EB1D-120E-439C-A952-9EA16A149B5E}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{2C517404-BA82-4408-B0A8-4F346020C48A}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{F72FCA63-FF93-4FF4-BBDA-33488B8055DD}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{EFA9E9D4-32B2-45EC-B9D1-51236F0F7762}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{8F36FB87-6AB3-4DB4-8684-504C88FE19D5}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{293B01C7-E55A-46C2-B88C-9637F14697A7}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{94472887-B653-4C63-9434-2509E524127D}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{095167D7-2C51-441D-A65F-7E736BFC9AE0}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{844E38E0-8F04-45FC-84B1-EC1F9B985AE2}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{BF42AD35-6918-4FCB-9BA7-18A532175689}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{9D148DDE-9D3C-4E0C-AC2F-A1CD42025440}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{113D4D04-8F38-4210-9619-D8099F2CF461}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{86324C0F-89E4-4CA6-8D60-DBCD403E0E29}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{64483317-EAB6-4911-8358-9DC3C27519C5}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{A41D5856-93DF-4A01-88C2-C0999B5F7877}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{7FF68D05-013B-49E1-83AD-7EFF6824B248}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{F9F9DB1F-BF03-49C0-9AD2-5F1C315116C9}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{DE446506-AF05-4532-BD7F-93CB4B3B6229}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{0B8797BF-EB58-4D85-94AD-07C9E2F0531A}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{079A526C-9C21-49CC-A91E-A3DB9B803FB1}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{506C43DD-FAC3-4545-AD61-4459CED94412}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{2091EC25-761D-49F3-AF30-B3518BA9EBB8}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{DE9C7501-2CF0-4DCF-8E68-E1DC3705ED2C}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{6442B08E-B225-4615-BBF6-08472D845F29}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{39034D3A-F584-4FD2-8405-19FA142D40E0}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{C479CA3E-F929-45BA-BC20-AAFEBC297AD1}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{7A722876-8DFD-43A0-B0B9-D24969FB2720}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{2DD63A5A-CF8D-4F9E-A038-8D4676CB411F}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{0BE348F8-ED9C-4CF7-A3AF-EF8BB021BAF4}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{D29DACA6-CBC8-435A-8638-BF1099279463}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{D21F904F-8DBB-4604-83FC-A93A26C58102}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{1404DFFD-D0FC-425B-B276-AA6A2AA0908B}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{E9B59512-7C4E-46F7-815B-02DBC4B3CFFE}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{EAE68030-B319-4D19-9B80-12FCD39F7BCB}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{E64BA640-3E0D-46E2-901E-13E83EDC07A9}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{5AAE1D1C-5E8F-42E7-9EA9-6DE50989B91A}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{92162138-3A9A-4CB0-B367-BE414739E7C1}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{46C50586-DB01-46E7-8F18-3AC5A29512A0}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{269BAC27-1B33-4F79-8C54-743C772B8B75}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{21F5BD1F-A6BE-4E00-92FC-F0C6BA0DFD1E}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{FF7D30AC-2B11-4E34-89CD-8A141B24F296}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{FFFA8B60-4DE1-4909-982C-C46D02DC6440}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -52959,9 +52959,7 @@
       <c r="A654" s="4">
         <v>653</v>
       </c>
-      <c r="B654" s="6" t="s">
-        <v>325</v>
-      </c>
+      <c r="B654" s="5"/>
       <c r="C654" s="6" t="s">
         <v>3101</v>
       </c>
@@ -53024,9 +53022,7 @@
       <c r="A655" s="4">
         <v>654</v>
       </c>
-      <c r="B655" s="6" t="s">
-        <v>325</v>
-      </c>
+      <c r="B655" s="5"/>
       <c r="C655" s="6" t="s">
         <v>3101</v>
       </c>
@@ -53089,9 +53085,7 @@
       <c r="A656" s="4">
         <v>655</v>
       </c>
-      <c r="B656" s="6" t="s">
-        <v>325</v>
-      </c>
+      <c r="B656" s="5"/>
       <c r="C656" s="6" t="s">
         <v>3101</v>
       </c>
@@ -62605,7 +62599,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="yk5Ku3Z/6XLu55AfLqWmy7ZsZaT+k5NQ9G7FByCb8RYMGTMsIqWSFa5sRmU5Yx/OICP9JQHgAsmH2C+9pn86vw==" saltValue="wNY7nLz74Z9gkiOI+vPbSw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="hK6WYCuxpwNyi1zyxskJ7mcZnVlxDY6So5yt+ie6JXvHj+Vx4FqeSFXCq2jsxxa1iRqkdR2p6amvCEVLH4YSdQ==" saltValue="ohA7+fhPLJOYIp1xfCADqg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8214975D-8352-4344-90FF-B2913E81E928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC678064-48B7-446D-BA26-1EC342272191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11227,41 +11227,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -11765,13 +11730,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -11790,6 +11748,48 @@
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -11804,30 +11804,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{678045F8-23DD-4863-8225-10DE1B56C25E}" name="Table1" displayName="Table1" ref="A1:U812" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U812" xr:uid="{678045F8-23DD-4863-8225-10DE1B56C25E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FF1F7753-EBD0-4FC8-BC74-94D26FD9FD2C}" name="Table1" displayName="Table1" ref="A1:U812" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
+  <autoFilter ref="A1:U812" xr:uid="{FF1F7753-EBD0-4FC8-BC74-94D26FD9FD2C}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{2091EC25-761D-49F3-AF30-B3518BA9EBB8}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{DE9C7501-2CF0-4DCF-8E68-E1DC3705ED2C}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{6442B08E-B225-4615-BBF6-08472D845F29}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{39034D3A-F584-4FD2-8405-19FA142D40E0}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{C479CA3E-F929-45BA-BC20-AAFEBC297AD1}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{7A722876-8DFD-43A0-B0B9-D24969FB2720}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{2DD63A5A-CF8D-4F9E-A038-8D4676CB411F}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{0BE348F8-ED9C-4CF7-A3AF-EF8BB021BAF4}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{D29DACA6-CBC8-435A-8638-BF1099279463}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{D21F904F-8DBB-4604-83FC-A93A26C58102}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{1404DFFD-D0FC-425B-B276-AA6A2AA0908B}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{E9B59512-7C4E-46F7-815B-02DBC4B3CFFE}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{EAE68030-B319-4D19-9B80-12FCD39F7BCB}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{E64BA640-3E0D-46E2-901E-13E83EDC07A9}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{5AAE1D1C-5E8F-42E7-9EA9-6DE50989B91A}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{92162138-3A9A-4CB0-B367-BE414739E7C1}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{46C50586-DB01-46E7-8F18-3AC5A29512A0}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{269BAC27-1B33-4F79-8C54-743C772B8B75}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{21F5BD1F-A6BE-4E00-92FC-F0C6BA0DFD1E}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{FF7D30AC-2B11-4E34-89CD-8A141B24F296}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{FFFA8B60-4DE1-4909-982C-C46D02DC6440}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8BF179F1-43D2-425D-9AC3-1224FFF07EB2}" name="PDS No." dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{35D5A97A-8BC5-4053-B651-85206B622C34}" name="STATUS" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{2DF8EB26-685C-47D3-9DF2-20878391D889}" name="Product Code" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{401290C1-B904-4748-A04F-602194D3D5DB}" name="Old Item Code" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{9F9B3650-6E2A-4B62-A906-58638F60F05E}" name="Item Code" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{DE710C2D-304E-41DB-9663-F640135F3C00}" name="Item Name" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{6354EBA8-D16D-4C46-93FC-988F58A2E309}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{6F3EA590-9117-4628-9A97-1D41D2D4FB41}" name="List of Matrix::Total Pcs" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{33413B75-37C5-4C2A-AC77-72D993F636FC}" name="List of Matrix::Total Pouch Used" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{8F9DA4A2-C3DF-4072-8A27-8578EB6222DD}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{593A641D-59F4-453C-888B-9A8912809DB7}" name="Technical DataSheet::Product Shape" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{0596D94D-46E2-4C94-84F9-8F8EBEE37F82}" name="Corrugated Box Code" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{F71DDDBC-38DF-4DAB-8A53-48788D28A54F}" name="Corrugated Box Size" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{72B592A0-8EC5-4601-8DE5-922563DB4CA6}" name="Pouch Product Code" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{C9F8752C-2AB7-4550-AFC7-1171BD73E910}" name="Pouch Size" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{582D82D5-84D3-4880-AAF8-93E02CBB5B7E}" name="Tape Roll Product Code" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{12060F56-7966-4489-B76F-BE09CDF0FFA1}" name="Tape Roll Size" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{3F00689A-1940-44B8-8285-F1CED781B621}" name="Technical DataSheet::Body Dia Major" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{4A7EF5BD-B714-4959-A5EE-55136F71A0F1}" name="Technical DataSheet::Total Height" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{DB3C1B15-65A7-41FA-8232-037B787B4AF4}" name="Technical DataSheet::Weight" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{AE88493D-4136-4C11-A639-FB714ECC8059}" name="Technical DataSheet::OFC" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -52994,10 +52994,10 @@
         <v>31</v>
       </c>
       <c r="N654" s="6" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="O654" s="6" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="P654" s="6" t="s">
         <v>34</v>
@@ -53057,10 +53057,10 @@
         <v>31</v>
       </c>
       <c r="N655" s="6" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="O655" s="6" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="P655" s="6" t="s">
         <v>34</v>
@@ -53120,10 +53120,10 @@
         <v>31</v>
       </c>
       <c r="N656" s="6" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="O656" s="6" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="P656" s="6" t="s">
         <v>34</v>
@@ -62599,7 +62599,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="hK6WYCuxpwNyi1zyxskJ7mcZnVlxDY6So5yt+ie6JXvHj+Vx4FqeSFXCq2jsxxa1iRqkdR2p6amvCEVLH4YSdQ==" saltValue="ohA7+fhPLJOYIp1xfCADqg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="oqp5MjbfoU1X7C4Neg48S+P9IxMmfW07eCX3pXHnt+xVcsUXmNHC9kCym4sWLcvNHmxBSjS5zqf+eaU4Cg2IfQ==" saltValue="aijnz2yTnupLX04A97i8eQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60177751-828A-4264-9C68-D52EC30683FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9706B52B-C0C9-4507-BEF2-EFB189E0547D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15144" uniqueCount="3664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15142" uniqueCount="3664">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11831,30 +11831,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4A1CFCA-179D-4D24-BFCB-D97027B27B9C}" name="Table1" displayName="Table1" ref="A1:U815" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U815" xr:uid="{A4A1CFCA-179D-4D24-BFCB-D97027B27B9C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E4988F4F-FB5F-44D2-B227-431663063B84}" name="Table1" displayName="Table1" ref="A1:U815" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U815" xr:uid="{E4988F4F-FB5F-44D2-B227-431663063B84}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{4C6E7D14-3340-496C-84BC-0EA0A67D5F2F}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{3D84B091-C1FC-4886-9150-00A46DDEFE87}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{66B2C513-AA36-4FE8-90F0-DA942ACD8658}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{BD1BB3C5-AB55-4D3F-BF98-6D68E5FB8078}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{06E4AF59-6DC3-4B73-8D74-A0B378AA41AB}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{E29A61CC-D90F-4DF0-975B-FDDF38CDAEE9}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{1B605783-5E5B-49D2-92B1-4488F662ED86}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{5C014F3B-B1F3-4875-8D29-46D103EF71A6}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{92729CB8-502D-409F-BAFA-6585DC23BAB6}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{56E14647-20A8-4D6A-876B-0F7EB88EBA55}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{A7D24C62-5CFC-47DC-A3D2-820F1A95854D}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{8F37D346-FF95-4AAF-A362-848C8E00DC91}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{0992072A-C6B9-4C30-A034-946BE2591102}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{BE269F37-9320-473A-B2A5-C98BF04355F5}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{C7091A8F-D015-40A3-9B9A-A1508758419F}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{BF389343-0176-41B6-9352-44F69D455F90}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{E24EDE87-2B00-430D-A353-0B877C0AB531}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{E60B118E-DD3F-4C3F-A9BD-5F1861ACB234}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{EB98E0FB-7348-487D-A963-FC932D4C9F27}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{52DE1771-BC4C-456C-8B89-FFF7F655C676}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{7934794A-A07A-4EF0-BFF6-F6890CF91EC7}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{69C833F3-2103-49FA-A59D-6FCB582C9A80}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{614EED0C-F45D-4B3D-A2CF-9C5C5E4BF16C}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{1E1BA831-BFF4-47FA-8DC0-B3318305460C}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{6EF480D8-CB6D-477D-8F26-BBC31229C687}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{8ADB38EB-CDC7-4E6A-9DBD-665AC8067397}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{5B807B99-2754-485F-9555-EEAA02FE3415}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{740B6A1C-67CC-4C06-90D9-B9146D5CA16F}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{2C994737-888A-4F66-986A-C7A47BC9B5AF}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{4B081BE9-5210-40DD-8DC8-6892FA4AD71C}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{9DB52FDE-1194-43E8-ACF4-0EAD67BDB66C}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{062BD510-A030-4C08-8F8F-B450348803B3}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{55CAEE59-54C4-4712-A353-859EC9298CEB}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{0E54ECCA-4BE0-4BC4-BCFA-EA2C256BC8AA}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{48A3C8E7-0408-48E3-AE7A-037DA1C54AC5}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{C5F94357-BB4A-429D-A1B6-03C0B05A2A46}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{5413B266-94D2-4E0E-892D-1495BA9460EB}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{B9FC8913-547E-48AB-A437-A28E33F2A85B}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{64C8E1AA-B630-4E7E-BFFD-79B3EB2ED8E2}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{85C4A6C9-50A7-4A1D-98B4-32FF4047E84B}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{0A79D8E1-0129-4855-8FA8-48AB7FB3E9FD}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{06D3D106-BFB2-44A4-A3C9-28BC6BB41ABC}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -48323,9 +48323,7 @@
       <c r="A577" s="4">
         <v>576</v>
       </c>
-      <c r="B577" s="6" t="s">
-        <v>325</v>
-      </c>
+      <c r="B577" s="5"/>
       <c r="C577" s="6" t="s">
         <v>2743</v>
       </c>
@@ -51480,9 +51478,7 @@
       <c r="A628" s="4">
         <v>627</v>
       </c>
-      <c r="B628" s="6" t="s">
-        <v>325</v>
-      </c>
+      <c r="B628" s="5"/>
       <c r="C628" s="6" t="s">
         <v>2986</v>
       </c>
@@ -62845,7 +62841,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Njt1HTiscgBqfCop7dAHyfvxe0Rf6cRc6Lzwbsmj4QNhyGqvd9c94L2AJOe813euJ/vr0a2cmLFn+KWyrTLVaA==" saltValue="41x4MvVwvLXOoCN3STsm3w==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="JhHQZwQdqrpqJxPRw4ZwheV5BTH5+w2j2d44suN7o83AXDusYyG9CAm1ZGYhKdQEnsNDvgxAMAxG5qTxnQw5hQ==" saltValue="4e6V/cJfAvtgLnm2inEmKg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9706B52B-C0C9-4507-BEF2-EFB189E0547D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5705780-7020-4C44-B2E3-D5A58B92A45B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15142" uniqueCount="3664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15160" uniqueCount="3666">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11060,6 +11060,12 @@
   </si>
   <si>
     <t>Pet 100ml Avon Dark Milky Short Neck 19mm 11gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0380.2</t>
+  </si>
+  <si>
+    <t>Pet 200ml Dome Clear 25mm 19.5gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -11831,30 +11837,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E4988F4F-FB5F-44D2-B227-431663063B84}" name="Table1" displayName="Table1" ref="A1:U815" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U815" xr:uid="{E4988F4F-FB5F-44D2-B227-431663063B84}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0DCC7983-B27F-492E-9A84-E1B563A206FB}" name="Table1" displayName="Table1" ref="A1:U816" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U816" xr:uid="{0DCC7983-B27F-492E-9A84-E1B563A206FB}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{69C833F3-2103-49FA-A59D-6FCB582C9A80}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{614EED0C-F45D-4B3D-A2CF-9C5C5E4BF16C}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{1E1BA831-BFF4-47FA-8DC0-B3318305460C}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{6EF480D8-CB6D-477D-8F26-BBC31229C687}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{8ADB38EB-CDC7-4E6A-9DBD-665AC8067397}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{5B807B99-2754-485F-9555-EEAA02FE3415}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{740B6A1C-67CC-4C06-90D9-B9146D5CA16F}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{2C994737-888A-4F66-986A-C7A47BC9B5AF}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{4B081BE9-5210-40DD-8DC8-6892FA4AD71C}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{9DB52FDE-1194-43E8-ACF4-0EAD67BDB66C}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{062BD510-A030-4C08-8F8F-B450348803B3}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{55CAEE59-54C4-4712-A353-859EC9298CEB}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{0E54ECCA-4BE0-4BC4-BCFA-EA2C256BC8AA}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{48A3C8E7-0408-48E3-AE7A-037DA1C54AC5}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{C5F94357-BB4A-429D-A1B6-03C0B05A2A46}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{5413B266-94D2-4E0E-892D-1495BA9460EB}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{B9FC8913-547E-48AB-A437-A28E33F2A85B}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{64C8E1AA-B630-4E7E-BFFD-79B3EB2ED8E2}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{85C4A6C9-50A7-4A1D-98B4-32FF4047E84B}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{0A79D8E1-0129-4855-8FA8-48AB7FB3E9FD}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{06D3D106-BFB2-44A4-A3C9-28BC6BB41ABC}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{B4EA67AB-6095-4797-9659-3F1EC5A5D3C8}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{B26D780D-838B-4865-837E-F4048E0EB8D7}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{60570EE3-E930-453C-8949-E8315EAE5C8D}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{B6B5DE0B-AD08-4480-BC78-866559AFC43B}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{DB6A3828-DEA0-4210-A6B6-6807B01276EA}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{1E1C7E34-9FFB-456C-890D-E2BF79F6F81F}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{9E9A2BFB-F69C-48A0-9591-8CB445EC5B1A}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{DD4DDF31-D57A-45B6-AED7-6B67CA089580}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{CD1736DB-116E-4480-9DF0-3CC891E1359E}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{2A794402-395A-4347-8034-35F3AEB6942C}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{346664F7-885A-47F8-B02B-E3116909DA16}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{B3452230-523B-497A-97F1-271333BEC862}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{540B4873-58DF-4F72-AD31-9B889F400729}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{3C95E29B-91C0-4747-85D0-DB9141B6E101}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{3BC55C5C-F31C-49BE-B8B2-FD636546470F}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{331976FD-F492-4C80-A025-DB8C292CC5E2}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{CF795C3F-1D5A-4FD0-82B6-7F5953975BB3}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{5A582A27-8523-407B-A95B-257693CB815C}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{961B3132-21B8-4908-A55C-A1D0F9C112AE}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{08AB16B8-08A2-4916-8F95-4766B7B89B59}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{A6BE7D4E-85A0-4FFB-87EE-29CEFB2A0457}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12157,7 +12163,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U815"/>
+  <dimension ref="A1:U816"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -62780,68 +62786,129 @@
       </c>
     </row>
     <row r="815" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A815" s="9">
+      <c r="A815" s="4">
         <v>814</v>
       </c>
-      <c r="B815" s="10"/>
-      <c r="C815" s="11" t="s">
+      <c r="B815" s="5"/>
+      <c r="C815" s="6" t="s">
         <v>3645</v>
       </c>
-      <c r="D815" s="10"/>
-      <c r="E815" s="11" t="s">
+      <c r="D815" s="5"/>
+      <c r="E815" s="6" t="s">
         <v>3662</v>
       </c>
-      <c r="F815" s="11" t="s">
+      <c r="F815" s="6" t="s">
         <v>3663</v>
       </c>
-      <c r="G815" s="11" t="s">
+      <c r="G815" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H815" s="11" t="s">
+      <c r="H815" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I815" s="11" t="s">
+      <c r="I815" s="6" t="s">
         <v>27</v>
       </c>
       <c r="J815" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="K815" s="11" t="s">
+      <c r="K815" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L815" s="11" t="s">
+      <c r="L815" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="M815" s="11" t="s">
+      <c r="M815" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="N815" s="11" t="s">
+      <c r="N815" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="O815" s="11" t="s">
+      <c r="O815" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="P815" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q815" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R815" s="11" t="s">
+      <c r="P815" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q815" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R815" s="6" t="s">
         <v>2115</v>
       </c>
-      <c r="S815" s="11" t="s">
+      <c r="S815" s="6" t="s">
         <v>2116</v>
       </c>
-      <c r="T815" s="11" t="s">
+      <c r="T815" s="6" t="s">
         <v>3648</v>
       </c>
-      <c r="U815" s="12" t="s">
+      <c r="U815" s="7" t="s">
         <v>2118</v>
       </c>
     </row>
+    <row r="816" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A816" s="9">
+        <v>815</v>
+      </c>
+      <c r="B816" s="10"/>
+      <c r="C816" s="11" t="s">
+        <v>2919</v>
+      </c>
+      <c r="D816" s="10"/>
+      <c r="E816" s="11" t="s">
+        <v>3664</v>
+      </c>
+      <c r="F816" s="11" t="s">
+        <v>3665</v>
+      </c>
+      <c r="G816" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H816" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="I816" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J816" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="K816" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="L816" s="11" t="s">
+        <v>664</v>
+      </c>
+      <c r="M816" s="11" t="s">
+        <v>665</v>
+      </c>
+      <c r="N816" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="O816" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="P816" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q816" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R816" s="11" t="s">
+        <v>2922</v>
+      </c>
+      <c r="S816" s="11" t="s">
+        <v>2923</v>
+      </c>
+      <c r="T816" s="11" t="s">
+        <v>2098</v>
+      </c>
+      <c r="U816" s="12" t="s">
+        <v>2924</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JhHQZwQdqrpqJxPRw4ZwheV5BTH5+w2j2d44suN7o83AXDusYyG9CAm1ZGYhKdQEnsNDvgxAMAxG5qTxnQw5hQ==" saltValue="4e6V/cJfAvtgLnm2inEmKg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OV/flbt6yemZn+vfOmi/VVvuPYyifrgLLbiwVI0pvRuFfLbhGYAVGUVudBOhND8LbMw+VIe8tClqaMSg4c0OaQ==" saltValue="69n+xP9xy72982pL2upSEQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5705780-7020-4C44-B2E3-D5A58B92A45B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18AFD67-BB36-44A3-B2F3-39298CB87EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15160" uniqueCount="3666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15178" uniqueCount="3669">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11066,6 +11066,15 @@
   </si>
   <si>
     <t>Pet 200ml Dome Clear 25mm 19.5gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0188</t>
+  </si>
+  <si>
+    <t>MP0188.1</t>
+  </si>
+  <si>
+    <t>Pet 100ml New Brute Amber 25mm 14gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -11837,30 +11846,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0DCC7983-B27F-492E-9A84-E1B563A206FB}" name="Table1" displayName="Table1" ref="A1:U816" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U816" xr:uid="{0DCC7983-B27F-492E-9A84-E1B563A206FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D2001379-3D88-4567-94BC-831ED3782E1B}" name="Table1" displayName="Table1" ref="A1:U817" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U817" xr:uid="{D2001379-3D88-4567-94BC-831ED3782E1B}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{B4EA67AB-6095-4797-9659-3F1EC5A5D3C8}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{B26D780D-838B-4865-837E-F4048E0EB8D7}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{60570EE3-E930-453C-8949-E8315EAE5C8D}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{B6B5DE0B-AD08-4480-BC78-866559AFC43B}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{DB6A3828-DEA0-4210-A6B6-6807B01276EA}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{1E1C7E34-9FFB-456C-890D-E2BF79F6F81F}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{9E9A2BFB-F69C-48A0-9591-8CB445EC5B1A}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{DD4DDF31-D57A-45B6-AED7-6B67CA089580}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{CD1736DB-116E-4480-9DF0-3CC891E1359E}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{2A794402-395A-4347-8034-35F3AEB6942C}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{346664F7-885A-47F8-B02B-E3116909DA16}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{B3452230-523B-497A-97F1-271333BEC862}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{540B4873-58DF-4F72-AD31-9B889F400729}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{3C95E29B-91C0-4747-85D0-DB9141B6E101}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{3BC55C5C-F31C-49BE-B8B2-FD636546470F}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{331976FD-F492-4C80-A025-DB8C292CC5E2}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{CF795C3F-1D5A-4FD0-82B6-7F5953975BB3}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{5A582A27-8523-407B-A95B-257693CB815C}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{961B3132-21B8-4908-A55C-A1D0F9C112AE}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{08AB16B8-08A2-4916-8F95-4766B7B89B59}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{A6BE7D4E-85A0-4FFB-87EE-29CEFB2A0457}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{CFE3FEA1-9CE1-432A-9346-BCFFEF9F79A2}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{9129626A-7BA2-419E-9CCB-BCF740F43007}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{2EDF2F20-8122-48C3-B707-57BD567FF71C}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{02600049-5FB7-470F-93C3-B548C8B49D27}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{8BD447DD-8096-4FDA-9679-43388653DDAA}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{ADFFF962-E717-40CA-A968-8B391F02DDAE}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{297EE0A0-3E4F-47A9-957F-6FBD87C7DCE6}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{58B3DCA4-0621-488E-AF50-0C7E7C450110}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{AE702F6A-86C9-451B-8A31-6E9521DDADD9}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{6AF36166-0D5B-4504-8BC8-82E342C6CAC5}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{9CC6F71F-E5C3-4353-A886-EB3EE8283D24}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{45CF3DC1-B9CE-42E0-B146-CF3AEC9D38E9}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{4197C04B-5283-42C7-8AA5-4CCF3DA91562}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{9A8F85E6-3112-453D-9BFC-6B71375D3BE9}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{F8303981-591C-4577-9E5F-E181921EAA67}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{E69CD932-64FB-4655-A5CF-446D490FBF48}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{B7757EEA-0FDD-4A3E-99B5-C2DEF57BE6A0}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{25E193B2-8FB3-4DA6-936C-35BDBBB2D9B7}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{67FAF9F0-D547-4303-95DE-D61F8D480369}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{5F7D815F-358D-4419-B771-BDA75A45AD1E}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{C122DCFC-40F9-43A0-B190-19F9841584FD}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12163,7 +12172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U816"/>
+  <dimension ref="A1:U817"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -62847,68 +62856,129 @@
       </c>
     </row>
     <row r="816" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A816" s="9">
+      <c r="A816" s="4">
         <v>815</v>
       </c>
-      <c r="B816" s="10"/>
-      <c r="C816" s="11" t="s">
+      <c r="B816" s="5"/>
+      <c r="C816" s="6" t="s">
         <v>2919</v>
       </c>
-      <c r="D816" s="10"/>
-      <c r="E816" s="11" t="s">
+      <c r="D816" s="5"/>
+      <c r="E816" s="6" t="s">
         <v>3664</v>
       </c>
-      <c r="F816" s="11" t="s">
+      <c r="F816" s="6" t="s">
         <v>3665</v>
       </c>
-      <c r="G816" s="11" t="s">
+      <c r="G816" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H816" s="11" t="s">
+      <c r="H816" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="I816" s="11" t="s">
+      <c r="I816" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J816" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="K816" s="11" t="s">
+      <c r="K816" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="L816" s="11" t="s">
+      <c r="L816" s="6" t="s">
         <v>664</v>
       </c>
-      <c r="M816" s="11" t="s">
+      <c r="M816" s="6" t="s">
         <v>665</v>
       </c>
-      <c r="N816" s="11" t="s">
+      <c r="N816" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="O816" s="11" t="s">
+      <c r="O816" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="P816" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q816" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R816" s="11" t="s">
+      <c r="P816" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q816" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R816" s="6" t="s">
         <v>2922</v>
       </c>
-      <c r="S816" s="11" t="s">
+      <c r="S816" s="6" t="s">
         <v>2923</v>
       </c>
-      <c r="T816" s="11" t="s">
+      <c r="T816" s="6" t="s">
         <v>2098</v>
       </c>
-      <c r="U816" s="12" t="s">
+      <c r="U816" s="7" t="s">
         <v>2924</v>
       </c>
     </row>
+    <row r="817" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A817" s="9">
+        <v>816</v>
+      </c>
+      <c r="B817" s="10"/>
+      <c r="C817" s="11" t="s">
+        <v>3666</v>
+      </c>
+      <c r="D817" s="10"/>
+      <c r="E817" s="11" t="s">
+        <v>3667</v>
+      </c>
+      <c r="F817" s="11" t="s">
+        <v>3668</v>
+      </c>
+      <c r="G817" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H817" s="11" t="s">
+        <v>3641</v>
+      </c>
+      <c r="I817" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J817" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="K817" s="11" t="s">
+        <v>3642</v>
+      </c>
+      <c r="L817" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M817" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N817" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="O817" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="P817" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q817" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R817" s="11" t="s">
+        <v>3643</v>
+      </c>
+      <c r="S817" s="11" t="s">
+        <v>3644</v>
+      </c>
+      <c r="T817" s="11" t="s">
+        <v>906</v>
+      </c>
+      <c r="U817" s="12" t="s">
+        <v>759</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OV/flbt6yemZn+vfOmi/VVvuPYyifrgLLbiwVI0pvRuFfLbhGYAVGUVudBOhND8LbMw+VIe8tClqaMSg4c0OaQ==" saltValue="69n+xP9xy72982pL2upSEQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Z/jpE8E3BjigoclYN94RBaG/cMdhhxVugUYv7/4Wn/ZxazhfFmho5yto0hYRBfa8xiR/CAm9pXViPhXnbSH+Yw==" saltValue="e9aFtPC962dOr+0r7dzlrQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18AFD67-BB36-44A3-B2F3-39298CB87EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9872142-0F35-4B24-AFF3-73DAF7B3B3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15178" uniqueCount="3669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15184" uniqueCount="3669">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11846,30 +11846,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D2001379-3D88-4567-94BC-831ED3782E1B}" name="Table1" displayName="Table1" ref="A1:U817" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U817" xr:uid="{D2001379-3D88-4567-94BC-831ED3782E1B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{858064A7-6E00-49D6-8DA1-4A6580F3143F}" name="Table1" displayName="Table1" ref="A1:U817" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U817" xr:uid="{858064A7-6E00-49D6-8DA1-4A6580F3143F}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{CFE3FEA1-9CE1-432A-9346-BCFFEF9F79A2}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{9129626A-7BA2-419E-9CCB-BCF740F43007}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{2EDF2F20-8122-48C3-B707-57BD567FF71C}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{02600049-5FB7-470F-93C3-B548C8B49D27}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{8BD447DD-8096-4FDA-9679-43388653DDAA}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{ADFFF962-E717-40CA-A968-8B391F02DDAE}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{297EE0A0-3E4F-47A9-957F-6FBD87C7DCE6}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{58B3DCA4-0621-488E-AF50-0C7E7C450110}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{AE702F6A-86C9-451B-8A31-6E9521DDADD9}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{6AF36166-0D5B-4504-8BC8-82E342C6CAC5}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{9CC6F71F-E5C3-4353-A886-EB3EE8283D24}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{45CF3DC1-B9CE-42E0-B146-CF3AEC9D38E9}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{4197C04B-5283-42C7-8AA5-4CCF3DA91562}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{9A8F85E6-3112-453D-9BFC-6B71375D3BE9}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{F8303981-591C-4577-9E5F-E181921EAA67}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{E69CD932-64FB-4655-A5CF-446D490FBF48}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{B7757EEA-0FDD-4A3E-99B5-C2DEF57BE6A0}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{25E193B2-8FB3-4DA6-936C-35BDBBB2D9B7}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{67FAF9F0-D547-4303-95DE-D61F8D480369}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{5F7D815F-358D-4419-B771-BDA75A45AD1E}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{C122DCFC-40F9-43A0-B190-19F9841584FD}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{C0F8B56B-649C-4923-BF65-1DF0B03B0947}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{B0DDC1CA-4FD1-4D94-9EF3-8EB6E480E30D}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{2E300766-1903-4282-A6A7-5A37D55A4764}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{B5F0DF15-1AC5-4779-A0A0-61DAEFE675DB}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{7CA15C36-1857-46A3-9D7F-FD014ED644EC}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{8C05FDB6-9669-4683-B0CA-4D61CA2CA2B8}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{AB260601-26D2-4E16-9ED3-8F1565E26E13}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{97238043-E293-4B28-A0D7-11FE80265CA3}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{E42A7EC1-B826-4ED3-BBB2-FBF265DDE899}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{3479CE17-5DCE-43B4-A4B2-DF4C5A855572}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{DBBADCF2-8659-49DE-89D3-2B9FDE13EF6F}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{ED695006-FCCE-46AD-B64E-B7CC59B25887}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{7A698D97-CB22-4DFE-BFA0-DA6B899C0C3F}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{369543FE-C7F9-4C0C-BC19-5ACA7B807577}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{6B575891-DAB6-4B48-BD3C-EAECA4AC0402}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{97DB1D09-B371-438D-8F37-724A83C4D052}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{176CB7B1-5BD3-4489-87A1-25D791319646}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{3E152A0F-45D6-4ED1-92F2-386952ECA641}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{0FCF580D-408D-4554-A96B-F86B2ED8E6AA}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{C82C8824-C2E3-411F-A142-4EEE22286369}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{F7DCF2BF-0D66-4BF7-9862-24AA78F95963}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -58926,12 +58926,24 @@
       <c r="K751" s="6" t="s">
         <v>3434</v>
       </c>
-      <c r="L751" s="5"/>
-      <c r="M751" s="5"/>
-      <c r="N751" s="5"/>
-      <c r="O751" s="5"/>
-      <c r="P751" s="5"/>
-      <c r="Q751" s="5"/>
+      <c r="L751" s="6" t="s">
+        <v>1567</v>
+      </c>
+      <c r="M751" s="6" t="s">
+        <v>1568</v>
+      </c>
+      <c r="N751" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O751" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="P751" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q751" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="R751" s="6" t="s">
         <v>136</v>
       </c>
@@ -62978,7 +62990,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Z/jpE8E3BjigoclYN94RBaG/cMdhhxVugUYv7/4Wn/ZxazhfFmho5yto0hYRBfa8xiR/CAm9pXViPhXnbSH+Yw==" saltValue="e9aFtPC962dOr+0r7dzlrQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="leJJtf9sfTDKS7TAwxdRNfqwkp5nUJNgy1NmBJ0Ctf7kuLeXmOqipQ/oYFkM5RMDFmhC8ysKz0JBTZCV4SvP7Q==" saltValue="I68fWK1ZBuiST6UKZtdRBA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9872142-0F35-4B24-AFF3-73DAF7B3B3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A671598-2D23-4F63-A700-9C9C245BE76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15184" uniqueCount="3669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15202" uniqueCount="3671">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11075,6 +11075,12 @@
   </si>
   <si>
     <t>Pet 100ml New Brute Amber 25mm 14gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0024.20</t>
+  </si>
+  <si>
+    <t>Pet 100ml Round Dark Milky White 25mm 12.5gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -11846,30 +11852,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{858064A7-6E00-49D6-8DA1-4A6580F3143F}" name="Table1" displayName="Table1" ref="A1:U817" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U817" xr:uid="{858064A7-6E00-49D6-8DA1-4A6580F3143F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71595CDC-6CAD-4122-8237-73CA67B3D45E}" name="Table1" displayName="Table1" ref="A1:U818" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U818" xr:uid="{71595CDC-6CAD-4122-8237-73CA67B3D45E}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{C0F8B56B-649C-4923-BF65-1DF0B03B0947}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{B0DDC1CA-4FD1-4D94-9EF3-8EB6E480E30D}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{2E300766-1903-4282-A6A7-5A37D55A4764}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{B5F0DF15-1AC5-4779-A0A0-61DAEFE675DB}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{7CA15C36-1857-46A3-9D7F-FD014ED644EC}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{8C05FDB6-9669-4683-B0CA-4D61CA2CA2B8}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{AB260601-26D2-4E16-9ED3-8F1565E26E13}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{97238043-E293-4B28-A0D7-11FE80265CA3}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{E42A7EC1-B826-4ED3-BBB2-FBF265DDE899}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{3479CE17-5DCE-43B4-A4B2-DF4C5A855572}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{DBBADCF2-8659-49DE-89D3-2B9FDE13EF6F}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{ED695006-FCCE-46AD-B64E-B7CC59B25887}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{7A698D97-CB22-4DFE-BFA0-DA6B899C0C3F}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{369543FE-C7F9-4C0C-BC19-5ACA7B807577}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{6B575891-DAB6-4B48-BD3C-EAECA4AC0402}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{97DB1D09-B371-438D-8F37-724A83C4D052}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{176CB7B1-5BD3-4489-87A1-25D791319646}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{3E152A0F-45D6-4ED1-92F2-386952ECA641}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{0FCF580D-408D-4554-A96B-F86B2ED8E6AA}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{C82C8824-C2E3-411F-A142-4EEE22286369}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{F7DCF2BF-0D66-4BF7-9862-24AA78F95963}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{FCF81929-463A-4D01-AA4F-FC70760AADD2}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{7A49A4D5-C96B-4980-8C9C-92CCF90CAD8A}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{8A41BD8B-29D3-43E2-9D8D-CBEC8E030F4A}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{58FA209A-A0EA-492B-AB56-527936B05CFB}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{18ADFD53-C47E-4A03-B75B-9B95920115C5}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{6CE15FE7-95F7-4B1E-BD4E-F23C0161CDE4}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{5286773E-5983-48BB-8100-A43544D407BB}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{F85FA0C8-2351-42B4-999F-2BB8CEA21332}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{67C8F25A-3E1E-483C-B58C-EF1106C7B0F5}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{9E9D6A68-CCB0-4DE5-998C-7D07A661AC9C}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{BC33FB7C-B7B1-4C47-BF7E-C7D5ED6B7527}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{A6014F19-10BD-4227-A74A-AB8EF3DC5F05}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{1C823406-37D4-48EE-A84E-FF8E40F6C164}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{306CC7A2-F593-4BED-9958-69266C9368F4}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{6B0C5DAB-E38D-41F2-93DD-9A6F5428A1A1}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{1F89DEA6-E423-4418-950F-B4CE5E7A7202}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{0FCF0322-EE65-42D0-8ADC-4375D154F988}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{2C111A47-AF77-4F38-BFCC-26478E786038}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{BF6F5584-FEB0-4660-B2E2-0B8958BB04C4}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{E9A1B2E1-0F84-48A3-AA39-FBB4A7DF7306}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{FEADB8AE-0CDC-47AD-90D5-1B9AB7496B1E}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12172,7 +12178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U817"/>
+  <dimension ref="A1:U818"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -62929,68 +62935,129 @@
       </c>
     </row>
     <row r="817" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A817" s="9">
+      <c r="A817" s="4">
         <v>816</v>
       </c>
-      <c r="B817" s="10"/>
-      <c r="C817" s="11" t="s">
+      <c r="B817" s="5"/>
+      <c r="C817" s="6" t="s">
         <v>3666</v>
       </c>
-      <c r="D817" s="10"/>
-      <c r="E817" s="11" t="s">
+      <c r="D817" s="5"/>
+      <c r="E817" s="6" t="s">
         <v>3667</v>
       </c>
-      <c r="F817" s="11" t="s">
+      <c r="F817" s="6" t="s">
         <v>3668</v>
       </c>
-      <c r="G817" s="11" t="s">
+      <c r="G817" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H817" s="11" t="s">
+      <c r="H817" s="6" t="s">
         <v>3641</v>
       </c>
-      <c r="I817" s="11" t="s">
+      <c r="I817" s="6" t="s">
         <v>27</v>
       </c>
       <c r="J817" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="K817" s="11" t="s">
+      <c r="K817" s="6" t="s">
         <v>3642</v>
       </c>
-      <c r="L817" s="11" t="s">
+      <c r="L817" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="M817" s="11" t="s">
+      <c r="M817" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="N817" s="11" t="s">
+      <c r="N817" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="O817" s="11" t="s">
+      <c r="O817" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="P817" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q817" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R817" s="11" t="s">
+      <c r="P817" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q817" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R817" s="6" t="s">
         <v>3643</v>
       </c>
-      <c r="S817" s="11" t="s">
+      <c r="S817" s="6" t="s">
         <v>3644</v>
       </c>
-      <c r="T817" s="11" t="s">
+      <c r="T817" s="6" t="s">
         <v>906</v>
       </c>
-      <c r="U817" s="12" t="s">
+      <c r="U817" s="7" t="s">
         <v>759</v>
       </c>
     </row>
+    <row r="818" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A818" s="9">
+        <v>817</v>
+      </c>
+      <c r="B818" s="10"/>
+      <c r="C818" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D818" s="10"/>
+      <c r="E818" s="11" t="s">
+        <v>3669</v>
+      </c>
+      <c r="F818" s="11" t="s">
+        <v>3670</v>
+      </c>
+      <c r="G818" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H818" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="I818" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J818" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="K818" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="L818" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="M818" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="N818" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="O818" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="P818" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q818" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R818" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="S818" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="T818" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="U818" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="leJJtf9sfTDKS7TAwxdRNfqwkp5nUJNgy1NmBJ0Ctf7kuLeXmOqipQ/oYFkM5RMDFmhC8ysKz0JBTZCV4SvP7Q==" saltValue="I68fWK1ZBuiST6UKZtdRBA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="sc9T+SRwgJMRmzGf3u4akGjHo+JTlocbhmKKP2UDQvgk8ilAx2Mcz/KiHPaX3PKmLSQ51xthd3CjLkf/d0BJLQ==" saltValue="YmHfC4sHJ4A3s6WWoL2wEQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A671598-2D23-4F63-A700-9C9C245BE76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B0546A-B173-447A-A800-3CF2267E482B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15202" uniqueCount="3671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15220" uniqueCount="3679">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11081,6 +11081,30 @@
   </si>
   <si>
     <t>Pet 100ml Round Dark Milky White 25mm 12.5gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0443</t>
+  </si>
+  <si>
+    <t>MP0443.1</t>
+  </si>
+  <si>
+    <t>Pet 400gm Malt Clear 53mm 30gm Jar</t>
+  </si>
+  <si>
+    <t>Malt</t>
+  </si>
+  <si>
+    <t>65.00 ± 1.00</t>
+  </si>
+  <si>
+    <t>142.00 ± 1.00</t>
+  </si>
+  <si>
+    <t>30.00 ± 2.00</t>
+  </si>
+  <si>
+    <t>412.00 ± 5.00</t>
   </si>
 </sst>
 </file>
@@ -11275,41 +11299,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -11813,13 +11802,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -11838,6 +11820,48 @@
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -11852,30 +11876,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71595CDC-6CAD-4122-8237-73CA67B3D45E}" name="Table1" displayName="Table1" ref="A1:U818" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U818" xr:uid="{71595CDC-6CAD-4122-8237-73CA67B3D45E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B93C588-85A2-4239-8014-0A5A2B3D3DAC}" name="Table1" displayName="Table1" ref="A1:U819" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
+  <autoFilter ref="A1:U819" xr:uid="{9B93C588-85A2-4239-8014-0A5A2B3D3DAC}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{FCF81929-463A-4D01-AA4F-FC70760AADD2}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{7A49A4D5-C96B-4980-8C9C-92CCF90CAD8A}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{8A41BD8B-29D3-43E2-9D8D-CBEC8E030F4A}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{58FA209A-A0EA-492B-AB56-527936B05CFB}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{18ADFD53-C47E-4A03-B75B-9B95920115C5}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{6CE15FE7-95F7-4B1E-BD4E-F23C0161CDE4}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{5286773E-5983-48BB-8100-A43544D407BB}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{F85FA0C8-2351-42B4-999F-2BB8CEA21332}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{67C8F25A-3E1E-483C-B58C-EF1106C7B0F5}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{9E9D6A68-CCB0-4DE5-998C-7D07A661AC9C}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{BC33FB7C-B7B1-4C47-BF7E-C7D5ED6B7527}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{A6014F19-10BD-4227-A74A-AB8EF3DC5F05}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{1C823406-37D4-48EE-A84E-FF8E40F6C164}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{306CC7A2-F593-4BED-9958-69266C9368F4}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{6B0C5DAB-E38D-41F2-93DD-9A6F5428A1A1}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{1F89DEA6-E423-4418-950F-B4CE5E7A7202}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{0FCF0322-EE65-42D0-8ADC-4375D154F988}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{2C111A47-AF77-4F38-BFCC-26478E786038}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{BF6F5584-FEB0-4660-B2E2-0B8958BB04C4}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{E9A1B2E1-0F84-48A3-AA39-FBB4A7DF7306}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{FEADB8AE-0CDC-47AD-90D5-1B9AB7496B1E}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{4A1D6137-705D-403F-8C93-3FD8A317C10B}" name="PDS No." dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{E5FE951D-0857-4209-8F81-B68A972A0A1E}" name="STATUS" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{4AD78A00-5D7A-4C7F-9731-8C409F2A3E58}" name="Product Code" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{BBC7C93F-62AF-4F10-B3A2-0984D5025258}" name="Old Item Code" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{B433C940-63B4-4577-869F-E2C5DF0AD419}" name="Item Code" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{C778AEE5-6C6B-4E3B-A82F-71B52FC7E0ED}" name="Item Name" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{8D17F7DA-314A-407C-A1EA-6D21C152E64E}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{B2707E22-F2FD-459F-AB7B-88647DD69CCF}" name="List of Matrix::Total Pcs" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{A719FD20-7AFA-46BC-94B6-B32D5F099E6A}" name="List of Matrix::Total Pouch Used" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{669B84FC-CC1E-45A0-ADAA-D9E14B15A9C5}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{7022B60B-65D6-4D9D-AFD9-BBAEAFF2EA3E}" name="Technical DataSheet::Product Shape" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{DE68ECF8-6B47-4B96-AD2C-28BDEFFF5939}" name="Corrugated Box Code" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{7B7D4370-CA06-462E-8707-17A0EAEB147E}" name="Corrugated Box Size" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{A7D06E6E-F118-43C7-9FA4-601384F71E74}" name="Pouch Product Code" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{3176F867-0C54-453D-A1CC-990911F760FD}" name="Pouch Size" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{D913C4C2-F520-4103-9C57-CD4E2C7E5AC1}" name="Tape Roll Product Code" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{99A46292-6DAE-47B2-BF70-3F1420AD37C9}" name="Tape Roll Size" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{CD0D80F5-317F-4D92-AB75-614B740BA08A}" name="Technical DataSheet::Body Dia Major" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{EC6023D4-60FA-4767-AB78-6EC630D8880C}" name="Technical DataSheet::Total Height" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{E344BE8A-8127-41F0-93AF-6904AA160F94}" name="Technical DataSheet::Weight" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{466BDF3B-48F6-430C-9F09-2A35B370C732}" name="Technical DataSheet::OFC" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12178,7 +12202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U818"/>
+  <dimension ref="A1:U819"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -62996,68 +63020,129 @@
       </c>
     </row>
     <row r="818" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A818" s="9">
+      <c r="A818" s="4">
         <v>817</v>
       </c>
-      <c r="B818" s="10"/>
-      <c r="C818" s="11" t="s">
+      <c r="B818" s="5"/>
+      <c r="C818" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D818" s="10"/>
-      <c r="E818" s="11" t="s">
+      <c r="D818" s="5"/>
+      <c r="E818" s="6" t="s">
         <v>3669</v>
       </c>
-      <c r="F818" s="11" t="s">
+      <c r="F818" s="6" t="s">
         <v>3670</v>
       </c>
-      <c r="G818" s="11" t="s">
+      <c r="G818" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H818" s="11" t="s">
+      <c r="H818" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="I818" s="11" t="s">
+      <c r="I818" s="6" t="s">
         <v>112</v>
       </c>
       <c r="J818" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="K818" s="11" t="s">
+      <c r="K818" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="L818" s="11" t="s">
+      <c r="L818" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="M818" s="11" t="s">
+      <c r="M818" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="N818" s="11" t="s">
+      <c r="N818" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="O818" s="11" t="s">
+      <c r="O818" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="P818" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q818" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R818" s="11" t="s">
+      <c r="P818" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q818" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R818" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="S818" s="11" t="s">
+      <c r="S818" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="T818" s="11" t="s">
+      <c r="T818" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="U818" s="12" t="s">
+      <c r="U818" s="7" t="s">
         <v>187</v>
       </c>
     </row>
+    <row r="819" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A819" s="9">
+        <v>818</v>
+      </c>
+      <c r="B819" s="10"/>
+      <c r="C819" s="11" t="s">
+        <v>3671</v>
+      </c>
+      <c r="D819" s="10"/>
+      <c r="E819" s="11" t="s">
+        <v>3672</v>
+      </c>
+      <c r="F819" s="11" t="s">
+        <v>3673</v>
+      </c>
+      <c r="G819" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H819" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="I819" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J819" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="K819" s="11" t="s">
+        <v>3674</v>
+      </c>
+      <c r="L819" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="M819" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="N819" s="11" t="s">
+        <v>764</v>
+      </c>
+      <c r="O819" s="11" t="s">
+        <v>765</v>
+      </c>
+      <c r="P819" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q819" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R819" s="11" t="s">
+        <v>3675</v>
+      </c>
+      <c r="S819" s="11" t="s">
+        <v>3676</v>
+      </c>
+      <c r="T819" s="11" t="s">
+        <v>3677</v>
+      </c>
+      <c r="U819" s="12" t="s">
+        <v>3678</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="sc9T+SRwgJMRmzGf3u4akGjHo+JTlocbhmKKP2UDQvgk8ilAx2Mcz/KiHPaX3PKmLSQ51xthd3CjLkf/d0BJLQ==" saltValue="YmHfC4sHJ4A3s6WWoL2wEQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Z/bYAPGTDPIrs0hh8WdXGfNf5zCRk82ZmlPLRsk9w4guKDMcPlmshzIFFKhV0caFcPzN3t5zo+15AUvFoZIdFQ==" saltValue="W4galu3hr9L+CIYnk3H2dQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B0546A-B173-447A-A800-3CF2267E482B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A8EE92-2116-4FA6-B21A-744ADEF00121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15220" uniqueCount="3679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15256" uniqueCount="3683">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11105,6 +11105,18 @@
   </si>
   <si>
     <t>412.00 ± 5.00</t>
+  </si>
+  <si>
+    <t>MP0332.6</t>
+  </si>
+  <si>
+    <t>Pet 200ml N Avon Dark Milky White 24mm 20gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0036.13</t>
+  </si>
+  <si>
+    <t>Pet 170ml Round Dark Milky White 25mm 16.5gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -11299,6 +11311,41 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -11802,6 +11849,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -11820,48 +11874,6 @@
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -11876,30 +11888,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B93C588-85A2-4239-8014-0A5A2B3D3DAC}" name="Table1" displayName="Table1" ref="A1:U819" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
-  <autoFilter ref="A1:U819" xr:uid="{9B93C588-85A2-4239-8014-0A5A2B3D3DAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C76B524B-DA90-4863-AB59-93CF0593C7D7}" name="Table1" displayName="Table1" ref="A1:U821" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U821" xr:uid="{C76B524B-DA90-4863-AB59-93CF0593C7D7}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{4A1D6137-705D-403F-8C93-3FD8A317C10B}" name="PDS No." dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{E5FE951D-0857-4209-8F81-B68A972A0A1E}" name="STATUS" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{4AD78A00-5D7A-4C7F-9731-8C409F2A3E58}" name="Product Code" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{BBC7C93F-62AF-4F10-B3A2-0984D5025258}" name="Old Item Code" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{B433C940-63B4-4577-869F-E2C5DF0AD419}" name="Item Code" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{C778AEE5-6C6B-4E3B-A82F-71B52FC7E0ED}" name="Item Name" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{8D17F7DA-314A-407C-A1EA-6D21C152E64E}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{B2707E22-F2FD-459F-AB7B-88647DD69CCF}" name="List of Matrix::Total Pcs" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{A719FD20-7AFA-46BC-94B6-B32D5F099E6A}" name="List of Matrix::Total Pouch Used" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{669B84FC-CC1E-45A0-ADAA-D9E14B15A9C5}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{7022B60B-65D6-4D9D-AFD9-BBAEAFF2EA3E}" name="Technical DataSheet::Product Shape" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{DE68ECF8-6B47-4B96-AD2C-28BDEFFF5939}" name="Corrugated Box Code" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{7B7D4370-CA06-462E-8707-17A0EAEB147E}" name="Corrugated Box Size" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{A7D06E6E-F118-43C7-9FA4-601384F71E74}" name="Pouch Product Code" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{3176F867-0C54-453D-A1CC-990911F760FD}" name="Pouch Size" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{D913C4C2-F520-4103-9C57-CD4E2C7E5AC1}" name="Tape Roll Product Code" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{99A46292-6DAE-47B2-BF70-3F1420AD37C9}" name="Tape Roll Size" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{CD0D80F5-317F-4D92-AB75-614B740BA08A}" name="Technical DataSheet::Body Dia Major" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{EC6023D4-60FA-4767-AB78-6EC630D8880C}" name="Technical DataSheet::Total Height" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{E344BE8A-8127-41F0-93AF-6904AA160F94}" name="Technical DataSheet::Weight" dataDxfId="1"/>
-    <tableColumn id="21" xr3:uid="{466BDF3B-48F6-430C-9F09-2A35B370C732}" name="Technical DataSheet::OFC" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{06F81FB7-CC74-47A2-A63E-CA831DF7B3B6}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{9EBD6EE2-1133-4C51-ADEE-773F2D28DC62}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{FFDAC918-ECE0-4436-8DDB-8A924A850ABF}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{D3699DE4-4732-4CDE-8607-A8BFFCA16097}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{5E75D5E0-1BC7-4C4C-9F2D-43952825C598}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{76D67656-25CA-4A46-A83E-FB04D9EE31D3}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{BD2AD9CD-C2B0-42D1-9496-FBF63B6CE2B5}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{19775B46-0EEE-4C55-94D4-24B416070D02}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{7C40178A-B7E2-4C3D-813A-B0506645A326}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{EBA818CF-61D8-49CC-95FD-CDAA7BC81F19}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{1D372D9A-9A76-4C3B-B92E-A14C23E0DC6E}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{250CE710-E700-4EB8-9725-B83A7319A547}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{D173C46E-BEC6-43E8-BBCE-AD18A973141B}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{B4EE620F-AFAE-4705-B14A-1675DB333527}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{B47F195D-A018-4E66-912C-44069D128003}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{5B0DBB6A-D634-4F85-8E5D-1CD845C959FA}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{0A87F835-BDBF-4E8E-9ADF-7A9F8BB9E8FA}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{F9E80B08-47F1-42B6-B326-EA19898666D6}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{63F762C8-A61C-49ED-BD03-F83D97627349}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{5126D4C1-A64D-440F-9677-1CD3AB360BDC}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{C0333158-4729-4744-A1B7-4CCCCD61DC08}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12202,7 +12214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U819"/>
+  <dimension ref="A1:U821"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -63081,68 +63093,190 @@
       </c>
     </row>
     <row r="819" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A819" s="9">
+      <c r="A819" s="4">
         <v>818</v>
       </c>
-      <c r="B819" s="10"/>
-      <c r="C819" s="11" t="s">
+      <c r="B819" s="5"/>
+      <c r="C819" s="6" t="s">
         <v>3671</v>
       </c>
-      <c r="D819" s="10"/>
-      <c r="E819" s="11" t="s">
+      <c r="D819" s="5"/>
+      <c r="E819" s="6" t="s">
         <v>3672</v>
       </c>
-      <c r="F819" s="11" t="s">
+      <c r="F819" s="6" t="s">
         <v>3673</v>
       </c>
-      <c r="G819" s="11" t="s">
+      <c r="G819" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H819" s="11" t="s">
+      <c r="H819" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="I819" s="11" t="s">
+      <c r="I819" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J819" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="K819" s="11" t="s">
+      <c r="K819" s="6" t="s">
         <v>3674</v>
       </c>
-      <c r="L819" s="11" t="s">
+      <c r="L819" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="M819" s="11" t="s">
+      <c r="M819" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="N819" s="11" t="s">
+      <c r="N819" s="6" t="s">
         <v>764</v>
       </c>
-      <c r="O819" s="11" t="s">
+      <c r="O819" s="6" t="s">
         <v>765</v>
       </c>
-      <c r="P819" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q819" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R819" s="11" t="s">
+      <c r="P819" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q819" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R819" s="6" t="s">
         <v>3675</v>
       </c>
-      <c r="S819" s="11" t="s">
+      <c r="S819" s="6" t="s">
         <v>3676</v>
       </c>
-      <c r="T819" s="11" t="s">
+      <c r="T819" s="6" t="s">
         <v>3677</v>
       </c>
-      <c r="U819" s="12" t="s">
+      <c r="U819" s="7" t="s">
         <v>3678</v>
       </c>
     </row>
+    <row r="820" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A820" s="4">
+        <v>819</v>
+      </c>
+      <c r="B820" s="5"/>
+      <c r="C820" s="6" t="s">
+        <v>3616</v>
+      </c>
+      <c r="D820" s="5"/>
+      <c r="E820" s="6" t="s">
+        <v>3679</v>
+      </c>
+      <c r="F820" s="6" t="s">
+        <v>3680</v>
+      </c>
+      <c r="G820" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H820" s="6" t="s">
+        <v>2287</v>
+      </c>
+      <c r="I820" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="J820" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="K820" s="6" t="s">
+        <v>3619</v>
+      </c>
+      <c r="L820" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M820" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N820" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="O820" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="P820" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q820" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R820" s="6" t="s">
+        <v>3620</v>
+      </c>
+      <c r="S820" s="6" t="s">
+        <v>2275</v>
+      </c>
+      <c r="T820" s="6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="U820" s="7" t="s">
+        <v>3621</v>
+      </c>
+    </row>
+    <row r="821" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A821" s="9">
+        <v>820</v>
+      </c>
+      <c r="B821" s="10"/>
+      <c r="C821" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="D821" s="10"/>
+      <c r="E821" s="11" t="s">
+        <v>3681</v>
+      </c>
+      <c r="F821" s="11" t="s">
+        <v>3682</v>
+      </c>
+      <c r="G821" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H821" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="I821" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J821" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="K821" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="L821" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="M821" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="N821" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="O821" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="P821" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q821" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R821" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="S821" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="T821" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="U821" s="12" t="s">
+        <v>427</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Z/bYAPGTDPIrs0hh8WdXGfNf5zCRk82ZmlPLRsk9w4guKDMcPlmshzIFFKhV0caFcPzN3t5zo+15AUvFoZIdFQ==" saltValue="W4galu3hr9L+CIYnk3H2dQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dPe4pv4XV2iCDkbYbAikjgqYQ6gkddkLV5VRB3mpkJmsByVklD8Gz0iyPFNYw15fwbRKLYv+uoNtvophTVZxVA==" saltValue="xeQaWMS9bYDJj9C6jX6KTg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A8EE92-2116-4FA6-B21A-744ADEF00121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706D438D-180E-4C7C-B8B9-33391D2CA3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15256" uniqueCount="3683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15292" uniqueCount="3687">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11117,6 +11117,18 @@
   </si>
   <si>
     <t>Pet 170ml Round Dark Milky White 25mm 16.5gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0456.4</t>
+  </si>
+  <si>
+    <t>Pet 100ml Avon Yellow Short Neck 19mm 11gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0338.6</t>
+  </si>
+  <si>
+    <t>Pet 300ml BIO Dark Milky White 24mm 23gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -11888,30 +11900,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C76B524B-DA90-4863-AB59-93CF0593C7D7}" name="Table1" displayName="Table1" ref="A1:U821" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U821" xr:uid="{C76B524B-DA90-4863-AB59-93CF0593C7D7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B973F920-91BB-4B47-91F6-69B94174153B}" name="Table1" displayName="Table1" ref="A1:U823" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U823" xr:uid="{B973F920-91BB-4B47-91F6-69B94174153B}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{06F81FB7-CC74-47A2-A63E-CA831DF7B3B6}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{9EBD6EE2-1133-4C51-ADEE-773F2D28DC62}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{FFDAC918-ECE0-4436-8DDB-8A924A850ABF}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{D3699DE4-4732-4CDE-8607-A8BFFCA16097}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{5E75D5E0-1BC7-4C4C-9F2D-43952825C598}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{76D67656-25CA-4A46-A83E-FB04D9EE31D3}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{BD2AD9CD-C2B0-42D1-9496-FBF63B6CE2B5}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{19775B46-0EEE-4C55-94D4-24B416070D02}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{7C40178A-B7E2-4C3D-813A-B0506645A326}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{EBA818CF-61D8-49CC-95FD-CDAA7BC81F19}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{1D372D9A-9A76-4C3B-B92E-A14C23E0DC6E}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{250CE710-E700-4EB8-9725-B83A7319A547}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{D173C46E-BEC6-43E8-BBCE-AD18A973141B}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{B4EE620F-AFAE-4705-B14A-1675DB333527}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{B47F195D-A018-4E66-912C-44069D128003}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{5B0DBB6A-D634-4F85-8E5D-1CD845C959FA}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{0A87F835-BDBF-4E8E-9ADF-7A9F8BB9E8FA}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{F9E80B08-47F1-42B6-B326-EA19898666D6}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{63F762C8-A61C-49ED-BD03-F83D97627349}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{5126D4C1-A64D-440F-9677-1CD3AB360BDC}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{C0333158-4729-4744-A1B7-4CCCCD61DC08}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{748C2FB8-E3AF-483B-AC70-5CD124E19585}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{A23BD4B7-256A-4B41-8C83-553E673E885F}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{9E62F48E-77BA-40A0-891C-FA38CCEA8A56}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{41E095DB-7881-4387-9B0A-42C2FDE2B52D}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{C81D88C5-F7FC-406B-B41E-ACEBD85E651C}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{28E72BAF-50B0-4F18-97D3-C8EE5630ED74}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{5EC8436E-AD3F-4588-873F-0D2E2BA18145}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{8DE00F9C-296A-475C-B7BA-E1B24D86F20A}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{492B30E9-6BCD-4C3D-A955-D7D24170A66D}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{EABBDB03-CC04-4CA6-90C2-F19B9FBF6E01}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{53D7BF20-6609-4DED-BFD4-6EE198897393}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{6AF6D016-ACCA-48BF-B83D-E0FD4283A9D4}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{CF60D1F1-67B0-44E1-B15A-027FD9CB4D67}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{50827F30-46B9-4142-909A-423C4550A242}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{FAB75CCC-6DFD-4334-8733-9CB011C36B65}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{0E7710C2-60CB-4F6A-80AF-956662408193}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{333A2CDA-998F-4087-B619-00FEF388D7F6}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{D9F8717D-ECBF-40CD-BE57-A3DD6D9C3C7B}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{47E40561-AE9E-43A2-824F-F708AC5E048E}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{44D2E8DB-0742-4F62-827C-D7DDFCFCF919}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{3094B315-BE56-41AC-97C5-61E4813C8B7E}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12214,7 +12226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U821"/>
+  <dimension ref="A1:U823"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -63215,68 +63227,190 @@
       </c>
     </row>
     <row r="821" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A821" s="9">
+      <c r="A821" s="4">
         <v>820</v>
       </c>
-      <c r="B821" s="10"/>
-      <c r="C821" s="11" t="s">
+      <c r="B821" s="5"/>
+      <c r="C821" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="D821" s="10"/>
-      <c r="E821" s="11" t="s">
+      <c r="D821" s="5"/>
+      <c r="E821" s="6" t="s">
         <v>3681</v>
       </c>
-      <c r="F821" s="11" t="s">
+      <c r="F821" s="6" t="s">
         <v>3682</v>
       </c>
-      <c r="G821" s="11" t="s">
+      <c r="G821" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H821" s="11" t="s">
+      <c r="H821" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="I821" s="11" t="s">
+      <c r="I821" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J821" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="K821" s="11" t="s">
+      <c r="K821" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="L821" s="11" t="s">
+      <c r="L821" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="M821" s="11" t="s">
+      <c r="M821" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="N821" s="11" t="s">
+      <c r="N821" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="O821" s="11" t="s">
+      <c r="O821" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="P821" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q821" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R821" s="11" t="s">
+      <c r="P821" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q821" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R821" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="S821" s="11" t="s">
+      <c r="S821" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="T821" s="11" t="s">
+      <c r="T821" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="U821" s="12" t="s">
+      <c r="U821" s="7" t="s">
         <v>427</v>
       </c>
     </row>
+    <row r="822" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A822" s="4">
+        <v>821</v>
+      </c>
+      <c r="B822" s="5"/>
+      <c r="C822" s="6" t="s">
+        <v>3645</v>
+      </c>
+      <c r="D822" s="5"/>
+      <c r="E822" s="6" t="s">
+        <v>3683</v>
+      </c>
+      <c r="F822" s="6" t="s">
+        <v>3684</v>
+      </c>
+      <c r="G822" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H822" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I822" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J822" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="K822" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L822" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M822" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N822" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="O822" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="P822" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q822" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R822" s="6" t="s">
+        <v>2115</v>
+      </c>
+      <c r="S822" s="6" t="s">
+        <v>2116</v>
+      </c>
+      <c r="T822" s="6" t="s">
+        <v>3648</v>
+      </c>
+      <c r="U822" s="7" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="823" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A823" s="9">
+        <v>822</v>
+      </c>
+      <c r="B823" s="10"/>
+      <c r="C823" s="11" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D823" s="10"/>
+      <c r="E823" s="11" t="s">
+        <v>3685</v>
+      </c>
+      <c r="F823" s="11" t="s">
+        <v>3686</v>
+      </c>
+      <c r="G823" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H823" s="11" t="s">
+        <v>2242</v>
+      </c>
+      <c r="I823" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J823" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="K823" s="11" t="s">
+        <v>2315</v>
+      </c>
+      <c r="L823" s="11" t="s">
+        <v>865</v>
+      </c>
+      <c r="M823" s="11" t="s">
+        <v>866</v>
+      </c>
+      <c r="N823" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="O823" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="P823" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q823" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R823" s="11" t="s">
+        <v>2244</v>
+      </c>
+      <c r="S823" s="11" t="s">
+        <v>2245</v>
+      </c>
+      <c r="T823" s="11" t="s">
+        <v>2316</v>
+      </c>
+      <c r="U823" s="12" t="s">
+        <v>2317</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dPe4pv4XV2iCDkbYbAikjgqYQ6gkddkLV5VRB3mpkJmsByVklD8Gz0iyPFNYw15fwbRKLYv+uoNtvophTVZxVA==" saltValue="xeQaWMS9bYDJj9C6jX6KTg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="3pEIf7rb4pgAvfeZ8JFDIXcBNRNd41s8oYKRmFIcr8Lr7YDA4SFrL/iBiLAIXLNGvRAx1TZklsST6ujHo5XMdg==" saltValue="aqNu+HfQRsfjMZs+kr4z8g==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706D438D-180E-4C7C-B8B9-33391D2CA3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F05181-532F-41BA-B61D-CFFE5C8AA52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15292" uniqueCount="3687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15328" uniqueCount="3691">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11129,6 +11129,18 @@
   </si>
   <si>
     <t>Pet 300ml BIO Dark Milky White 24mm 23gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0358.6</t>
+  </si>
+  <si>
+    <t>Pet 100ml Round Nice Tr Red 24mm 20gm CR16.5 Bottle</t>
+  </si>
+  <si>
+    <t>MP0358.7</t>
+  </si>
+  <si>
+    <t>Pet 100ml Round Nice Tr Yellow 24mm 20gm CR16.5 Bottle</t>
   </si>
 </sst>
 </file>
@@ -11160,7 +11172,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -11244,46 +11256,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -11305,16 +11282,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -11900,30 +11867,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B973F920-91BB-4B47-91F6-69B94174153B}" name="Table1" displayName="Table1" ref="A1:U823" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U823" xr:uid="{B973F920-91BB-4B47-91F6-69B94174153B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E46E294-B088-4DB8-8387-0E162EEEFA90}" name="Table1" displayName="Table1" ref="A1:U825" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U825" xr:uid="{2E46E294-B088-4DB8-8387-0E162EEEFA90}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{748C2FB8-E3AF-483B-AC70-5CD124E19585}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{A23BD4B7-256A-4B41-8C83-553E673E885F}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{9E62F48E-77BA-40A0-891C-FA38CCEA8A56}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{41E095DB-7881-4387-9B0A-42C2FDE2B52D}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{C81D88C5-F7FC-406B-B41E-ACEBD85E651C}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{28E72BAF-50B0-4F18-97D3-C8EE5630ED74}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{5EC8436E-AD3F-4588-873F-0D2E2BA18145}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{8DE00F9C-296A-475C-B7BA-E1B24D86F20A}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{492B30E9-6BCD-4C3D-A955-D7D24170A66D}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{EABBDB03-CC04-4CA6-90C2-F19B9FBF6E01}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{53D7BF20-6609-4DED-BFD4-6EE198897393}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{6AF6D016-ACCA-48BF-B83D-E0FD4283A9D4}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{CF60D1F1-67B0-44E1-B15A-027FD9CB4D67}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{50827F30-46B9-4142-909A-423C4550A242}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{FAB75CCC-6DFD-4334-8733-9CB011C36B65}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{0E7710C2-60CB-4F6A-80AF-956662408193}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{333A2CDA-998F-4087-B619-00FEF388D7F6}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{D9F8717D-ECBF-40CD-BE57-A3DD6D9C3C7B}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{47E40561-AE9E-43A2-824F-F708AC5E048E}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{44D2E8DB-0742-4F62-827C-D7DDFCFCF919}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{3094B315-BE56-41AC-97C5-61E4813C8B7E}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{0C89E0F0-F1FB-4A9F-801E-9CD84C5616AB}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{2ACE245C-3C38-4B8C-810E-06730C82F587}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{ED7BC507-8B96-4F4B-8ADD-52239D4C85A7}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{5B2F85D3-BC04-487E-9A42-CB690EC3D6A7}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{35267AEE-E64C-4A66-A009-EC46E9CC427D}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{8706712F-6B8F-44C9-98D7-E0FB239E365E}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{68A9FF35-768A-4365-800A-D29DAA71A696}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{8EAB0662-0C0C-4832-842F-A72FD133196D}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{D77393E5-241E-413A-9D73-BDEF7CEA44B2}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{359EFAE0-E67C-4245-BAF4-E1830608992C}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{AFF5CF7C-7CE4-42C1-B846-0119ADBABC01}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{DA345948-5CD6-47CD-8F14-F948D73A0363}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{85A9FEA4-CDD3-453F-AB35-D34AAB43E065}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{3871E833-0C7C-4AA0-BA7F-610DE8D6B71C}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{7345E8E8-BEF5-46B8-8CAA-4EB2D23E39A4}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{E760E468-C45B-421C-85A5-10E09825B974}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{908336F8-F4E4-43AD-B505-3EBC8AD7AEB6}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{F62B61C7-F7D7-47AA-A0F6-DDDC5B798BEB}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{5464777B-0554-40E3-B719-36AA4E9AAD1B}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{FE33DF98-5D7E-4255-809E-AD10C613CC36}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{87E5796F-57E3-40C7-B220-99EDB73DC2BD}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12226,7 +12193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U823"/>
+  <dimension ref="A1:U825"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -12343,7 +12310,7 @@
       <c r="I2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -12406,7 +12373,7 @@
       <c r="I3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="9" t="s">
         <v>46</v>
       </c>
       <c r="K3" s="6" t="s">
@@ -12469,7 +12436,7 @@
       <c r="I4" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="9" t="s">
         <v>62</v>
       </c>
       <c r="K4" s="6" t="s">
@@ -12532,7 +12499,7 @@
       <c r="I5" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="9" t="s">
         <v>75</v>
       </c>
       <c r="K5" s="6" t="s">
@@ -12595,7 +12562,7 @@
       <c r="I6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="9" t="s">
         <v>89</v>
       </c>
       <c r="K6" s="6" t="s">
@@ -12658,7 +12625,7 @@
       <c r="I7" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="9" t="s">
         <v>100</v>
       </c>
       <c r="K7" s="6" t="s">
@@ -12721,7 +12688,7 @@
       <c r="I8" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="9" t="s">
         <v>113</v>
       </c>
       <c r="K8" s="6" t="s">
@@ -12784,7 +12751,7 @@
       <c r="I9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="9" t="s">
         <v>126</v>
       </c>
       <c r="K9" s="6" t="s">
@@ -12847,7 +12814,7 @@
       <c r="I10" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="9" t="s">
         <v>135</v>
       </c>
       <c r="K10" s="6" t="s">
@@ -12910,7 +12877,7 @@
       <c r="I11" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K11" s="6" t="s">
@@ -12973,7 +12940,7 @@
       <c r="I12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="9" t="s">
         <v>158</v>
       </c>
       <c r="K12" s="6" t="s">
@@ -13036,7 +13003,7 @@
       <c r="I13" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K13" s="6" t="s">
@@ -13099,7 +13066,7 @@
       <c r="I14" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K14" s="6" t="s">
@@ -13162,7 +13129,7 @@
       <c r="I15" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K15" s="6" t="s">
@@ -13225,7 +13192,7 @@
       <c r="I16" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="J16" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K16" s="6" t="s">
@@ -13286,7 +13253,7 @@
       <c r="I17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="9" t="s">
         <v>210</v>
       </c>
       <c r="K17" s="6" t="s">
@@ -13349,7 +13316,7 @@
       <c r="I18" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K18" s="6" t="s">
@@ -13412,7 +13379,7 @@
       <c r="I19" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J19" s="13" t="s">
+      <c r="J19" s="9" t="s">
         <v>230</v>
       </c>
       <c r="K19" s="6" t="s">
@@ -13471,7 +13438,7 @@
       <c r="I20" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="9" t="s">
         <v>241</v>
       </c>
       <c r="K20" s="6" t="s">
@@ -13534,7 +13501,7 @@
       <c r="I21" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J21" s="13" t="s">
+      <c r="J21" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K21" s="6" t="s">
@@ -13597,7 +13564,7 @@
       <c r="I22" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J22" s="13" t="s">
+      <c r="J22" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K22" s="6" t="s">
@@ -13660,7 +13627,7 @@
       <c r="I23" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J23" s="13" t="s">
+      <c r="J23" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K23" s="6" t="s">
@@ -13723,7 +13690,7 @@
       <c r="I24" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J24" s="13" t="s">
+      <c r="J24" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K24" s="6" t="s">
@@ -13786,7 +13753,7 @@
       <c r="I25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J25" s="13" t="s">
+      <c r="J25" s="9" t="s">
         <v>290</v>
       </c>
       <c r="K25" s="6" t="s">
@@ -13849,7 +13816,7 @@
       <c r="I26" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J26" s="13" t="s">
+      <c r="J26" s="9" t="s">
         <v>299</v>
       </c>
       <c r="K26" s="6" t="s">
@@ -13912,7 +13879,7 @@
       <c r="I27" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J27" s="13" t="s">
+      <c r="J27" s="9" t="s">
         <v>308</v>
       </c>
       <c r="K27" s="6" t="s">
@@ -13975,7 +13942,7 @@
       <c r="I28" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J28" s="13" t="s">
+      <c r="J28" s="9" t="s">
         <v>308</v>
       </c>
       <c r="K28" s="6" t="s">
@@ -14038,7 +14005,7 @@
       <c r="I29" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J29" s="13" t="s">
+      <c r="J29" s="9" t="s">
         <v>308</v>
       </c>
       <c r="K29" s="6" t="s">
@@ -14103,7 +14070,7 @@
       <c r="I30" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J30" s="13" t="s">
+      <c r="J30" s="9" t="s">
         <v>332</v>
       </c>
       <c r="K30" s="6" t="s">
@@ -14166,7 +14133,7 @@
       <c r="I31" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J31" s="13" t="s">
+      <c r="J31" s="9" t="s">
         <v>341</v>
       </c>
       <c r="K31" s="6" t="s">
@@ -14225,7 +14192,7 @@
       <c r="I32" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J32" s="13" t="s">
+      <c r="J32" s="9" t="s">
         <v>351</v>
       </c>
       <c r="K32" s="6" t="s">
@@ -14288,7 +14255,7 @@
       <c r="I33" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="J33" s="13" t="s">
+      <c r="J33" s="9" t="s">
         <v>113</v>
       </c>
       <c r="K33" s="6" t="s">
@@ -14351,7 +14318,7 @@
       <c r="I34" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J34" s="13" t="s">
+      <c r="J34" s="9" t="s">
         <v>376</v>
       </c>
       <c r="K34" s="6" t="s">
@@ -14414,7 +14381,7 @@
       <c r="I35" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J35" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K35" s="6" t="s">
@@ -14477,7 +14444,7 @@
       <c r="I36" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J36" s="13" t="s">
+      <c r="J36" s="9" t="s">
         <v>395</v>
       </c>
       <c r="K36" s="6" t="s">
@@ -14540,7 +14507,7 @@
       <c r="I37" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J37" s="13" t="s">
+      <c r="J37" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K37" s="6" t="s">
@@ -14603,7 +14570,7 @@
       <c r="I38" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J38" s="13" t="s">
+      <c r="J38" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K38" s="6" t="s">
@@ -14666,7 +14633,7 @@
       <c r="I39" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J39" s="13" t="s">
+      <c r="J39" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K39" s="6" t="s">
@@ -14729,7 +14696,7 @@
       <c r="I40" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J40" s="13" t="s">
+      <c r="J40" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K40" s="6" t="s">
@@ -14792,7 +14759,7 @@
       <c r="I41" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J41" s="13" t="s">
+      <c r="J41" s="9" t="s">
         <v>448</v>
       </c>
       <c r="K41" s="6" t="s">
@@ -14851,7 +14818,7 @@
       <c r="I42" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J42" s="13" t="s">
+      <c r="J42" s="9" t="s">
         <v>113</v>
       </c>
       <c r="K42" s="6" t="s">
@@ -14914,7 +14881,7 @@
       <c r="I43" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J43" s="13" t="s">
+      <c r="J43" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K43" s="6" t="s">
@@ -14977,7 +14944,7 @@
       <c r="I44" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J44" s="13" t="s">
+      <c r="J44" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K44" s="6" t="s">
@@ -15040,7 +15007,7 @@
       <c r="I45" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J45" s="13" t="s">
+      <c r="J45" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K45" s="6" t="s">
@@ -15103,7 +15070,7 @@
       <c r="I46" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J46" s="13" t="s">
+      <c r="J46" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K46" s="6" t="s">
@@ -15166,7 +15133,7 @@
       <c r="I47" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J47" s="13" t="s">
+      <c r="J47" s="9" t="s">
         <v>507</v>
       </c>
       <c r="K47" s="6" t="s">
@@ -15229,7 +15196,7 @@
       <c r="I48" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J48" s="13" t="s">
+      <c r="J48" s="9" t="s">
         <v>518</v>
       </c>
       <c r="K48" s="6" t="s">
@@ -15292,7 +15259,7 @@
       <c r="I49" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J49" s="13" t="s">
+      <c r="J49" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K49" s="6" t="s">
@@ -15355,7 +15322,7 @@
       <c r="I50" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J50" s="13" t="s">
+      <c r="J50" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K50" s="6" t="s">
@@ -15418,7 +15385,7 @@
       <c r="I51" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J51" s="13" t="s">
+      <c r="J51" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K51" s="6" t="s">
@@ -15481,7 +15448,7 @@
       <c r="I52" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J52" s="13" t="s">
+      <c r="J52" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K52" s="6" t="s">
@@ -15544,7 +15511,7 @@
       <c r="I53" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J53" s="13" t="s">
+      <c r="J53" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K53" s="6" t="s">
@@ -15607,7 +15574,7 @@
       <c r="I54" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J54" s="13" t="s">
+      <c r="J54" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K54" s="6" t="s">
@@ -15672,7 +15639,7 @@
       <c r="I55" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J55" s="13" t="s">
+      <c r="J55" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K55" s="6" t="s">
@@ -15735,7 +15702,7 @@
       <c r="I56" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J56" s="13" t="s">
+      <c r="J56" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K56" s="6" t="s">
@@ -15798,7 +15765,7 @@
       <c r="I57" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J57" s="13" t="s">
+      <c r="J57" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K57" s="6" t="s">
@@ -15861,7 +15828,7 @@
       <c r="I58" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J58" s="13" t="s">
+      <c r="J58" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K58" s="6" t="s">
@@ -15924,7 +15891,7 @@
       <c r="I59" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J59" s="13" t="s">
+      <c r="J59" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K59" s="6" t="s">
@@ -15987,7 +15954,7 @@
       <c r="I60" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J60" s="13" t="s">
+      <c r="J60" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K60" s="6" t="s">
@@ -16050,7 +16017,7 @@
       <c r="I61" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J61" s="13" t="s">
+      <c r="J61" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K61" s="6" t="s">
@@ -16113,7 +16080,7 @@
       <c r="I62" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J62" s="13" t="s">
+      <c r="J62" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K62" s="6" t="s">
@@ -16176,7 +16143,7 @@
       <c r="I63" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J63" s="13" t="s">
+      <c r="J63" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K63" s="6" t="s">
@@ -16239,7 +16206,7 @@
       <c r="I64" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J64" s="13" t="s">
+      <c r="J64" s="9" t="s">
         <v>625</v>
       </c>
       <c r="K64" s="6" t="s">
@@ -16302,7 +16269,7 @@
       <c r="I65" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J65" s="13" t="s">
+      <c r="J65" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K65" s="6" t="s">
@@ -16365,7 +16332,7 @@
       <c r="I66" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J66" s="13" t="s">
+      <c r="J66" s="9" t="s">
         <v>643</v>
       </c>
       <c r="K66" s="6" t="s">
@@ -16428,7 +16395,7 @@
       <c r="I67" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J67" s="13" t="s">
+      <c r="J67" s="9" t="s">
         <v>652</v>
       </c>
       <c r="K67" s="6" t="s">
@@ -16491,7 +16458,7 @@
       <c r="I68" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J68" s="13" t="s">
+      <c r="J68" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K68" s="6" t="s">
@@ -16554,7 +16521,7 @@
       <c r="I69" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J69" s="13" t="s">
+      <c r="J69" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K69" s="6" t="s">
@@ -16617,7 +16584,7 @@
       <c r="I70" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J70" s="13" t="s">
+      <c r="J70" s="9" t="s">
         <v>688</v>
       </c>
       <c r="K70" s="6" t="s">
@@ -16680,7 +16647,7 @@
       <c r="I71" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J71" s="13" t="s">
+      <c r="J71" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K71" s="6" t="s">
@@ -16743,7 +16710,7 @@
       <c r="I72" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J72" s="13" t="s">
+      <c r="J72" s="9" t="s">
         <v>308</v>
       </c>
       <c r="K72" s="6" t="s">
@@ -16806,7 +16773,7 @@
       <c r="I73" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J73" s="13" t="s">
+      <c r="J73" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K73" s="6" t="s">
@@ -16869,7 +16836,7 @@
       <c r="I74" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J74" s="13" t="s">
+      <c r="J74" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K74" s="6" t="s">
@@ -16926,7 +16893,7 @@
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
-      <c r="J75" s="13"/>
+      <c r="J75" s="9"/>
       <c r="K75" s="6" t="s">
         <v>729</v>
       </c>
@@ -16975,7 +16942,7 @@
       <c r="I76" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J76" s="13" t="s">
+      <c r="J76" s="9" t="s">
         <v>113</v>
       </c>
       <c r="K76" s="6" t="s">
@@ -17038,7 +17005,7 @@
       <c r="I77" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J77" s="13" t="s">
+      <c r="J77" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K77" s="6" t="s">
@@ -17101,7 +17068,7 @@
       <c r="I78" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J78" s="13" t="s">
+      <c r="J78" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K78" s="6" t="s">
@@ -17164,7 +17131,7 @@
       <c r="I79" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J79" s="13" t="s">
+      <c r="J79" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K79" s="6" t="s">
@@ -17227,7 +17194,7 @@
       <c r="I80" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J80" s="13" t="s">
+      <c r="J80" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K80" s="6" t="s">
@@ -17290,7 +17257,7 @@
       <c r="I81" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J81" s="13" t="s">
+      <c r="J81" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K81" s="6" t="s">
@@ -17353,7 +17320,7 @@
       <c r="I82" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J82" s="13" t="s">
+      <c r="J82" s="9" t="s">
         <v>781</v>
       </c>
       <c r="K82" s="6" t="s">
@@ -17416,7 +17383,7 @@
       <c r="I83" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J83" s="13" t="s">
+      <c r="J83" s="9" t="s">
         <v>791</v>
       </c>
       <c r="K83" s="6" t="s">
@@ -17479,7 +17446,7 @@
       <c r="I84" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J84" s="13" t="s">
+      <c r="J84" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K84" s="6" t="s">
@@ -17542,7 +17509,7 @@
       <c r="I85" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J85" s="13" t="s">
+      <c r="J85" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K85" s="6" t="s">
@@ -17605,7 +17572,7 @@
       <c r="I86" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J86" s="13" t="s">
+      <c r="J86" s="9" t="s">
         <v>814</v>
       </c>
       <c r="K86" s="6" t="s">
@@ -17668,7 +17635,7 @@
       <c r="I87" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J87" s="13" t="s">
+      <c r="J87" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K87" s="6" t="s">
@@ -17731,7 +17698,7 @@
       <c r="I88" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J88" s="13" t="s">
+      <c r="J88" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K88" s="6" t="s">
@@ -17794,7 +17761,7 @@
       <c r="I89" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J89" s="13" t="s">
+      <c r="J89" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K89" s="6" t="s">
@@ -17857,7 +17824,7 @@
       <c r="I90" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J90" s="13" t="s">
+      <c r="J90" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K90" s="6" t="s">
@@ -17920,7 +17887,7 @@
       <c r="I91" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J91" s="13" t="s">
+      <c r="J91" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K91" s="6" t="s">
@@ -17983,7 +17950,7 @@
       <c r="I92" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J92" s="13" t="s">
+      <c r="J92" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K92" s="6" t="s">
@@ -18046,7 +18013,7 @@
       <c r="I93" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J93" s="13" t="s">
+      <c r="J93" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K93" s="6" t="s">
@@ -18109,7 +18076,7 @@
       <c r="I94" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J94" s="13" t="s">
+      <c r="J94" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K94" s="6" t="s">
@@ -18172,7 +18139,7 @@
       <c r="I95" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J95" s="13" t="s">
+      <c r="J95" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K95" s="6" t="s">
@@ -18235,7 +18202,7 @@
       <c r="I96" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J96" s="13" t="s">
+      <c r="J96" s="9" t="s">
         <v>893</v>
       </c>
       <c r="K96" s="6" t="s">
@@ -18298,7 +18265,7 @@
       <c r="I97" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J97" s="13" t="s">
+      <c r="J97" s="9" t="s">
         <v>903</v>
       </c>
       <c r="K97" s="6" t="s">
@@ -18361,7 +18328,7 @@
       <c r="I98" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J98" s="13" t="s">
+      <c r="J98" s="9" t="s">
         <v>158</v>
       </c>
       <c r="K98" s="6" t="s">
@@ -18424,7 +18391,7 @@
       <c r="I99" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J99" s="13" t="s">
+      <c r="J99" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K99" s="6" t="s">
@@ -18487,7 +18454,7 @@
       <c r="I100" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J100" s="13" t="s">
+      <c r="J100" s="9" t="s">
         <v>925</v>
       </c>
       <c r="K100" s="6" t="s">
@@ -18550,7 +18517,7 @@
       <c r="I101" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J101" s="13" t="s">
+      <c r="J101" s="9" t="s">
         <v>158</v>
       </c>
       <c r="K101" s="6" t="s">
@@ -18613,7 +18580,7 @@
       <c r="I102" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J102" s="13" t="s">
+      <c r="J102" s="9" t="s">
         <v>376</v>
       </c>
       <c r="K102" s="6" t="s">
@@ -18676,7 +18643,7 @@
       <c r="I103" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J103" s="13" t="s">
+      <c r="J103" s="9" t="s">
         <v>376</v>
       </c>
       <c r="K103" s="6" t="s">
@@ -18739,7 +18706,7 @@
       <c r="I104" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J104" s="13" t="s">
+      <c r="J104" s="9" t="s">
         <v>376</v>
       </c>
       <c r="K104" s="6" t="s">
@@ -18802,7 +18769,7 @@
       <c r="I105" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J105" s="13" t="s">
+      <c r="J105" s="9" t="s">
         <v>376</v>
       </c>
       <c r="K105" s="6" t="s">
@@ -18865,7 +18832,7 @@
       <c r="I106" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J106" s="13" t="s">
+      <c r="J106" s="9" t="s">
         <v>376</v>
       </c>
       <c r="K106" s="6" t="s">
@@ -18928,7 +18895,7 @@
       <c r="I107" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J107" s="13" t="s">
+      <c r="J107" s="9" t="s">
         <v>376</v>
       </c>
       <c r="K107" s="6" t="s">
@@ -18991,7 +18958,7 @@
       <c r="I108" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J108" s="13" t="s">
+      <c r="J108" s="9" t="s">
         <v>376</v>
       </c>
       <c r="K108" s="6" t="s">
@@ -19054,7 +19021,7 @@
       <c r="I109" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J109" s="13" t="s">
+      <c r="J109" s="9" t="s">
         <v>376</v>
       </c>
       <c r="K109" s="6" t="s">
@@ -19117,7 +19084,7 @@
       <c r="I110" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J110" s="13" t="s">
+      <c r="J110" s="9" t="s">
         <v>925</v>
       </c>
       <c r="K110" s="6" t="s">
@@ -19180,7 +19147,7 @@
       <c r="I111" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J111" s="13" t="s">
+      <c r="J111" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K111" s="6" t="s">
@@ -19243,7 +19210,7 @@
       <c r="I112" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J112" s="13" t="s">
+      <c r="J112" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K112" s="6" t="s">
@@ -19306,7 +19273,7 @@
       <c r="I113" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J113" s="13" t="s">
+      <c r="J113" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K113" s="6" t="s">
@@ -19369,7 +19336,7 @@
       <c r="I114" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J114" s="13" t="s">
+      <c r="J114" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K114" s="6" t="s">
@@ -19432,7 +19399,7 @@
       <c r="I115" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J115" s="13" t="s">
+      <c r="J115" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K115" s="6" t="s">
@@ -19495,7 +19462,7 @@
       <c r="I116" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J116" s="13" t="s">
+      <c r="J116" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K116" s="6" t="s">
@@ -19558,7 +19525,7 @@
       <c r="I117" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J117" s="13" t="s">
+      <c r="J117" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K117" s="6" t="s">
@@ -19621,7 +19588,7 @@
       <c r="I118" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J118" s="13" t="s">
+      <c r="J118" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K118" s="6" t="s">
@@ -19684,7 +19651,7 @@
       <c r="I119" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J119" s="13" t="s">
+      <c r="J119" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K119" s="6" t="s">
@@ -19747,7 +19714,7 @@
       <c r="I120" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J120" s="13" t="s">
+      <c r="J120" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K120" s="6" t="s">
@@ -19810,7 +19777,7 @@
       <c r="I121" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J121" s="13" t="s">
+      <c r="J121" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K121" s="6" t="s">
@@ -19873,7 +19840,7 @@
       <c r="I122" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J122" s="13" t="s">
+      <c r="J122" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K122" s="6" t="s">
@@ -19936,7 +19903,7 @@
       <c r="I123" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J123" s="13" t="s">
+      <c r="J123" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K123" s="6" t="s">
@@ -19999,7 +19966,7 @@
       <c r="I124" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J124" s="13" t="s">
+      <c r="J124" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K124" s="6" t="s">
@@ -20062,7 +20029,7 @@
       <c r="I125" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J125" s="13" t="s">
+      <c r="J125" s="9" t="s">
         <v>395</v>
       </c>
       <c r="K125" s="6" t="s">
@@ -20125,7 +20092,7 @@
       <c r="I126" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J126" s="13" t="s">
+      <c r="J126" s="9" t="s">
         <v>395</v>
       </c>
       <c r="K126" s="6" t="s">
@@ -20188,7 +20155,7 @@
       <c r="I127" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J127" s="13" t="s">
+      <c r="J127" s="9" t="s">
         <v>395</v>
       </c>
       <c r="K127" s="6" t="s">
@@ -20251,7 +20218,7 @@
       <c r="I128" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J128" s="13" t="s">
+      <c r="J128" s="9" t="s">
         <v>395</v>
       </c>
       <c r="K128" s="6" t="s">
@@ -20314,7 +20281,7 @@
       <c r="I129" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J129" s="13" t="s">
+      <c r="J129" s="9" t="s">
         <v>395</v>
       </c>
       <c r="K129" s="6" t="s">
@@ -20377,7 +20344,7 @@
       <c r="I130" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J130" s="13" t="s">
+      <c r="J130" s="9" t="s">
         <v>395</v>
       </c>
       <c r="K130" s="6" t="s">
@@ -20440,7 +20407,7 @@
       <c r="I131" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J131" s="13" t="s">
+      <c r="J131" s="9" t="s">
         <v>395</v>
       </c>
       <c r="K131" s="6" t="s">
@@ -20503,7 +20470,7 @@
       <c r="I132" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J132" s="13" t="s">
+      <c r="J132" s="9" t="s">
         <v>395</v>
       </c>
       <c r="K132" s="6" t="s">
@@ -20566,7 +20533,7 @@
       <c r="I133" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J133" s="13" t="s">
+      <c r="J133" s="9" t="s">
         <v>395</v>
       </c>
       <c r="K133" s="6" t="s">
@@ -20629,7 +20596,7 @@
       <c r="I134" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J134" s="13" t="s">
+      <c r="J134" s="9" t="s">
         <v>395</v>
       </c>
       <c r="K134" s="6" t="s">
@@ -20692,7 +20659,7 @@
       <c r="I135" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J135" s="13" t="s">
+      <c r="J135" s="9" t="s">
         <v>395</v>
       </c>
       <c r="K135" s="6" t="s">
@@ -20755,7 +20722,7 @@
       <c r="I136" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J136" s="13" t="s">
+      <c r="J136" s="9" t="s">
         <v>395</v>
       </c>
       <c r="K136" s="6" t="s">
@@ -20818,7 +20785,7 @@
       <c r="I137" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J137" s="13" t="s">
+      <c r="J137" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K137" s="6" t="s">
@@ -20881,7 +20848,7 @@
       <c r="I138" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J138" s="13" t="s">
+      <c r="J138" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K138" s="6" t="s">
@@ -20944,7 +20911,7 @@
       <c r="I139" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J139" s="13" t="s">
+      <c r="J139" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K139" s="6" t="s">
@@ -21007,7 +20974,7 @@
       <c r="I140" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J140" s="13" t="s">
+      <c r="J140" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K140" s="6" t="s">
@@ -21070,7 +21037,7 @@
       <c r="I141" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J141" s="13" t="s">
+      <c r="J141" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K141" s="6" t="s">
@@ -21133,7 +21100,7 @@
       <c r="I142" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J142" s="13" t="s">
+      <c r="J142" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K142" s="6" t="s">
@@ -21196,7 +21163,7 @@
       <c r="I143" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J143" s="13" t="s">
+      <c r="J143" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K143" s="6" t="s">
@@ -21259,7 +21226,7 @@
       <c r="I144" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J144" s="13" t="s">
+      <c r="J144" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K144" s="6" t="s">
@@ -21322,7 +21289,7 @@
       <c r="I145" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J145" s="13" t="s">
+      <c r="J145" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K145" s="6" t="s">
@@ -21385,7 +21352,7 @@
       <c r="I146" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J146" s="13" t="s">
+      <c r="J146" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K146" s="6" t="s">
@@ -21448,7 +21415,7 @@
       <c r="I147" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J147" s="13" t="s">
+      <c r="J147" s="9" t="s">
         <v>158</v>
       </c>
       <c r="K147" s="6" t="s">
@@ -21511,7 +21478,7 @@
       <c r="I148" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J148" s="13" t="s">
+      <c r="J148" s="9" t="s">
         <v>158</v>
       </c>
       <c r="K148" s="6" t="s">
@@ -21574,7 +21541,7 @@
       <c r="I149" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J149" s="13" t="s">
+      <c r="J149" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K149" s="6" t="s">
@@ -21637,7 +21604,7 @@
       <c r="I150" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J150" s="13" t="s">
+      <c r="J150" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K150" s="6" t="s">
@@ -21700,7 +21667,7 @@
       <c r="I151" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J151" s="13" t="s">
+      <c r="J151" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K151" s="6" t="s">
@@ -21763,7 +21730,7 @@
       <c r="I152" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J152" s="13" t="s">
+      <c r="J152" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K152" s="6" t="s">
@@ -21826,7 +21793,7 @@
       <c r="I153" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J153" s="13" t="s">
+      <c r="J153" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K153" s="6" t="s">
@@ -21889,7 +21856,7 @@
       <c r="I154" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J154" s="13" t="s">
+      <c r="J154" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K154" s="6" t="s">
@@ -21952,7 +21919,7 @@
       <c r="I155" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J155" s="13" t="s">
+      <c r="J155" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K155" s="6" t="s">
@@ -22015,7 +21982,7 @@
       <c r="I156" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J156" s="13" t="s">
+      <c r="J156" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K156" s="6" t="s">
@@ -22078,7 +22045,7 @@
       <c r="I157" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J157" s="13" t="s">
+      <c r="J157" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K157" s="6" t="s">
@@ -22141,7 +22108,7 @@
       <c r="I158" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J158" s="13" t="s">
+      <c r="J158" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K158" s="6" t="s">
@@ -22204,7 +22171,7 @@
       <c r="I159" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J159" s="13" t="s">
+      <c r="J159" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K159" s="6" t="s">
@@ -22267,7 +22234,7 @@
       <c r="I160" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J160" s="13" t="s">
+      <c r="J160" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K160" s="6" t="s">
@@ -22330,7 +22297,7 @@
       <c r="I161" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J161" s="13" t="s">
+      <c r="J161" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K161" s="6" t="s">
@@ -22393,7 +22360,7 @@
       <c r="I162" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J162" s="13" t="s">
+      <c r="J162" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K162" s="6" t="s">
@@ -22456,7 +22423,7 @@
       <c r="I163" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J163" s="13" t="s">
+      <c r="J163" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K163" s="6" t="s">
@@ -22519,7 +22486,7 @@
       <c r="I164" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J164" s="13" t="s">
+      <c r="J164" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K164" s="6" t="s">
@@ -22582,7 +22549,7 @@
       <c r="I165" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J165" s="13" t="s">
+      <c r="J165" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K165" s="6" t="s">
@@ -22645,7 +22612,7 @@
       <c r="I166" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J166" s="13" t="s">
+      <c r="J166" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K166" s="6" t="s">
@@ -22708,7 +22675,7 @@
       <c r="I167" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J167" s="13" t="s">
+      <c r="J167" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K167" s="6" t="s">
@@ -22771,7 +22738,7 @@
       <c r="I168" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J168" s="13" t="s">
+      <c r="J168" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K168" s="6" t="s">
@@ -22834,7 +22801,7 @@
       <c r="I169" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J169" s="13" t="s">
+      <c r="J169" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K169" s="6" t="s">
@@ -22897,7 +22864,7 @@
       <c r="I170" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J170" s="13" t="s">
+      <c r="J170" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K170" s="6" t="s">
@@ -22960,7 +22927,7 @@
       <c r="I171" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J171" s="13" t="s">
+      <c r="J171" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K171" s="6" t="s">
@@ -23023,7 +22990,7 @@
       <c r="I172" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J172" s="13" t="s">
+      <c r="J172" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K172" s="6" t="s">
@@ -23086,7 +23053,7 @@
       <c r="I173" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J173" s="13" t="s">
+      <c r="J173" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K173" s="6" t="s">
@@ -23149,7 +23116,7 @@
       <c r="I174" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J174" s="13" t="s">
+      <c r="J174" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K174" s="6" t="s">
@@ -23212,7 +23179,7 @@
       <c r="I175" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J175" s="13" t="s">
+      <c r="J175" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K175" s="6" t="s">
@@ -23275,7 +23242,7 @@
       <c r="I176" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J176" s="13" t="s">
+      <c r="J176" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K176" s="6" t="s">
@@ -23338,7 +23305,7 @@
       <c r="I177" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J177" s="13" t="s">
+      <c r="J177" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K177" s="6" t="s">
@@ -23401,7 +23368,7 @@
       <c r="I178" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J178" s="13" t="s">
+      <c r="J178" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K178" s="6" t="s">
@@ -23464,7 +23431,7 @@
       <c r="I179" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J179" s="13" t="s">
+      <c r="J179" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K179" s="6" t="s">
@@ -23527,7 +23494,7 @@
       <c r="I180" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J180" s="13" t="s">
+      <c r="J180" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K180" s="6" t="s">
@@ -23590,7 +23557,7 @@
       <c r="I181" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J181" s="13" t="s">
+      <c r="J181" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K181" s="6" t="s">
@@ -23653,7 +23620,7 @@
       <c r="I182" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J182" s="13" t="s">
+      <c r="J182" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K182" s="6" t="s">
@@ -23716,7 +23683,7 @@
       <c r="I183" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J183" s="13" t="s">
+      <c r="J183" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K183" s="6" t="s">
@@ -23779,7 +23746,7 @@
       <c r="I184" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J184" s="13" t="s">
+      <c r="J184" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K184" s="6" t="s">
@@ -23842,7 +23809,7 @@
       <c r="I185" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J185" s="13" t="s">
+      <c r="J185" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K185" s="6" t="s">
@@ -23905,7 +23872,7 @@
       <c r="I186" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J186" s="13" t="s">
+      <c r="J186" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K186" s="6" t="s">
@@ -23968,7 +23935,7 @@
       <c r="I187" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J187" s="13" t="s">
+      <c r="J187" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K187" s="6" t="s">
@@ -24031,7 +23998,7 @@
       <c r="I188" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J188" s="13" t="s">
+      <c r="J188" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K188" s="6" t="s">
@@ -24094,7 +24061,7 @@
       <c r="I189" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J189" s="13" t="s">
+      <c r="J189" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K189" s="6" t="s">
@@ -24157,7 +24124,7 @@
       <c r="I190" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J190" s="13" t="s">
+      <c r="J190" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K190" s="6" t="s">
@@ -24220,7 +24187,7 @@
       <c r="I191" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J191" s="13" t="s">
+      <c r="J191" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K191" s="6" t="s">
@@ -24283,7 +24250,7 @@
       <c r="I192" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J192" s="13" t="s">
+      <c r="J192" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K192" s="6" t="s">
@@ -24346,7 +24313,7 @@
       <c r="I193" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J193" s="13" t="s">
+      <c r="J193" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K193" s="6" t="s">
@@ -24409,7 +24376,7 @@
       <c r="I194" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J194" s="13" t="s">
+      <c r="J194" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K194" s="6" t="s">
@@ -24472,7 +24439,7 @@
       <c r="I195" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J195" s="13" t="s">
+      <c r="J195" s="9" t="s">
         <v>814</v>
       </c>
       <c r="K195" s="6" t="s">
@@ -24535,7 +24502,7 @@
       <c r="I196" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J196" s="13" t="s">
+      <c r="J196" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K196" s="6" t="s">
@@ -24598,7 +24565,7 @@
       <c r="I197" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J197" s="13" t="s">
+      <c r="J197" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K197" s="6" t="s">
@@ -24661,7 +24628,7 @@
       <c r="I198" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J198" s="13" t="s">
+      <c r="J198" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K198" s="6" t="s">
@@ -24724,7 +24691,7 @@
       <c r="I199" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J199" s="13" t="s">
+      <c r="J199" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K199" s="6" t="s">
@@ -24787,7 +24754,7 @@
       <c r="I200" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J200" s="13" t="s">
+      <c r="J200" s="9" t="s">
         <v>903</v>
       </c>
       <c r="K200" s="6" t="s">
@@ -24850,7 +24817,7 @@
       <c r="I201" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J201" s="13" t="s">
+      <c r="J201" s="9" t="s">
         <v>903</v>
       </c>
       <c r="K201" s="6" t="s">
@@ -24913,7 +24880,7 @@
       <c r="I202" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J202" s="13" t="s">
+      <c r="J202" s="9" t="s">
         <v>903</v>
       </c>
       <c r="K202" s="6" t="s">
@@ -24976,7 +24943,7 @@
       <c r="I203" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J203" s="13" t="s">
+      <c r="J203" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K203" s="6" t="s">
@@ -25039,7 +25006,7 @@
       <c r="I204" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J204" s="13" t="s">
+      <c r="J204" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K204" s="6" t="s">
@@ -25102,7 +25069,7 @@
       <c r="I205" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J205" s="13" t="s">
+      <c r="J205" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K205" s="6" t="s">
@@ -25165,7 +25132,7 @@
       <c r="I206" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J206" s="13" t="s">
+      <c r="J206" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K206" s="6" t="s">
@@ -25228,7 +25195,7 @@
       <c r="I207" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J207" s="13" t="s">
+      <c r="J207" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K207" s="6" t="s">
@@ -25291,7 +25258,7 @@
       <c r="I208" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J208" s="13" t="s">
+      <c r="J208" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K208" s="6" t="s">
@@ -25354,7 +25321,7 @@
       <c r="I209" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J209" s="13" t="s">
+      <c r="J209" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K209" s="6" t="s">
@@ -25417,7 +25384,7 @@
       <c r="I210" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J210" s="13" t="s">
+      <c r="J210" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K210" s="6" t="s">
@@ -25480,7 +25447,7 @@
       <c r="I211" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J211" s="13" t="s">
+      <c r="J211" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K211" s="6" t="s">
@@ -25543,7 +25510,7 @@
       <c r="I212" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J212" s="13" t="s">
+      <c r="J212" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K212" s="6" t="s">
@@ -25606,7 +25573,7 @@
       <c r="I213" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J213" s="13" t="s">
+      <c r="J213" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K213" s="6" t="s">
@@ -25669,7 +25636,7 @@
       <c r="I214" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J214" s="13" t="s">
+      <c r="J214" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K214" s="6" t="s">
@@ -25732,7 +25699,7 @@
       <c r="I215" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J215" s="13" t="s">
+      <c r="J215" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K215" s="6" t="s">
@@ -25795,7 +25762,7 @@
       <c r="I216" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J216" s="13" t="s">
+      <c r="J216" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K216" s="6" t="s">
@@ -25858,7 +25825,7 @@
       <c r="I217" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J217" s="13" t="s">
+      <c r="J217" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K217" s="6" t="s">
@@ -25921,7 +25888,7 @@
       <c r="I218" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J218" s="13" t="s">
+      <c r="J218" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K218" s="6" t="s">
@@ -25984,7 +25951,7 @@
       <c r="I219" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J219" s="13" t="s">
+      <c r="J219" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K219" s="6" t="s">
@@ -26047,7 +26014,7 @@
       <c r="I220" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J220" s="13" t="s">
+      <c r="J220" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K220" s="6" t="s">
@@ -26110,7 +26077,7 @@
       <c r="I221" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J221" s="13" t="s">
+      <c r="J221" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K221" s="6" t="s">
@@ -26173,7 +26140,7 @@
       <c r="I222" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J222" s="13" t="s">
+      <c r="J222" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K222" s="6" t="s">
@@ -26236,7 +26203,7 @@
       <c r="I223" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J223" s="13" t="s">
+      <c r="J223" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K223" s="6" t="s">
@@ -26299,7 +26266,7 @@
       <c r="I224" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J224" s="13" t="s">
+      <c r="J224" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K224" s="6" t="s">
@@ -26362,7 +26329,7 @@
       <c r="I225" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J225" s="13" t="s">
+      <c r="J225" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K225" s="6" t="s">
@@ -26425,7 +26392,7 @@
       <c r="I226" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J226" s="13" t="s">
+      <c r="J226" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K226" s="6" t="s">
@@ -26488,7 +26455,7 @@
       <c r="I227" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J227" s="13" t="s">
+      <c r="J227" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K227" s="6" t="s">
@@ -26551,7 +26518,7 @@
       <c r="I228" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J228" s="13" t="s">
+      <c r="J228" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K228" s="6" t="s">
@@ -26614,7 +26581,7 @@
       <c r="I229" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J229" s="13" t="s">
+      <c r="J229" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K229" s="6" t="s">
@@ -26677,7 +26644,7 @@
       <c r="I230" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J230" s="13" t="s">
+      <c r="J230" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K230" s="6" t="s">
@@ -26740,7 +26707,7 @@
       <c r="I231" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J231" s="13" t="s">
+      <c r="J231" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K231" s="6" t="s">
@@ -26803,7 +26770,7 @@
       <c r="I232" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J232" s="13" t="s">
+      <c r="J232" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K232" s="6" t="s">
@@ -26866,7 +26833,7 @@
       <c r="I233" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J233" s="13" t="s">
+      <c r="J233" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K233" s="6" t="s">
@@ -26929,7 +26896,7 @@
       <c r="I234" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J234" s="13" t="s">
+      <c r="J234" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K234" s="6" t="s">
@@ -26992,7 +26959,7 @@
       <c r="I235" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J235" s="13" t="s">
+      <c r="J235" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K235" s="6" t="s">
@@ -27055,7 +27022,7 @@
       <c r="I236" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J236" s="13" t="s">
+      <c r="J236" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K236" s="6" t="s">
@@ -27118,7 +27085,7 @@
       <c r="I237" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J237" s="13" t="s">
+      <c r="J237" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K237" s="6" t="s">
@@ -27181,7 +27148,7 @@
       <c r="I238" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J238" s="13" t="s">
+      <c r="J238" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K238" s="6" t="s">
@@ -27244,7 +27211,7 @@
       <c r="I239" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J239" s="13" t="s">
+      <c r="J239" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K239" s="6" t="s">
@@ -27307,7 +27274,7 @@
       <c r="I240" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J240" s="13" t="s">
+      <c r="J240" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K240" s="6" t="s">
@@ -27370,7 +27337,7 @@
       <c r="I241" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J241" s="13" t="s">
+      <c r="J241" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K241" s="6" t="s">
@@ -27433,7 +27400,7 @@
       <c r="I242" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J242" s="13" t="s">
+      <c r="J242" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K242" s="6" t="s">
@@ -27496,7 +27463,7 @@
       <c r="I243" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J243" s="13" t="s">
+      <c r="J243" s="9" t="s">
         <v>893</v>
       </c>
       <c r="K243" s="6" t="s">
@@ -27559,7 +27526,7 @@
       <c r="I244" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J244" s="13" t="s">
+      <c r="J244" s="9" t="s">
         <v>893</v>
       </c>
       <c r="K244" s="6" t="s">
@@ -27622,7 +27589,7 @@
       <c r="I245" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J245" s="13" t="s">
+      <c r="J245" s="9" t="s">
         <v>893</v>
       </c>
       <c r="K245" s="6" t="s">
@@ -27685,7 +27652,7 @@
       <c r="I246" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J246" s="13" t="s">
+      <c r="J246" s="9" t="s">
         <v>893</v>
       </c>
       <c r="K246" s="6" t="s">
@@ -27748,7 +27715,7 @@
       <c r="I247" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J247" s="13" t="s">
+      <c r="J247" s="9" t="s">
         <v>893</v>
       </c>
       <c r="K247" s="6" t="s">
@@ -27811,7 +27778,7 @@
       <c r="I248" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J248" s="13" t="s">
+      <c r="J248" s="9" t="s">
         <v>893</v>
       </c>
       <c r="K248" s="6" t="s">
@@ -27874,7 +27841,7 @@
       <c r="I249" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J249" s="13" t="s">
+      <c r="J249" s="9" t="s">
         <v>893</v>
       </c>
       <c r="K249" s="6" t="s">
@@ -27937,7 +27904,7 @@
       <c r="I250" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J250" s="13" t="s">
+      <c r="J250" s="9" t="s">
         <v>893</v>
       </c>
       <c r="K250" s="6" t="s">
@@ -28000,7 +27967,7 @@
       <c r="I251" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J251" s="13" t="s">
+      <c r="J251" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K251" s="6" t="s">
@@ -28063,7 +28030,7 @@
       <c r="I252" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J252" s="13" t="s">
+      <c r="J252" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K252" s="6" t="s">
@@ -28126,7 +28093,7 @@
       <c r="I253" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J253" s="13" t="s">
+      <c r="J253" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K253" s="6" t="s">
@@ -28189,7 +28156,7 @@
       <c r="I254" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J254" s="13" t="s">
+      <c r="J254" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K254" s="6" t="s">
@@ -28252,7 +28219,7 @@
       <c r="I255" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J255" s="13" t="s">
+      <c r="J255" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K255" s="6" t="s">
@@ -28315,7 +28282,7 @@
       <c r="I256" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J256" s="13" t="s">
+      <c r="J256" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K256" s="6" t="s">
@@ -28378,7 +28345,7 @@
       <c r="I257" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J257" s="13" t="s">
+      <c r="J257" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K257" s="6" t="s">
@@ -28441,7 +28408,7 @@
       <c r="I258" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J258" s="13" t="s">
+      <c r="J258" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K258" s="6" t="s">
@@ -28504,7 +28471,7 @@
       <c r="I259" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J259" s="13" t="s">
+      <c r="J259" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K259" s="6" t="s">
@@ -28567,7 +28534,7 @@
       <c r="I260" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J260" s="13" t="s">
+      <c r="J260" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K260" s="6" t="s">
@@ -28630,7 +28597,7 @@
       <c r="I261" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J261" s="13" t="s">
+      <c r="J261" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K261" s="6" t="s">
@@ -28693,7 +28660,7 @@
       <c r="I262" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J262" s="13" t="s">
+      <c r="J262" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K262" s="6" t="s">
@@ -28756,7 +28723,7 @@
       <c r="I263" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J263" s="13" t="s">
+      <c r="J263" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K263" s="6" t="s">
@@ -28813,7 +28780,7 @@
       <c r="I264" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J264" s="13" t="s">
+      <c r="J264" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K264" s="6" t="s">
@@ -28876,7 +28843,7 @@
       <c r="I265" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J265" s="13" t="s">
+      <c r="J265" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K265" s="6" t="s">
@@ -28939,7 +28906,7 @@
       <c r="I266" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J266" s="13" t="s">
+      <c r="J266" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K266" s="6" t="s">
@@ -29002,7 +28969,7 @@
       <c r="I267" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J267" s="13" t="s">
+      <c r="J267" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K267" s="6" t="s">
@@ -29065,7 +29032,7 @@
       <c r="I268" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J268" s="13" t="s">
+      <c r="J268" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K268" s="6" t="s">
@@ -29128,7 +29095,7 @@
       <c r="I269" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J269" s="13" t="s">
+      <c r="J269" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K269" s="6" t="s">
@@ -29191,7 +29158,7 @@
       <c r="I270" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J270" s="13" t="s">
+      <c r="J270" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K270" s="6" t="s">
@@ -29254,7 +29221,7 @@
       <c r="I271" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J271" s="13" t="s">
+      <c r="J271" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K271" s="6" t="s">
@@ -29317,7 +29284,7 @@
       <c r="I272" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J272" s="13" t="s">
+      <c r="J272" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K272" s="6" t="s">
@@ -29380,7 +29347,7 @@
       <c r="I273" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J273" s="13" t="s">
+      <c r="J273" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K273" s="6" t="s">
@@ -29443,7 +29410,7 @@
       <c r="I274" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J274" s="13" t="s">
+      <c r="J274" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K274" s="6" t="s">
@@ -29506,7 +29473,7 @@
       <c r="I275" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J275" s="13" t="s">
+      <c r="J275" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K275" s="6" t="s">
@@ -29569,7 +29536,7 @@
       <c r="I276" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J276" s="13" t="s">
+      <c r="J276" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K276" s="6" t="s">
@@ -29632,7 +29599,7 @@
       <c r="I277" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J277" s="13" t="s">
+      <c r="J277" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K277" s="6" t="s">
@@ -29695,7 +29662,7 @@
       <c r="I278" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J278" s="13" t="s">
+      <c r="J278" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K278" s="6" t="s">
@@ -29758,7 +29725,7 @@
       <c r="I279" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J279" s="13" t="s">
+      <c r="J279" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K279" s="6" t="s">
@@ -29821,7 +29788,7 @@
       <c r="I280" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J280" s="13" t="s">
+      <c r="J280" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K280" s="6" t="s">
@@ -29884,7 +29851,7 @@
       <c r="I281" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J281" s="13" t="s">
+      <c r="J281" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K281" s="6" t="s">
@@ -29947,7 +29914,7 @@
       <c r="I282" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J282" s="13" t="s">
+      <c r="J282" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K282" s="6" t="s">
@@ -30010,7 +29977,7 @@
       <c r="I283" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J283" s="13" t="s">
+      <c r="J283" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K283" s="6" t="s">
@@ -30073,7 +30040,7 @@
       <c r="I284" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J284" s="13" t="s">
+      <c r="J284" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K284" s="6" t="s">
@@ -30136,7 +30103,7 @@
       <c r="I285" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J285" s="13" t="s">
+      <c r="J285" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K285" s="6" t="s">
@@ -30199,7 +30166,7 @@
       <c r="I286" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J286" s="13" t="s">
+      <c r="J286" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K286" s="6" t="s">
@@ -30262,7 +30229,7 @@
       <c r="I287" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J287" s="13" t="s">
+      <c r="J287" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K287" s="6" t="s">
@@ -30325,7 +30292,7 @@
       <c r="I288" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J288" s="13" t="s">
+      <c r="J288" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K288" s="6" t="s">
@@ -30388,7 +30355,7 @@
       <c r="I289" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J289" s="13" t="s">
+      <c r="J289" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K289" s="6" t="s">
@@ -30451,7 +30418,7 @@
       <c r="I290" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J290" s="13" t="s">
+      <c r="J290" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K290" s="6" t="s">
@@ -30514,7 +30481,7 @@
       <c r="I291" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J291" s="13" t="s">
+      <c r="J291" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K291" s="6" t="s">
@@ -30577,7 +30544,7 @@
       <c r="I292" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J292" s="13" t="s">
+      <c r="J292" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K292" s="6" t="s">
@@ -30640,7 +30607,7 @@
       <c r="I293" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J293" s="13" t="s">
+      <c r="J293" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K293" s="6" t="s">
@@ -30703,7 +30670,7 @@
       <c r="I294" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J294" s="13" t="s">
+      <c r="J294" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K294" s="6" t="s">
@@ -30766,7 +30733,7 @@
       <c r="I295" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J295" s="13" t="s">
+      <c r="J295" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K295" s="6" t="s">
@@ -30829,7 +30796,7 @@
       <c r="I296" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J296" s="13" t="s">
+      <c r="J296" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K296" s="6" t="s">
@@ -30892,7 +30859,7 @@
       <c r="I297" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J297" s="13" t="s">
+      <c r="J297" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K297" s="6" t="s">
@@ -30955,7 +30922,7 @@
       <c r="I298" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J298" s="13" t="s">
+      <c r="J298" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K298" s="6" t="s">
@@ -31018,7 +30985,7 @@
       <c r="I299" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J299" s="13" t="s">
+      <c r="J299" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K299" s="6" t="s">
@@ -31081,7 +31048,7 @@
       <c r="I300" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J300" s="13" t="s">
+      <c r="J300" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K300" s="6" t="s">
@@ -31144,7 +31111,7 @@
       <c r="I301" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J301" s="13" t="s">
+      <c r="J301" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K301" s="6" t="s">
@@ -31207,7 +31174,7 @@
       <c r="I302" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J302" s="13" t="s">
+      <c r="J302" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K302" s="6" t="s">
@@ -31270,7 +31237,7 @@
       <c r="I303" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J303" s="13" t="s">
+      <c r="J303" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K303" s="6" t="s">
@@ -31333,7 +31300,7 @@
       <c r="I304" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J304" s="13" t="s">
+      <c r="J304" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K304" s="6" t="s">
@@ -31396,7 +31363,7 @@
       <c r="I305" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J305" s="13" t="s">
+      <c r="J305" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K305" s="6" t="s">
@@ -31459,7 +31426,7 @@
       <c r="I306" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J306" s="13" t="s">
+      <c r="J306" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K306" s="6" t="s">
@@ -31522,7 +31489,7 @@
       <c r="I307" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J307" s="13" t="s">
+      <c r="J307" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K307" s="6" t="s">
@@ -31585,7 +31552,7 @@
       <c r="I308" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J308" s="13" t="s">
+      <c r="J308" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K308" s="6" t="s">
@@ -31648,7 +31615,7 @@
       <c r="I309" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J309" s="13" t="s">
+      <c r="J309" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K309" s="6" t="s">
@@ -31711,7 +31678,7 @@
       <c r="I310" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J310" s="13" t="s">
+      <c r="J310" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K310" s="6" t="s">
@@ -31774,7 +31741,7 @@
       <c r="I311" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J311" s="13" t="s">
+      <c r="J311" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K311" s="6" t="s">
@@ -31837,7 +31804,7 @@
       <c r="I312" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J312" s="13" t="s">
+      <c r="J312" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K312" s="6" t="s">
@@ -31900,7 +31867,7 @@
       <c r="I313" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J313" s="13" t="s">
+      <c r="J313" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K313" s="6" t="s">
@@ -31963,7 +31930,7 @@
       <c r="I314" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J314" s="13" t="s">
+      <c r="J314" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K314" s="6" t="s">
@@ -32026,7 +31993,7 @@
       <c r="I315" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J315" s="13" t="s">
+      <c r="J315" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K315" s="6" t="s">
@@ -32089,7 +32056,7 @@
       <c r="I316" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J316" s="13" t="s">
+      <c r="J316" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K316" s="6" t="s">
@@ -32152,7 +32119,7 @@
       <c r="I317" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J317" s="13" t="s">
+      <c r="J317" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K317" s="6" t="s">
@@ -32215,7 +32182,7 @@
       <c r="I318" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J318" s="13" t="s">
+      <c r="J318" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K318" s="6" t="s">
@@ -32278,7 +32245,7 @@
       <c r="I319" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J319" s="13" t="s">
+      <c r="J319" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K319" s="6" t="s">
@@ -32341,7 +32308,7 @@
       <c r="I320" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J320" s="13" t="s">
+      <c r="J320" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K320" s="6" t="s">
@@ -32404,7 +32371,7 @@
       <c r="I321" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J321" s="13" t="s">
+      <c r="J321" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K321" s="6" t="s">
@@ -32467,7 +32434,7 @@
       <c r="I322" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J322" s="13" t="s">
+      <c r="J322" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K322" s="6" t="s">
@@ -32530,7 +32497,7 @@
       <c r="I323" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J323" s="13" t="s">
+      <c r="J323" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K323" s="6" t="s">
@@ -32593,7 +32560,7 @@
       <c r="I324" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J324" s="13" t="s">
+      <c r="J324" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K324" s="6" t="s">
@@ -32656,7 +32623,7 @@
       <c r="I325" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J325" s="13" t="s">
+      <c r="J325" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K325" s="6" t="s">
@@ -32719,7 +32686,7 @@
       <c r="I326" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J326" s="13" t="s">
+      <c r="J326" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K326" s="6" t="s">
@@ -32782,7 +32749,7 @@
       <c r="I327" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J327" s="13" t="s">
+      <c r="J327" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K327" s="6" t="s">
@@ -32845,7 +32812,7 @@
       <c r="I328" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J328" s="13" t="s">
+      <c r="J328" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K328" s="6" t="s">
@@ -32908,7 +32875,7 @@
       <c r="I329" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J329" s="13" t="s">
+      <c r="J329" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K329" s="6" t="s">
@@ -32971,7 +32938,7 @@
       <c r="I330" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J330" s="13" t="s">
+      <c r="J330" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K330" s="6" t="s">
@@ -33034,7 +33001,7 @@
       <c r="I331" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J331" s="13" t="s">
+      <c r="J331" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K331" s="6" t="s">
@@ -33097,7 +33064,7 @@
       <c r="I332" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J332" s="13" t="s">
+      <c r="J332" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K332" s="6" t="s">
@@ -33160,7 +33127,7 @@
       <c r="I333" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J333" s="13" t="s">
+      <c r="J333" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K333" s="6" t="s">
@@ -33223,7 +33190,7 @@
       <c r="I334" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J334" s="13" t="s">
+      <c r="J334" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K334" s="6" t="s">
@@ -33286,7 +33253,7 @@
       <c r="I335" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J335" s="13" t="s">
+      <c r="J335" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K335" s="6" t="s">
@@ -33349,7 +33316,7 @@
       <c r="I336" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J336" s="13" t="s">
+      <c r="J336" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K336" s="6" t="s">
@@ -33412,7 +33379,7 @@
       <c r="I337" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J337" s="13" t="s">
+      <c r="J337" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K337" s="6" t="s">
@@ -33475,7 +33442,7 @@
       <c r="I338" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J338" s="13" t="s">
+      <c r="J338" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K338" s="6" t="s">
@@ -33538,7 +33505,7 @@
       <c r="I339" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J339" s="13" t="s">
+      <c r="J339" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K339" s="6" t="s">
@@ -33601,7 +33568,7 @@
       <c r="I340" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J340" s="13" t="s">
+      <c r="J340" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K340" s="6" t="s">
@@ -33664,7 +33631,7 @@
       <c r="I341" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J341" s="13" t="s">
+      <c r="J341" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K341" s="6" t="s">
@@ -33727,7 +33694,7 @@
       <c r="I342" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J342" s="13" t="s">
+      <c r="J342" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K342" s="6" t="s">
@@ -33790,7 +33757,7 @@
       <c r="I343" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J343" s="13" t="s">
+      <c r="J343" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K343" s="6" t="s">
@@ -33853,7 +33820,7 @@
       <c r="I344" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J344" s="13" t="s">
+      <c r="J344" s="9" t="s">
         <v>230</v>
       </c>
       <c r="K344" s="6" t="s">
@@ -33916,7 +33883,7 @@
       <c r="I345" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J345" s="13" t="s">
+      <c r="J345" s="9" t="s">
         <v>230</v>
       </c>
       <c r="K345" s="6" t="s">
@@ -33979,7 +33946,7 @@
       <c r="I346" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J346" s="13" t="s">
+      <c r="J346" s="9" t="s">
         <v>230</v>
       </c>
       <c r="K346" s="6" t="s">
@@ -34042,7 +34009,7 @@
       <c r="I347" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J347" s="13" t="s">
+      <c r="J347" s="9" t="s">
         <v>230</v>
       </c>
       <c r="K347" s="6" t="s">
@@ -34105,7 +34072,7 @@
       <c r="I348" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J348" s="13" t="s">
+      <c r="J348" s="9" t="s">
         <v>241</v>
       </c>
       <c r="K348" s="6" t="s">
@@ -34168,7 +34135,7 @@
       <c r="I349" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J349" s="13" t="s">
+      <c r="J349" s="9" t="s">
         <v>241</v>
       </c>
       <c r="K349" s="6" t="s">
@@ -34231,7 +34198,7 @@
       <c r="I350" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J350" s="13" t="s">
+      <c r="J350" s="9" t="s">
         <v>241</v>
       </c>
       <c r="K350" s="6" t="s">
@@ -34294,7 +34261,7 @@
       <c r="I351" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J351" s="13" t="s">
+      <c r="J351" s="9" t="s">
         <v>241</v>
       </c>
       <c r="K351" s="6" t="s">
@@ -34357,7 +34324,7 @@
       <c r="I352" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J352" s="13" t="s">
+      <c r="J352" s="9" t="s">
         <v>241</v>
       </c>
       <c r="K352" s="6" t="s">
@@ -34420,7 +34387,7 @@
       <c r="I353" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J353" s="13" t="s">
+      <c r="J353" s="9" t="s">
         <v>241</v>
       </c>
       <c r="K353" s="6" t="s">
@@ -34483,7 +34450,7 @@
       <c r="I354" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J354" s="13" t="s">
+      <c r="J354" s="9" t="s">
         <v>210</v>
       </c>
       <c r="K354" s="6" t="s">
@@ -34546,7 +34513,7 @@
       <c r="I355" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J355" s="13" t="s">
+      <c r="J355" s="9" t="s">
         <v>210</v>
       </c>
       <c r="K355" s="6" t="s">
@@ -34609,7 +34576,7 @@
       <c r="I356" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J356" s="13" t="s">
+      <c r="J356" s="9" t="s">
         <v>210</v>
       </c>
       <c r="K356" s="6" t="s">
@@ -34672,7 +34639,7 @@
       <c r="I357" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J357" s="13" t="s">
+      <c r="J357" s="9" t="s">
         <v>351</v>
       </c>
       <c r="K357" s="6" t="s">
@@ -34735,7 +34702,7 @@
       <c r="I358" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J358" s="13" t="s">
+      <c r="J358" s="9" t="s">
         <v>351</v>
       </c>
       <c r="K358" s="6" t="s">
@@ -34798,7 +34765,7 @@
       <c r="I359" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J359" s="13" t="s">
+      <c r="J359" s="9" t="s">
         <v>351</v>
       </c>
       <c r="K359" s="6" t="s">
@@ -34861,7 +34828,7 @@
       <c r="I360" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="J360" s="13" t="s">
+      <c r="J360" s="9" t="s">
         <v>113</v>
       </c>
       <c r="K360" s="6" t="s">
@@ -34924,7 +34891,7 @@
       <c r="I361" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="J361" s="13" t="s">
+      <c r="J361" s="9" t="s">
         <v>113</v>
       </c>
       <c r="K361" s="6" t="s">
@@ -34987,7 +34954,7 @@
       <c r="I362" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="J362" s="13" t="s">
+      <c r="J362" s="9" t="s">
         <v>113</v>
       </c>
       <c r="K362" s="6" t="s">
@@ -35050,7 +35017,7 @@
       <c r="I363" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J363" s="13" t="s">
+      <c r="J363" s="9" t="s">
         <v>341</v>
       </c>
       <c r="K363" s="6" t="s">
@@ -35109,7 +35076,7 @@
       <c r="I364" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J364" s="13" t="s">
+      <c r="J364" s="9" t="s">
         <v>341</v>
       </c>
       <c r="K364" s="6" t="s">
@@ -35168,7 +35135,7 @@
       <c r="I365" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J365" s="13" t="s">
+      <c r="J365" s="9" t="s">
         <v>341</v>
       </c>
       <c r="K365" s="6" t="s">
@@ -35227,7 +35194,7 @@
       <c r="I366" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J366" s="13" t="s">
+      <c r="J366" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K366" s="6" t="s">
@@ -35290,7 +35257,7 @@
       <c r="I367" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J367" s="13" t="s">
+      <c r="J367" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K367" s="6" t="s">
@@ -35353,7 +35320,7 @@
       <c r="I368" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J368" s="13" t="s">
+      <c r="J368" s="9" t="s">
         <v>290</v>
       </c>
       <c r="K368" s="6" t="s">
@@ -35416,7 +35383,7 @@
       <c r="I369" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J369" s="13" t="s">
+      <c r="J369" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K369" s="6" t="s">
@@ -35479,7 +35446,7 @@
       <c r="I370" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J370" s="13" t="s">
+      <c r="J370" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K370" s="6" t="s">
@@ -35542,7 +35509,7 @@
       <c r="I371" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J371" s="13" t="s">
+      <c r="J371" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K371" s="6" t="s">
@@ -35605,7 +35572,7 @@
       <c r="I372" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J372" s="13" t="s">
+      <c r="J372" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K372" s="6" t="s">
@@ -35668,7 +35635,7 @@
       <c r="I373" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J373" s="13" t="s">
+      <c r="J373" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K373" s="6" t="s">
@@ -35731,7 +35698,7 @@
       <c r="I374" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J374" s="13" t="s">
+      <c r="J374" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K374" s="6" t="s">
@@ -35794,7 +35761,7 @@
       <c r="I375" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J375" s="13" t="s">
+      <c r="J375" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K375" s="6" t="s">
@@ -35857,7 +35824,7 @@
       <c r="I376" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J376" s="13" t="s">
+      <c r="J376" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K376" s="6" t="s">
@@ -35920,7 +35887,7 @@
       <c r="I377" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J377" s="13" t="s">
+      <c r="J377" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K377" s="6" t="s">
@@ -35983,7 +35950,7 @@
       <c r="I378" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J378" s="13" t="s">
+      <c r="J378" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K378" s="6" t="s">
@@ -36046,7 +36013,7 @@
       <c r="I379" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J379" s="13" t="s">
+      <c r="J379" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K379" s="6" t="s">
@@ -36105,7 +36072,7 @@
       <c r="I380" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J380" s="13" t="s">
+      <c r="J380" s="9" t="s">
         <v>270</v>
       </c>
       <c r="K380" s="6" t="s">
@@ -36168,7 +36135,7 @@
       <c r="I381" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J381" s="13" t="s">
+      <c r="J381" s="9" t="s">
         <v>652</v>
       </c>
       <c r="K381" s="6" t="s">
@@ -36231,7 +36198,7 @@
       <c r="I382" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J382" s="13" t="s">
+      <c r="J382" s="9" t="s">
         <v>652</v>
       </c>
       <c r="K382" s="6" t="s">
@@ -36296,7 +36263,7 @@
       <c r="I383" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J383" s="13" t="s">
+      <c r="J383" s="9" t="s">
         <v>332</v>
       </c>
       <c r="K383" s="6" t="s">
@@ -36361,7 +36328,7 @@
       <c r="I384" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J384" s="13" t="s">
+      <c r="J384" s="9" t="s">
         <v>332</v>
       </c>
       <c r="K384" s="6" t="s">
@@ -36426,7 +36393,7 @@
       <c r="I385" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J385" s="13" t="s">
+      <c r="J385" s="9" t="s">
         <v>332</v>
       </c>
       <c r="K385" s="6" t="s">
@@ -36491,7 +36458,7 @@
       <c r="I386" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J386" s="13" t="s">
+      <c r="J386" s="9" t="s">
         <v>332</v>
       </c>
       <c r="K386" s="6" t="s">
@@ -36556,7 +36523,7 @@
       <c r="I387" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J387" s="13" t="s">
+      <c r="J387" s="9" t="s">
         <v>332</v>
       </c>
       <c r="K387" s="6" t="s">
@@ -36619,7 +36586,7 @@
       <c r="I388" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J388" s="13" t="s">
+      <c r="J388" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K388" s="6" t="s">
@@ -36682,7 +36649,7 @@
       <c r="I389" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J389" s="13" t="s">
+      <c r="J389" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K389" s="6" t="s">
@@ -36745,7 +36712,7 @@
       <c r="I390" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J390" s="13" t="s">
+      <c r="J390" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K390" s="6" t="s">
@@ -36808,7 +36775,7 @@
       <c r="I391" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J391" s="13" t="s">
+      <c r="J391" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K391" s="6" t="s">
@@ -36871,7 +36838,7 @@
       <c r="I392" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J392" s="13" t="s">
+      <c r="J392" s="9" t="s">
         <v>1819</v>
       </c>
       <c r="K392" s="6" t="s">
@@ -36934,7 +36901,7 @@
       <c r="I393" s="6" t="s">
         <v>1829</v>
       </c>
-      <c r="J393" s="13" t="s">
+      <c r="J393" s="9" t="s">
         <v>1830</v>
       </c>
       <c r="K393" s="6" t="s">
@@ -36997,7 +36964,7 @@
       <c r="I394" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J394" s="13" t="s">
+      <c r="J394" s="9" t="s">
         <v>791</v>
       </c>
       <c r="K394" s="6" t="s">
@@ -37060,7 +37027,7 @@
       <c r="I395" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J395" s="13" t="s">
+      <c r="J395" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K395" s="6" t="s">
@@ -37123,7 +37090,7 @@
       <c r="I396" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J396" s="13" t="s">
+      <c r="J396" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K396" s="6" t="s">
@@ -37186,7 +37153,7 @@
       <c r="I397" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J397" s="13" t="s">
+      <c r="J397" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K397" s="6" t="s">
@@ -37249,7 +37216,7 @@
       <c r="I398" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J398" s="13" t="s">
+      <c r="J398" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K398" s="6" t="s">
@@ -37312,7 +37279,7 @@
       <c r="I399" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J399" s="13" t="s">
+      <c r="J399" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K399" s="6" t="s">
@@ -37375,7 +37342,7 @@
       <c r="I400" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J400" s="13" t="s">
+      <c r="J400" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K400" s="6" t="s">
@@ -37438,7 +37405,7 @@
       <c r="I401" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J401" s="13" t="s">
+      <c r="J401" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K401" s="6" t="s">
@@ -37501,7 +37468,7 @@
       <c r="I402" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J402" s="13" t="s">
+      <c r="J402" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K402" s="6" t="s">
@@ -37564,7 +37531,7 @@
       <c r="I403" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J403" s="13" t="s">
+      <c r="J403" s="9" t="s">
         <v>1873</v>
       </c>
       <c r="K403" s="6" t="s">
@@ -37627,7 +37594,7 @@
       <c r="I404" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J404" s="13" t="s">
+      <c r="J404" s="9" t="s">
         <v>1873</v>
       </c>
       <c r="K404" s="6" t="s">
@@ -37690,7 +37657,7 @@
       <c r="I405" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J405" s="13" t="s">
+      <c r="J405" s="9" t="s">
         <v>1886</v>
       </c>
       <c r="K405" s="6" t="s">
@@ -37753,7 +37720,7 @@
       <c r="I406" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J406" s="13" t="s">
+      <c r="J406" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K406" s="6" t="s">
@@ -37816,7 +37783,7 @@
       <c r="I407" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J407" s="13" t="s">
+      <c r="J407" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K407" s="6" t="s">
@@ -37879,7 +37846,7 @@
       <c r="I408" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J408" s="13" t="s">
+      <c r="J408" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K408" s="6" t="s">
@@ -37942,7 +37909,7 @@
       <c r="I409" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J409" s="13" t="s">
+      <c r="J409" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K409" s="6" t="s">
@@ -38005,7 +37972,7 @@
       <c r="I410" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J410" s="13" t="s">
+      <c r="J410" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K410" s="6" t="s">
@@ -38068,7 +38035,7 @@
       <c r="I411" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J411" s="13" t="s">
+      <c r="J411" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K411" s="6" t="s">
@@ -38131,7 +38098,7 @@
       <c r="I412" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J412" s="13" t="s">
+      <c r="J412" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K412" s="6" t="s">
@@ -38194,7 +38161,7 @@
       <c r="I413" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J413" s="13" t="s">
+      <c r="J413" s="9" t="s">
         <v>75</v>
       </c>
       <c r="K413" s="6" t="s">
@@ -38257,7 +38224,7 @@
       <c r="I414" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J414" s="13" t="s">
+      <c r="J414" s="9" t="s">
         <v>75</v>
       </c>
       <c r="K414" s="6" t="s">
@@ -38320,7 +38287,7 @@
       <c r="I415" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J415" s="13" t="s">
+      <c r="J415" s="9" t="s">
         <v>75</v>
       </c>
       <c r="K415" s="6" t="s">
@@ -38383,7 +38350,7 @@
       <c r="I416" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J416" s="13" t="s">
+      <c r="J416" s="9" t="s">
         <v>75</v>
       </c>
       <c r="K416" s="6" t="s">
@@ -38446,7 +38413,7 @@
       <c r="I417" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J417" s="13" t="s">
+      <c r="J417" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K417" s="6" t="s">
@@ -38509,7 +38476,7 @@
       <c r="I418" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J418" s="13" t="s">
+      <c r="J418" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K418" s="6" t="s">
@@ -38572,7 +38539,7 @@
       <c r="I419" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J419" s="13" t="s">
+      <c r="J419" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K419" s="6" t="s">
@@ -38635,7 +38602,7 @@
       <c r="I420" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J420" s="13" t="s">
+      <c r="J420" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K420" s="6" t="s">
@@ -38698,7 +38665,7 @@
       <c r="I421" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J421" s="13" t="s">
+      <c r="J421" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K421" s="6" t="s">
@@ -38761,7 +38728,7 @@
       <c r="I422" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J422" s="13" t="s">
+      <c r="J422" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K422" s="6" t="s">
@@ -38824,7 +38791,7 @@
       <c r="I423" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J423" s="13" t="s">
+      <c r="J423" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K423" s="6" t="s">
@@ -38887,7 +38854,7 @@
       <c r="I424" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J424" s="13" t="s">
+      <c r="J424" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K424" s="6" t="s">
@@ -38950,7 +38917,7 @@
       <c r="I425" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J425" s="13" t="s">
+      <c r="J425" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K425" s="6" t="s">
@@ -39013,7 +38980,7 @@
       <c r="I426" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J426" s="13" t="s">
+      <c r="J426" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K426" s="6" t="s">
@@ -39076,7 +39043,7 @@
       <c r="I427" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J427" s="13" t="s">
+      <c r="J427" s="9" t="s">
         <v>2001</v>
       </c>
       <c r="K427" s="6" t="s">
@@ -39139,7 +39106,7 @@
       <c r="I428" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J428" s="13" t="s">
+      <c r="J428" s="9" t="s">
         <v>2001</v>
       </c>
       <c r="K428" s="6" t="s">
@@ -39202,7 +39169,7 @@
       <c r="I429" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J429" s="13" t="s">
+      <c r="J429" s="9" t="s">
         <v>2001</v>
       </c>
       <c r="K429" s="6" t="s">
@@ -39265,7 +39232,7 @@
       <c r="I430" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J430" s="13" t="s">
+      <c r="J430" s="9" t="s">
         <v>2001</v>
       </c>
       <c r="K430" s="6" t="s">
@@ -39328,7 +39295,7 @@
       <c r="I431" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J431" s="13" t="s">
+      <c r="J431" s="9" t="s">
         <v>2020</v>
       </c>
       <c r="K431" s="6" t="s">
@@ -39391,7 +39358,7 @@
       <c r="I432" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J432" s="13" t="s">
+      <c r="J432" s="9" t="s">
         <v>2020</v>
       </c>
       <c r="K432" s="6" t="s">
@@ -39454,7 +39421,7 @@
       <c r="I433" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J433" s="13" t="s">
+      <c r="J433" s="9" t="s">
         <v>2020</v>
       </c>
       <c r="K433" s="6" t="s">
@@ -39517,7 +39484,7 @@
       <c r="I434" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J434" s="13" t="s">
+      <c r="J434" s="9" t="s">
         <v>2036</v>
       </c>
       <c r="K434" s="6" t="s">
@@ -39580,7 +39547,7 @@
       <c r="I435" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J435" s="13" t="s">
+      <c r="J435" s="9" t="s">
         <v>2036</v>
       </c>
       <c r="K435" s="6" t="s">
@@ -39643,7 +39610,7 @@
       <c r="I436" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J436" s="13" t="s">
+      <c r="J436" s="9" t="s">
         <v>2036</v>
       </c>
       <c r="K436" s="6" t="s">
@@ -39706,7 +39673,7 @@
       <c r="I437" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J437" s="13" t="s">
+      <c r="J437" s="9" t="s">
         <v>652</v>
       </c>
       <c r="K437" s="6" t="s">
@@ -39769,7 +39736,7 @@
       <c r="I438" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J438" s="13" t="s">
+      <c r="J438" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K438" s="6" t="s">
@@ -39832,7 +39799,7 @@
       <c r="I439" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J439" s="13" t="s">
+      <c r="J439" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K439" s="6" t="s">
@@ -39895,7 +39862,7 @@
       <c r="I440" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J440" s="13" t="s">
+      <c r="J440" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K440" s="6" t="s">
@@ -39958,7 +39925,7 @@
       <c r="I441" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J441" s="13" t="s">
+      <c r="J441" s="9" t="s">
         <v>2072</v>
       </c>
       <c r="K441" s="6" t="s">
@@ -40021,7 +39988,7 @@
       <c r="I442" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J442" s="13" t="s">
+      <c r="J442" s="9" t="s">
         <v>2072</v>
       </c>
       <c r="K442" s="6" t="s">
@@ -40084,7 +40051,7 @@
       <c r="I443" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J443" s="13" t="s">
+      <c r="J443" s="9" t="s">
         <v>2072</v>
       </c>
       <c r="K443" s="6" t="s">
@@ -40147,7 +40114,7 @@
       <c r="I444" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J444" s="13" t="s">
+      <c r="J444" s="9" t="s">
         <v>2072</v>
       </c>
       <c r="K444" s="6" t="s">
@@ -40210,7 +40177,7 @@
       <c r="I445" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J445" s="13" t="s">
+      <c r="J445" s="9" t="s">
         <v>2072</v>
       </c>
       <c r="K445" s="6" t="s">
@@ -40273,7 +40240,7 @@
       <c r="I446" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J446" s="13" t="s">
+      <c r="J446" s="9" t="s">
         <v>2072</v>
       </c>
       <c r="K446" s="6" t="s">
@@ -40336,7 +40303,7 @@
       <c r="I447" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J447" s="13" t="s">
+      <c r="J447" s="9" t="s">
         <v>113</v>
       </c>
       <c r="K447" s="6" t="s">
@@ -40399,7 +40366,7 @@
       <c r="I448" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J448" s="13" t="s">
+      <c r="J448" s="9" t="s">
         <v>893</v>
       </c>
       <c r="K448" s="6" t="s">
@@ -40462,7 +40429,7 @@
       <c r="I449" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J449" s="13" t="s">
+      <c r="J449" s="9" t="s">
         <v>1819</v>
       </c>
       <c r="K449" s="6" t="s">
@@ -40525,7 +40492,7 @@
       <c r="I450" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J450" s="13" t="s">
+      <c r="J450" s="9" t="s">
         <v>1819</v>
       </c>
       <c r="K450" s="6" t="s">
@@ -40588,7 +40555,7 @@
       <c r="I451" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J451" s="13" t="s">
+      <c r="J451" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K451" s="6" t="s">
@@ -40651,7 +40618,7 @@
       <c r="I452" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J452" s="13" t="s">
+      <c r="J452" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K452" s="6" t="s">
@@ -40714,7 +40681,7 @@
       <c r="I453" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J453" s="13" t="s">
+      <c r="J453" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K453" s="6" t="s">
@@ -40777,7 +40744,7 @@
       <c r="I454" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J454" s="13" t="s">
+      <c r="J454" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K454" s="6" t="s">
@@ -40840,7 +40807,7 @@
       <c r="I455" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J455" s="13" t="s">
+      <c r="J455" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K455" s="6" t="s">
@@ -40903,7 +40870,7 @@
       <c r="I456" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J456" s="13" t="s">
+      <c r="J456" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K456" s="6" t="s">
@@ -40966,7 +40933,7 @@
       <c r="I457" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J457" s="13" t="s">
+      <c r="J457" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K457" s="6" t="s">
@@ -41029,7 +40996,7 @@
       <c r="I458" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J458" s="13" t="s">
+      <c r="J458" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K458" s="6" t="s">
@@ -41092,7 +41059,7 @@
       <c r="I459" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J459" s="13" t="s">
+      <c r="J459" s="9" t="s">
         <v>135</v>
       </c>
       <c r="K459" s="6" t="s">
@@ -41155,7 +41122,7 @@
       <c r="I460" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J460" s="13" t="s">
+      <c r="J460" s="9" t="s">
         <v>893</v>
       </c>
       <c r="K460" s="6" t="s">
@@ -41218,7 +41185,7 @@
       <c r="I461" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J461" s="13" t="s">
+      <c r="J461" s="9" t="s">
         <v>2161</v>
       </c>
       <c r="K461" s="6" t="s">
@@ -41281,7 +41248,7 @@
       <c r="I462" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J462" s="13" t="s">
+      <c r="J462" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K462" s="6" t="s">
@@ -41344,7 +41311,7 @@
       <c r="I463" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J463" s="13" t="s">
+      <c r="J463" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K463" s="6" t="s">
@@ -41407,7 +41374,7 @@
       <c r="I464" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J464" s="13" t="s">
+      <c r="J464" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K464" s="6" t="s">
@@ -41470,7 +41437,7 @@
       <c r="I465" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J465" s="13" t="s">
+      <c r="J465" s="9" t="s">
         <v>2185</v>
       </c>
       <c r="K465" s="6" t="s">
@@ -41533,7 +41500,7 @@
       <c r="I466" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J466" s="13" t="s">
+      <c r="J466" s="9" t="s">
         <v>2194</v>
       </c>
       <c r="K466" s="6" t="s">
@@ -41596,7 +41563,7 @@
       <c r="I467" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J467" s="13" t="s">
+      <c r="J467" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K467" s="6" t="s">
@@ -41659,7 +41626,7 @@
       <c r="I468" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J468" s="13" t="s">
+      <c r="J468" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K468" s="6" t="s">
@@ -41722,7 +41689,7 @@
       <c r="I469" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J469" s="13" t="s">
+      <c r="J469" s="9" t="s">
         <v>2214</v>
       </c>
       <c r="K469" s="6" t="s">
@@ -41785,7 +41752,7 @@
       <c r="I470" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J470" s="13" t="s">
+      <c r="J470" s="9" t="s">
         <v>2224</v>
       </c>
       <c r="K470" s="6" t="s">
@@ -41848,7 +41815,7 @@
       <c r="I471" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J471" s="13" t="s">
+      <c r="J471" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K471" s="6" t="s">
@@ -41911,7 +41878,7 @@
       <c r="I472" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J472" s="13" t="s">
+      <c r="J472" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K472" s="6" t="s">
@@ -41974,7 +41941,7 @@
       <c r="I473" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J473" s="13" t="s">
+      <c r="J473" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K473" s="6" t="s">
@@ -42037,7 +42004,7 @@
       <c r="I474" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J474" s="13" t="s">
+      <c r="J474" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K474" s="6" t="s">
@@ -42100,7 +42067,7 @@
       <c r="I475" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J475" s="13" t="s">
+      <c r="J475" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K475" s="6" t="s">
@@ -42163,7 +42130,7 @@
       <c r="I476" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J476" s="13" t="s">
+      <c r="J476" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K476" s="6" t="s">
@@ -42226,7 +42193,7 @@
       <c r="I477" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J477" s="13" t="s">
+      <c r="J477" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K477" s="6" t="s">
@@ -42291,7 +42258,7 @@
       <c r="I478" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J478" s="13" t="s">
+      <c r="J478" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K478" s="6" t="s">
@@ -42356,7 +42323,7 @@
       <c r="I479" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J479" s="13" t="s">
+      <c r="J479" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K479" s="6" t="s">
@@ -42421,7 +42388,7 @@
       <c r="I480" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J480" s="13" t="s">
+      <c r="J480" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K480" s="6" t="s">
@@ -42484,7 +42451,7 @@
       <c r="I481" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J481" s="13" t="s">
+      <c r="J481" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K481" s="6" t="s">
@@ -42547,7 +42514,7 @@
       <c r="I482" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J482" s="13" t="s">
+      <c r="J482" s="9" t="s">
         <v>2297</v>
       </c>
       <c r="K482" s="6" t="s">
@@ -42610,7 +42577,7 @@
       <c r="I483" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J483" s="13" t="s">
+      <c r="J483" s="9" t="s">
         <v>2307</v>
       </c>
       <c r="K483" s="6" t="s">
@@ -42673,7 +42640,7 @@
       <c r="I484" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J484" s="13" t="s">
+      <c r="J484" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K484" s="6" t="s">
@@ -42736,7 +42703,7 @@
       <c r="I485" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J485" s="13" t="s">
+      <c r="J485" s="9" t="s">
         <v>448</v>
       </c>
       <c r="K485" s="6" t="s">
@@ -42795,7 +42762,7 @@
       <c r="I486" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J486" s="13" t="s">
+      <c r="J486" s="9" t="s">
         <v>135</v>
       </c>
       <c r="K486" s="6" t="s">
@@ -42858,7 +42825,7 @@
       <c r="I487" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J487" s="13" t="s">
+      <c r="J487" s="9" t="s">
         <v>2333</v>
       </c>
       <c r="K487" s="6" t="s">
@@ -42921,7 +42888,7 @@
       <c r="I488" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J488" s="13" t="s">
+      <c r="J488" s="9" t="s">
         <v>308</v>
       </c>
       <c r="K488" s="6" t="s">
@@ -42984,7 +42951,7 @@
       <c r="I489" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J489" s="13" t="s">
+      <c r="J489" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K489" s="6" t="s">
@@ -43047,7 +43014,7 @@
       <c r="I490" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J490" s="13" t="s">
+      <c r="J490" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K490" s="6" t="s">
@@ -43110,7 +43077,7 @@
       <c r="I491" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J491" s="13" t="s">
+      <c r="J491" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K491" s="6" t="s">
@@ -43173,7 +43140,7 @@
       <c r="I492" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J492" s="13" t="s">
+      <c r="J492" s="9" t="s">
         <v>2001</v>
       </c>
       <c r="K492" s="6" t="s">
@@ -43236,7 +43203,7 @@
       <c r="I493" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J493" s="13" t="s">
+      <c r="J493" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K493" s="6" t="s">
@@ -43299,7 +43266,7 @@
       <c r="I494" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J494" s="13" t="s">
+      <c r="J494" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K494" s="6" t="s">
@@ -43362,7 +43329,7 @@
       <c r="I495" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J495" s="13" t="s">
+      <c r="J495" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K495" s="6" t="s">
@@ -43425,7 +43392,7 @@
       <c r="I496" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J496" s="13" t="s">
+      <c r="J496" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K496" s="6" t="s">
@@ -43488,7 +43455,7 @@
       <c r="I497" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J497" s="13" t="s">
+      <c r="J497" s="9" t="s">
         <v>2399</v>
       </c>
       <c r="K497" s="6" t="s">
@@ -43551,7 +43518,7 @@
       <c r="I498" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J498" s="13" t="s">
+      <c r="J498" s="9" t="s">
         <v>2399</v>
       </c>
       <c r="K498" s="6" t="s">
@@ -43614,7 +43581,7 @@
       <c r="I499" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J499" s="13" t="s">
+      <c r="J499" s="9" t="s">
         <v>2399</v>
       </c>
       <c r="K499" s="6" t="s">
@@ -43677,7 +43644,7 @@
       <c r="I500" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J500" s="13" t="s">
+      <c r="J500" s="9" t="s">
         <v>1873</v>
       </c>
       <c r="K500" s="6" t="s">
@@ -43740,7 +43707,7 @@
       <c r="I501" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J501" s="13" t="s">
+      <c r="J501" s="9" t="s">
         <v>2419</v>
       </c>
       <c r="K501" s="6" t="s">
@@ -43803,7 +43770,7 @@
       <c r="I502" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J502" s="13" t="s">
+      <c r="J502" s="9" t="s">
         <v>2419</v>
       </c>
       <c r="K502" s="6" t="s">
@@ -43866,7 +43833,7 @@
       <c r="I503" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J503" s="13" t="s">
+      <c r="J503" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K503" s="6" t="s">
@@ -43929,7 +43896,7 @@
       <c r="I504" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J504" s="13" t="s">
+      <c r="J504" s="9" t="s">
         <v>2433</v>
       </c>
       <c r="K504" s="6" t="s">
@@ -43992,7 +43959,7 @@
       <c r="I505" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J505" s="13" t="s">
+      <c r="J505" s="9" t="s">
         <v>2433</v>
       </c>
       <c r="K505" s="6" t="s">
@@ -44055,7 +44022,7 @@
       <c r="I506" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J506" s="13" t="s">
+      <c r="J506" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K506" s="6" t="s">
@@ -44118,7 +44085,7 @@
       <c r="I507" s="6" t="s">
         <v>2453</v>
       </c>
-      <c r="J507" s="13" t="s">
+      <c r="J507" s="9" t="s">
         <v>2214</v>
       </c>
       <c r="K507" s="6" t="s">
@@ -44181,7 +44148,7 @@
       <c r="I508" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J508" s="13" t="s">
+      <c r="J508" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K508" s="6" t="s">
@@ -44244,7 +44211,7 @@
       <c r="I509" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J509" s="13" t="s">
+      <c r="J509" s="9" t="s">
         <v>2185</v>
       </c>
       <c r="K509" s="6" t="s">
@@ -44307,7 +44274,7 @@
       <c r="I510" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J510" s="13" t="s">
+      <c r="J510" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K510" s="6" t="s">
@@ -44370,7 +44337,7 @@
       <c r="I511" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J511" s="13" t="s">
+      <c r="J511" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K511" s="6" t="s">
@@ -44433,7 +44400,7 @@
       <c r="I512" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J512" s="13" t="s">
+      <c r="J512" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K512" s="6" t="s">
@@ -44496,7 +44463,7 @@
       <c r="I513" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J513" s="13" t="s">
+      <c r="J513" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K513" s="6" t="s">
@@ -44559,7 +44526,7 @@
       <c r="I514" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J514" s="13" t="s">
+      <c r="J514" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K514" s="6" t="s">
@@ -44622,7 +44589,7 @@
       <c r="I515" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J515" s="13" t="s">
+      <c r="J515" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K515" s="6" t="s">
@@ -44685,7 +44652,7 @@
       <c r="I516" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J516" s="13" t="s">
+      <c r="J516" s="9" t="s">
         <v>2001</v>
       </c>
       <c r="K516" s="6" t="s">
@@ -44748,7 +44715,7 @@
       <c r="I517" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J517" s="13" t="s">
+      <c r="J517" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K517" s="6" t="s">
@@ -44811,7 +44778,7 @@
       <c r="I518" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J518" s="13" t="s">
+      <c r="J518" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K518" s="6" t="s">
@@ -44874,7 +44841,7 @@
       <c r="I519" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J519" s="13" t="s">
+      <c r="J519" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K519" s="6" t="s">
@@ -44937,7 +44904,7 @@
       <c r="I520" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J520" s="13" t="s">
+      <c r="J520" s="9" t="s">
         <v>351</v>
       </c>
       <c r="K520" s="6" t="s">
@@ -45000,7 +44967,7 @@
       <c r="I521" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J521" s="13" t="s">
+      <c r="J521" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K521" s="6" t="s">
@@ -45063,7 +45030,7 @@
       <c r="I522" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J522" s="13" t="s">
+      <c r="J522" s="9" t="s">
         <v>100</v>
       </c>
       <c r="K522" s="6" t="s">
@@ -45126,7 +45093,7 @@
       <c r="I523" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J523" s="13" t="s">
+      <c r="J523" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K523" s="6" t="s">
@@ -45189,7 +45156,7 @@
       <c r="I524" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J524" s="13" t="s">
+      <c r="J524" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K524" s="6" t="s">
@@ -45252,7 +45219,7 @@
       <c r="I525" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J525" s="13" t="s">
+      <c r="J525" s="9" t="s">
         <v>2535</v>
       </c>
       <c r="K525" s="6" t="s">
@@ -45315,7 +45282,7 @@
       <c r="I526" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J526" s="13" t="s">
+      <c r="J526" s="9" t="s">
         <v>1886</v>
       </c>
       <c r="K526" s="6" t="s">
@@ -45378,7 +45345,7 @@
       <c r="I527" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J527" s="13" t="s">
+      <c r="J527" s="9" t="s">
         <v>1819</v>
       </c>
       <c r="K527" s="6" t="s">
@@ -45441,7 +45408,7 @@
       <c r="I528" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J528" s="13" t="s">
+      <c r="J528" s="9" t="s">
         <v>2560</v>
       </c>
       <c r="K528" s="6" t="s">
@@ -45504,7 +45471,7 @@
       <c r="I529" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J529" s="13" t="s">
+      <c r="J529" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K529" s="6" t="s">
@@ -45567,7 +45534,7 @@
       <c r="I530" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J530" s="13" t="s">
+      <c r="J530" s="9" t="s">
         <v>75</v>
       </c>
       <c r="K530" s="6" t="s">
@@ -45630,7 +45597,7 @@
       <c r="I531" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J531" s="13" t="s">
+      <c r="J531" s="9" t="s">
         <v>75</v>
       </c>
       <c r="K531" s="6" t="s">
@@ -45693,7 +45660,7 @@
       <c r="I532" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J532" s="13" t="s">
+      <c r="J532" s="9" t="s">
         <v>2072</v>
       </c>
       <c r="K532" s="6" t="s">
@@ -45756,7 +45723,7 @@
       <c r="I533" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J533" s="13" t="s">
+      <c r="J533" s="9" t="s">
         <v>2582</v>
       </c>
       <c r="K533" s="6" t="s">
@@ -45819,7 +45786,7 @@
       <c r="I534" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J534" s="13" t="s">
+      <c r="J534" s="9" t="s">
         <v>903</v>
       </c>
       <c r="K534" s="6" t="s">
@@ -45882,7 +45849,7 @@
       <c r="I535" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J535" s="13" t="s">
+      <c r="J535" s="9" t="s">
         <v>308</v>
       </c>
       <c r="K535" s="6" t="s">
@@ -45945,7 +45912,7 @@
       <c r="I536" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J536" s="13" t="s">
+      <c r="J536" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K536" s="6" t="s">
@@ -46008,7 +45975,7 @@
       <c r="I537" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J537" s="13" t="s">
+      <c r="J537" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K537" s="6" t="s">
@@ -46071,7 +46038,7 @@
       <c r="I538" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J538" s="13" t="s">
+      <c r="J538" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K538" s="6" t="s">
@@ -46134,7 +46101,7 @@
       <c r="I539" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J539" s="13" t="s">
+      <c r="J539" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K539" s="6" t="s">
@@ -46197,7 +46164,7 @@
       <c r="I540" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J540" s="13" t="s">
+      <c r="J540" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K540" s="6" t="s">
@@ -46260,7 +46227,7 @@
       <c r="I541" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J541" s="13" t="s">
+      <c r="J541" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K541" s="6" t="s">
@@ -46323,7 +46290,7 @@
       <c r="I542" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J542" s="13" t="s">
+      <c r="J542" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K542" s="6" t="s">
@@ -46386,7 +46353,7 @@
       <c r="I543" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J543" s="13" t="s">
+      <c r="J543" s="9" t="s">
         <v>2001</v>
       </c>
       <c r="K543" s="6" t="s">
@@ -46449,7 +46416,7 @@
       <c r="I544" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J544" s="13" t="s">
+      <c r="J544" s="9" t="s">
         <v>2036</v>
       </c>
       <c r="K544" s="6" t="s">
@@ -46512,7 +46479,7 @@
       <c r="I545" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J545" s="13" t="s">
+      <c r="J545" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K545" s="6" t="s">
@@ -46575,7 +46542,7 @@
       <c r="I546" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J546" s="13" t="s">
+      <c r="J546" s="9" t="s">
         <v>2634</v>
       </c>
       <c r="K546" s="6" t="s">
@@ -46638,7 +46605,7 @@
       <c r="I547" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J547" s="13" t="s">
+      <c r="J547" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K547" s="6" t="s">
@@ -46701,7 +46668,7 @@
       <c r="I548" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J548" s="13" t="s">
+      <c r="J548" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K548" s="6" t="s">
@@ -46764,7 +46731,7 @@
       <c r="I549" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J549" s="13" t="s">
+      <c r="J549" s="9" t="s">
         <v>376</v>
       </c>
       <c r="K549" s="6" t="s">
@@ -46825,7 +46792,7 @@
       <c r="I550" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J550" s="13" t="s">
+      <c r="J550" s="9" t="s">
         <v>2297</v>
       </c>
       <c r="K550" s="6" t="s">
@@ -46888,7 +46855,7 @@
       <c r="I551" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J551" s="13" t="s">
+      <c r="J551" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K551" s="6" t="s">
@@ -46951,7 +46918,7 @@
       <c r="I552" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J552" s="13" t="s">
+      <c r="J552" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K552" s="6" t="s">
@@ -47014,7 +46981,7 @@
       <c r="I553" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J553" s="13" t="s">
+      <c r="J553" s="9" t="s">
         <v>126</v>
       </c>
       <c r="K553" s="6" t="s">
@@ -47077,7 +47044,7 @@
       <c r="I554" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J554" s="13" t="s">
+      <c r="J554" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K554" s="6" t="s">
@@ -47140,7 +47107,7 @@
       <c r="I555" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J555" s="13" t="s">
+      <c r="J555" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K555" s="6" t="s">
@@ -47203,7 +47170,7 @@
       <c r="I556" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J556" s="13" t="s">
+      <c r="J556" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K556" s="6" t="s">
@@ -47266,7 +47233,7 @@
       <c r="I557" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J557" s="13" t="s">
+      <c r="J557" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K557" s="6" t="s">
@@ -47329,7 +47296,7 @@
       <c r="I558" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J558" s="13" t="s">
+      <c r="J558" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K558" s="6" t="s">
@@ -47392,7 +47359,7 @@
       <c r="I559" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J559" s="13" t="s">
+      <c r="J559" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K559" s="6" t="s">
@@ -47455,7 +47422,7 @@
       <c r="I560" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J560" s="13" t="s">
+      <c r="J560" s="9" t="s">
         <v>2634</v>
       </c>
       <c r="K560" s="6" t="s">
@@ -47518,7 +47485,7 @@
       <c r="I561" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J561" s="13" t="s">
+      <c r="J561" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K561" s="6" t="s">
@@ -47573,7 +47540,7 @@
       <c r="I562" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J562" s="13" t="s">
+      <c r="J562" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K562" s="6" t="s">
@@ -47628,7 +47595,7 @@
       <c r="I563" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J563" s="13" t="s">
+      <c r="J563" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K563" s="6" t="s">
@@ -47683,7 +47650,7 @@
       <c r="I564" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J564" s="13" t="s">
+      <c r="J564" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K564" s="6" t="s">
@@ -47736,7 +47703,7 @@
       <c r="I565" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J565" s="13" t="s">
+      <c r="J565" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K565" s="6" t="s">
@@ -47799,7 +47766,7 @@
       <c r="I566" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J566" s="13" t="s">
+      <c r="J566" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K566" s="6" t="s">
@@ -47854,7 +47821,7 @@
       <c r="I567" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J567" s="13" t="s">
+      <c r="J567" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K567" s="6" t="s">
@@ -47909,7 +47876,7 @@
       <c r="I568" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J568" s="13" t="s">
+      <c r="J568" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K568" s="6" t="s">
@@ -47964,7 +47931,7 @@
       <c r="I569" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J569" s="13" t="s">
+      <c r="J569" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K569" s="6" t="s">
@@ -48019,7 +47986,7 @@
       <c r="I570" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J570" s="13" t="s">
+      <c r="J570" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K570" s="6" t="s">
@@ -48074,7 +48041,7 @@
       <c r="I571" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J571" s="13" t="s">
+      <c r="J571" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K571" s="6" t="s">
@@ -48129,7 +48096,7 @@
       <c r="I572" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J572" s="13" t="s">
+      <c r="J572" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K572" s="6" t="s">
@@ -48184,7 +48151,7 @@
       <c r="I573" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J573" s="13" t="s">
+      <c r="J573" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K573" s="6" t="s">
@@ -48239,7 +48206,7 @@
       <c r="I574" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J574" s="13" t="s">
+      <c r="J574" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K574" s="6" t="s">
@@ -48294,7 +48261,7 @@
       <c r="I575" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J575" s="13" t="s">
+      <c r="J575" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K575" s="6" t="s">
@@ -48351,7 +48318,7 @@
       <c r="I576" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J576" s="13" t="s">
+      <c r="J576" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K576" s="6" t="s">
@@ -48414,7 +48381,7 @@
       <c r="I577" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J577" s="13" t="s">
+      <c r="J577" s="9" t="s">
         <v>903</v>
       </c>
       <c r="K577" s="6" t="s">
@@ -48479,7 +48446,7 @@
       <c r="I578" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J578" s="13" t="s">
+      <c r="J578" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K578" s="6" t="s">
@@ -48540,7 +48507,7 @@
       <c r="I579" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J579" s="13" t="s">
+      <c r="J579" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K579" s="6" t="s">
@@ -48601,7 +48568,7 @@
       <c r="I580" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J580" s="13" t="s">
+      <c r="J580" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K580" s="6" t="s">
@@ -48666,7 +48633,7 @@
       <c r="I581" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J581" s="13" t="s">
+      <c r="J581" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K581" s="6" t="s">
@@ -48731,7 +48698,7 @@
       <c r="I582" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J582" s="13" t="s">
+      <c r="J582" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K582" s="6" t="s">
@@ -48788,7 +48755,7 @@
       <c r="I583" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J583" s="13" t="s">
+      <c r="J583" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K583" s="6" t="s">
@@ -48851,7 +48818,7 @@
       <c r="I584" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J584" s="13" t="s">
+      <c r="J584" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K584" s="6" t="s">
@@ -48912,7 +48879,7 @@
       <c r="I585" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J585" s="13" t="s">
+      <c r="J585" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K585" s="6" t="s">
@@ -48975,7 +48942,7 @@
       <c r="I586" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J586" s="13" t="s">
+      <c r="J586" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K586" s="6" t="s">
@@ -49036,7 +49003,7 @@
       <c r="I587" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J587" s="13" t="s">
+      <c r="J587" s="9" t="s">
         <v>781</v>
       </c>
       <c r="K587" s="6" t="s">
@@ -49099,7 +49066,7 @@
       <c r="I588" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J588" s="13" t="s">
+      <c r="J588" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K588" s="6" t="s">
@@ -49162,7 +49129,7 @@
       <c r="I589" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J589" s="13" t="s">
+      <c r="J589" s="9" t="s">
         <v>2634</v>
       </c>
       <c r="K589" s="6" t="s">
@@ -49223,7 +49190,7 @@
       <c r="I590" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J590" s="13" t="s">
+      <c r="J590" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K590" s="6" t="s">
@@ -49284,7 +49251,7 @@
       <c r="I591" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J591" s="13" t="s">
+      <c r="J591" s="9" t="s">
         <v>2805</v>
       </c>
       <c r="K591" s="6" t="s">
@@ -49345,7 +49312,7 @@
       <c r="I592" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J592" s="13" t="s">
+      <c r="J592" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K592" s="6" t="s">
@@ -49406,7 +49373,7 @@
       <c r="I593" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J593" s="13" t="s">
+      <c r="J593" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K593" s="6" t="s">
@@ -49467,7 +49434,7 @@
       <c r="I594" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J594" s="13" t="s">
+      <c r="J594" s="9" t="s">
         <v>113</v>
       </c>
       <c r="K594" s="6" t="s">
@@ -49532,7 +49499,7 @@
       <c r="I595" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J595" s="13" t="s">
+      <c r="J595" s="9" t="s">
         <v>2820</v>
       </c>
       <c r="K595" s="6" t="s">
@@ -49593,7 +49560,7 @@
       <c r="I596" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J596" s="13" t="s">
+      <c r="J596" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K596" s="6" t="s">
@@ -49656,7 +49623,7 @@
       <c r="I597" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J597" s="13" t="s">
+      <c r="J597" s="9" t="s">
         <v>2833</v>
       </c>
       <c r="K597" s="6" t="s">
@@ -49721,7 +49688,7 @@
       <c r="I598" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J598" s="13" t="s">
+      <c r="J598" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K598" s="6" t="s">
@@ -49782,7 +49749,7 @@
       <c r="I599" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J599" s="13" t="s">
+      <c r="J599" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K599" s="6" t="s">
@@ -49845,7 +49812,7 @@
       <c r="I600" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J600" s="13" t="s">
+      <c r="J600" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K600" s="6" t="s">
@@ -49910,7 +49877,7 @@
       <c r="I601" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J601" s="13" t="s">
+      <c r="J601" s="9" t="s">
         <v>89</v>
       </c>
       <c r="K601" s="6" t="s">
@@ -49975,7 +49942,7 @@
       <c r="I602" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J602" s="13" t="s">
+      <c r="J602" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K602" s="6" t="s">
@@ -50028,7 +49995,7 @@
       <c r="I603" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J603" s="13" t="s">
+      <c r="J603" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K603" s="6" t="s">
@@ -50081,7 +50048,7 @@
       <c r="I604" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J604" s="13" t="s">
+      <c r="J604" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K604" s="6" t="s">
@@ -50134,7 +50101,7 @@
       <c r="I605" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J605" s="13" t="s">
+      <c r="J605" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K605" s="6" t="s">
@@ -50199,7 +50166,7 @@
       <c r="I606" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J606" s="13" t="s">
+      <c r="J606" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K606" s="6" t="s">
@@ -50256,7 +50223,7 @@
       <c r="I607" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J607" s="13" t="s">
+      <c r="J607" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K607" s="6" t="s">
@@ -50309,7 +50276,7 @@
       <c r="I608" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J608" s="13" t="s">
+      <c r="J608" s="9" t="s">
         <v>2882</v>
       </c>
       <c r="K608" s="6" t="s">
@@ -50374,7 +50341,7 @@
       <c r="I609" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J609" s="13" t="s">
+      <c r="J609" s="9" t="s">
         <v>2399</v>
       </c>
       <c r="K609" s="6" t="s">
@@ -50415,7 +50382,7 @@
       <c r="I610" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J610" s="13" t="s">
+      <c r="J610" s="9" t="s">
         <v>2896</v>
       </c>
       <c r="K610" s="6" t="s">
@@ -50480,7 +50447,7 @@
       <c r="I611" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J611" s="13" t="s">
+      <c r="J611" s="9" t="s">
         <v>2896</v>
       </c>
       <c r="K611" s="6" t="s">
@@ -50545,7 +50512,7 @@
       <c r="I612" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J612" s="13" t="s">
+      <c r="J612" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K612" s="6" t="s">
@@ -50606,7 +50573,7 @@
       <c r="I613" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J613" s="13" t="s">
+      <c r="J613" s="9" t="s">
         <v>893</v>
       </c>
       <c r="K613" s="6" t="s">
@@ -50667,7 +50634,7 @@
       <c r="I614" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J614" s="13" t="s">
+      <c r="J614" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K614" s="6" t="s">
@@ -50728,7 +50695,7 @@
       <c r="I615" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J615" s="13" t="s">
+      <c r="J615" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K615" s="6" t="s">
@@ -50793,7 +50760,7 @@
       <c r="I616" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J616" s="13" t="s">
+      <c r="J616" s="9" t="s">
         <v>2820</v>
       </c>
       <c r="K616" s="6" t="s">
@@ -50858,7 +50825,7 @@
       <c r="I617" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J617" s="13" t="s">
+      <c r="J617" s="9" t="s">
         <v>2941</v>
       </c>
       <c r="K617" s="6" t="s">
@@ -50923,7 +50890,7 @@
       <c r="I618" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J618" s="13" t="s">
+      <c r="J618" s="9" t="s">
         <v>814</v>
       </c>
       <c r="K618" s="6" t="s">
@@ -50988,7 +50955,7 @@
       <c r="I619" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J619" s="13" t="s">
+      <c r="J619" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K619" s="6" t="s">
@@ -51053,7 +51020,7 @@
       <c r="I620" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J620" s="13" t="s">
+      <c r="J620" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K620" s="6" t="s">
@@ -51118,7 +51085,7 @@
       <c r="I621" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J621" s="13" t="s">
+      <c r="J621" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K621" s="6" t="s">
@@ -51183,7 +51150,7 @@
       <c r="I622" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J622" s="13" t="s">
+      <c r="J622" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K622" s="6" t="s">
@@ -51248,7 +51215,7 @@
       <c r="I623" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J623" s="13" t="s">
+      <c r="J623" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K623" s="6" t="s">
@@ -51313,7 +51280,7 @@
       <c r="I624" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J624" s="13" t="s">
+      <c r="J624" s="9" t="s">
         <v>89</v>
       </c>
       <c r="K624" s="6" t="s">
@@ -51378,7 +51345,7 @@
       <c r="I625" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J625" s="13" t="s">
+      <c r="J625" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K625" s="6" t="s">
@@ -51443,7 +51410,7 @@
       <c r="I626" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J626" s="13" t="s">
+      <c r="J626" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K626" s="6" t="s">
@@ -51506,7 +51473,7 @@
       <c r="I627" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J627" s="13" t="s">
+      <c r="J627" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K627" s="6" t="s">
@@ -51569,7 +51536,7 @@
       <c r="I628" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J628" s="13" t="s">
+      <c r="J628" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K628" s="6" t="s">
@@ -51634,7 +51601,7 @@
       <c r="I629" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J629" s="13" t="s">
+      <c r="J629" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K629" s="6" t="s">
@@ -51693,7 +51660,7 @@
       <c r="G630" s="5"/>
       <c r="H630" s="5"/>
       <c r="I630" s="5"/>
-      <c r="J630" s="13"/>
+      <c r="J630" s="9"/>
       <c r="K630" s="6" t="s">
         <v>800</v>
       </c>
@@ -51738,7 +51705,7 @@
       <c r="G631" s="5"/>
       <c r="H631" s="5"/>
       <c r="I631" s="5"/>
-      <c r="J631" s="13"/>
+      <c r="J631" s="9"/>
       <c r="K631" s="6" t="s">
         <v>800</v>
       </c>
@@ -51783,7 +51750,7 @@
       <c r="G632" s="5"/>
       <c r="H632" s="5"/>
       <c r="I632" s="5"/>
-      <c r="J632" s="13"/>
+      <c r="J632" s="9"/>
       <c r="K632" s="6" t="s">
         <v>800</v>
       </c>
@@ -51828,7 +51795,7 @@
       <c r="G633" s="5"/>
       <c r="H633" s="5"/>
       <c r="I633" s="5"/>
-      <c r="J633" s="13"/>
+      <c r="J633" s="9"/>
       <c r="K633" s="6" t="s">
         <v>800</v>
       </c>
@@ -51873,7 +51840,7 @@
       <c r="G634" s="5"/>
       <c r="H634" s="5"/>
       <c r="I634" s="5"/>
-      <c r="J634" s="13"/>
+      <c r="J634" s="9"/>
       <c r="K634" s="6" t="s">
         <v>800</v>
       </c>
@@ -51918,7 +51885,7 @@
       <c r="G635" s="5"/>
       <c r="H635" s="5"/>
       <c r="I635" s="5"/>
-      <c r="J635" s="13"/>
+      <c r="J635" s="9"/>
       <c r="K635" s="6" t="s">
         <v>800</v>
       </c>
@@ -51969,7 +51936,7 @@
       <c r="I636" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J636" s="13" t="s">
+      <c r="J636" s="9" t="s">
         <v>2535</v>
       </c>
       <c r="K636" s="6" t="s">
@@ -52034,7 +52001,7 @@
       <c r="I637" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J637" s="13" t="s">
+      <c r="J637" s="9" t="s">
         <v>2001</v>
       </c>
       <c r="K637" s="6" t="s">
@@ -52087,7 +52054,7 @@
       <c r="I638" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J638" s="13" t="s">
+      <c r="J638" s="9" t="s">
         <v>2001</v>
       </c>
       <c r="K638" s="6" t="s">
@@ -52140,7 +52107,7 @@
       <c r="I639" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J639" s="13" t="s">
+      <c r="J639" s="9" t="s">
         <v>3032</v>
       </c>
       <c r="K639" s="6" t="s">
@@ -52205,7 +52172,7 @@
       <c r="I640" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J640" s="13" t="s">
+      <c r="J640" s="9" t="s">
         <v>2161</v>
       </c>
       <c r="K640" s="6" t="s">
@@ -52270,7 +52237,7 @@
       <c r="I641" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J641" s="13" t="s">
+      <c r="J641" s="9" t="s">
         <v>2297</v>
       </c>
       <c r="K641" s="6" t="s">
@@ -52335,7 +52302,7 @@
       <c r="I642" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J642" s="13" t="s">
+      <c r="J642" s="9" t="s">
         <v>2297</v>
       </c>
       <c r="K642" s="6" t="s">
@@ -52400,7 +52367,7 @@
       <c r="I643" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J643" s="13" t="s">
+      <c r="J643" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K643" s="6" t="s">
@@ -52457,7 +52424,7 @@
       <c r="I644" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J644" s="13" t="s">
+      <c r="J644" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K644" s="6" t="s">
@@ -52514,7 +52481,7 @@
       <c r="I645" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J645" s="13" t="s">
+      <c r="J645" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K645" s="6" t="s">
@@ -52579,7 +52546,7 @@
       <c r="I646" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J646" s="13" t="s">
+      <c r="J646" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K646" s="6" t="s">
@@ -52644,7 +52611,7 @@
       <c r="I647" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J647" s="13" t="s">
+      <c r="J647" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K647" s="6" t="s">
@@ -52709,7 +52676,7 @@
       <c r="I648" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J648" s="13" t="s">
+      <c r="J648" s="9" t="s">
         <v>2194</v>
       </c>
       <c r="K648" s="6" t="s">
@@ -52774,7 +52741,7 @@
       <c r="I649" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J649" s="13" t="s">
+      <c r="J649" s="9" t="s">
         <v>2194</v>
       </c>
       <c r="K649" s="6" t="s">
@@ -52839,7 +52806,7 @@
       <c r="I650" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J650" s="13" t="s">
+      <c r="J650" s="9" t="s">
         <v>2194</v>
       </c>
       <c r="K650" s="6" t="s">
@@ -52904,7 +52871,7 @@
       <c r="I651" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J651" s="13" t="s">
+      <c r="J651" s="9" t="s">
         <v>3032</v>
       </c>
       <c r="K651" s="6" t="s">
@@ -52961,7 +52928,7 @@
       <c r="I652" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J652" s="13" t="s">
+      <c r="J652" s="9" t="s">
         <v>2020</v>
       </c>
       <c r="K652" s="6" t="s">
@@ -53018,7 +52985,7 @@
       <c r="I653" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J653" s="13" t="s">
+      <c r="J653" s="9" t="s">
         <v>2560</v>
       </c>
       <c r="K653" s="6" t="s">
@@ -53073,7 +53040,7 @@
       <c r="I654" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J654" s="13" t="s">
+      <c r="J654" s="9" t="s">
         <v>3105</v>
       </c>
       <c r="K654" s="6" t="s">
@@ -53136,7 +53103,7 @@
       <c r="I655" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J655" s="13" t="s">
+      <c r="J655" s="9" t="s">
         <v>3105</v>
       </c>
       <c r="K655" s="6" t="s">
@@ -53199,7 +53166,7 @@
       <c r="I656" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J656" s="13" t="s">
+      <c r="J656" s="9" t="s">
         <v>3105</v>
       </c>
       <c r="K656" s="6" t="s">
@@ -53264,7 +53231,7 @@
       <c r="I657" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J657" s="13" t="s">
+      <c r="J657" s="9" t="s">
         <v>3118</v>
       </c>
       <c r="K657" s="6" t="s">
@@ -53329,7 +53296,7 @@
       <c r="I658" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J658" s="13" t="s">
+      <c r="J658" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K658" s="6" t="s">
@@ -53386,7 +53353,7 @@
       <c r="I659" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J659" s="13" t="s">
+      <c r="J659" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K659" s="6" t="s">
@@ -53443,7 +53410,7 @@
       <c r="I660" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J660" s="13" t="s">
+      <c r="J660" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K660" s="6" t="s">
@@ -53500,7 +53467,7 @@
       <c r="I661" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J661" s="13" t="s">
+      <c r="J661" s="9" t="s">
         <v>2896</v>
       </c>
       <c r="K661" s="6" t="s">
@@ -53565,7 +53532,7 @@
       <c r="I662" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J662" s="13" t="s">
+      <c r="J662" s="9" t="s">
         <v>2896</v>
       </c>
       <c r="K662" s="6" t="s">
@@ -53630,7 +53597,7 @@
       <c r="I663" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J663" s="13" t="s">
+      <c r="J663" s="9" t="s">
         <v>2307</v>
       </c>
       <c r="K663" s="6" t="s">
@@ -53687,7 +53654,7 @@
       <c r="I664" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J664" s="13" t="s">
+      <c r="J664" s="9" t="s">
         <v>1886</v>
       </c>
       <c r="K664" s="6" t="s">
@@ -53744,7 +53711,7 @@
       <c r="I665" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J665" s="13" t="s">
+      <c r="J665" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K665" s="6" t="s">
@@ -53801,7 +53768,7 @@
       <c r="I666" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J666" s="13" t="s">
+      <c r="J666" s="9" t="s">
         <v>3159</v>
       </c>
       <c r="K666" s="6" t="s">
@@ -53858,7 +53825,7 @@
       <c r="I667" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J667" s="13" t="s">
+      <c r="J667" s="9" t="s">
         <v>3159</v>
       </c>
       <c r="K667" s="6" t="s">
@@ -53915,7 +53882,7 @@
       <c r="I668" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J668" s="13" t="s">
+      <c r="J668" s="9" t="s">
         <v>3159</v>
       </c>
       <c r="K668" s="6" t="s">
@@ -53972,7 +53939,7 @@
       <c r="I669" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J669" s="13" t="s">
+      <c r="J669" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K669" s="6" t="s">
@@ -54029,7 +53996,7 @@
       <c r="I670" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J670" s="13" t="s">
+      <c r="J670" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K670" s="6" t="s">
@@ -54086,7 +54053,7 @@
       <c r="I671" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J671" s="13" t="s">
+      <c r="J671" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K671" s="6" t="s">
@@ -54143,7 +54110,7 @@
       <c r="I672" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J672" s="13" t="s">
+      <c r="J672" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K672" s="6" t="s">
@@ -54200,7 +54167,7 @@
       <c r="I673" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J673" s="13" t="s">
+      <c r="J673" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K673" s="6" t="s">
@@ -54257,7 +54224,7 @@
       <c r="I674" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J674" s="13" t="s">
+      <c r="J674" s="9" t="s">
         <v>2399</v>
       </c>
       <c r="K674" s="6" t="s">
@@ -54314,7 +54281,7 @@
       <c r="I675" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J675" s="13" t="s">
+      <c r="J675" s="9" t="s">
         <v>2399</v>
       </c>
       <c r="K675" s="6" t="s">
@@ -54371,7 +54338,7 @@
       <c r="I676" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J676" s="13" t="s">
+      <c r="J676" s="9" t="s">
         <v>2399</v>
       </c>
       <c r="K676" s="6" t="s">
@@ -54428,7 +54395,7 @@
       <c r="I677" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J677" s="13" t="s">
+      <c r="J677" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K677" s="6" t="s">
@@ -54485,7 +54452,7 @@
       <c r="I678" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J678" s="13" t="s">
+      <c r="J678" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K678" s="6" t="s">
@@ -54540,7 +54507,7 @@
       <c r="I679" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J679" s="13" t="s">
+      <c r="J679" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K679" s="6" t="s">
@@ -54603,7 +54570,7 @@
       <c r="I680" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J680" s="13" t="s">
+      <c r="J680" s="9" t="s">
         <v>625</v>
       </c>
       <c r="K680" s="6" t="s">
@@ -54668,7 +54635,7 @@
       <c r="I681" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J681" s="13" t="s">
+      <c r="J681" s="9" t="s">
         <v>903</v>
       </c>
       <c r="K681" s="6" t="s">
@@ -54725,7 +54692,7 @@
       <c r="I682" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J682" s="13" t="s">
+      <c r="J682" s="9" t="s">
         <v>903</v>
       </c>
       <c r="K682" s="6" t="s">
@@ -54780,7 +54747,7 @@
       <c r="I683" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J683" s="13" t="s">
+      <c r="J683" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K683" s="6" t="s">
@@ -54843,7 +54810,7 @@
       <c r="I684" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J684" s="13" t="s">
+      <c r="J684" s="9" t="s">
         <v>351</v>
       </c>
       <c r="K684" s="6" t="s">
@@ -54908,7 +54875,7 @@
       <c r="I685" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J685" s="13" t="s">
+      <c r="J685" s="9" t="s">
         <v>210</v>
       </c>
       <c r="K685" s="6" t="s">
@@ -54973,7 +54940,7 @@
       <c r="I686" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J686" s="13" t="s">
+      <c r="J686" s="9" t="s">
         <v>210</v>
       </c>
       <c r="K686" s="6" t="s">
@@ -55038,7 +55005,7 @@
       <c r="I687" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J687" s="13" t="s">
+      <c r="J687" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K687" s="6" t="s">
@@ -55103,7 +55070,7 @@
       <c r="I688" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J688" s="13" t="s">
+      <c r="J688" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K688" s="6" t="s">
@@ -55168,7 +55135,7 @@
       <c r="I689" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J689" s="13" t="s">
+      <c r="J689" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K689" s="6" t="s">
@@ -55233,7 +55200,7 @@
       <c r="I690" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J690" s="13" t="s">
+      <c r="J690" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K690" s="6" t="s">
@@ -55298,7 +55265,7 @@
       <c r="I691" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J691" s="13" t="s">
+      <c r="J691" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K691" s="6" t="s">
@@ -55363,7 +55330,7 @@
       <c r="I692" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J692" s="13" t="s">
+      <c r="J692" s="9" t="s">
         <v>814</v>
       </c>
       <c r="K692" s="6" t="s">
@@ -55424,7 +55391,7 @@
       <c r="I693" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J693" s="13" t="s">
+      <c r="J693" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K693" s="6" t="s">
@@ -55485,7 +55452,7 @@
       <c r="I694" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J694" s="13" t="s">
+      <c r="J694" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K694" s="6" t="s">
@@ -55546,7 +55513,7 @@
       <c r="I695" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J695" s="13" t="s">
+      <c r="J695" s="9" t="s">
         <v>893</v>
       </c>
       <c r="K695" s="6" t="s">
@@ -55607,7 +55574,7 @@
       <c r="I696" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J696" s="13" t="s">
+      <c r="J696" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K696" s="6" t="s">
@@ -55668,7 +55635,7 @@
       <c r="I697" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J697" s="13" t="s">
+      <c r="J697" s="9" t="s">
         <v>652</v>
       </c>
       <c r="K697" s="6" t="s">
@@ -55729,7 +55696,7 @@
       <c r="I698" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J698" s="13" t="s">
+      <c r="J698" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K698" s="6" t="s">
@@ -55794,7 +55761,7 @@
       <c r="I699" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J699" s="13" t="s">
+      <c r="J699" s="9" t="s">
         <v>3273</v>
       </c>
       <c r="K699" s="6" t="s">
@@ -55859,7 +55826,7 @@
       <c r="I700" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J700" s="13" t="s">
+      <c r="J700" s="9" t="s">
         <v>3118</v>
       </c>
       <c r="K700" s="6" t="s">
@@ -55912,7 +55879,7 @@
       <c r="I701" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J701" s="13" t="s">
+      <c r="J701" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K701" s="6" t="s">
@@ -55977,7 +55944,7 @@
       <c r="I702" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J702" s="13" t="s">
+      <c r="J702" s="9" t="s">
         <v>3289</v>
       </c>
       <c r="K702" s="6" t="s">
@@ -56038,7 +56005,7 @@
       <c r="I703" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J703" s="13" t="s">
+      <c r="J703" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K703" s="6" t="s">
@@ -56099,7 +56066,7 @@
       <c r="I704" s="6" t="s">
         <v>3299</v>
       </c>
-      <c r="J704" s="13" t="s">
+      <c r="J704" s="9" t="s">
         <v>3300</v>
       </c>
       <c r="K704" s="6" t="s">
@@ -56160,7 +56127,7 @@
       <c r="I705" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J705" s="13" t="s">
+      <c r="J705" s="9" t="s">
         <v>126</v>
       </c>
       <c r="K705" s="6" t="s">
@@ -56221,7 +56188,7 @@
       <c r="I706" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J706" s="13" t="s">
+      <c r="J706" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K706" s="6" t="s">
@@ -56282,7 +56249,7 @@
       <c r="I707" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J707" s="13" t="s">
+      <c r="J707" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K707" s="6" t="s">
@@ -56345,7 +56312,7 @@
       <c r="I708" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J708" s="13" t="s">
+      <c r="J708" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K708" s="6" t="s">
@@ -56406,7 +56373,7 @@
       <c r="I709" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J709" s="13" t="s">
+      <c r="J709" s="9" t="s">
         <v>3273</v>
       </c>
       <c r="K709" s="6" t="s">
@@ -56467,7 +56434,7 @@
       <c r="I710" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J710" s="13" t="s">
+      <c r="J710" s="9" t="s">
         <v>3322</v>
       </c>
       <c r="K710" s="6" t="s">
@@ -56528,7 +56495,7 @@
       <c r="I711" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J711" s="13" t="s">
+      <c r="J711" s="9" t="s">
         <v>3331</v>
       </c>
       <c r="K711" s="6" t="s">
@@ -56589,7 +56556,7 @@
       <c r="I712" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J712" s="13" t="s">
+      <c r="J712" s="9" t="s">
         <v>113</v>
       </c>
       <c r="K712" s="6" t="s">
@@ -56650,7 +56617,7 @@
       <c r="I713" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J713" s="13" t="s">
+      <c r="J713" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K713" s="6" t="s">
@@ -56713,7 +56680,7 @@
       <c r="I714" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J714" s="13" t="s">
+      <c r="J714" s="9" t="s">
         <v>89</v>
       </c>
       <c r="K714" s="6" t="s">
@@ -56778,7 +56745,7 @@
       <c r="I715" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J715" s="13" t="s">
+      <c r="J715" s="9" t="s">
         <v>2297</v>
       </c>
       <c r="K715" s="6" t="s">
@@ -56839,7 +56806,7 @@
       <c r="I716" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J716" s="13" t="s">
+      <c r="J716" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K716" s="6" t="s">
@@ -56900,7 +56867,7 @@
       <c r="I717" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J717" s="13" t="s">
+      <c r="J717" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K717" s="6" t="s">
@@ -56961,7 +56928,7 @@
       <c r="I718" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J718" s="13" t="s">
+      <c r="J718" s="9" t="s">
         <v>308</v>
       </c>
       <c r="K718" s="6" t="s">
@@ -57022,7 +56989,7 @@
       <c r="I719" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J719" s="13" t="s">
+      <c r="J719" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K719" s="6" t="s">
@@ -57083,7 +57050,7 @@
       <c r="I720" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J720" s="13" t="s">
+      <c r="J720" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K720" s="6" t="s">
@@ -57144,7 +57111,7 @@
       <c r="I721" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J721" s="13" t="s">
+      <c r="J721" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K721" s="6" t="s">
@@ -57205,7 +57172,7 @@
       <c r="I722" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J722" s="13" t="s">
+      <c r="J722" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K722" s="6" t="s">
@@ -57266,7 +57233,7 @@
       <c r="I723" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J723" s="13" t="s">
+      <c r="J723" s="9" t="s">
         <v>3369</v>
       </c>
       <c r="K723" s="6" t="s">
@@ -57327,7 +57294,7 @@
       <c r="I724" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J724" s="13" t="s">
+      <c r="J724" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K724" s="6" t="s">
@@ -57388,7 +57355,7 @@
       <c r="I725" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J725" s="13" t="s">
+      <c r="J725" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K725" s="6" t="s">
@@ -57449,7 +57416,7 @@
       <c r="I726" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J726" s="13" t="s">
+      <c r="J726" s="9" t="s">
         <v>3380</v>
       </c>
       <c r="K726" s="6" t="s">
@@ -57510,7 +57477,7 @@
       <c r="I727" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J727" s="13" t="s">
+      <c r="J727" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K727" s="6" t="s">
@@ -57571,7 +57538,7 @@
       <c r="I728" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J728" s="13" t="s">
+      <c r="J728" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K728" s="6" t="s">
@@ -57632,7 +57599,7 @@
       <c r="I729" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J729" s="13" t="s">
+      <c r="J729" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K729" s="6" t="s">
@@ -57693,7 +57660,7 @@
       <c r="I730" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J730" s="13" t="s">
+      <c r="J730" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K730" s="6" t="s">
@@ -57754,7 +57721,7 @@
       <c r="I731" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J731" s="13" t="s">
+      <c r="J731" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K731" s="6" t="s">
@@ -57815,7 +57782,7 @@
       <c r="I732" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J732" s="13" t="s">
+      <c r="J732" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K732" s="6" t="s">
@@ -57876,7 +57843,7 @@
       <c r="I733" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J733" s="13" t="s">
+      <c r="J733" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K733" s="6" t="s">
@@ -57937,7 +57904,7 @@
       <c r="I734" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J734" s="13" t="s">
+      <c r="J734" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K734" s="6" t="s">
@@ -57998,7 +57965,7 @@
       <c r="I735" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J735" s="13" t="s">
+      <c r="J735" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K735" s="6" t="s">
@@ -58059,7 +58026,7 @@
       <c r="I736" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J736" s="13" t="s">
+      <c r="J736" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K736" s="6" t="s">
@@ -58120,7 +58087,7 @@
       <c r="I737" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J737" s="13" t="s">
+      <c r="J737" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K737" s="6" t="s">
@@ -58181,7 +58148,7 @@
       <c r="I738" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J738" s="13" t="s">
+      <c r="J738" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K738" s="6" t="s">
@@ -58242,7 +58209,7 @@
       <c r="I739" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J739" s="13" t="s">
+      <c r="J739" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K739" s="6" t="s">
@@ -58303,7 +58270,7 @@
       <c r="I740" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J740" s="13" t="s">
+      <c r="J740" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K740" s="6" t="s">
@@ -58364,7 +58331,7 @@
       <c r="I741" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J741" s="13" t="s">
+      <c r="J741" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K741" s="6" t="s">
@@ -58425,7 +58392,7 @@
       <c r="I742" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J742" s="13" t="s">
+      <c r="J742" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K742" s="6" t="s">
@@ -58486,7 +58453,7 @@
       <c r="I743" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J743" s="13" t="s">
+      <c r="J743" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K743" s="6" t="s">
@@ -58547,7 +58514,7 @@
       <c r="I744" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J744" s="13" t="s">
+      <c r="J744" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K744" s="6" t="s">
@@ -58608,7 +58575,7 @@
       <c r="I745" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J745" s="13" t="s">
+      <c r="J745" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K745" s="6" t="s">
@@ -58669,7 +58636,7 @@
       <c r="I746" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J746" s="13" t="s">
+      <c r="J746" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K746" s="6" t="s">
@@ -58730,7 +58697,7 @@
       <c r="I747" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J747" s="13" t="s">
+      <c r="J747" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K747" s="6" t="s">
@@ -58791,7 +58758,7 @@
       <c r="I748" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J748" s="13" t="s">
+      <c r="J748" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K748" s="6" t="s">
@@ -58852,7 +58819,7 @@
       <c r="I749" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J749" s="13" t="s">
+      <c r="J749" s="9" t="s">
         <v>2399</v>
       </c>
       <c r="K749" s="6" t="s">
@@ -58913,7 +58880,7 @@
       <c r="I750" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J750" s="13" t="s">
+      <c r="J750" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K750" s="6" t="s">
@@ -58974,7 +58941,7 @@
       <c r="I751" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J751" s="13" t="s">
+      <c r="J751" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K751" s="6" t="s">
@@ -59035,7 +59002,7 @@
       <c r="I752" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J752" s="13" t="s">
+      <c r="J752" s="9" t="s">
         <v>3454</v>
       </c>
       <c r="K752" s="6" t="s">
@@ -59096,7 +59063,7 @@
       <c r="I753" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J753" s="13" t="s">
+      <c r="J753" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K753" s="6" t="s">
@@ -59157,7 +59124,7 @@
       <c r="I754" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J754" s="13" t="s">
+      <c r="J754" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K754" s="6" t="s">
@@ -59218,7 +59185,7 @@
       <c r="I755" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J755" s="13" t="s">
+      <c r="J755" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K755" s="6" t="s">
@@ -59279,7 +59246,7 @@
       <c r="I756" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J756" s="13" t="s">
+      <c r="J756" s="9" t="s">
         <v>89</v>
       </c>
       <c r="K756" s="6" t="s">
@@ -59340,7 +59307,7 @@
       <c r="I757" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J757" s="13" t="s">
+      <c r="J757" s="9" t="s">
         <v>299</v>
       </c>
       <c r="K757" s="6" t="s">
@@ -59401,7 +59368,7 @@
       <c r="I758" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J758" s="13" t="s">
+      <c r="J758" s="9" t="s">
         <v>220</v>
       </c>
       <c r="K758" s="6" t="s">
@@ -59462,7 +59429,7 @@
       <c r="I759" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J759" s="13" t="s">
+      <c r="J759" s="9" t="s">
         <v>3488</v>
       </c>
       <c r="K759" s="6" t="s">
@@ -59523,7 +59490,7 @@
       <c r="I760" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J760" s="13" t="s">
+      <c r="J760" s="9" t="s">
         <v>2560</v>
       </c>
       <c r="K760" s="6" t="s">
@@ -59586,7 +59553,7 @@
       <c r="I761" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J761" s="13" t="s">
+      <c r="J761" s="9" t="s">
         <v>675</v>
       </c>
       <c r="K761" s="6" t="s">
@@ -59649,7 +59616,7 @@
       <c r="I762" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J762" s="13" t="s">
+      <c r="J762" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K762" s="6" t="s">
@@ -59710,7 +59677,7 @@
       <c r="I763" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J763" s="13" t="s">
+      <c r="J763" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K763" s="6" t="s">
@@ -59771,7 +59738,7 @@
       <c r="I764" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J764" s="13" t="s">
+      <c r="J764" s="9" t="s">
         <v>2001</v>
       </c>
       <c r="K764" s="6" t="s">
@@ -59832,7 +59799,7 @@
       <c r="I765" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J765" s="13" t="s">
+      <c r="J765" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K765" s="6" t="s">
@@ -59893,7 +59860,7 @@
       <c r="I766" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J766" s="13" t="s">
+      <c r="J766" s="9" t="s">
         <v>2882</v>
       </c>
       <c r="K766" s="6" t="s">
@@ -59954,7 +59921,7 @@
       <c r="I767" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J767" s="13" t="s">
+      <c r="J767" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K767" s="6" t="s">
@@ -60015,7 +59982,7 @@
       <c r="I768" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J768" s="13" t="s">
+      <c r="J768" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K768" s="6" t="s">
@@ -60076,7 +60043,7 @@
       <c r="I769" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J769" s="13" t="s">
+      <c r="J769" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K769" s="6" t="s">
@@ -60137,7 +60104,7 @@
       <c r="I770" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J770" s="13" t="s">
+      <c r="J770" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K770" s="6" t="s">
@@ -60198,7 +60165,7 @@
       <c r="I771" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J771" s="13" t="s">
+      <c r="J771" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K771" s="6" t="s">
@@ -60259,7 +60226,7 @@
       <c r="I772" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J772" s="13" t="s">
+      <c r="J772" s="9" t="s">
         <v>662</v>
       </c>
       <c r="K772" s="6" t="s">
@@ -60320,7 +60287,7 @@
       <c r="I773" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J773" s="13" t="s">
+      <c r="J773" s="9" t="s">
         <v>3530</v>
       </c>
       <c r="K773" s="6" t="s">
@@ -60381,7 +60348,7 @@
       <c r="I774" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J774" s="13" t="s">
+      <c r="J774" s="9" t="s">
         <v>332</v>
       </c>
       <c r="K774" s="6" t="s">
@@ -60442,7 +60409,7 @@
       <c r="I775" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J775" s="13" t="s">
+      <c r="J775" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K775" s="6" t="s">
@@ -60503,7 +60470,7 @@
       <c r="I776" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J776" s="13" t="s">
+      <c r="J776" s="9" t="s">
         <v>332</v>
       </c>
       <c r="K776" s="6" t="s">
@@ -60564,7 +60531,7 @@
       <c r="I777" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J777" s="13" t="s">
+      <c r="J777" s="9" t="s">
         <v>2820</v>
       </c>
       <c r="K777" s="6" t="s">
@@ -60625,7 +60592,7 @@
       <c r="I778" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J778" s="13" t="s">
+      <c r="J778" s="9" t="s">
         <v>2072</v>
       </c>
       <c r="K778" s="6" t="s">
@@ -60686,7 +60653,7 @@
       <c r="I779" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J779" s="13" t="s">
+      <c r="J779" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K779" s="6" t="s">
@@ -60747,7 +60714,7 @@
       <c r="I780" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J780" s="13" t="s">
+      <c r="J780" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K780" s="6" t="s">
@@ -60808,7 +60775,7 @@
       <c r="I781" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J781" s="13" t="s">
+      <c r="J781" s="9" t="s">
         <v>3557</v>
       </c>
       <c r="K781" s="6" t="s">
@@ -60869,7 +60836,7 @@
       <c r="I782" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J782" s="13" t="s">
+      <c r="J782" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K782" s="6" t="s">
@@ -60930,7 +60897,7 @@
       <c r="I783" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J783" s="13" t="s">
+      <c r="J783" s="9" t="s">
         <v>2001</v>
       </c>
       <c r="K783" s="6" t="s">
@@ -60991,7 +60958,7 @@
       <c r="I784" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J784" s="13" t="s">
+      <c r="J784" s="9" t="s">
         <v>433</v>
       </c>
       <c r="K784" s="6" t="s">
@@ -61052,7 +61019,7 @@
       <c r="I785" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J785" s="13" t="s">
+      <c r="J785" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K785" s="6" t="s">
@@ -61113,7 +61080,7 @@
       <c r="I786" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J786" s="13" t="s">
+      <c r="J786" s="9" t="s">
         <v>1819</v>
       </c>
       <c r="K786" s="6" t="s">
@@ -61174,7 +61141,7 @@
       <c r="I787" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J787" s="13" t="s">
+      <c r="J787" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K787" s="6" t="s">
@@ -61235,7 +61202,7 @@
       <c r="I788" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J788" s="13" t="s">
+      <c r="J788" s="9" t="s">
         <v>3578</v>
       </c>
       <c r="K788" s="6" t="s">
@@ -61296,7 +61263,7 @@
       <c r="I789" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J789" s="13" t="s">
+      <c r="J789" s="9" t="s">
         <v>3578</v>
       </c>
       <c r="K789" s="6" t="s">
@@ -61357,7 +61324,7 @@
       <c r="I790" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J790" s="13" t="s">
+      <c r="J790" s="9" t="s">
         <v>3578</v>
       </c>
       <c r="K790" s="6" t="s">
@@ -61418,7 +61385,7 @@
       <c r="I791" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J791" s="13" t="s">
+      <c r="J791" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K791" s="6" t="s">
@@ -61479,7 +61446,7 @@
       <c r="I792" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J792" s="13" t="s">
+      <c r="J792" s="9" t="s">
         <v>781</v>
       </c>
       <c r="K792" s="6" t="s">
@@ -61540,7 +61507,7 @@
       <c r="I793" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J793" s="13" t="s">
+      <c r="J793" s="9" t="s">
         <v>3598</v>
       </c>
       <c r="K793" s="6" t="s">
@@ -61601,7 +61568,7 @@
       <c r="I794" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J794" s="13" t="s">
+      <c r="J794" s="9" t="s">
         <v>332</v>
       </c>
       <c r="K794" s="6" t="s">
@@ -61662,7 +61629,7 @@
       <c r="I795" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J795" s="13" t="s">
+      <c r="J795" s="9" t="s">
         <v>332</v>
       </c>
       <c r="K795" s="6" t="s">
@@ -61723,7 +61690,7 @@
       <c r="I796" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J796" s="13" t="s">
+      <c r="J796" s="9" t="s">
         <v>257</v>
       </c>
       <c r="K796" s="6" t="s">
@@ -61784,7 +61751,7 @@
       <c r="I797" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J797" s="13" t="s">
+      <c r="J797" s="9" t="s">
         <v>701</v>
       </c>
       <c r="K797" s="6" t="s">
@@ -61845,7 +61812,7 @@
       <c r="I798" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J798" s="13" t="s">
+      <c r="J798" s="9" t="s">
         <v>3322</v>
       </c>
       <c r="K798" s="6" t="s">
@@ -61906,7 +61873,7 @@
       <c r="I799" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J799" s="13" t="s">
+      <c r="J799" s="9" t="s">
         <v>3322</v>
       </c>
       <c r="K799" s="6" t="s">
@@ -61967,7 +61934,7 @@
       <c r="I800" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J800" s="13" t="s">
+      <c r="J800" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K800" s="6" t="s">
@@ -62028,7 +61995,7 @@
       <c r="I801" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J801" s="13" t="s">
+      <c r="J801" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K801" s="6" t="s">
@@ -62089,7 +62056,7 @@
       <c r="I802" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J802" s="13" t="s">
+      <c r="J802" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K802" s="6" t="s">
@@ -62150,7 +62117,7 @@
       <c r="I803" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J803" s="13" t="s">
+      <c r="J803" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K803" s="6" t="s">
@@ -62211,7 +62178,7 @@
       <c r="I804" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J804" s="13" t="s">
+      <c r="J804" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K804" s="6" t="s">
@@ -62272,7 +62239,7 @@
       <c r="I805" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J805" s="13" t="s">
+      <c r="J805" s="9" t="s">
         <v>2297</v>
       </c>
       <c r="K805" s="6" t="s">
@@ -62333,7 +62300,7 @@
       <c r="I806" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J806" s="13" t="s">
+      <c r="J806" s="9" t="s">
         <v>171</v>
       </c>
       <c r="K806" s="6" t="s">
@@ -62394,7 +62361,7 @@
       <c r="I807" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J807" s="13" t="s">
+      <c r="J807" s="9" t="s">
         <v>2896</v>
       </c>
       <c r="K807" s="6" t="s">
@@ -62455,7 +62422,7 @@
       <c r="I808" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J808" s="13" t="s">
+      <c r="J808" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K808" s="6" t="s">
@@ -62516,7 +62483,7 @@
       <c r="I809" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J809" s="13" t="s">
+      <c r="J809" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K809" s="6" t="s">
@@ -62577,7 +62544,7 @@
       <c r="I810" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J810" s="13" t="s">
+      <c r="J810" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K810" s="6" t="s">
@@ -62638,7 +62605,7 @@
       <c r="I811" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J811" s="13" t="s">
+      <c r="J811" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K811" s="6" t="s">
@@ -62701,7 +62668,7 @@
       <c r="I812" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J812" s="13" t="s">
+      <c r="J812" s="9" t="s">
         <v>376</v>
       </c>
       <c r="K812" s="6" t="s">
@@ -62762,7 +62729,7 @@
       <c r="I813" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J813" s="13" t="s">
+      <c r="J813" s="9" t="s">
         <v>136</v>
       </c>
       <c r="K813" s="6" t="s">
@@ -62823,7 +62790,7 @@
       <c r="I814" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J814" s="13" t="s">
+      <c r="J814" s="9" t="s">
         <v>2072</v>
       </c>
       <c r="K814" s="6" t="s">
@@ -62884,7 +62851,7 @@
       <c r="I815" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J815" s="13" t="s">
+      <c r="J815" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K815" s="6" t="s">
@@ -62945,7 +62912,7 @@
       <c r="I816" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J816" s="13" t="s">
+      <c r="J816" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K816" s="6" t="s">
@@ -63006,7 +62973,7 @@
       <c r="I817" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J817" s="13" t="s">
+      <c r="J817" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K817" s="6" t="s">
@@ -63067,7 +63034,7 @@
       <c r="I818" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J818" s="13" t="s">
+      <c r="J818" s="9" t="s">
         <v>181</v>
       </c>
       <c r="K818" s="6" t="s">
@@ -63128,7 +63095,7 @@
       <c r="I819" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J819" s="13" t="s">
+      <c r="J819" s="9" t="s">
         <v>89</v>
       </c>
       <c r="K819" s="6" t="s">
@@ -63189,7 +63156,7 @@
       <c r="I820" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J820" s="13" t="s">
+      <c r="J820" s="9" t="s">
         <v>147</v>
       </c>
       <c r="K820" s="6" t="s">
@@ -63250,7 +63217,7 @@
       <c r="I821" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J821" s="13" t="s">
+      <c r="J821" s="9" t="s">
         <v>421</v>
       </c>
       <c r="K821" s="6" t="s">
@@ -63311,7 +63278,7 @@
       <c r="I822" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J822" s="13" t="s">
+      <c r="J822" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K822" s="6" t="s">
@@ -63349,68 +63316,190 @@
       </c>
     </row>
     <row r="823" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A823" s="9">
+      <c r="A823" s="4">
         <v>822</v>
       </c>
-      <c r="B823" s="10"/>
-      <c r="C823" s="11" t="s">
+      <c r="B823" s="5"/>
+      <c r="C823" s="6" t="s">
         <v>2311</v>
       </c>
-      <c r="D823" s="10"/>
-      <c r="E823" s="11" t="s">
+      <c r="D823" s="5"/>
+      <c r="E823" s="6" t="s">
         <v>3685</v>
       </c>
-      <c r="F823" s="11" t="s">
+      <c r="F823" s="6" t="s">
         <v>3686</v>
       </c>
-      <c r="G823" s="11" t="s">
+      <c r="G823" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H823" s="11" t="s">
+      <c r="H823" s="6" t="s">
         <v>2242</v>
       </c>
-      <c r="I823" s="11" t="s">
+      <c r="I823" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J823" s="13" t="s">
+      <c r="J823" s="9" t="s">
         <v>701</v>
       </c>
-      <c r="K823" s="11" t="s">
+      <c r="K823" s="6" t="s">
         <v>2315</v>
       </c>
-      <c r="L823" s="11" t="s">
+      <c r="L823" s="6" t="s">
         <v>865</v>
       </c>
-      <c r="M823" s="11" t="s">
+      <c r="M823" s="6" t="s">
         <v>866</v>
       </c>
-      <c r="N823" s="11" t="s">
+      <c r="N823" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="O823" s="11" t="s">
+      <c r="O823" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="P823" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q823" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R823" s="11" t="s">
+      <c r="P823" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q823" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R823" s="6" t="s">
         <v>2244</v>
       </c>
-      <c r="S823" s="11" t="s">
+      <c r="S823" s="6" t="s">
         <v>2245</v>
       </c>
-      <c r="T823" s="11" t="s">
+      <c r="T823" s="6" t="s">
         <v>2316</v>
       </c>
-      <c r="U823" s="12" t="s">
+      <c r="U823" s="7" t="s">
         <v>2317</v>
       </c>
     </row>
+    <row r="824" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A824" s="4">
+        <v>823</v>
+      </c>
+      <c r="B824" s="5"/>
+      <c r="C824" s="6" t="s">
+        <v>2456</v>
+      </c>
+      <c r="D824" s="5"/>
+      <c r="E824" s="6" t="s">
+        <v>3687</v>
+      </c>
+      <c r="F824" s="6" t="s">
+        <v>3688</v>
+      </c>
+      <c r="G824" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H824" s="6" t="s">
+        <v>2460</v>
+      </c>
+      <c r="I824" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J824" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="K824" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L824" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="M824" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="N824" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="O824" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="P824" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q824" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R824" s="6" t="s">
+        <v>2461</v>
+      </c>
+      <c r="S824" s="6" t="s">
+        <v>2462</v>
+      </c>
+      <c r="T824" s="6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="U824" s="7" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="825" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A825" s="4">
+        <v>824</v>
+      </c>
+      <c r="B825" s="5"/>
+      <c r="C825" s="6" t="s">
+        <v>2456</v>
+      </c>
+      <c r="D825" s="5"/>
+      <c r="E825" s="6" t="s">
+        <v>3689</v>
+      </c>
+      <c r="F825" s="6" t="s">
+        <v>3690</v>
+      </c>
+      <c r="G825" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H825" s="6" t="s">
+        <v>2460</v>
+      </c>
+      <c r="I825" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J825" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="K825" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L825" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="M825" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="N825" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="O825" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="P825" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q825" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R825" s="6" t="s">
+        <v>2461</v>
+      </c>
+      <c r="S825" s="6" t="s">
+        <v>2462</v>
+      </c>
+      <c r="T825" s="6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="U825" s="7" t="s">
+        <v>2463</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="3pEIf7rb4pgAvfeZ8JFDIXcBNRNd41s8oYKRmFIcr8Lr7YDA4SFrL/iBiLAIXLNGvRAx1TZklsST6ujHo5XMdg==" saltValue="aqNu+HfQRsfjMZs+kr4z8g==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="c287mowFeTIS07wWhE59G0zH1yAXkEt7xvUZ+zo8PKdSGatvWg2dWcEJtO3g34z9+h55GTMYeUpizHkQJ/fTjg==" saltValue="pMGTec4t5O5mZorez8gtKg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F05181-532F-41BA-B61D-CFFE5C8AA52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A003177-A6B5-444F-8828-406435E16C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15328" uniqueCount="3691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15364" uniqueCount="3700">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11141,6 +11141,33 @@
   </si>
   <si>
     <t>Pet 100ml Round Nice Tr Yellow 24mm 20gm CR16.5 Bottle</t>
+  </si>
+  <si>
+    <t>MP0431</t>
+  </si>
+  <si>
+    <t>MP0431.1</t>
+  </si>
+  <si>
+    <t>Pet 1Kg Ghee Clear 83mm 55gm Jar</t>
+  </si>
+  <si>
+    <t>Ghee</t>
+  </si>
+  <si>
+    <t>130.80 ± 1.20</t>
+  </si>
+  <si>
+    <t>134.00 ± 1.20</t>
+  </si>
+  <si>
+    <t>1115.00 ± 20.00</t>
+  </si>
+  <si>
+    <t>MP0345.5</t>
+  </si>
+  <si>
+    <t>Pet 500ml Oval Brute Amber 28mm 38gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -11172,7 +11199,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -11256,11 +11283,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -11282,6 +11344,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -11867,30 +11939,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E46E294-B088-4DB8-8387-0E162EEEFA90}" name="Table1" displayName="Table1" ref="A1:U825" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U825" xr:uid="{2E46E294-B088-4DB8-8387-0E162EEEFA90}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BEA239D2-BA3A-49FA-850A-21756DC8B60D}" name="Table1" displayName="Table1" ref="A1:U827" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U827" xr:uid="{BEA239D2-BA3A-49FA-850A-21756DC8B60D}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{0C89E0F0-F1FB-4A9F-801E-9CD84C5616AB}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{2ACE245C-3C38-4B8C-810E-06730C82F587}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{ED7BC507-8B96-4F4B-8ADD-52239D4C85A7}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{5B2F85D3-BC04-487E-9A42-CB690EC3D6A7}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{35267AEE-E64C-4A66-A009-EC46E9CC427D}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{8706712F-6B8F-44C9-98D7-E0FB239E365E}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{68A9FF35-768A-4365-800A-D29DAA71A696}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{8EAB0662-0C0C-4832-842F-A72FD133196D}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{D77393E5-241E-413A-9D73-BDEF7CEA44B2}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{359EFAE0-E67C-4245-BAF4-E1830608992C}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{AFF5CF7C-7CE4-42C1-B846-0119ADBABC01}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{DA345948-5CD6-47CD-8F14-F948D73A0363}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{85A9FEA4-CDD3-453F-AB35-D34AAB43E065}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{3871E833-0C7C-4AA0-BA7F-610DE8D6B71C}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{7345E8E8-BEF5-46B8-8CAA-4EB2D23E39A4}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{E760E468-C45B-421C-85A5-10E09825B974}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{908336F8-F4E4-43AD-B505-3EBC8AD7AEB6}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{F62B61C7-F7D7-47AA-A0F6-DDDC5B798BEB}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{5464777B-0554-40E3-B719-36AA4E9AAD1B}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{FE33DF98-5D7E-4255-809E-AD10C613CC36}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{87E5796F-57E3-40C7-B220-99EDB73DC2BD}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{A2E4B76E-A2B7-4FA0-BB31-DD44EE579E60}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{E56FE5A6-8EE7-4363-A22F-D84F8DA2C794}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{A18F5801-CFDE-4C2D-8FC3-FAB65903DBB2}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{0FD892AB-44ED-4F30-A432-3F324AB67E95}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{B69ECC3E-2447-47ED-8A61-39C918F065EF}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{94EF4D37-0EE3-4E42-985D-4EEBCCD8D853}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{53CD9CBC-38AD-4211-AA57-338F3F12495B}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{DBC8A86C-0747-44A8-A4DB-7DF3866257C6}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{EB52085F-9061-4405-94C8-9E8824B58222}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{A6324EE8-96E2-4A25-985F-2BEB0ED98D93}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{A1C82E3F-7385-4C05-BDBB-440347128CDA}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{162EEE7D-F6A3-4417-80CE-575E60BE8740}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{08CF1DD6-1E4A-434C-B8AC-5F9B89BAC87A}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{22586DF3-DF19-40B0-A156-CE3A81417C64}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{2A0118F0-252B-4050-9355-FDFE02D946A5}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{651A7FD4-66E9-475E-9ED1-BCC36C3F9990}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{0D6BB643-6BF6-4D7F-AB6D-6D1700B29983}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{B4CE74F1-FAA9-4A1F-9173-66CB01237BC3}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{E0EC006E-0EB5-483B-B0AB-DAE0D969C0BA}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{D82D71A2-6126-477A-9B7B-80A6B45FB138}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{E3B4BF5C-C882-48FC-9279-65EF307E09B6}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12193,7 +12265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U825"/>
+  <dimension ref="A1:U827"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -12310,7 +12382,7 @@
       <c r="I2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -12373,7 +12445,7 @@
       <c r="I3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="13" t="s">
         <v>46</v>
       </c>
       <c r="K3" s="6" t="s">
@@ -12436,7 +12508,7 @@
       <c r="I4" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="13" t="s">
         <v>62</v>
       </c>
       <c r="K4" s="6" t="s">
@@ -12499,7 +12571,7 @@
       <c r="I5" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="13" t="s">
         <v>75</v>
       </c>
       <c r="K5" s="6" t="s">
@@ -12562,7 +12634,7 @@
       <c r="I6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="13" t="s">
         <v>89</v>
       </c>
       <c r="K6" s="6" t="s">
@@ -12625,7 +12697,7 @@
       <c r="I7" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="13" t="s">
         <v>100</v>
       </c>
       <c r="K7" s="6" t="s">
@@ -12688,7 +12760,7 @@
       <c r="I8" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K8" s="6" t="s">
@@ -12751,7 +12823,7 @@
       <c r="I9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="13" t="s">
         <v>126</v>
       </c>
       <c r="K9" s="6" t="s">
@@ -12814,7 +12886,7 @@
       <c r="I10" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="13" t="s">
         <v>135</v>
       </c>
       <c r="K10" s="6" t="s">
@@ -12877,7 +12949,7 @@
       <c r="I11" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K11" s="6" t="s">
@@ -12940,7 +13012,7 @@
       <c r="I12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="13" t="s">
         <v>158</v>
       </c>
       <c r="K12" s="6" t="s">
@@ -13003,7 +13075,7 @@
       <c r="I13" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K13" s="6" t="s">
@@ -13066,7 +13138,7 @@
       <c r="I14" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K14" s="6" t="s">
@@ -13129,7 +13201,7 @@
       <c r="I15" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K15" s="6" t="s">
@@ -13192,7 +13264,7 @@
       <c r="I16" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K16" s="6" t="s">
@@ -13253,7 +13325,7 @@
       <c r="I17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="13" t="s">
         <v>210</v>
       </c>
       <c r="K17" s="6" t="s">
@@ -13316,7 +13388,7 @@
       <c r="I18" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K18" s="6" t="s">
@@ -13379,7 +13451,7 @@
       <c r="I19" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="13" t="s">
         <v>230</v>
       </c>
       <c r="K19" s="6" t="s">
@@ -13438,7 +13510,7 @@
       <c r="I20" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="13" t="s">
         <v>241</v>
       </c>
       <c r="K20" s="6" t="s">
@@ -13501,7 +13573,7 @@
       <c r="I21" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K21" s="6" t="s">
@@ -13564,7 +13636,7 @@
       <c r="I22" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="J22" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K22" s="6" t="s">
@@ -13627,7 +13699,7 @@
       <c r="I23" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="J23" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K23" s="6" t="s">
@@ -13690,7 +13762,7 @@
       <c r="I24" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="J24" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K24" s="6" t="s">
@@ -13753,7 +13825,7 @@
       <c r="I25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J25" s="9" t="s">
+      <c r="J25" s="13" t="s">
         <v>290</v>
       </c>
       <c r="K25" s="6" t="s">
@@ -13816,7 +13888,7 @@
       <c r="I26" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J26" s="9" t="s">
+      <c r="J26" s="13" t="s">
         <v>299</v>
       </c>
       <c r="K26" s="6" t="s">
@@ -13879,7 +13951,7 @@
       <c r="I27" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J27" s="9" t="s">
+      <c r="J27" s="13" t="s">
         <v>308</v>
       </c>
       <c r="K27" s="6" t="s">
@@ -13942,7 +14014,7 @@
       <c r="I28" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J28" s="9" t="s">
+      <c r="J28" s="13" t="s">
         <v>308</v>
       </c>
       <c r="K28" s="6" t="s">
@@ -14005,7 +14077,7 @@
       <c r="I29" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="J29" s="13" t="s">
         <v>308</v>
       </c>
       <c r="K29" s="6" t="s">
@@ -14070,7 +14142,7 @@
       <c r="I30" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="J30" s="13" t="s">
         <v>332</v>
       </c>
       <c r="K30" s="6" t="s">
@@ -14133,7 +14205,7 @@
       <c r="I31" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J31" s="9" t="s">
+      <c r="J31" s="13" t="s">
         <v>341</v>
       </c>
       <c r="K31" s="6" t="s">
@@ -14192,7 +14264,7 @@
       <c r="I32" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J32" s="9" t="s">
+      <c r="J32" s="13" t="s">
         <v>351</v>
       </c>
       <c r="K32" s="6" t="s">
@@ -14255,7 +14327,7 @@
       <c r="I33" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="J33" s="9" t="s">
+      <c r="J33" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K33" s="6" t="s">
@@ -14318,7 +14390,7 @@
       <c r="I34" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J34" s="9" t="s">
+      <c r="J34" s="13" t="s">
         <v>376</v>
       </c>
       <c r="K34" s="6" t="s">
@@ -14381,7 +14453,7 @@
       <c r="I35" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J35" s="9" t="s">
+      <c r="J35" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K35" s="6" t="s">
@@ -14444,7 +14516,7 @@
       <c r="I36" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="J36" s="13" t="s">
         <v>395</v>
       </c>
       <c r="K36" s="6" t="s">
@@ -14507,7 +14579,7 @@
       <c r="I37" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J37" s="9" t="s">
+      <c r="J37" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K37" s="6" t="s">
@@ -14570,7 +14642,7 @@
       <c r="I38" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J38" s="9" t="s">
+      <c r="J38" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K38" s="6" t="s">
@@ -14633,7 +14705,7 @@
       <c r="I39" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J39" s="9" t="s">
+      <c r="J39" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K39" s="6" t="s">
@@ -14696,7 +14768,7 @@
       <c r="I40" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J40" s="9" t="s">
+      <c r="J40" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K40" s="6" t="s">
@@ -14759,7 +14831,7 @@
       <c r="I41" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J41" s="9" t="s">
+      <c r="J41" s="13" t="s">
         <v>448</v>
       </c>
       <c r="K41" s="6" t="s">
@@ -14818,7 +14890,7 @@
       <c r="I42" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J42" s="9" t="s">
+      <c r="J42" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K42" s="6" t="s">
@@ -14881,7 +14953,7 @@
       <c r="I43" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J43" s="9" t="s">
+      <c r="J43" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K43" s="6" t="s">
@@ -14944,7 +15016,7 @@
       <c r="I44" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J44" s="9" t="s">
+      <c r="J44" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K44" s="6" t="s">
@@ -15007,7 +15079,7 @@
       <c r="I45" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J45" s="9" t="s">
+      <c r="J45" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K45" s="6" t="s">
@@ -15070,7 +15142,7 @@
       <c r="I46" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J46" s="9" t="s">
+      <c r="J46" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K46" s="6" t="s">
@@ -15133,7 +15205,7 @@
       <c r="I47" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J47" s="9" t="s">
+      <c r="J47" s="13" t="s">
         <v>507</v>
       </c>
       <c r="K47" s="6" t="s">
@@ -15196,7 +15268,7 @@
       <c r="I48" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J48" s="9" t="s">
+      <c r="J48" s="13" t="s">
         <v>518</v>
       </c>
       <c r="K48" s="6" t="s">
@@ -15259,7 +15331,7 @@
       <c r="I49" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J49" s="9" t="s">
+      <c r="J49" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K49" s="6" t="s">
@@ -15322,7 +15394,7 @@
       <c r="I50" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J50" s="9" t="s">
+      <c r="J50" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K50" s="6" t="s">
@@ -15385,7 +15457,7 @@
       <c r="I51" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J51" s="9" t="s">
+      <c r="J51" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K51" s="6" t="s">
@@ -15448,7 +15520,7 @@
       <c r="I52" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J52" s="9" t="s">
+      <c r="J52" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K52" s="6" t="s">
@@ -15511,7 +15583,7 @@
       <c r="I53" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J53" s="9" t="s">
+      <c r="J53" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K53" s="6" t="s">
@@ -15574,7 +15646,7 @@
       <c r="I54" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J54" s="9" t="s">
+      <c r="J54" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K54" s="6" t="s">
@@ -15639,7 +15711,7 @@
       <c r="I55" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J55" s="9" t="s">
+      <c r="J55" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K55" s="6" t="s">
@@ -15702,7 +15774,7 @@
       <c r="I56" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J56" s="9" t="s">
+      <c r="J56" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K56" s="6" t="s">
@@ -15765,7 +15837,7 @@
       <c r="I57" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J57" s="9" t="s">
+      <c r="J57" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K57" s="6" t="s">
@@ -15828,7 +15900,7 @@
       <c r="I58" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J58" s="9" t="s">
+      <c r="J58" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K58" s="6" t="s">
@@ -15891,7 +15963,7 @@
       <c r="I59" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J59" s="9" t="s">
+      <c r="J59" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K59" s="6" t="s">
@@ -15954,7 +16026,7 @@
       <c r="I60" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J60" s="9" t="s">
+      <c r="J60" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K60" s="6" t="s">
@@ -16017,7 +16089,7 @@
       <c r="I61" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J61" s="9" t="s">
+      <c r="J61" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K61" s="6" t="s">
@@ -16080,7 +16152,7 @@
       <c r="I62" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J62" s="9" t="s">
+      <c r="J62" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K62" s="6" t="s">
@@ -16143,7 +16215,7 @@
       <c r="I63" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J63" s="9" t="s">
+      <c r="J63" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K63" s="6" t="s">
@@ -16206,7 +16278,7 @@
       <c r="I64" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J64" s="9" t="s">
+      <c r="J64" s="13" t="s">
         <v>625</v>
       </c>
       <c r="K64" s="6" t="s">
@@ -16269,7 +16341,7 @@
       <c r="I65" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J65" s="9" t="s">
+      <c r="J65" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K65" s="6" t="s">
@@ -16332,7 +16404,7 @@
       <c r="I66" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J66" s="9" t="s">
+      <c r="J66" s="13" t="s">
         <v>643</v>
       </c>
       <c r="K66" s="6" t="s">
@@ -16395,7 +16467,7 @@
       <c r="I67" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J67" s="9" t="s">
+      <c r="J67" s="13" t="s">
         <v>652</v>
       </c>
       <c r="K67" s="6" t="s">
@@ -16458,7 +16530,7 @@
       <c r="I68" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J68" s="9" t="s">
+      <c r="J68" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K68" s="6" t="s">
@@ -16521,7 +16593,7 @@
       <c r="I69" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J69" s="9" t="s">
+      <c r="J69" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K69" s="6" t="s">
@@ -16584,7 +16656,7 @@
       <c r="I70" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J70" s="9" t="s">
+      <c r="J70" s="13" t="s">
         <v>688</v>
       </c>
       <c r="K70" s="6" t="s">
@@ -16647,7 +16719,7 @@
       <c r="I71" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J71" s="9" t="s">
+      <c r="J71" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K71" s="6" t="s">
@@ -16710,7 +16782,7 @@
       <c r="I72" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J72" s="9" t="s">
+      <c r="J72" s="13" t="s">
         <v>308</v>
       </c>
       <c r="K72" s="6" t="s">
@@ -16773,7 +16845,7 @@
       <c r="I73" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J73" s="9" t="s">
+      <c r="J73" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K73" s="6" t="s">
@@ -16836,7 +16908,7 @@
       <c r="I74" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J74" s="9" t="s">
+      <c r="J74" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K74" s="6" t="s">
@@ -16893,7 +16965,7 @@
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
-      <c r="J75" s="9"/>
+      <c r="J75" s="13"/>
       <c r="K75" s="6" t="s">
         <v>729</v>
       </c>
@@ -16942,7 +17014,7 @@
       <c r="I76" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J76" s="9" t="s">
+      <c r="J76" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K76" s="6" t="s">
@@ -17005,7 +17077,7 @@
       <c r="I77" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J77" s="9" t="s">
+      <c r="J77" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K77" s="6" t="s">
@@ -17068,7 +17140,7 @@
       <c r="I78" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J78" s="9" t="s">
+      <c r="J78" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K78" s="6" t="s">
@@ -17131,7 +17203,7 @@
       <c r="I79" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J79" s="9" t="s">
+      <c r="J79" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K79" s="6" t="s">
@@ -17194,7 +17266,7 @@
       <c r="I80" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J80" s="9" t="s">
+      <c r="J80" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K80" s="6" t="s">
@@ -17257,7 +17329,7 @@
       <c r="I81" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J81" s="9" t="s">
+      <c r="J81" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K81" s="6" t="s">
@@ -17320,7 +17392,7 @@
       <c r="I82" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J82" s="9" t="s">
+      <c r="J82" s="13" t="s">
         <v>781</v>
       </c>
       <c r="K82" s="6" t="s">
@@ -17383,7 +17455,7 @@
       <c r="I83" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J83" s="9" t="s">
+      <c r="J83" s="13" t="s">
         <v>791</v>
       </c>
       <c r="K83" s="6" t="s">
@@ -17446,7 +17518,7 @@
       <c r="I84" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J84" s="9" t="s">
+      <c r="J84" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K84" s="6" t="s">
@@ -17509,7 +17581,7 @@
       <c r="I85" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J85" s="9" t="s">
+      <c r="J85" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K85" s="6" t="s">
@@ -17572,7 +17644,7 @@
       <c r="I86" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J86" s="9" t="s">
+      <c r="J86" s="13" t="s">
         <v>814</v>
       </c>
       <c r="K86" s="6" t="s">
@@ -17635,7 +17707,7 @@
       <c r="I87" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J87" s="9" t="s">
+      <c r="J87" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K87" s="6" t="s">
@@ -17698,7 +17770,7 @@
       <c r="I88" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J88" s="9" t="s">
+      <c r="J88" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K88" s="6" t="s">
@@ -17761,7 +17833,7 @@
       <c r="I89" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J89" s="9" t="s">
+      <c r="J89" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K89" s="6" t="s">
@@ -17824,7 +17896,7 @@
       <c r="I90" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J90" s="9" t="s">
+      <c r="J90" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K90" s="6" t="s">
@@ -17887,7 +17959,7 @@
       <c r="I91" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J91" s="9" t="s">
+      <c r="J91" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K91" s="6" t="s">
@@ -17950,7 +18022,7 @@
       <c r="I92" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J92" s="9" t="s">
+      <c r="J92" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K92" s="6" t="s">
@@ -18013,7 +18085,7 @@
       <c r="I93" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J93" s="9" t="s">
+      <c r="J93" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K93" s="6" t="s">
@@ -18076,7 +18148,7 @@
       <c r="I94" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J94" s="9" t="s">
+      <c r="J94" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K94" s="6" t="s">
@@ -18139,7 +18211,7 @@
       <c r="I95" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J95" s="9" t="s">
+      <c r="J95" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K95" s="6" t="s">
@@ -18202,7 +18274,7 @@
       <c r="I96" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J96" s="9" t="s">
+      <c r="J96" s="13" t="s">
         <v>893</v>
       </c>
       <c r="K96" s="6" t="s">
@@ -18265,7 +18337,7 @@
       <c r="I97" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J97" s="9" t="s">
+      <c r="J97" s="13" t="s">
         <v>903</v>
       </c>
       <c r="K97" s="6" t="s">
@@ -18328,7 +18400,7 @@
       <c r="I98" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J98" s="9" t="s">
+      <c r="J98" s="13" t="s">
         <v>158</v>
       </c>
       <c r="K98" s="6" t="s">
@@ -18391,7 +18463,7 @@
       <c r="I99" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J99" s="9" t="s">
+      <c r="J99" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K99" s="6" t="s">
@@ -18454,7 +18526,7 @@
       <c r="I100" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J100" s="9" t="s">
+      <c r="J100" s="13" t="s">
         <v>925</v>
       </c>
       <c r="K100" s="6" t="s">
@@ -18517,7 +18589,7 @@
       <c r="I101" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J101" s="9" t="s">
+      <c r="J101" s="13" t="s">
         <v>158</v>
       </c>
       <c r="K101" s="6" t="s">
@@ -18580,7 +18652,7 @@
       <c r="I102" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J102" s="9" t="s">
+      <c r="J102" s="13" t="s">
         <v>376</v>
       </c>
       <c r="K102" s="6" t="s">
@@ -18643,7 +18715,7 @@
       <c r="I103" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J103" s="9" t="s">
+      <c r="J103" s="13" t="s">
         <v>376</v>
       </c>
       <c r="K103" s="6" t="s">
@@ -18706,7 +18778,7 @@
       <c r="I104" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J104" s="9" t="s">
+      <c r="J104" s="13" t="s">
         <v>376</v>
       </c>
       <c r="K104" s="6" t="s">
@@ -18769,7 +18841,7 @@
       <c r="I105" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J105" s="9" t="s">
+      <c r="J105" s="13" t="s">
         <v>376</v>
       </c>
       <c r="K105" s="6" t="s">
@@ -18832,7 +18904,7 @@
       <c r="I106" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J106" s="9" t="s">
+      <c r="J106" s="13" t="s">
         <v>376</v>
       </c>
       <c r="K106" s="6" t="s">
@@ -18895,7 +18967,7 @@
       <c r="I107" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J107" s="9" t="s">
+      <c r="J107" s="13" t="s">
         <v>376</v>
       </c>
       <c r="K107" s="6" t="s">
@@ -18958,7 +19030,7 @@
       <c r="I108" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J108" s="9" t="s">
+      <c r="J108" s="13" t="s">
         <v>376</v>
       </c>
       <c r="K108" s="6" t="s">
@@ -19021,7 +19093,7 @@
       <c r="I109" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J109" s="9" t="s">
+      <c r="J109" s="13" t="s">
         <v>376</v>
       </c>
       <c r="K109" s="6" t="s">
@@ -19084,7 +19156,7 @@
       <c r="I110" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J110" s="9" t="s">
+      <c r="J110" s="13" t="s">
         <v>925</v>
       </c>
       <c r="K110" s="6" t="s">
@@ -19147,7 +19219,7 @@
       <c r="I111" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J111" s="9" t="s">
+      <c r="J111" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K111" s="6" t="s">
@@ -19210,7 +19282,7 @@
       <c r="I112" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J112" s="9" t="s">
+      <c r="J112" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K112" s="6" t="s">
@@ -19273,7 +19345,7 @@
       <c r="I113" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J113" s="9" t="s">
+      <c r="J113" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K113" s="6" t="s">
@@ -19336,7 +19408,7 @@
       <c r="I114" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J114" s="9" t="s">
+      <c r="J114" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K114" s="6" t="s">
@@ -19399,7 +19471,7 @@
       <c r="I115" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J115" s="9" t="s">
+      <c r="J115" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K115" s="6" t="s">
@@ -19462,7 +19534,7 @@
       <c r="I116" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J116" s="9" t="s">
+      <c r="J116" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K116" s="6" t="s">
@@ -19525,7 +19597,7 @@
       <c r="I117" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J117" s="9" t="s">
+      <c r="J117" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K117" s="6" t="s">
@@ -19588,7 +19660,7 @@
       <c r="I118" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J118" s="9" t="s">
+      <c r="J118" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K118" s="6" t="s">
@@ -19651,7 +19723,7 @@
       <c r="I119" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J119" s="9" t="s">
+      <c r="J119" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K119" s="6" t="s">
@@ -19714,7 +19786,7 @@
       <c r="I120" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J120" s="9" t="s">
+      <c r="J120" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K120" s="6" t="s">
@@ -19777,7 +19849,7 @@
       <c r="I121" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J121" s="9" t="s">
+      <c r="J121" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K121" s="6" t="s">
@@ -19840,7 +19912,7 @@
       <c r="I122" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J122" s="9" t="s">
+      <c r="J122" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K122" s="6" t="s">
@@ -19903,7 +19975,7 @@
       <c r="I123" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J123" s="9" t="s">
+      <c r="J123" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K123" s="6" t="s">
@@ -19966,7 +20038,7 @@
       <c r="I124" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J124" s="9" t="s">
+      <c r="J124" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K124" s="6" t="s">
@@ -20029,7 +20101,7 @@
       <c r="I125" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J125" s="9" t="s">
+      <c r="J125" s="13" t="s">
         <v>395</v>
       </c>
       <c r="K125" s="6" t="s">
@@ -20092,7 +20164,7 @@
       <c r="I126" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J126" s="9" t="s">
+      <c r="J126" s="13" t="s">
         <v>395</v>
       </c>
       <c r="K126" s="6" t="s">
@@ -20155,7 +20227,7 @@
       <c r="I127" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J127" s="9" t="s">
+      <c r="J127" s="13" t="s">
         <v>395</v>
       </c>
       <c r="K127" s="6" t="s">
@@ -20218,7 +20290,7 @@
       <c r="I128" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J128" s="9" t="s">
+      <c r="J128" s="13" t="s">
         <v>395</v>
       </c>
       <c r="K128" s="6" t="s">
@@ -20281,7 +20353,7 @@
       <c r="I129" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J129" s="9" t="s">
+      <c r="J129" s="13" t="s">
         <v>395</v>
       </c>
       <c r="K129" s="6" t="s">
@@ -20344,7 +20416,7 @@
       <c r="I130" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J130" s="9" t="s">
+      <c r="J130" s="13" t="s">
         <v>395</v>
       </c>
       <c r="K130" s="6" t="s">
@@ -20407,7 +20479,7 @@
       <c r="I131" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J131" s="9" t="s">
+      <c r="J131" s="13" t="s">
         <v>395</v>
       </c>
       <c r="K131" s="6" t="s">
@@ -20470,7 +20542,7 @@
       <c r="I132" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J132" s="9" t="s">
+      <c r="J132" s="13" t="s">
         <v>395</v>
       </c>
       <c r="K132" s="6" t="s">
@@ -20533,7 +20605,7 @@
       <c r="I133" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J133" s="9" t="s">
+      <c r="J133" s="13" t="s">
         <v>395</v>
       </c>
       <c r="K133" s="6" t="s">
@@ -20596,7 +20668,7 @@
       <c r="I134" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J134" s="9" t="s">
+      <c r="J134" s="13" t="s">
         <v>395</v>
       </c>
       <c r="K134" s="6" t="s">
@@ -20659,7 +20731,7 @@
       <c r="I135" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J135" s="9" t="s">
+      <c r="J135" s="13" t="s">
         <v>395</v>
       </c>
       <c r="K135" s="6" t="s">
@@ -20722,7 +20794,7 @@
       <c r="I136" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J136" s="9" t="s">
+      <c r="J136" s="13" t="s">
         <v>395</v>
       </c>
       <c r="K136" s="6" t="s">
@@ -20785,7 +20857,7 @@
       <c r="I137" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J137" s="9" t="s">
+      <c r="J137" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K137" s="6" t="s">
@@ -20848,7 +20920,7 @@
       <c r="I138" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J138" s="9" t="s">
+      <c r="J138" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K138" s="6" t="s">
@@ -20911,7 +20983,7 @@
       <c r="I139" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J139" s="9" t="s">
+      <c r="J139" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K139" s="6" t="s">
@@ -20974,7 +21046,7 @@
       <c r="I140" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J140" s="9" t="s">
+      <c r="J140" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K140" s="6" t="s">
@@ -21037,7 +21109,7 @@
       <c r="I141" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J141" s="9" t="s">
+      <c r="J141" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K141" s="6" t="s">
@@ -21100,7 +21172,7 @@
       <c r="I142" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J142" s="9" t="s">
+      <c r="J142" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K142" s="6" t="s">
@@ -21163,7 +21235,7 @@
       <c r="I143" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J143" s="9" t="s">
+      <c r="J143" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K143" s="6" t="s">
@@ -21226,7 +21298,7 @@
       <c r="I144" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J144" s="9" t="s">
+      <c r="J144" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K144" s="6" t="s">
@@ -21289,7 +21361,7 @@
       <c r="I145" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J145" s="9" t="s">
+      <c r="J145" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K145" s="6" t="s">
@@ -21352,7 +21424,7 @@
       <c r="I146" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J146" s="9" t="s">
+      <c r="J146" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K146" s="6" t="s">
@@ -21415,7 +21487,7 @@
       <c r="I147" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J147" s="9" t="s">
+      <c r="J147" s="13" t="s">
         <v>158</v>
       </c>
       <c r="K147" s="6" t="s">
@@ -21478,7 +21550,7 @@
       <c r="I148" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J148" s="9" t="s">
+      <c r="J148" s="13" t="s">
         <v>158</v>
       </c>
       <c r="K148" s="6" t="s">
@@ -21541,7 +21613,7 @@
       <c r="I149" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J149" s="9" t="s">
+      <c r="J149" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K149" s="6" t="s">
@@ -21604,7 +21676,7 @@
       <c r="I150" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J150" s="9" t="s">
+      <c r="J150" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K150" s="6" t="s">
@@ -21667,7 +21739,7 @@
       <c r="I151" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J151" s="9" t="s">
+      <c r="J151" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K151" s="6" t="s">
@@ -21730,7 +21802,7 @@
       <c r="I152" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J152" s="9" t="s">
+      <c r="J152" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K152" s="6" t="s">
@@ -21793,7 +21865,7 @@
       <c r="I153" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J153" s="9" t="s">
+      <c r="J153" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K153" s="6" t="s">
@@ -21856,7 +21928,7 @@
       <c r="I154" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J154" s="9" t="s">
+      <c r="J154" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K154" s="6" t="s">
@@ -21919,7 +21991,7 @@
       <c r="I155" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J155" s="9" t="s">
+      <c r="J155" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K155" s="6" t="s">
@@ -21982,7 +22054,7 @@
       <c r="I156" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J156" s="9" t="s">
+      <c r="J156" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K156" s="6" t="s">
@@ -22045,7 +22117,7 @@
       <c r="I157" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J157" s="9" t="s">
+      <c r="J157" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K157" s="6" t="s">
@@ -22108,7 +22180,7 @@
       <c r="I158" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J158" s="9" t="s">
+      <c r="J158" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K158" s="6" t="s">
@@ -22171,7 +22243,7 @@
       <c r="I159" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J159" s="9" t="s">
+      <c r="J159" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K159" s="6" t="s">
@@ -22234,7 +22306,7 @@
       <c r="I160" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J160" s="9" t="s">
+      <c r="J160" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K160" s="6" t="s">
@@ -22297,7 +22369,7 @@
       <c r="I161" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J161" s="9" t="s">
+      <c r="J161" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K161" s="6" t="s">
@@ -22360,7 +22432,7 @@
       <c r="I162" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J162" s="9" t="s">
+      <c r="J162" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K162" s="6" t="s">
@@ -22423,7 +22495,7 @@
       <c r="I163" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J163" s="9" t="s">
+      <c r="J163" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K163" s="6" t="s">
@@ -22486,7 +22558,7 @@
       <c r="I164" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J164" s="9" t="s">
+      <c r="J164" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K164" s="6" t="s">
@@ -22549,7 +22621,7 @@
       <c r="I165" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J165" s="9" t="s">
+      <c r="J165" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K165" s="6" t="s">
@@ -22612,7 +22684,7 @@
       <c r="I166" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J166" s="9" t="s">
+      <c r="J166" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K166" s="6" t="s">
@@ -22675,7 +22747,7 @@
       <c r="I167" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J167" s="9" t="s">
+      <c r="J167" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K167" s="6" t="s">
@@ -22738,7 +22810,7 @@
       <c r="I168" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J168" s="9" t="s">
+      <c r="J168" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K168" s="6" t="s">
@@ -22801,7 +22873,7 @@
       <c r="I169" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J169" s="9" t="s">
+      <c r="J169" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K169" s="6" t="s">
@@ -22864,7 +22936,7 @@
       <c r="I170" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J170" s="9" t="s">
+      <c r="J170" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K170" s="6" t="s">
@@ -22927,7 +22999,7 @@
       <c r="I171" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J171" s="9" t="s">
+      <c r="J171" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K171" s="6" t="s">
@@ -22990,7 +23062,7 @@
       <c r="I172" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J172" s="9" t="s">
+      <c r="J172" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K172" s="6" t="s">
@@ -23053,7 +23125,7 @@
       <c r="I173" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J173" s="9" t="s">
+      <c r="J173" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K173" s="6" t="s">
@@ -23116,7 +23188,7 @@
       <c r="I174" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J174" s="9" t="s">
+      <c r="J174" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K174" s="6" t="s">
@@ -23179,7 +23251,7 @@
       <c r="I175" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J175" s="9" t="s">
+      <c r="J175" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K175" s="6" t="s">
@@ -23242,7 +23314,7 @@
       <c r="I176" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J176" s="9" t="s">
+      <c r="J176" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K176" s="6" t="s">
@@ -23305,7 +23377,7 @@
       <c r="I177" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J177" s="9" t="s">
+      <c r="J177" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K177" s="6" t="s">
@@ -23368,7 +23440,7 @@
       <c r="I178" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J178" s="9" t="s">
+      <c r="J178" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K178" s="6" t="s">
@@ -23431,7 +23503,7 @@
       <c r="I179" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J179" s="9" t="s">
+      <c r="J179" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K179" s="6" t="s">
@@ -23494,7 +23566,7 @@
       <c r="I180" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J180" s="9" t="s">
+      <c r="J180" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K180" s="6" t="s">
@@ -23557,7 +23629,7 @@
       <c r="I181" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J181" s="9" t="s">
+      <c r="J181" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K181" s="6" t="s">
@@ -23620,7 +23692,7 @@
       <c r="I182" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J182" s="9" t="s">
+      <c r="J182" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K182" s="6" t="s">
@@ -23683,7 +23755,7 @@
       <c r="I183" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J183" s="9" t="s">
+      <c r="J183" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K183" s="6" t="s">
@@ -23746,7 +23818,7 @@
       <c r="I184" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J184" s="9" t="s">
+      <c r="J184" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K184" s="6" t="s">
@@ -23809,7 +23881,7 @@
       <c r="I185" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J185" s="9" t="s">
+      <c r="J185" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K185" s="6" t="s">
@@ -23872,7 +23944,7 @@
       <c r="I186" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J186" s="9" t="s">
+      <c r="J186" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K186" s="6" t="s">
@@ -23935,7 +24007,7 @@
       <c r="I187" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J187" s="9" t="s">
+      <c r="J187" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K187" s="6" t="s">
@@ -23998,7 +24070,7 @@
       <c r="I188" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J188" s="9" t="s">
+      <c r="J188" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K188" s="6" t="s">
@@ -24061,7 +24133,7 @@
       <c r="I189" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J189" s="9" t="s">
+      <c r="J189" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K189" s="6" t="s">
@@ -24124,7 +24196,7 @@
       <c r="I190" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J190" s="9" t="s">
+      <c r="J190" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K190" s="6" t="s">
@@ -24187,7 +24259,7 @@
       <c r="I191" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J191" s="9" t="s">
+      <c r="J191" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K191" s="6" t="s">
@@ -24250,7 +24322,7 @@
       <c r="I192" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J192" s="9" t="s">
+      <c r="J192" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K192" s="6" t="s">
@@ -24313,7 +24385,7 @@
       <c r="I193" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J193" s="9" t="s">
+      <c r="J193" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K193" s="6" t="s">
@@ -24376,7 +24448,7 @@
       <c r="I194" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J194" s="9" t="s">
+      <c r="J194" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K194" s="6" t="s">
@@ -24439,7 +24511,7 @@
       <c r="I195" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J195" s="9" t="s">
+      <c r="J195" s="13" t="s">
         <v>814</v>
       </c>
       <c r="K195" s="6" t="s">
@@ -24502,7 +24574,7 @@
       <c r="I196" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J196" s="9" t="s">
+      <c r="J196" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K196" s="6" t="s">
@@ -24565,7 +24637,7 @@
       <c r="I197" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J197" s="9" t="s">
+      <c r="J197" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K197" s="6" t="s">
@@ -24628,7 +24700,7 @@
       <c r="I198" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J198" s="9" t="s">
+      <c r="J198" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K198" s="6" t="s">
@@ -24691,7 +24763,7 @@
       <c r="I199" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J199" s="9" t="s">
+      <c r="J199" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K199" s="6" t="s">
@@ -24754,7 +24826,7 @@
       <c r="I200" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J200" s="9" t="s">
+      <c r="J200" s="13" t="s">
         <v>903</v>
       </c>
       <c r="K200" s="6" t="s">
@@ -24817,7 +24889,7 @@
       <c r="I201" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J201" s="9" t="s">
+      <c r="J201" s="13" t="s">
         <v>903</v>
       </c>
       <c r="K201" s="6" t="s">
@@ -24880,7 +24952,7 @@
       <c r="I202" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J202" s="9" t="s">
+      <c r="J202" s="13" t="s">
         <v>903</v>
       </c>
       <c r="K202" s="6" t="s">
@@ -24943,7 +25015,7 @@
       <c r="I203" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J203" s="9" t="s">
+      <c r="J203" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K203" s="6" t="s">
@@ -25006,7 +25078,7 @@
       <c r="I204" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J204" s="9" t="s">
+      <c r="J204" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K204" s="6" t="s">
@@ -25069,7 +25141,7 @@
       <c r="I205" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J205" s="9" t="s">
+      <c r="J205" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K205" s="6" t="s">
@@ -25132,7 +25204,7 @@
       <c r="I206" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J206" s="9" t="s">
+      <c r="J206" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K206" s="6" t="s">
@@ -25195,7 +25267,7 @@
       <c r="I207" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J207" s="9" t="s">
+      <c r="J207" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K207" s="6" t="s">
@@ -25258,7 +25330,7 @@
       <c r="I208" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J208" s="9" t="s">
+      <c r="J208" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K208" s="6" t="s">
@@ -25321,7 +25393,7 @@
       <c r="I209" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J209" s="9" t="s">
+      <c r="J209" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K209" s="6" t="s">
@@ -25384,7 +25456,7 @@
       <c r="I210" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J210" s="9" t="s">
+      <c r="J210" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K210" s="6" t="s">
@@ -25447,7 +25519,7 @@
       <c r="I211" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J211" s="9" t="s">
+      <c r="J211" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K211" s="6" t="s">
@@ -25510,7 +25582,7 @@
       <c r="I212" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J212" s="9" t="s">
+      <c r="J212" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K212" s="6" t="s">
@@ -25573,7 +25645,7 @@
       <c r="I213" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J213" s="9" t="s">
+      <c r="J213" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K213" s="6" t="s">
@@ -25636,7 +25708,7 @@
       <c r="I214" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J214" s="9" t="s">
+      <c r="J214" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K214" s="6" t="s">
@@ -25699,7 +25771,7 @@
       <c r="I215" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J215" s="9" t="s">
+      <c r="J215" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K215" s="6" t="s">
@@ -25762,7 +25834,7 @@
       <c r="I216" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J216" s="9" t="s">
+      <c r="J216" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K216" s="6" t="s">
@@ -25825,7 +25897,7 @@
       <c r="I217" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J217" s="9" t="s">
+      <c r="J217" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K217" s="6" t="s">
@@ -25888,7 +25960,7 @@
       <c r="I218" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J218" s="9" t="s">
+      <c r="J218" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K218" s="6" t="s">
@@ -25951,7 +26023,7 @@
       <c r="I219" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J219" s="9" t="s">
+      <c r="J219" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K219" s="6" t="s">
@@ -26014,7 +26086,7 @@
       <c r="I220" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J220" s="9" t="s">
+      <c r="J220" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K220" s="6" t="s">
@@ -26077,7 +26149,7 @@
       <c r="I221" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J221" s="9" t="s">
+      <c r="J221" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K221" s="6" t="s">
@@ -26140,7 +26212,7 @@
       <c r="I222" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J222" s="9" t="s">
+      <c r="J222" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K222" s="6" t="s">
@@ -26203,7 +26275,7 @@
       <c r="I223" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J223" s="9" t="s">
+      <c r="J223" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K223" s="6" t="s">
@@ -26266,7 +26338,7 @@
       <c r="I224" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J224" s="9" t="s">
+      <c r="J224" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K224" s="6" t="s">
@@ -26329,7 +26401,7 @@
       <c r="I225" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J225" s="9" t="s">
+      <c r="J225" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K225" s="6" t="s">
@@ -26392,7 +26464,7 @@
       <c r="I226" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J226" s="9" t="s">
+      <c r="J226" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K226" s="6" t="s">
@@ -26455,7 +26527,7 @@
       <c r="I227" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J227" s="9" t="s">
+      <c r="J227" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K227" s="6" t="s">
@@ -26518,7 +26590,7 @@
       <c r="I228" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J228" s="9" t="s">
+      <c r="J228" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K228" s="6" t="s">
@@ -26581,7 +26653,7 @@
       <c r="I229" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J229" s="9" t="s">
+      <c r="J229" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K229" s="6" t="s">
@@ -26644,7 +26716,7 @@
       <c r="I230" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J230" s="9" t="s">
+      <c r="J230" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K230" s="6" t="s">
@@ -26707,7 +26779,7 @@
       <c r="I231" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J231" s="9" t="s">
+      <c r="J231" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K231" s="6" t="s">
@@ -26770,7 +26842,7 @@
       <c r="I232" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J232" s="9" t="s">
+      <c r="J232" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K232" s="6" t="s">
@@ -26833,7 +26905,7 @@
       <c r="I233" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J233" s="9" t="s">
+      <c r="J233" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K233" s="6" t="s">
@@ -26896,7 +26968,7 @@
       <c r="I234" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J234" s="9" t="s">
+      <c r="J234" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K234" s="6" t="s">
@@ -26959,7 +27031,7 @@
       <c r="I235" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J235" s="9" t="s">
+      <c r="J235" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K235" s="6" t="s">
@@ -27022,7 +27094,7 @@
       <c r="I236" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J236" s="9" t="s">
+      <c r="J236" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K236" s="6" t="s">
@@ -27085,7 +27157,7 @@
       <c r="I237" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J237" s="9" t="s">
+      <c r="J237" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K237" s="6" t="s">
@@ -27148,7 +27220,7 @@
       <c r="I238" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J238" s="9" t="s">
+      <c r="J238" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K238" s="6" t="s">
@@ -27211,7 +27283,7 @@
       <c r="I239" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J239" s="9" t="s">
+      <c r="J239" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K239" s="6" t="s">
@@ -27274,7 +27346,7 @@
       <c r="I240" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J240" s="9" t="s">
+      <c r="J240" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K240" s="6" t="s">
@@ -27337,7 +27409,7 @@
       <c r="I241" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J241" s="9" t="s">
+      <c r="J241" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K241" s="6" t="s">
@@ -27400,7 +27472,7 @@
       <c r="I242" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J242" s="9" t="s">
+      <c r="J242" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K242" s="6" t="s">
@@ -27463,7 +27535,7 @@
       <c r="I243" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J243" s="9" t="s">
+      <c r="J243" s="13" t="s">
         <v>893</v>
       </c>
       <c r="K243" s="6" t="s">
@@ -27526,7 +27598,7 @@
       <c r="I244" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J244" s="9" t="s">
+      <c r="J244" s="13" t="s">
         <v>893</v>
       </c>
       <c r="K244" s="6" t="s">
@@ -27589,7 +27661,7 @@
       <c r="I245" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J245" s="9" t="s">
+      <c r="J245" s="13" t="s">
         <v>893</v>
       </c>
       <c r="K245" s="6" t="s">
@@ -27652,7 +27724,7 @@
       <c r="I246" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J246" s="9" t="s">
+      <c r="J246" s="13" t="s">
         <v>893</v>
       </c>
       <c r="K246" s="6" t="s">
@@ -27715,7 +27787,7 @@
       <c r="I247" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J247" s="9" t="s">
+      <c r="J247" s="13" t="s">
         <v>893</v>
       </c>
       <c r="K247" s="6" t="s">
@@ -27778,7 +27850,7 @@
       <c r="I248" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J248" s="9" t="s">
+      <c r="J248" s="13" t="s">
         <v>893</v>
       </c>
       <c r="K248" s="6" t="s">
@@ -27841,7 +27913,7 @@
       <c r="I249" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J249" s="9" t="s">
+      <c r="J249" s="13" t="s">
         <v>893</v>
       </c>
       <c r="K249" s="6" t="s">
@@ -27904,7 +27976,7 @@
       <c r="I250" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J250" s="9" t="s">
+      <c r="J250" s="13" t="s">
         <v>893</v>
       </c>
       <c r="K250" s="6" t="s">
@@ -27967,7 +28039,7 @@
       <c r="I251" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J251" s="9" t="s">
+      <c r="J251" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K251" s="6" t="s">
@@ -28030,7 +28102,7 @@
       <c r="I252" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J252" s="9" t="s">
+      <c r="J252" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K252" s="6" t="s">
@@ -28093,7 +28165,7 @@
       <c r="I253" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J253" s="9" t="s">
+      <c r="J253" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K253" s="6" t="s">
@@ -28156,7 +28228,7 @@
       <c r="I254" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J254" s="9" t="s">
+      <c r="J254" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K254" s="6" t="s">
@@ -28219,7 +28291,7 @@
       <c r="I255" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J255" s="9" t="s">
+      <c r="J255" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K255" s="6" t="s">
@@ -28282,7 +28354,7 @@
       <c r="I256" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J256" s="9" t="s">
+      <c r="J256" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K256" s="6" t="s">
@@ -28345,7 +28417,7 @@
       <c r="I257" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J257" s="9" t="s">
+      <c r="J257" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K257" s="6" t="s">
@@ -28408,7 +28480,7 @@
       <c r="I258" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J258" s="9" t="s">
+      <c r="J258" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K258" s="6" t="s">
@@ -28471,7 +28543,7 @@
       <c r="I259" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J259" s="9" t="s">
+      <c r="J259" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K259" s="6" t="s">
@@ -28534,7 +28606,7 @@
       <c r="I260" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J260" s="9" t="s">
+      <c r="J260" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K260" s="6" t="s">
@@ -28597,7 +28669,7 @@
       <c r="I261" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J261" s="9" t="s">
+      <c r="J261" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K261" s="6" t="s">
@@ -28660,7 +28732,7 @@
       <c r="I262" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J262" s="9" t="s">
+      <c r="J262" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K262" s="6" t="s">
@@ -28723,7 +28795,7 @@
       <c r="I263" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J263" s="9" t="s">
+      <c r="J263" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K263" s="6" t="s">
@@ -28780,7 +28852,7 @@
       <c r="I264" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J264" s="9" t="s">
+      <c r="J264" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K264" s="6" t="s">
@@ -28843,7 +28915,7 @@
       <c r="I265" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J265" s="9" t="s">
+      <c r="J265" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K265" s="6" t="s">
@@ -28906,7 +28978,7 @@
       <c r="I266" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J266" s="9" t="s">
+      <c r="J266" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K266" s="6" t="s">
@@ -28969,7 +29041,7 @@
       <c r="I267" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J267" s="9" t="s">
+      <c r="J267" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K267" s="6" t="s">
@@ -29032,7 +29104,7 @@
       <c r="I268" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J268" s="9" t="s">
+      <c r="J268" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K268" s="6" t="s">
@@ -29095,7 +29167,7 @@
       <c r="I269" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J269" s="9" t="s">
+      <c r="J269" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K269" s="6" t="s">
@@ -29158,7 +29230,7 @@
       <c r="I270" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J270" s="9" t="s">
+      <c r="J270" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K270" s="6" t="s">
@@ -29221,7 +29293,7 @@
       <c r="I271" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J271" s="9" t="s">
+      <c r="J271" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K271" s="6" t="s">
@@ -29284,7 +29356,7 @@
       <c r="I272" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J272" s="9" t="s">
+      <c r="J272" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K272" s="6" t="s">
@@ -29347,7 +29419,7 @@
       <c r="I273" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J273" s="9" t="s">
+      <c r="J273" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K273" s="6" t="s">
@@ -29410,7 +29482,7 @@
       <c r="I274" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J274" s="9" t="s">
+      <c r="J274" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K274" s="6" t="s">
@@ -29473,7 +29545,7 @@
       <c r="I275" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J275" s="9" t="s">
+      <c r="J275" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K275" s="6" t="s">
@@ -29536,7 +29608,7 @@
       <c r="I276" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J276" s="9" t="s">
+      <c r="J276" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K276" s="6" t="s">
@@ -29599,7 +29671,7 @@
       <c r="I277" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J277" s="9" t="s">
+      <c r="J277" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K277" s="6" t="s">
@@ -29662,7 +29734,7 @@
       <c r="I278" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J278" s="9" t="s">
+      <c r="J278" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K278" s="6" t="s">
@@ -29725,7 +29797,7 @@
       <c r="I279" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J279" s="9" t="s">
+      <c r="J279" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K279" s="6" t="s">
@@ -29788,7 +29860,7 @@
       <c r="I280" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J280" s="9" t="s">
+      <c r="J280" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K280" s="6" t="s">
@@ -29851,7 +29923,7 @@
       <c r="I281" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J281" s="9" t="s">
+      <c r="J281" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K281" s="6" t="s">
@@ -29914,7 +29986,7 @@
       <c r="I282" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J282" s="9" t="s">
+      <c r="J282" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K282" s="6" t="s">
@@ -29977,7 +30049,7 @@
       <c r="I283" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J283" s="9" t="s">
+      <c r="J283" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K283" s="6" t="s">
@@ -30040,7 +30112,7 @@
       <c r="I284" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J284" s="9" t="s">
+      <c r="J284" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K284" s="6" t="s">
@@ -30103,7 +30175,7 @@
       <c r="I285" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J285" s="9" t="s">
+      <c r="J285" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K285" s="6" t="s">
@@ -30166,7 +30238,7 @@
       <c r="I286" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J286" s="9" t="s">
+      <c r="J286" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K286" s="6" t="s">
@@ -30229,7 +30301,7 @@
       <c r="I287" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J287" s="9" t="s">
+      <c r="J287" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K287" s="6" t="s">
@@ -30292,7 +30364,7 @@
       <c r="I288" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J288" s="9" t="s">
+      <c r="J288" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K288" s="6" t="s">
@@ -30355,7 +30427,7 @@
       <c r="I289" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J289" s="9" t="s">
+      <c r="J289" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K289" s="6" t="s">
@@ -30418,7 +30490,7 @@
       <c r="I290" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J290" s="9" t="s">
+      <c r="J290" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K290" s="6" t="s">
@@ -30481,7 +30553,7 @@
       <c r="I291" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J291" s="9" t="s">
+      <c r="J291" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K291" s="6" t="s">
@@ -30544,7 +30616,7 @@
       <c r="I292" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J292" s="9" t="s">
+      <c r="J292" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K292" s="6" t="s">
@@ -30607,7 +30679,7 @@
       <c r="I293" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J293" s="9" t="s">
+      <c r="J293" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K293" s="6" t="s">
@@ -30670,7 +30742,7 @@
       <c r="I294" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J294" s="9" t="s">
+      <c r="J294" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K294" s="6" t="s">
@@ -30733,7 +30805,7 @@
       <c r="I295" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J295" s="9" t="s">
+      <c r="J295" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K295" s="6" t="s">
@@ -30796,7 +30868,7 @@
       <c r="I296" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J296" s="9" t="s">
+      <c r="J296" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K296" s="6" t="s">
@@ -30859,7 +30931,7 @@
       <c r="I297" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J297" s="9" t="s">
+      <c r="J297" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K297" s="6" t="s">
@@ -30922,7 +30994,7 @@
       <c r="I298" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J298" s="9" t="s">
+      <c r="J298" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K298" s="6" t="s">
@@ -30985,7 +31057,7 @@
       <c r="I299" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J299" s="9" t="s">
+      <c r="J299" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K299" s="6" t="s">
@@ -31048,7 +31120,7 @@
       <c r="I300" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J300" s="9" t="s">
+      <c r="J300" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K300" s="6" t="s">
@@ -31111,7 +31183,7 @@
       <c r="I301" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J301" s="9" t="s">
+      <c r="J301" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K301" s="6" t="s">
@@ -31174,7 +31246,7 @@
       <c r="I302" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J302" s="9" t="s">
+      <c r="J302" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K302" s="6" t="s">
@@ -31237,7 +31309,7 @@
       <c r="I303" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J303" s="9" t="s">
+      <c r="J303" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K303" s="6" t="s">
@@ -31300,7 +31372,7 @@
       <c r="I304" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J304" s="9" t="s">
+      <c r="J304" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K304" s="6" t="s">
@@ -31363,7 +31435,7 @@
       <c r="I305" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J305" s="9" t="s">
+      <c r="J305" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K305" s="6" t="s">
@@ -31426,7 +31498,7 @@
       <c r="I306" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J306" s="9" t="s">
+      <c r="J306" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K306" s="6" t="s">
@@ -31489,7 +31561,7 @@
       <c r="I307" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J307" s="9" t="s">
+      <c r="J307" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K307" s="6" t="s">
@@ -31552,7 +31624,7 @@
       <c r="I308" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J308" s="9" t="s">
+      <c r="J308" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K308" s="6" t="s">
@@ -31615,7 +31687,7 @@
       <c r="I309" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J309" s="9" t="s">
+      <c r="J309" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K309" s="6" t="s">
@@ -31678,7 +31750,7 @@
       <c r="I310" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J310" s="9" t="s">
+      <c r="J310" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K310" s="6" t="s">
@@ -31741,7 +31813,7 @@
       <c r="I311" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J311" s="9" t="s">
+      <c r="J311" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K311" s="6" t="s">
@@ -31804,7 +31876,7 @@
       <c r="I312" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J312" s="9" t="s">
+      <c r="J312" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K312" s="6" t="s">
@@ -31867,7 +31939,7 @@
       <c r="I313" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J313" s="9" t="s">
+      <c r="J313" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K313" s="6" t="s">
@@ -31930,7 +32002,7 @@
       <c r="I314" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J314" s="9" t="s">
+      <c r="J314" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K314" s="6" t="s">
@@ -31993,7 +32065,7 @@
       <c r="I315" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J315" s="9" t="s">
+      <c r="J315" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K315" s="6" t="s">
@@ -32056,7 +32128,7 @@
       <c r="I316" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J316" s="9" t="s">
+      <c r="J316" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K316" s="6" t="s">
@@ -32119,7 +32191,7 @@
       <c r="I317" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J317" s="9" t="s">
+      <c r="J317" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K317" s="6" t="s">
@@ -32182,7 +32254,7 @@
       <c r="I318" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J318" s="9" t="s">
+      <c r="J318" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K318" s="6" t="s">
@@ -32245,7 +32317,7 @@
       <c r="I319" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J319" s="9" t="s">
+      <c r="J319" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K319" s="6" t="s">
@@ -32308,7 +32380,7 @@
       <c r="I320" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J320" s="9" t="s">
+      <c r="J320" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K320" s="6" t="s">
@@ -32371,7 +32443,7 @@
       <c r="I321" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J321" s="9" t="s">
+      <c r="J321" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K321" s="6" t="s">
@@ -32434,7 +32506,7 @@
       <c r="I322" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J322" s="9" t="s">
+      <c r="J322" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K322" s="6" t="s">
@@ -32497,7 +32569,7 @@
       <c r="I323" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J323" s="9" t="s">
+      <c r="J323" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K323" s="6" t="s">
@@ -32560,7 +32632,7 @@
       <c r="I324" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J324" s="9" t="s">
+      <c r="J324" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K324" s="6" t="s">
@@ -32623,7 +32695,7 @@
       <c r="I325" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J325" s="9" t="s">
+      <c r="J325" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K325" s="6" t="s">
@@ -32686,7 +32758,7 @@
       <c r="I326" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J326" s="9" t="s">
+      <c r="J326" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K326" s="6" t="s">
@@ -32749,7 +32821,7 @@
       <c r="I327" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J327" s="9" t="s">
+      <c r="J327" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K327" s="6" t="s">
@@ -32812,7 +32884,7 @@
       <c r="I328" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J328" s="9" t="s">
+      <c r="J328" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K328" s="6" t="s">
@@ -32875,7 +32947,7 @@
       <c r="I329" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J329" s="9" t="s">
+      <c r="J329" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K329" s="6" t="s">
@@ -32938,7 +33010,7 @@
       <c r="I330" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J330" s="9" t="s">
+      <c r="J330" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K330" s="6" t="s">
@@ -33001,7 +33073,7 @@
       <c r="I331" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J331" s="9" t="s">
+      <c r="J331" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K331" s="6" t="s">
@@ -33064,7 +33136,7 @@
       <c r="I332" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J332" s="9" t="s">
+      <c r="J332" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K332" s="6" t="s">
@@ -33127,7 +33199,7 @@
       <c r="I333" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J333" s="9" t="s">
+      <c r="J333" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K333" s="6" t="s">
@@ -33190,7 +33262,7 @@
       <c r="I334" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J334" s="9" t="s">
+      <c r="J334" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K334" s="6" t="s">
@@ -33253,7 +33325,7 @@
       <c r="I335" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J335" s="9" t="s">
+      <c r="J335" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K335" s="6" t="s">
@@ -33316,7 +33388,7 @@
       <c r="I336" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J336" s="9" t="s">
+      <c r="J336" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K336" s="6" t="s">
@@ -33379,7 +33451,7 @@
       <c r="I337" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J337" s="9" t="s">
+      <c r="J337" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K337" s="6" t="s">
@@ -33442,7 +33514,7 @@
       <c r="I338" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J338" s="9" t="s">
+      <c r="J338" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K338" s="6" t="s">
@@ -33505,7 +33577,7 @@
       <c r="I339" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J339" s="9" t="s">
+      <c r="J339" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K339" s="6" t="s">
@@ -33568,7 +33640,7 @@
       <c r="I340" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J340" s="9" t="s">
+      <c r="J340" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K340" s="6" t="s">
@@ -33631,7 +33703,7 @@
       <c r="I341" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J341" s="9" t="s">
+      <c r="J341" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K341" s="6" t="s">
@@ -33694,7 +33766,7 @@
       <c r="I342" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J342" s="9" t="s">
+      <c r="J342" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K342" s="6" t="s">
@@ -33757,7 +33829,7 @@
       <c r="I343" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J343" s="9" t="s">
+      <c r="J343" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K343" s="6" t="s">
@@ -33820,7 +33892,7 @@
       <c r="I344" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J344" s="9" t="s">
+      <c r="J344" s="13" t="s">
         <v>230</v>
       </c>
       <c r="K344" s="6" t="s">
@@ -33883,7 +33955,7 @@
       <c r="I345" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J345" s="9" t="s">
+      <c r="J345" s="13" t="s">
         <v>230</v>
       </c>
       <c r="K345" s="6" t="s">
@@ -33946,7 +34018,7 @@
       <c r="I346" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J346" s="9" t="s">
+      <c r="J346" s="13" t="s">
         <v>230</v>
       </c>
       <c r="K346" s="6" t="s">
@@ -34009,7 +34081,7 @@
       <c r="I347" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J347" s="9" t="s">
+      <c r="J347" s="13" t="s">
         <v>230</v>
       </c>
       <c r="K347" s="6" t="s">
@@ -34072,7 +34144,7 @@
       <c r="I348" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J348" s="9" t="s">
+      <c r="J348" s="13" t="s">
         <v>241</v>
       </c>
       <c r="K348" s="6" t="s">
@@ -34135,7 +34207,7 @@
       <c r="I349" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J349" s="9" t="s">
+      <c r="J349" s="13" t="s">
         <v>241</v>
       </c>
       <c r="K349" s="6" t="s">
@@ -34198,7 +34270,7 @@
       <c r="I350" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J350" s="9" t="s">
+      <c r="J350" s="13" t="s">
         <v>241</v>
       </c>
       <c r="K350" s="6" t="s">
@@ -34261,7 +34333,7 @@
       <c r="I351" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J351" s="9" t="s">
+      <c r="J351" s="13" t="s">
         <v>241</v>
       </c>
       <c r="K351" s="6" t="s">
@@ -34324,7 +34396,7 @@
       <c r="I352" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J352" s="9" t="s">
+      <c r="J352" s="13" t="s">
         <v>241</v>
       </c>
       <c r="K352" s="6" t="s">
@@ -34387,7 +34459,7 @@
       <c r="I353" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J353" s="9" t="s">
+      <c r="J353" s="13" t="s">
         <v>241</v>
       </c>
       <c r="K353" s="6" t="s">
@@ -34450,7 +34522,7 @@
       <c r="I354" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J354" s="9" t="s">
+      <c r="J354" s="13" t="s">
         <v>210</v>
       </c>
       <c r="K354" s="6" t="s">
@@ -34513,7 +34585,7 @@
       <c r="I355" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J355" s="9" t="s">
+      <c r="J355" s="13" t="s">
         <v>210</v>
       </c>
       <c r="K355" s="6" t="s">
@@ -34576,7 +34648,7 @@
       <c r="I356" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J356" s="9" t="s">
+      <c r="J356" s="13" t="s">
         <v>210</v>
       </c>
       <c r="K356" s="6" t="s">
@@ -34639,7 +34711,7 @@
       <c r="I357" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J357" s="9" t="s">
+      <c r="J357" s="13" t="s">
         <v>351</v>
       </c>
       <c r="K357" s="6" t="s">
@@ -34702,7 +34774,7 @@
       <c r="I358" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J358" s="9" t="s">
+      <c r="J358" s="13" t="s">
         <v>351</v>
       </c>
       <c r="K358" s="6" t="s">
@@ -34765,7 +34837,7 @@
       <c r="I359" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J359" s="9" t="s">
+      <c r="J359" s="13" t="s">
         <v>351</v>
       </c>
       <c r="K359" s="6" t="s">
@@ -34828,7 +34900,7 @@
       <c r="I360" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="J360" s="9" t="s">
+      <c r="J360" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K360" s="6" t="s">
@@ -34891,7 +34963,7 @@
       <c r="I361" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="J361" s="9" t="s">
+      <c r="J361" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K361" s="6" t="s">
@@ -34954,7 +35026,7 @@
       <c r="I362" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="J362" s="9" t="s">
+      <c r="J362" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K362" s="6" t="s">
@@ -35017,7 +35089,7 @@
       <c r="I363" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J363" s="9" t="s">
+      <c r="J363" s="13" t="s">
         <v>341</v>
       </c>
       <c r="K363" s="6" t="s">
@@ -35076,7 +35148,7 @@
       <c r="I364" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J364" s="9" t="s">
+      <c r="J364" s="13" t="s">
         <v>341</v>
       </c>
       <c r="K364" s="6" t="s">
@@ -35135,7 +35207,7 @@
       <c r="I365" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J365" s="9" t="s">
+      <c r="J365" s="13" t="s">
         <v>341</v>
       </c>
       <c r="K365" s="6" t="s">
@@ -35194,7 +35266,7 @@
       <c r="I366" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J366" s="9" t="s">
+      <c r="J366" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K366" s="6" t="s">
@@ -35257,7 +35329,7 @@
       <c r="I367" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J367" s="9" t="s">
+      <c r="J367" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K367" s="6" t="s">
@@ -35320,7 +35392,7 @@
       <c r="I368" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J368" s="9" t="s">
+      <c r="J368" s="13" t="s">
         <v>290</v>
       </c>
       <c r="K368" s="6" t="s">
@@ -35383,7 +35455,7 @@
       <c r="I369" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J369" s="9" t="s">
+      <c r="J369" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K369" s="6" t="s">
@@ -35446,7 +35518,7 @@
       <c r="I370" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J370" s="9" t="s">
+      <c r="J370" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K370" s="6" t="s">
@@ -35509,7 +35581,7 @@
       <c r="I371" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J371" s="9" t="s">
+      <c r="J371" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K371" s="6" t="s">
@@ -35572,7 +35644,7 @@
       <c r="I372" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J372" s="9" t="s">
+      <c r="J372" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K372" s="6" t="s">
@@ -35635,7 +35707,7 @@
       <c r="I373" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J373" s="9" t="s">
+      <c r="J373" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K373" s="6" t="s">
@@ -35698,7 +35770,7 @@
       <c r="I374" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J374" s="9" t="s">
+      <c r="J374" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K374" s="6" t="s">
@@ -35761,7 +35833,7 @@
       <c r="I375" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J375" s="9" t="s">
+      <c r="J375" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K375" s="6" t="s">
@@ -35824,7 +35896,7 @@
       <c r="I376" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J376" s="9" t="s">
+      <c r="J376" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K376" s="6" t="s">
@@ -35887,7 +35959,7 @@
       <c r="I377" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J377" s="9" t="s">
+      <c r="J377" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K377" s="6" t="s">
@@ -35950,7 +36022,7 @@
       <c r="I378" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J378" s="9" t="s">
+      <c r="J378" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K378" s="6" t="s">
@@ -36013,7 +36085,7 @@
       <c r="I379" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J379" s="9" t="s">
+      <c r="J379" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K379" s="6" t="s">
@@ -36072,7 +36144,7 @@
       <c r="I380" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J380" s="9" t="s">
+      <c r="J380" s="13" t="s">
         <v>270</v>
       </c>
       <c r="K380" s="6" t="s">
@@ -36135,7 +36207,7 @@
       <c r="I381" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J381" s="9" t="s">
+      <c r="J381" s="13" t="s">
         <v>652</v>
       </c>
       <c r="K381" s="6" t="s">
@@ -36198,7 +36270,7 @@
       <c r="I382" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J382" s="9" t="s">
+      <c r="J382" s="13" t="s">
         <v>652</v>
       </c>
       <c r="K382" s="6" t="s">
@@ -36263,7 +36335,7 @@
       <c r="I383" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J383" s="9" t="s">
+      <c r="J383" s="13" t="s">
         <v>332</v>
       </c>
       <c r="K383" s="6" t="s">
@@ -36328,7 +36400,7 @@
       <c r="I384" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J384" s="9" t="s">
+      <c r="J384" s="13" t="s">
         <v>332</v>
       </c>
       <c r="K384" s="6" t="s">
@@ -36393,7 +36465,7 @@
       <c r="I385" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J385" s="9" t="s">
+      <c r="J385" s="13" t="s">
         <v>332</v>
       </c>
       <c r="K385" s="6" t="s">
@@ -36458,7 +36530,7 @@
       <c r="I386" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J386" s="9" t="s">
+      <c r="J386" s="13" t="s">
         <v>332</v>
       </c>
       <c r="K386" s="6" t="s">
@@ -36523,7 +36595,7 @@
       <c r="I387" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J387" s="9" t="s">
+      <c r="J387" s="13" t="s">
         <v>332</v>
       </c>
       <c r="K387" s="6" t="s">
@@ -36586,7 +36658,7 @@
       <c r="I388" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J388" s="9" t="s">
+      <c r="J388" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K388" s="6" t="s">
@@ -36649,7 +36721,7 @@
       <c r="I389" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J389" s="9" t="s">
+      <c r="J389" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K389" s="6" t="s">
@@ -36712,7 +36784,7 @@
       <c r="I390" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J390" s="9" t="s">
+      <c r="J390" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K390" s="6" t="s">
@@ -36775,7 +36847,7 @@
       <c r="I391" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J391" s="9" t="s">
+      <c r="J391" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K391" s="6" t="s">
@@ -36838,7 +36910,7 @@
       <c r="I392" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J392" s="9" t="s">
+      <c r="J392" s="13" t="s">
         <v>1819</v>
       </c>
       <c r="K392" s="6" t="s">
@@ -36901,7 +36973,7 @@
       <c r="I393" s="6" t="s">
         <v>1829</v>
       </c>
-      <c r="J393" s="9" t="s">
+      <c r="J393" s="13" t="s">
         <v>1830</v>
       </c>
       <c r="K393" s="6" t="s">
@@ -36964,7 +37036,7 @@
       <c r="I394" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J394" s="9" t="s">
+      <c r="J394" s="13" t="s">
         <v>791</v>
       </c>
       <c r="K394" s="6" t="s">
@@ -37027,7 +37099,7 @@
       <c r="I395" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J395" s="9" t="s">
+      <c r="J395" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K395" s="6" t="s">
@@ -37090,7 +37162,7 @@
       <c r="I396" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J396" s="9" t="s">
+      <c r="J396" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K396" s="6" t="s">
@@ -37153,7 +37225,7 @@
       <c r="I397" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J397" s="9" t="s">
+      <c r="J397" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K397" s="6" t="s">
@@ -37216,7 +37288,7 @@
       <c r="I398" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J398" s="9" t="s">
+      <c r="J398" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K398" s="6" t="s">
@@ -37279,7 +37351,7 @@
       <c r="I399" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J399" s="9" t="s">
+      <c r="J399" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K399" s="6" t="s">
@@ -37342,7 +37414,7 @@
       <c r="I400" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J400" s="9" t="s">
+      <c r="J400" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K400" s="6" t="s">
@@ -37405,7 +37477,7 @@
       <c r="I401" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J401" s="9" t="s">
+      <c r="J401" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K401" s="6" t="s">
@@ -37468,7 +37540,7 @@
       <c r="I402" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J402" s="9" t="s">
+      <c r="J402" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K402" s="6" t="s">
@@ -37531,7 +37603,7 @@
       <c r="I403" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J403" s="9" t="s">
+      <c r="J403" s="13" t="s">
         <v>1873</v>
       </c>
       <c r="K403" s="6" t="s">
@@ -37594,7 +37666,7 @@
       <c r="I404" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J404" s="9" t="s">
+      <c r="J404" s="13" t="s">
         <v>1873</v>
       </c>
       <c r="K404" s="6" t="s">
@@ -37657,7 +37729,7 @@
       <c r="I405" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J405" s="9" t="s">
+      <c r="J405" s="13" t="s">
         <v>1886</v>
       </c>
       <c r="K405" s="6" t="s">
@@ -37720,7 +37792,7 @@
       <c r="I406" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J406" s="9" t="s">
+      <c r="J406" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K406" s="6" t="s">
@@ -37783,7 +37855,7 @@
       <c r="I407" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J407" s="9" t="s">
+      <c r="J407" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K407" s="6" t="s">
@@ -37846,7 +37918,7 @@
       <c r="I408" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J408" s="9" t="s">
+      <c r="J408" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K408" s="6" t="s">
@@ -37909,7 +37981,7 @@
       <c r="I409" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J409" s="9" t="s">
+      <c r="J409" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K409" s="6" t="s">
@@ -37972,7 +38044,7 @@
       <c r="I410" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J410" s="9" t="s">
+      <c r="J410" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K410" s="6" t="s">
@@ -38035,7 +38107,7 @@
       <c r="I411" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J411" s="9" t="s">
+      <c r="J411" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K411" s="6" t="s">
@@ -38098,7 +38170,7 @@
       <c r="I412" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J412" s="9" t="s">
+      <c r="J412" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K412" s="6" t="s">
@@ -38161,7 +38233,7 @@
       <c r="I413" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J413" s="9" t="s">
+      <c r="J413" s="13" t="s">
         <v>75</v>
       </c>
       <c r="K413" s="6" t="s">
@@ -38224,7 +38296,7 @@
       <c r="I414" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J414" s="9" t="s">
+      <c r="J414" s="13" t="s">
         <v>75</v>
       </c>
       <c r="K414" s="6" t="s">
@@ -38287,7 +38359,7 @@
       <c r="I415" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J415" s="9" t="s">
+      <c r="J415" s="13" t="s">
         <v>75</v>
       </c>
       <c r="K415" s="6" t="s">
@@ -38350,7 +38422,7 @@
       <c r="I416" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J416" s="9" t="s">
+      <c r="J416" s="13" t="s">
         <v>75</v>
       </c>
       <c r="K416" s="6" t="s">
@@ -38413,7 +38485,7 @@
       <c r="I417" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J417" s="9" t="s">
+      <c r="J417" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K417" s="6" t="s">
@@ -38476,7 +38548,7 @@
       <c r="I418" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J418" s="9" t="s">
+      <c r="J418" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K418" s="6" t="s">
@@ -38539,7 +38611,7 @@
       <c r="I419" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J419" s="9" t="s">
+      <c r="J419" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K419" s="6" t="s">
@@ -38602,7 +38674,7 @@
       <c r="I420" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J420" s="9" t="s">
+      <c r="J420" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K420" s="6" t="s">
@@ -38665,7 +38737,7 @@
       <c r="I421" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J421" s="9" t="s">
+      <c r="J421" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K421" s="6" t="s">
@@ -38728,7 +38800,7 @@
       <c r="I422" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J422" s="9" t="s">
+      <c r="J422" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K422" s="6" t="s">
@@ -38791,7 +38863,7 @@
       <c r="I423" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J423" s="9" t="s">
+      <c r="J423" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K423" s="6" t="s">
@@ -38854,7 +38926,7 @@
       <c r="I424" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J424" s="9" t="s">
+      <c r="J424" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K424" s="6" t="s">
@@ -38917,7 +38989,7 @@
       <c r="I425" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J425" s="9" t="s">
+      <c r="J425" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K425" s="6" t="s">
@@ -38980,7 +39052,7 @@
       <c r="I426" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J426" s="9" t="s">
+      <c r="J426" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K426" s="6" t="s">
@@ -39043,7 +39115,7 @@
       <c r="I427" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J427" s="9" t="s">
+      <c r="J427" s="13" t="s">
         <v>2001</v>
       </c>
       <c r="K427" s="6" t="s">
@@ -39106,7 +39178,7 @@
       <c r="I428" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J428" s="9" t="s">
+      <c r="J428" s="13" t="s">
         <v>2001</v>
       </c>
       <c r="K428" s="6" t="s">
@@ -39169,7 +39241,7 @@
       <c r="I429" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J429" s="9" t="s">
+      <c r="J429" s="13" t="s">
         <v>2001</v>
       </c>
       <c r="K429" s="6" t="s">
@@ -39232,7 +39304,7 @@
       <c r="I430" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J430" s="9" t="s">
+      <c r="J430" s="13" t="s">
         <v>2001</v>
       </c>
       <c r="K430" s="6" t="s">
@@ -39295,7 +39367,7 @@
       <c r="I431" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J431" s="9" t="s">
+      <c r="J431" s="13" t="s">
         <v>2020</v>
       </c>
       <c r="K431" s="6" t="s">
@@ -39358,7 +39430,7 @@
       <c r="I432" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J432" s="9" t="s">
+      <c r="J432" s="13" t="s">
         <v>2020</v>
       </c>
       <c r="K432" s="6" t="s">
@@ -39421,7 +39493,7 @@
       <c r="I433" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J433" s="9" t="s">
+      <c r="J433" s="13" t="s">
         <v>2020</v>
       </c>
       <c r="K433" s="6" t="s">
@@ -39484,7 +39556,7 @@
       <c r="I434" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J434" s="9" t="s">
+      <c r="J434" s="13" t="s">
         <v>2036</v>
       </c>
       <c r="K434" s="6" t="s">
@@ -39547,7 +39619,7 @@
       <c r="I435" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J435" s="9" t="s">
+      <c r="J435" s="13" t="s">
         <v>2036</v>
       </c>
       <c r="K435" s="6" t="s">
@@ -39610,7 +39682,7 @@
       <c r="I436" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J436" s="9" t="s">
+      <c r="J436" s="13" t="s">
         <v>2036</v>
       </c>
       <c r="K436" s="6" t="s">
@@ -39673,7 +39745,7 @@
       <c r="I437" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J437" s="9" t="s">
+      <c r="J437" s="13" t="s">
         <v>652</v>
       </c>
       <c r="K437" s="6" t="s">
@@ -39736,7 +39808,7 @@
       <c r="I438" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J438" s="9" t="s">
+      <c r="J438" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K438" s="6" t="s">
@@ -39799,7 +39871,7 @@
       <c r="I439" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J439" s="9" t="s">
+      <c r="J439" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K439" s="6" t="s">
@@ -39862,7 +39934,7 @@
       <c r="I440" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J440" s="9" t="s">
+      <c r="J440" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K440" s="6" t="s">
@@ -39925,7 +39997,7 @@
       <c r="I441" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J441" s="9" t="s">
+      <c r="J441" s="13" t="s">
         <v>2072</v>
       </c>
       <c r="K441" s="6" t="s">
@@ -39988,7 +40060,7 @@
       <c r="I442" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J442" s="9" t="s">
+      <c r="J442" s="13" t="s">
         <v>2072</v>
       </c>
       <c r="K442" s="6" t="s">
@@ -40051,7 +40123,7 @@
       <c r="I443" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J443" s="9" t="s">
+      <c r="J443" s="13" t="s">
         <v>2072</v>
       </c>
       <c r="K443" s="6" t="s">
@@ -40114,7 +40186,7 @@
       <c r="I444" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J444" s="9" t="s">
+      <c r="J444" s="13" t="s">
         <v>2072</v>
       </c>
       <c r="K444" s="6" t="s">
@@ -40177,7 +40249,7 @@
       <c r="I445" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J445" s="9" t="s">
+      <c r="J445" s="13" t="s">
         <v>2072</v>
       </c>
       <c r="K445" s="6" t="s">
@@ -40240,7 +40312,7 @@
       <c r="I446" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J446" s="9" t="s">
+      <c r="J446" s="13" t="s">
         <v>2072</v>
       </c>
       <c r="K446" s="6" t="s">
@@ -40303,7 +40375,7 @@
       <c r="I447" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J447" s="9" t="s">
+      <c r="J447" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K447" s="6" t="s">
@@ -40366,7 +40438,7 @@
       <c r="I448" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J448" s="9" t="s">
+      <c r="J448" s="13" t="s">
         <v>893</v>
       </c>
       <c r="K448" s="6" t="s">
@@ -40429,7 +40501,7 @@
       <c r="I449" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J449" s="9" t="s">
+      <c r="J449" s="13" t="s">
         <v>1819</v>
       </c>
       <c r="K449" s="6" t="s">
@@ -40492,7 +40564,7 @@
       <c r="I450" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J450" s="9" t="s">
+      <c r="J450" s="13" t="s">
         <v>1819</v>
       </c>
       <c r="K450" s="6" t="s">
@@ -40555,7 +40627,7 @@
       <c r="I451" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J451" s="9" t="s">
+      <c r="J451" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K451" s="6" t="s">
@@ -40618,7 +40690,7 @@
       <c r="I452" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J452" s="9" t="s">
+      <c r="J452" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K452" s="6" t="s">
@@ -40681,7 +40753,7 @@
       <c r="I453" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J453" s="9" t="s">
+      <c r="J453" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K453" s="6" t="s">
@@ -40744,7 +40816,7 @@
       <c r="I454" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J454" s="9" t="s">
+      <c r="J454" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K454" s="6" t="s">
@@ -40807,7 +40879,7 @@
       <c r="I455" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J455" s="9" t="s">
+      <c r="J455" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K455" s="6" t="s">
@@ -40870,7 +40942,7 @@
       <c r="I456" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J456" s="9" t="s">
+      <c r="J456" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K456" s="6" t="s">
@@ -40933,7 +41005,7 @@
       <c r="I457" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J457" s="9" t="s">
+      <c r="J457" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K457" s="6" t="s">
@@ -40996,7 +41068,7 @@
       <c r="I458" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J458" s="9" t="s">
+      <c r="J458" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K458" s="6" t="s">
@@ -41059,7 +41131,7 @@
       <c r="I459" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J459" s="9" t="s">
+      <c r="J459" s="13" t="s">
         <v>135</v>
       </c>
       <c r="K459" s="6" t="s">
@@ -41122,7 +41194,7 @@
       <c r="I460" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J460" s="9" t="s">
+      <c r="J460" s="13" t="s">
         <v>893</v>
       </c>
       <c r="K460" s="6" t="s">
@@ -41185,7 +41257,7 @@
       <c r="I461" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J461" s="9" t="s">
+      <c r="J461" s="13" t="s">
         <v>2161</v>
       </c>
       <c r="K461" s="6" t="s">
@@ -41248,7 +41320,7 @@
       <c r="I462" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J462" s="9" t="s">
+      <c r="J462" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K462" s="6" t="s">
@@ -41311,7 +41383,7 @@
       <c r="I463" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J463" s="9" t="s">
+      <c r="J463" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K463" s="6" t="s">
@@ -41374,7 +41446,7 @@
       <c r="I464" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J464" s="9" t="s">
+      <c r="J464" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K464" s="6" t="s">
@@ -41437,7 +41509,7 @@
       <c r="I465" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J465" s="9" t="s">
+      <c r="J465" s="13" t="s">
         <v>2185</v>
       </c>
       <c r="K465" s="6" t="s">
@@ -41500,7 +41572,7 @@
       <c r="I466" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J466" s="9" t="s">
+      <c r="J466" s="13" t="s">
         <v>2194</v>
       </c>
       <c r="K466" s="6" t="s">
@@ -41563,7 +41635,7 @@
       <c r="I467" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J467" s="9" t="s">
+      <c r="J467" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K467" s="6" t="s">
@@ -41626,7 +41698,7 @@
       <c r="I468" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J468" s="9" t="s">
+      <c r="J468" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K468" s="6" t="s">
@@ -41689,7 +41761,7 @@
       <c r="I469" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J469" s="9" t="s">
+      <c r="J469" s="13" t="s">
         <v>2214</v>
       </c>
       <c r="K469" s="6" t="s">
@@ -41752,7 +41824,7 @@
       <c r="I470" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J470" s="9" t="s">
+      <c r="J470" s="13" t="s">
         <v>2224</v>
       </c>
       <c r="K470" s="6" t="s">
@@ -41815,7 +41887,7 @@
       <c r="I471" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J471" s="9" t="s">
+      <c r="J471" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K471" s="6" t="s">
@@ -41878,7 +41950,7 @@
       <c r="I472" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J472" s="9" t="s">
+      <c r="J472" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K472" s="6" t="s">
@@ -41941,7 +42013,7 @@
       <c r="I473" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J473" s="9" t="s">
+      <c r="J473" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K473" s="6" t="s">
@@ -42004,7 +42076,7 @@
       <c r="I474" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J474" s="9" t="s">
+      <c r="J474" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K474" s="6" t="s">
@@ -42067,7 +42139,7 @@
       <c r="I475" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J475" s="9" t="s">
+      <c r="J475" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K475" s="6" t="s">
@@ -42130,7 +42202,7 @@
       <c r="I476" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J476" s="9" t="s">
+      <c r="J476" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K476" s="6" t="s">
@@ -42193,7 +42265,7 @@
       <c r="I477" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J477" s="9" t="s">
+      <c r="J477" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K477" s="6" t="s">
@@ -42258,7 +42330,7 @@
       <c r="I478" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J478" s="9" t="s">
+      <c r="J478" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K478" s="6" t="s">
@@ -42323,7 +42395,7 @@
       <c r="I479" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J479" s="9" t="s">
+      <c r="J479" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K479" s="6" t="s">
@@ -42388,7 +42460,7 @@
       <c r="I480" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J480" s="9" t="s">
+      <c r="J480" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K480" s="6" t="s">
@@ -42451,7 +42523,7 @@
       <c r="I481" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J481" s="9" t="s">
+      <c r="J481" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K481" s="6" t="s">
@@ -42514,7 +42586,7 @@
       <c r="I482" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J482" s="9" t="s">
+      <c r="J482" s="13" t="s">
         <v>2297</v>
       </c>
       <c r="K482" s="6" t="s">
@@ -42577,7 +42649,7 @@
       <c r="I483" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J483" s="9" t="s">
+      <c r="J483" s="13" t="s">
         <v>2307</v>
       </c>
       <c r="K483" s="6" t="s">
@@ -42640,7 +42712,7 @@
       <c r="I484" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J484" s="9" t="s">
+      <c r="J484" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K484" s="6" t="s">
@@ -42703,7 +42775,7 @@
       <c r="I485" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J485" s="9" t="s">
+      <c r="J485" s="13" t="s">
         <v>448</v>
       </c>
       <c r="K485" s="6" t="s">
@@ -42762,7 +42834,7 @@
       <c r="I486" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J486" s="9" t="s">
+      <c r="J486" s="13" t="s">
         <v>135</v>
       </c>
       <c r="K486" s="6" t="s">
@@ -42825,7 +42897,7 @@
       <c r="I487" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J487" s="9" t="s">
+      <c r="J487" s="13" t="s">
         <v>2333</v>
       </c>
       <c r="K487" s="6" t="s">
@@ -42888,7 +42960,7 @@
       <c r="I488" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J488" s="9" t="s">
+      <c r="J488" s="13" t="s">
         <v>308</v>
       </c>
       <c r="K488" s="6" t="s">
@@ -42951,7 +43023,7 @@
       <c r="I489" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J489" s="9" t="s">
+      <c r="J489" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K489" s="6" t="s">
@@ -43014,7 +43086,7 @@
       <c r="I490" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J490" s="9" t="s">
+      <c r="J490" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K490" s="6" t="s">
@@ -43077,7 +43149,7 @@
       <c r="I491" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J491" s="9" t="s">
+      <c r="J491" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K491" s="6" t="s">
@@ -43140,7 +43212,7 @@
       <c r="I492" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J492" s="9" t="s">
+      <c r="J492" s="13" t="s">
         <v>2001</v>
       </c>
       <c r="K492" s="6" t="s">
@@ -43203,7 +43275,7 @@
       <c r="I493" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J493" s="9" t="s">
+      <c r="J493" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K493" s="6" t="s">
@@ -43266,7 +43338,7 @@
       <c r="I494" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J494" s="9" t="s">
+      <c r="J494" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K494" s="6" t="s">
@@ -43329,7 +43401,7 @@
       <c r="I495" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J495" s="9" t="s">
+      <c r="J495" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K495" s="6" t="s">
@@ -43392,7 +43464,7 @@
       <c r="I496" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J496" s="9" t="s">
+      <c r="J496" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K496" s="6" t="s">
@@ -43455,7 +43527,7 @@
       <c r="I497" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J497" s="9" t="s">
+      <c r="J497" s="13" t="s">
         <v>2399</v>
       </c>
       <c r="K497" s="6" t="s">
@@ -43518,7 +43590,7 @@
       <c r="I498" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J498" s="9" t="s">
+      <c r="J498" s="13" t="s">
         <v>2399</v>
       </c>
       <c r="K498" s="6" t="s">
@@ -43581,7 +43653,7 @@
       <c r="I499" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J499" s="9" t="s">
+      <c r="J499" s="13" t="s">
         <v>2399</v>
       </c>
       <c r="K499" s="6" t="s">
@@ -43644,7 +43716,7 @@
       <c r="I500" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J500" s="9" t="s">
+      <c r="J500" s="13" t="s">
         <v>1873</v>
       </c>
       <c r="K500" s="6" t="s">
@@ -43707,7 +43779,7 @@
       <c r="I501" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J501" s="9" t="s">
+      <c r="J501" s="13" t="s">
         <v>2419</v>
       </c>
       <c r="K501" s="6" t="s">
@@ -43770,7 +43842,7 @@
       <c r="I502" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J502" s="9" t="s">
+      <c r="J502" s="13" t="s">
         <v>2419</v>
       </c>
       <c r="K502" s="6" t="s">
@@ -43833,7 +43905,7 @@
       <c r="I503" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J503" s="9" t="s">
+      <c r="J503" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K503" s="6" t="s">
@@ -43896,7 +43968,7 @@
       <c r="I504" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J504" s="9" t="s">
+      <c r="J504" s="13" t="s">
         <v>2433</v>
       </c>
       <c r="K504" s="6" t="s">
@@ -43959,7 +44031,7 @@
       <c r="I505" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J505" s="9" t="s">
+      <c r="J505" s="13" t="s">
         <v>2433</v>
       </c>
       <c r="K505" s="6" t="s">
@@ -44022,7 +44094,7 @@
       <c r="I506" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J506" s="9" t="s">
+      <c r="J506" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K506" s="6" t="s">
@@ -44085,7 +44157,7 @@
       <c r="I507" s="6" t="s">
         <v>2453</v>
       </c>
-      <c r="J507" s="9" t="s">
+      <c r="J507" s="13" t="s">
         <v>2214</v>
       </c>
       <c r="K507" s="6" t="s">
@@ -44148,7 +44220,7 @@
       <c r="I508" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J508" s="9" t="s">
+      <c r="J508" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K508" s="6" t="s">
@@ -44211,7 +44283,7 @@
       <c r="I509" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J509" s="9" t="s">
+      <c r="J509" s="13" t="s">
         <v>2185</v>
       </c>
       <c r="K509" s="6" t="s">
@@ -44274,7 +44346,7 @@
       <c r="I510" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J510" s="9" t="s">
+      <c r="J510" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K510" s="6" t="s">
@@ -44337,7 +44409,7 @@
       <c r="I511" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J511" s="9" t="s">
+      <c r="J511" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K511" s="6" t="s">
@@ -44400,7 +44472,7 @@
       <c r="I512" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J512" s="9" t="s">
+      <c r="J512" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K512" s="6" t="s">
@@ -44463,7 +44535,7 @@
       <c r="I513" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J513" s="9" t="s">
+      <c r="J513" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K513" s="6" t="s">
@@ -44526,7 +44598,7 @@
       <c r="I514" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J514" s="9" t="s">
+      <c r="J514" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K514" s="6" t="s">
@@ -44589,7 +44661,7 @@
       <c r="I515" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J515" s="9" t="s">
+      <c r="J515" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K515" s="6" t="s">
@@ -44652,7 +44724,7 @@
       <c r="I516" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J516" s="9" t="s">
+      <c r="J516" s="13" t="s">
         <v>2001</v>
       </c>
       <c r="K516" s="6" t="s">
@@ -44715,7 +44787,7 @@
       <c r="I517" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J517" s="9" t="s">
+      <c r="J517" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K517" s="6" t="s">
@@ -44778,7 +44850,7 @@
       <c r="I518" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J518" s="9" t="s">
+      <c r="J518" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K518" s="6" t="s">
@@ -44841,7 +44913,7 @@
       <c r="I519" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J519" s="9" t="s">
+      <c r="J519" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K519" s="6" t="s">
@@ -44904,7 +44976,7 @@
       <c r="I520" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J520" s="9" t="s">
+      <c r="J520" s="13" t="s">
         <v>351</v>
       </c>
       <c r="K520" s="6" t="s">
@@ -44967,7 +45039,7 @@
       <c r="I521" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J521" s="9" t="s">
+      <c r="J521" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K521" s="6" t="s">
@@ -45030,7 +45102,7 @@
       <c r="I522" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J522" s="9" t="s">
+      <c r="J522" s="13" t="s">
         <v>100</v>
       </c>
       <c r="K522" s="6" t="s">
@@ -45093,7 +45165,7 @@
       <c r="I523" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J523" s="9" t="s">
+      <c r="J523" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K523" s="6" t="s">
@@ -45156,7 +45228,7 @@
       <c r="I524" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J524" s="9" t="s">
+      <c r="J524" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K524" s="6" t="s">
@@ -45219,7 +45291,7 @@
       <c r="I525" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J525" s="9" t="s">
+      <c r="J525" s="13" t="s">
         <v>2535</v>
       </c>
       <c r="K525" s="6" t="s">
@@ -45282,7 +45354,7 @@
       <c r="I526" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J526" s="9" t="s">
+      <c r="J526" s="13" t="s">
         <v>1886</v>
       </c>
       <c r="K526" s="6" t="s">
@@ -45345,7 +45417,7 @@
       <c r="I527" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J527" s="9" t="s">
+      <c r="J527" s="13" t="s">
         <v>1819</v>
       </c>
       <c r="K527" s="6" t="s">
@@ -45408,7 +45480,7 @@
       <c r="I528" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J528" s="9" t="s">
+      <c r="J528" s="13" t="s">
         <v>2560</v>
       </c>
       <c r="K528" s="6" t="s">
@@ -45471,7 +45543,7 @@
       <c r="I529" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J529" s="9" t="s">
+      <c r="J529" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K529" s="6" t="s">
@@ -45534,7 +45606,7 @@
       <c r="I530" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J530" s="9" t="s">
+      <c r="J530" s="13" t="s">
         <v>75</v>
       </c>
       <c r="K530" s="6" t="s">
@@ -45597,7 +45669,7 @@
       <c r="I531" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J531" s="9" t="s">
+      <c r="J531" s="13" t="s">
         <v>75</v>
       </c>
       <c r="K531" s="6" t="s">
@@ -45660,7 +45732,7 @@
       <c r="I532" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J532" s="9" t="s">
+      <c r="J532" s="13" t="s">
         <v>2072</v>
       </c>
       <c r="K532" s="6" t="s">
@@ -45723,7 +45795,7 @@
       <c r="I533" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J533" s="9" t="s">
+      <c r="J533" s="13" t="s">
         <v>2582</v>
       </c>
       <c r="K533" s="6" t="s">
@@ -45786,7 +45858,7 @@
       <c r="I534" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J534" s="9" t="s">
+      <c r="J534" s="13" t="s">
         <v>903</v>
       </c>
       <c r="K534" s="6" t="s">
@@ -45849,7 +45921,7 @@
       <c r="I535" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J535" s="9" t="s">
+      <c r="J535" s="13" t="s">
         <v>308</v>
       </c>
       <c r="K535" s="6" t="s">
@@ -45912,7 +45984,7 @@
       <c r="I536" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J536" s="9" t="s">
+      <c r="J536" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K536" s="6" t="s">
@@ -45975,7 +46047,7 @@
       <c r="I537" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J537" s="9" t="s">
+      <c r="J537" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K537" s="6" t="s">
@@ -46038,7 +46110,7 @@
       <c r="I538" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J538" s="9" t="s">
+      <c r="J538" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K538" s="6" t="s">
@@ -46101,7 +46173,7 @@
       <c r="I539" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J539" s="9" t="s">
+      <c r="J539" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K539" s="6" t="s">
@@ -46164,7 +46236,7 @@
       <c r="I540" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J540" s="9" t="s">
+      <c r="J540" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K540" s="6" t="s">
@@ -46227,7 +46299,7 @@
       <c r="I541" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J541" s="9" t="s">
+      <c r="J541" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K541" s="6" t="s">
@@ -46290,7 +46362,7 @@
       <c r="I542" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J542" s="9" t="s">
+      <c r="J542" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K542" s="6" t="s">
@@ -46353,7 +46425,7 @@
       <c r="I543" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J543" s="9" t="s">
+      <c r="J543" s="13" t="s">
         <v>2001</v>
       </c>
       <c r="K543" s="6" t="s">
@@ -46416,7 +46488,7 @@
       <c r="I544" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J544" s="9" t="s">
+      <c r="J544" s="13" t="s">
         <v>2036</v>
       </c>
       <c r="K544" s="6" t="s">
@@ -46479,7 +46551,7 @@
       <c r="I545" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J545" s="9" t="s">
+      <c r="J545" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K545" s="6" t="s">
@@ -46542,7 +46614,7 @@
       <c r="I546" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J546" s="9" t="s">
+      <c r="J546" s="13" t="s">
         <v>2634</v>
       </c>
       <c r="K546" s="6" t="s">
@@ -46605,7 +46677,7 @@
       <c r="I547" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J547" s="9" t="s">
+      <c r="J547" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K547" s="6" t="s">
@@ -46668,7 +46740,7 @@
       <c r="I548" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J548" s="9" t="s">
+      <c r="J548" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K548" s="6" t="s">
@@ -46731,7 +46803,7 @@
       <c r="I549" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J549" s="9" t="s">
+      <c r="J549" s="13" t="s">
         <v>376</v>
       </c>
       <c r="K549" s="6" t="s">
@@ -46792,7 +46864,7 @@
       <c r="I550" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J550" s="9" t="s">
+      <c r="J550" s="13" t="s">
         <v>2297</v>
       </c>
       <c r="K550" s="6" t="s">
@@ -46855,7 +46927,7 @@
       <c r="I551" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J551" s="9" t="s">
+      <c r="J551" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K551" s="6" t="s">
@@ -46918,7 +46990,7 @@
       <c r="I552" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J552" s="9" t="s">
+      <c r="J552" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K552" s="6" t="s">
@@ -46981,7 +47053,7 @@
       <c r="I553" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J553" s="9" t="s">
+      <c r="J553" s="13" t="s">
         <v>126</v>
       </c>
       <c r="K553" s="6" t="s">
@@ -47044,7 +47116,7 @@
       <c r="I554" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J554" s="9" t="s">
+      <c r="J554" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K554" s="6" t="s">
@@ -47107,7 +47179,7 @@
       <c r="I555" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J555" s="9" t="s">
+      <c r="J555" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K555" s="6" t="s">
@@ -47170,7 +47242,7 @@
       <c r="I556" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J556" s="9" t="s">
+      <c r="J556" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K556" s="6" t="s">
@@ -47233,7 +47305,7 @@
       <c r="I557" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J557" s="9" t="s">
+      <c r="J557" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K557" s="6" t="s">
@@ -47296,7 +47368,7 @@
       <c r="I558" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J558" s="9" t="s">
+      <c r="J558" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K558" s="6" t="s">
@@ -47359,7 +47431,7 @@
       <c r="I559" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J559" s="9" t="s">
+      <c r="J559" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K559" s="6" t="s">
@@ -47422,7 +47494,7 @@
       <c r="I560" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J560" s="9" t="s">
+      <c r="J560" s="13" t="s">
         <v>2634</v>
       </c>
       <c r="K560" s="6" t="s">
@@ -47485,7 +47557,7 @@
       <c r="I561" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J561" s="9" t="s">
+      <c r="J561" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K561" s="6" t="s">
@@ -47540,7 +47612,7 @@
       <c r="I562" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J562" s="9" t="s">
+      <c r="J562" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K562" s="6" t="s">
@@ -47595,7 +47667,7 @@
       <c r="I563" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J563" s="9" t="s">
+      <c r="J563" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K563" s="6" t="s">
@@ -47650,7 +47722,7 @@
       <c r="I564" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J564" s="9" t="s">
+      <c r="J564" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K564" s="6" t="s">
@@ -47703,7 +47775,7 @@
       <c r="I565" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J565" s="9" t="s">
+      <c r="J565" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K565" s="6" t="s">
@@ -47766,7 +47838,7 @@
       <c r="I566" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J566" s="9" t="s">
+      <c r="J566" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K566" s="6" t="s">
@@ -47821,7 +47893,7 @@
       <c r="I567" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J567" s="9" t="s">
+      <c r="J567" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K567" s="6" t="s">
@@ -47876,7 +47948,7 @@
       <c r="I568" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J568" s="9" t="s">
+      <c r="J568" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K568" s="6" t="s">
@@ -47931,7 +48003,7 @@
       <c r="I569" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J569" s="9" t="s">
+      <c r="J569" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K569" s="6" t="s">
@@ -47986,7 +48058,7 @@
       <c r="I570" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J570" s="9" t="s">
+      <c r="J570" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K570" s="6" t="s">
@@ -48041,7 +48113,7 @@
       <c r="I571" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J571" s="9" t="s">
+      <c r="J571" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K571" s="6" t="s">
@@ -48096,7 +48168,7 @@
       <c r="I572" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J572" s="9" t="s">
+      <c r="J572" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K572" s="6" t="s">
@@ -48151,7 +48223,7 @@
       <c r="I573" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J573" s="9" t="s">
+      <c r="J573" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K573" s="6" t="s">
@@ -48206,7 +48278,7 @@
       <c r="I574" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J574" s="9" t="s">
+      <c r="J574" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K574" s="6" t="s">
@@ -48261,7 +48333,7 @@
       <c r="I575" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J575" s="9" t="s">
+      <c r="J575" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K575" s="6" t="s">
@@ -48318,7 +48390,7 @@
       <c r="I576" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J576" s="9" t="s">
+      <c r="J576" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K576" s="6" t="s">
@@ -48381,7 +48453,7 @@
       <c r="I577" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J577" s="9" t="s">
+      <c r="J577" s="13" t="s">
         <v>903</v>
       </c>
       <c r="K577" s="6" t="s">
@@ -48446,7 +48518,7 @@
       <c r="I578" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J578" s="9" t="s">
+      <c r="J578" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K578" s="6" t="s">
@@ -48507,7 +48579,7 @@
       <c r="I579" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J579" s="9" t="s">
+      <c r="J579" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K579" s="6" t="s">
@@ -48568,7 +48640,7 @@
       <c r="I580" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J580" s="9" t="s">
+      <c r="J580" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K580" s="6" t="s">
@@ -48633,7 +48705,7 @@
       <c r="I581" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J581" s="9" t="s">
+      <c r="J581" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K581" s="6" t="s">
@@ -48698,7 +48770,7 @@
       <c r="I582" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J582" s="9" t="s">
+      <c r="J582" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K582" s="6" t="s">
@@ -48755,7 +48827,7 @@
       <c r="I583" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J583" s="9" t="s">
+      <c r="J583" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K583" s="6" t="s">
@@ -48818,7 +48890,7 @@
       <c r="I584" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J584" s="9" t="s">
+      <c r="J584" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K584" s="6" t="s">
@@ -48879,7 +48951,7 @@
       <c r="I585" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J585" s="9" t="s">
+      <c r="J585" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K585" s="6" t="s">
@@ -48942,7 +49014,7 @@
       <c r="I586" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J586" s="9" t="s">
+      <c r="J586" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K586" s="6" t="s">
@@ -49003,7 +49075,7 @@
       <c r="I587" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J587" s="9" t="s">
+      <c r="J587" s="13" t="s">
         <v>781</v>
       </c>
       <c r="K587" s="6" t="s">
@@ -49066,7 +49138,7 @@
       <c r="I588" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J588" s="9" t="s">
+      <c r="J588" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K588" s="6" t="s">
@@ -49129,7 +49201,7 @@
       <c r="I589" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J589" s="9" t="s">
+      <c r="J589" s="13" t="s">
         <v>2634</v>
       </c>
       <c r="K589" s="6" t="s">
@@ -49190,7 +49262,7 @@
       <c r="I590" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J590" s="9" t="s">
+      <c r="J590" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K590" s="6" t="s">
@@ -49251,7 +49323,7 @@
       <c r="I591" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J591" s="9" t="s">
+      <c r="J591" s="13" t="s">
         <v>2805</v>
       </c>
       <c r="K591" s="6" t="s">
@@ -49312,7 +49384,7 @@
       <c r="I592" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J592" s="9" t="s">
+      <c r="J592" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K592" s="6" t="s">
@@ -49373,7 +49445,7 @@
       <c r="I593" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J593" s="9" t="s">
+      <c r="J593" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K593" s="6" t="s">
@@ -49434,7 +49506,7 @@
       <c r="I594" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J594" s="9" t="s">
+      <c r="J594" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K594" s="6" t="s">
@@ -49499,7 +49571,7 @@
       <c r="I595" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J595" s="9" t="s">
+      <c r="J595" s="13" t="s">
         <v>2820</v>
       </c>
       <c r="K595" s="6" t="s">
@@ -49560,7 +49632,7 @@
       <c r="I596" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J596" s="9" t="s">
+      <c r="J596" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K596" s="6" t="s">
@@ -49623,7 +49695,7 @@
       <c r="I597" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J597" s="9" t="s">
+      <c r="J597" s="13" t="s">
         <v>2833</v>
       </c>
       <c r="K597" s="6" t="s">
@@ -49688,7 +49760,7 @@
       <c r="I598" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J598" s="9" t="s">
+      <c r="J598" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K598" s="6" t="s">
@@ -49749,7 +49821,7 @@
       <c r="I599" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J599" s="9" t="s">
+      <c r="J599" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K599" s="6" t="s">
@@ -49812,7 +49884,7 @@
       <c r="I600" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J600" s="9" t="s">
+      <c r="J600" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K600" s="6" t="s">
@@ -49877,7 +49949,7 @@
       <c r="I601" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J601" s="9" t="s">
+      <c r="J601" s="13" t="s">
         <v>89</v>
       </c>
       <c r="K601" s="6" t="s">
@@ -49942,7 +50014,7 @@
       <c r="I602" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J602" s="9" t="s">
+      <c r="J602" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K602" s="6" t="s">
@@ -49995,7 +50067,7 @@
       <c r="I603" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J603" s="9" t="s">
+      <c r="J603" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K603" s="6" t="s">
@@ -50048,7 +50120,7 @@
       <c r="I604" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J604" s="9" t="s">
+      <c r="J604" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K604" s="6" t="s">
@@ -50101,7 +50173,7 @@
       <c r="I605" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J605" s="9" t="s">
+      <c r="J605" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K605" s="6" t="s">
@@ -50166,7 +50238,7 @@
       <c r="I606" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J606" s="9" t="s">
+      <c r="J606" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K606" s="6" t="s">
@@ -50223,7 +50295,7 @@
       <c r="I607" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J607" s="9" t="s">
+      <c r="J607" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K607" s="6" t="s">
@@ -50276,7 +50348,7 @@
       <c r="I608" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J608" s="9" t="s">
+      <c r="J608" s="13" t="s">
         <v>2882</v>
       </c>
       <c r="K608" s="6" t="s">
@@ -50341,7 +50413,7 @@
       <c r="I609" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J609" s="9" t="s">
+      <c r="J609" s="13" t="s">
         <v>2399</v>
       </c>
       <c r="K609" s="6" t="s">
@@ -50382,7 +50454,7 @@
       <c r="I610" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J610" s="9" t="s">
+      <c r="J610" s="13" t="s">
         <v>2896</v>
       </c>
       <c r="K610" s="6" t="s">
@@ -50447,7 +50519,7 @@
       <c r="I611" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J611" s="9" t="s">
+      <c r="J611" s="13" t="s">
         <v>2896</v>
       </c>
       <c r="K611" s="6" t="s">
@@ -50512,7 +50584,7 @@
       <c r="I612" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J612" s="9" t="s">
+      <c r="J612" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K612" s="6" t="s">
@@ -50573,7 +50645,7 @@
       <c r="I613" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J613" s="9" t="s">
+      <c r="J613" s="13" t="s">
         <v>893</v>
       </c>
       <c r="K613" s="6" t="s">
@@ -50634,7 +50706,7 @@
       <c r="I614" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J614" s="9" t="s">
+      <c r="J614" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K614" s="6" t="s">
@@ -50695,7 +50767,7 @@
       <c r="I615" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J615" s="9" t="s">
+      <c r="J615" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K615" s="6" t="s">
@@ -50760,7 +50832,7 @@
       <c r="I616" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J616" s="9" t="s">
+      <c r="J616" s="13" t="s">
         <v>2820</v>
       </c>
       <c r="K616" s="6" t="s">
@@ -50825,7 +50897,7 @@
       <c r="I617" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J617" s="9" t="s">
+      <c r="J617" s="13" t="s">
         <v>2941</v>
       </c>
       <c r="K617" s="6" t="s">
@@ -50890,7 +50962,7 @@
       <c r="I618" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J618" s="9" t="s">
+      <c r="J618" s="13" t="s">
         <v>814</v>
       </c>
       <c r="K618" s="6" t="s">
@@ -50955,7 +51027,7 @@
       <c r="I619" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J619" s="9" t="s">
+      <c r="J619" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K619" s="6" t="s">
@@ -51020,7 +51092,7 @@
       <c r="I620" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J620" s="9" t="s">
+      <c r="J620" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K620" s="6" t="s">
@@ -51085,7 +51157,7 @@
       <c r="I621" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J621" s="9" t="s">
+      <c r="J621" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K621" s="6" t="s">
@@ -51150,7 +51222,7 @@
       <c r="I622" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J622" s="9" t="s">
+      <c r="J622" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K622" s="6" t="s">
@@ -51215,7 +51287,7 @@
       <c r="I623" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J623" s="9" t="s">
+      <c r="J623" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K623" s="6" t="s">
@@ -51280,7 +51352,7 @@
       <c r="I624" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J624" s="9" t="s">
+      <c r="J624" s="13" t="s">
         <v>89</v>
       </c>
       <c r="K624" s="6" t="s">
@@ -51345,7 +51417,7 @@
       <c r="I625" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J625" s="9" t="s">
+      <c r="J625" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K625" s="6" t="s">
@@ -51410,7 +51482,7 @@
       <c r="I626" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J626" s="9" t="s">
+      <c r="J626" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K626" s="6" t="s">
@@ -51473,7 +51545,7 @@
       <c r="I627" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J627" s="9" t="s">
+      <c r="J627" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K627" s="6" t="s">
@@ -51536,7 +51608,7 @@
       <c r="I628" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J628" s="9" t="s">
+      <c r="J628" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K628" s="6" t="s">
@@ -51601,7 +51673,7 @@
       <c r="I629" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J629" s="9" t="s">
+      <c r="J629" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K629" s="6" t="s">
@@ -51660,7 +51732,7 @@
       <c r="G630" s="5"/>
       <c r="H630" s="5"/>
       <c r="I630" s="5"/>
-      <c r="J630" s="9"/>
+      <c r="J630" s="13"/>
       <c r="K630" s="6" t="s">
         <v>800</v>
       </c>
@@ -51705,7 +51777,7 @@
       <c r="G631" s="5"/>
       <c r="H631" s="5"/>
       <c r="I631" s="5"/>
-      <c r="J631" s="9"/>
+      <c r="J631" s="13"/>
       <c r="K631" s="6" t="s">
         <v>800</v>
       </c>
@@ -51750,7 +51822,7 @@
       <c r="G632" s="5"/>
       <c r="H632" s="5"/>
       <c r="I632" s="5"/>
-      <c r="J632" s="9"/>
+      <c r="J632" s="13"/>
       <c r="K632" s="6" t="s">
         <v>800</v>
       </c>
@@ -51795,7 +51867,7 @@
       <c r="G633" s="5"/>
       <c r="H633" s="5"/>
       <c r="I633" s="5"/>
-      <c r="J633" s="9"/>
+      <c r="J633" s="13"/>
       <c r="K633" s="6" t="s">
         <v>800</v>
       </c>
@@ -51840,7 +51912,7 @@
       <c r="G634" s="5"/>
       <c r="H634" s="5"/>
       <c r="I634" s="5"/>
-      <c r="J634" s="9"/>
+      <c r="J634" s="13"/>
       <c r="K634" s="6" t="s">
         <v>800</v>
       </c>
@@ -51885,7 +51957,7 @@
       <c r="G635" s="5"/>
       <c r="H635" s="5"/>
       <c r="I635" s="5"/>
-      <c r="J635" s="9"/>
+      <c r="J635" s="13"/>
       <c r="K635" s="6" t="s">
         <v>800</v>
       </c>
@@ -51936,7 +52008,7 @@
       <c r="I636" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J636" s="9" t="s">
+      <c r="J636" s="13" t="s">
         <v>2535</v>
       </c>
       <c r="K636" s="6" t="s">
@@ -52001,7 +52073,7 @@
       <c r="I637" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J637" s="9" t="s">
+      <c r="J637" s="13" t="s">
         <v>2001</v>
       </c>
       <c r="K637" s="6" t="s">
@@ -52054,7 +52126,7 @@
       <c r="I638" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J638" s="9" t="s">
+      <c r="J638" s="13" t="s">
         <v>2001</v>
       </c>
       <c r="K638" s="6" t="s">
@@ -52107,7 +52179,7 @@
       <c r="I639" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J639" s="9" t="s">
+      <c r="J639" s="13" t="s">
         <v>3032</v>
       </c>
       <c r="K639" s="6" t="s">
@@ -52172,7 +52244,7 @@
       <c r="I640" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J640" s="9" t="s">
+      <c r="J640" s="13" t="s">
         <v>2161</v>
       </c>
       <c r="K640" s="6" t="s">
@@ -52237,7 +52309,7 @@
       <c r="I641" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J641" s="9" t="s">
+      <c r="J641" s="13" t="s">
         <v>2297</v>
       </c>
       <c r="K641" s="6" t="s">
@@ -52302,7 +52374,7 @@
       <c r="I642" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J642" s="9" t="s">
+      <c r="J642" s="13" t="s">
         <v>2297</v>
       </c>
       <c r="K642" s="6" t="s">
@@ -52367,7 +52439,7 @@
       <c r="I643" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J643" s="9" t="s">
+      <c r="J643" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K643" s="6" t="s">
@@ -52424,7 +52496,7 @@
       <c r="I644" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J644" s="9" t="s">
+      <c r="J644" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K644" s="6" t="s">
@@ -52481,7 +52553,7 @@
       <c r="I645" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J645" s="9" t="s">
+      <c r="J645" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K645" s="6" t="s">
@@ -52546,7 +52618,7 @@
       <c r="I646" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J646" s="9" t="s">
+      <c r="J646" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K646" s="6" t="s">
@@ -52611,7 +52683,7 @@
       <c r="I647" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J647" s="9" t="s">
+      <c r="J647" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K647" s="6" t="s">
@@ -52676,7 +52748,7 @@
       <c r="I648" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J648" s="9" t="s">
+      <c r="J648" s="13" t="s">
         <v>2194</v>
       </c>
       <c r="K648" s="6" t="s">
@@ -52741,7 +52813,7 @@
       <c r="I649" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J649" s="9" t="s">
+      <c r="J649" s="13" t="s">
         <v>2194</v>
       </c>
       <c r="K649" s="6" t="s">
@@ -52806,7 +52878,7 @@
       <c r="I650" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J650" s="9" t="s">
+      <c r="J650" s="13" t="s">
         <v>2194</v>
       </c>
       <c r="K650" s="6" t="s">
@@ -52871,7 +52943,7 @@
       <c r="I651" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J651" s="9" t="s">
+      <c r="J651" s="13" t="s">
         <v>3032</v>
       </c>
       <c r="K651" s="6" t="s">
@@ -52928,7 +53000,7 @@
       <c r="I652" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J652" s="9" t="s">
+      <c r="J652" s="13" t="s">
         <v>2020</v>
       </c>
       <c r="K652" s="6" t="s">
@@ -52985,7 +53057,7 @@
       <c r="I653" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J653" s="9" t="s">
+      <c r="J653" s="13" t="s">
         <v>2560</v>
       </c>
       <c r="K653" s="6" t="s">
@@ -53040,7 +53112,7 @@
       <c r="I654" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J654" s="9" t="s">
+      <c r="J654" s="13" t="s">
         <v>3105</v>
       </c>
       <c r="K654" s="6" t="s">
@@ -53103,7 +53175,7 @@
       <c r="I655" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J655" s="9" t="s">
+      <c r="J655" s="13" t="s">
         <v>3105</v>
       </c>
       <c r="K655" s="6" t="s">
@@ -53166,7 +53238,7 @@
       <c r="I656" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J656" s="9" t="s">
+      <c r="J656" s="13" t="s">
         <v>3105</v>
       </c>
       <c r="K656" s="6" t="s">
@@ -53231,7 +53303,7 @@
       <c r="I657" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J657" s="9" t="s">
+      <c r="J657" s="13" t="s">
         <v>3118</v>
       </c>
       <c r="K657" s="6" t="s">
@@ -53296,7 +53368,7 @@
       <c r="I658" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J658" s="9" t="s">
+      <c r="J658" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K658" s="6" t="s">
@@ -53353,7 +53425,7 @@
       <c r="I659" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J659" s="9" t="s">
+      <c r="J659" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K659" s="6" t="s">
@@ -53410,7 +53482,7 @@
       <c r="I660" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J660" s="9" t="s">
+      <c r="J660" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K660" s="6" t="s">
@@ -53467,7 +53539,7 @@
       <c r="I661" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J661" s="9" t="s">
+      <c r="J661" s="13" t="s">
         <v>2896</v>
       </c>
       <c r="K661" s="6" t="s">
@@ -53532,7 +53604,7 @@
       <c r="I662" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J662" s="9" t="s">
+      <c r="J662" s="13" t="s">
         <v>2896</v>
       </c>
       <c r="K662" s="6" t="s">
@@ -53597,7 +53669,7 @@
       <c r="I663" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J663" s="9" t="s">
+      <c r="J663" s="13" t="s">
         <v>2307</v>
       </c>
       <c r="K663" s="6" t="s">
@@ -53654,7 +53726,7 @@
       <c r="I664" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J664" s="9" t="s">
+      <c r="J664" s="13" t="s">
         <v>1886</v>
       </c>
       <c r="K664" s="6" t="s">
@@ -53711,7 +53783,7 @@
       <c r="I665" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J665" s="9" t="s">
+      <c r="J665" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K665" s="6" t="s">
@@ -53768,7 +53840,7 @@
       <c r="I666" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J666" s="9" t="s">
+      <c r="J666" s="13" t="s">
         <v>3159</v>
       </c>
       <c r="K666" s="6" t="s">
@@ -53825,7 +53897,7 @@
       <c r="I667" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J667" s="9" t="s">
+      <c r="J667" s="13" t="s">
         <v>3159</v>
       </c>
       <c r="K667" s="6" t="s">
@@ -53882,7 +53954,7 @@
       <c r="I668" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J668" s="9" t="s">
+      <c r="J668" s="13" t="s">
         <v>3159</v>
       </c>
       <c r="K668" s="6" t="s">
@@ -53939,7 +54011,7 @@
       <c r="I669" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J669" s="9" t="s">
+      <c r="J669" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K669" s="6" t="s">
@@ -53996,7 +54068,7 @@
       <c r="I670" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J670" s="9" t="s">
+      <c r="J670" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K670" s="6" t="s">
@@ -54053,7 +54125,7 @@
       <c r="I671" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J671" s="9" t="s">
+      <c r="J671" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K671" s="6" t="s">
@@ -54110,7 +54182,7 @@
       <c r="I672" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J672" s="9" t="s">
+      <c r="J672" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K672" s="6" t="s">
@@ -54167,7 +54239,7 @@
       <c r="I673" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J673" s="9" t="s">
+      <c r="J673" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K673" s="6" t="s">
@@ -54224,7 +54296,7 @@
       <c r="I674" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J674" s="9" t="s">
+      <c r="J674" s="13" t="s">
         <v>2399</v>
       </c>
       <c r="K674" s="6" t="s">
@@ -54281,7 +54353,7 @@
       <c r="I675" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J675" s="9" t="s">
+      <c r="J675" s="13" t="s">
         <v>2399</v>
       </c>
       <c r="K675" s="6" t="s">
@@ -54338,7 +54410,7 @@
       <c r="I676" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J676" s="9" t="s">
+      <c r="J676" s="13" t="s">
         <v>2399</v>
       </c>
       <c r="K676" s="6" t="s">
@@ -54395,7 +54467,7 @@
       <c r="I677" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J677" s="9" t="s">
+      <c r="J677" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K677" s="6" t="s">
@@ -54452,7 +54524,7 @@
       <c r="I678" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J678" s="9" t="s">
+      <c r="J678" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K678" s="6" t="s">
@@ -54507,7 +54579,7 @@
       <c r="I679" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J679" s="9" t="s">
+      <c r="J679" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K679" s="6" t="s">
@@ -54570,7 +54642,7 @@
       <c r="I680" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J680" s="9" t="s">
+      <c r="J680" s="13" t="s">
         <v>625</v>
       </c>
       <c r="K680" s="6" t="s">
@@ -54635,7 +54707,7 @@
       <c r="I681" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J681" s="9" t="s">
+      <c r="J681" s="13" t="s">
         <v>903</v>
       </c>
       <c r="K681" s="6" t="s">
@@ -54692,7 +54764,7 @@
       <c r="I682" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J682" s="9" t="s">
+      <c r="J682" s="13" t="s">
         <v>903</v>
       </c>
       <c r="K682" s="6" t="s">
@@ -54747,7 +54819,7 @@
       <c r="I683" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J683" s="9" t="s">
+      <c r="J683" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K683" s="6" t="s">
@@ -54810,7 +54882,7 @@
       <c r="I684" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J684" s="9" t="s">
+      <c r="J684" s="13" t="s">
         <v>351</v>
       </c>
       <c r="K684" s="6" t="s">
@@ -54875,7 +54947,7 @@
       <c r="I685" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J685" s="9" t="s">
+      <c r="J685" s="13" t="s">
         <v>210</v>
       </c>
       <c r="K685" s="6" t="s">
@@ -54940,7 +55012,7 @@
       <c r="I686" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J686" s="9" t="s">
+      <c r="J686" s="13" t="s">
         <v>210</v>
       </c>
       <c r="K686" s="6" t="s">
@@ -55005,7 +55077,7 @@
       <c r="I687" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J687" s="9" t="s">
+      <c r="J687" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K687" s="6" t="s">
@@ -55070,7 +55142,7 @@
       <c r="I688" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J688" s="9" t="s">
+      <c r="J688" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K688" s="6" t="s">
@@ -55135,7 +55207,7 @@
       <c r="I689" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J689" s="9" t="s">
+      <c r="J689" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K689" s="6" t="s">
@@ -55200,7 +55272,7 @@
       <c r="I690" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J690" s="9" t="s">
+      <c r="J690" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K690" s="6" t="s">
@@ -55265,7 +55337,7 @@
       <c r="I691" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J691" s="9" t="s">
+      <c r="J691" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K691" s="6" t="s">
@@ -55330,7 +55402,7 @@
       <c r="I692" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J692" s="9" t="s">
+      <c r="J692" s="13" t="s">
         <v>814</v>
       </c>
       <c r="K692" s="6" t="s">
@@ -55391,7 +55463,7 @@
       <c r="I693" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J693" s="9" t="s">
+      <c r="J693" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K693" s="6" t="s">
@@ -55452,7 +55524,7 @@
       <c r="I694" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J694" s="9" t="s">
+      <c r="J694" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K694" s="6" t="s">
@@ -55513,7 +55585,7 @@
       <c r="I695" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J695" s="9" t="s">
+      <c r="J695" s="13" t="s">
         <v>893</v>
       </c>
       <c r="K695" s="6" t="s">
@@ -55574,7 +55646,7 @@
       <c r="I696" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J696" s="9" t="s">
+      <c r="J696" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K696" s="6" t="s">
@@ -55635,7 +55707,7 @@
       <c r="I697" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J697" s="9" t="s">
+      <c r="J697" s="13" t="s">
         <v>652</v>
       </c>
       <c r="K697" s="6" t="s">
@@ -55696,7 +55768,7 @@
       <c r="I698" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J698" s="9" t="s">
+      <c r="J698" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K698" s="6" t="s">
@@ -55761,7 +55833,7 @@
       <c r="I699" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J699" s="9" t="s">
+      <c r="J699" s="13" t="s">
         <v>3273</v>
       </c>
       <c r="K699" s="6" t="s">
@@ -55826,7 +55898,7 @@
       <c r="I700" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J700" s="9" t="s">
+      <c r="J700" s="13" t="s">
         <v>3118</v>
       </c>
       <c r="K700" s="6" t="s">
@@ -55879,7 +55951,7 @@
       <c r="I701" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J701" s="9" t="s">
+      <c r="J701" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K701" s="6" t="s">
@@ -55944,7 +56016,7 @@
       <c r="I702" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J702" s="9" t="s">
+      <c r="J702" s="13" t="s">
         <v>3289</v>
       </c>
       <c r="K702" s="6" t="s">
@@ -56005,7 +56077,7 @@
       <c r="I703" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J703" s="9" t="s">
+      <c r="J703" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K703" s="6" t="s">
@@ -56066,7 +56138,7 @@
       <c r="I704" s="6" t="s">
         <v>3299</v>
       </c>
-      <c r="J704" s="9" t="s">
+      <c r="J704" s="13" t="s">
         <v>3300</v>
       </c>
       <c r="K704" s="6" t="s">
@@ -56127,7 +56199,7 @@
       <c r="I705" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J705" s="9" t="s">
+      <c r="J705" s="13" t="s">
         <v>126</v>
       </c>
       <c r="K705" s="6" t="s">
@@ -56188,7 +56260,7 @@
       <c r="I706" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J706" s="9" t="s">
+      <c r="J706" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K706" s="6" t="s">
@@ -56249,7 +56321,7 @@
       <c r="I707" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J707" s="9" t="s">
+      <c r="J707" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K707" s="6" t="s">
@@ -56312,7 +56384,7 @@
       <c r="I708" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J708" s="9" t="s">
+      <c r="J708" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K708" s="6" t="s">
@@ -56373,7 +56445,7 @@
       <c r="I709" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J709" s="9" t="s">
+      <c r="J709" s="13" t="s">
         <v>3273</v>
       </c>
       <c r="K709" s="6" t="s">
@@ -56434,7 +56506,7 @@
       <c r="I710" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J710" s="9" t="s">
+      <c r="J710" s="13" t="s">
         <v>3322</v>
       </c>
       <c r="K710" s="6" t="s">
@@ -56495,7 +56567,7 @@
       <c r="I711" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J711" s="9" t="s">
+      <c r="J711" s="13" t="s">
         <v>3331</v>
       </c>
       <c r="K711" s="6" t="s">
@@ -56556,7 +56628,7 @@
       <c r="I712" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J712" s="9" t="s">
+      <c r="J712" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K712" s="6" t="s">
@@ -56617,7 +56689,7 @@
       <c r="I713" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J713" s="9" t="s">
+      <c r="J713" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K713" s="6" t="s">
@@ -56680,7 +56752,7 @@
       <c r="I714" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J714" s="9" t="s">
+      <c r="J714" s="13" t="s">
         <v>89</v>
       </c>
       <c r="K714" s="6" t="s">
@@ -56745,7 +56817,7 @@
       <c r="I715" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J715" s="9" t="s">
+      <c r="J715" s="13" t="s">
         <v>2297</v>
       </c>
       <c r="K715" s="6" t="s">
@@ -56806,7 +56878,7 @@
       <c r="I716" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J716" s="9" t="s">
+      <c r="J716" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K716" s="6" t="s">
@@ -56867,7 +56939,7 @@
       <c r="I717" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J717" s="9" t="s">
+      <c r="J717" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K717" s="6" t="s">
@@ -56928,7 +57000,7 @@
       <c r="I718" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J718" s="9" t="s">
+      <c r="J718" s="13" t="s">
         <v>308</v>
       </c>
       <c r="K718" s="6" t="s">
@@ -56989,7 +57061,7 @@
       <c r="I719" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J719" s="9" t="s">
+      <c r="J719" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K719" s="6" t="s">
@@ -57050,7 +57122,7 @@
       <c r="I720" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J720" s="9" t="s">
+      <c r="J720" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K720" s="6" t="s">
@@ -57111,7 +57183,7 @@
       <c r="I721" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J721" s="9" t="s">
+      <c r="J721" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K721" s="6" t="s">
@@ -57172,7 +57244,7 @@
       <c r="I722" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J722" s="9" t="s">
+      <c r="J722" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K722" s="6" t="s">
@@ -57233,7 +57305,7 @@
       <c r="I723" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="J723" s="9" t="s">
+      <c r="J723" s="13" t="s">
         <v>3369</v>
       </c>
       <c r="K723" s="6" t="s">
@@ -57294,7 +57366,7 @@
       <c r="I724" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J724" s="9" t="s">
+      <c r="J724" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K724" s="6" t="s">
@@ -57355,7 +57427,7 @@
       <c r="I725" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J725" s="9" t="s">
+      <c r="J725" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K725" s="6" t="s">
@@ -57416,7 +57488,7 @@
       <c r="I726" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J726" s="9" t="s">
+      <c r="J726" s="13" t="s">
         <v>3380</v>
       </c>
       <c r="K726" s="6" t="s">
@@ -57477,7 +57549,7 @@
       <c r="I727" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J727" s="9" t="s">
+      <c r="J727" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K727" s="6" t="s">
@@ -57538,7 +57610,7 @@
       <c r="I728" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J728" s="9" t="s">
+      <c r="J728" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K728" s="6" t="s">
@@ -57599,7 +57671,7 @@
       <c r="I729" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J729" s="9" t="s">
+      <c r="J729" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K729" s="6" t="s">
@@ -57660,7 +57732,7 @@
       <c r="I730" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J730" s="9" t="s">
+      <c r="J730" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K730" s="6" t="s">
@@ -57721,7 +57793,7 @@
       <c r="I731" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J731" s="9" t="s">
+      <c r="J731" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K731" s="6" t="s">
@@ -57782,7 +57854,7 @@
       <c r="I732" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J732" s="9" t="s">
+      <c r="J732" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K732" s="6" t="s">
@@ -57843,7 +57915,7 @@
       <c r="I733" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J733" s="9" t="s">
+      <c r="J733" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K733" s="6" t="s">
@@ -57904,7 +57976,7 @@
       <c r="I734" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J734" s="9" t="s">
+      <c r="J734" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K734" s="6" t="s">
@@ -57965,7 +58037,7 @@
       <c r="I735" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J735" s="9" t="s">
+      <c r="J735" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K735" s="6" t="s">
@@ -58026,7 +58098,7 @@
       <c r="I736" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J736" s="9" t="s">
+      <c r="J736" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K736" s="6" t="s">
@@ -58087,7 +58159,7 @@
       <c r="I737" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J737" s="9" t="s">
+      <c r="J737" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K737" s="6" t="s">
@@ -58148,7 +58220,7 @@
       <c r="I738" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J738" s="9" t="s">
+      <c r="J738" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K738" s="6" t="s">
@@ -58209,7 +58281,7 @@
       <c r="I739" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J739" s="9" t="s">
+      <c r="J739" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K739" s="6" t="s">
@@ -58270,7 +58342,7 @@
       <c r="I740" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J740" s="9" t="s">
+      <c r="J740" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K740" s="6" t="s">
@@ -58331,7 +58403,7 @@
       <c r="I741" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J741" s="9" t="s">
+      <c r="J741" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K741" s="6" t="s">
@@ -58392,7 +58464,7 @@
       <c r="I742" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J742" s="9" t="s">
+      <c r="J742" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K742" s="6" t="s">
@@ -58453,7 +58525,7 @@
       <c r="I743" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J743" s="9" t="s">
+      <c r="J743" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K743" s="6" t="s">
@@ -58514,7 +58586,7 @@
       <c r="I744" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J744" s="9" t="s">
+      <c r="J744" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K744" s="6" t="s">
@@ -58575,7 +58647,7 @@
       <c r="I745" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J745" s="9" t="s">
+      <c r="J745" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K745" s="6" t="s">
@@ -58636,7 +58708,7 @@
       <c r="I746" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J746" s="9" t="s">
+      <c r="J746" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K746" s="6" t="s">
@@ -58697,7 +58769,7 @@
       <c r="I747" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J747" s="9" t="s">
+      <c r="J747" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K747" s="6" t="s">
@@ -58758,7 +58830,7 @@
       <c r="I748" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J748" s="9" t="s">
+      <c r="J748" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K748" s="6" t="s">
@@ -58819,7 +58891,7 @@
       <c r="I749" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J749" s="9" t="s">
+      <c r="J749" s="13" t="s">
         <v>2399</v>
       </c>
       <c r="K749" s="6" t="s">
@@ -58880,7 +58952,7 @@
       <c r="I750" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J750" s="9" t="s">
+      <c r="J750" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K750" s="6" t="s">
@@ -58941,7 +59013,7 @@
       <c r="I751" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J751" s="9" t="s">
+      <c r="J751" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K751" s="6" t="s">
@@ -59002,7 +59074,7 @@
       <c r="I752" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J752" s="9" t="s">
+      <c r="J752" s="13" t="s">
         <v>3454</v>
       </c>
       <c r="K752" s="6" t="s">
@@ -59063,7 +59135,7 @@
       <c r="I753" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J753" s="9" t="s">
+      <c r="J753" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K753" s="6" t="s">
@@ -59124,7 +59196,7 @@
       <c r="I754" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J754" s="9" t="s">
+      <c r="J754" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K754" s="6" t="s">
@@ -59185,7 +59257,7 @@
       <c r="I755" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J755" s="9" t="s">
+      <c r="J755" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K755" s="6" t="s">
@@ -59246,7 +59318,7 @@
       <c r="I756" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J756" s="9" t="s">
+      <c r="J756" s="13" t="s">
         <v>89</v>
       </c>
       <c r="K756" s="6" t="s">
@@ -59307,7 +59379,7 @@
       <c r="I757" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J757" s="9" t="s">
+      <c r="J757" s="13" t="s">
         <v>299</v>
       </c>
       <c r="K757" s="6" t="s">
@@ -59368,7 +59440,7 @@
       <c r="I758" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J758" s="9" t="s">
+      <c r="J758" s="13" t="s">
         <v>220</v>
       </c>
       <c r="K758" s="6" t="s">
@@ -59429,7 +59501,7 @@
       <c r="I759" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J759" s="9" t="s">
+      <c r="J759" s="13" t="s">
         <v>3488</v>
       </c>
       <c r="K759" s="6" t="s">
@@ -59490,7 +59562,7 @@
       <c r="I760" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J760" s="9" t="s">
+      <c r="J760" s="13" t="s">
         <v>2560</v>
       </c>
       <c r="K760" s="6" t="s">
@@ -59553,7 +59625,7 @@
       <c r="I761" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J761" s="9" t="s">
+      <c r="J761" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K761" s="6" t="s">
@@ -59616,7 +59688,7 @@
       <c r="I762" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J762" s="9" t="s">
+      <c r="J762" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K762" s="6" t="s">
@@ -59677,7 +59749,7 @@
       <c r="I763" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J763" s="9" t="s">
+      <c r="J763" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K763" s="6" t="s">
@@ -59738,7 +59810,7 @@
       <c r="I764" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J764" s="9" t="s">
+      <c r="J764" s="13" t="s">
         <v>2001</v>
       </c>
       <c r="K764" s="6" t="s">
@@ -59799,7 +59871,7 @@
       <c r="I765" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J765" s="9" t="s">
+      <c r="J765" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K765" s="6" t="s">
@@ -59860,7 +59932,7 @@
       <c r="I766" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J766" s="9" t="s">
+      <c r="J766" s="13" t="s">
         <v>2882</v>
       </c>
       <c r="K766" s="6" t="s">
@@ -59921,7 +59993,7 @@
       <c r="I767" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J767" s="9" t="s">
+      <c r="J767" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K767" s="6" t="s">
@@ -59982,7 +60054,7 @@
       <c r="I768" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J768" s="9" t="s">
+      <c r="J768" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K768" s="6" t="s">
@@ -60043,7 +60115,7 @@
       <c r="I769" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J769" s="9" t="s">
+      <c r="J769" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K769" s="6" t="s">
@@ -60104,7 +60176,7 @@
       <c r="I770" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J770" s="9" t="s">
+      <c r="J770" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K770" s="6" t="s">
@@ -60165,7 +60237,7 @@
       <c r="I771" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J771" s="9" t="s">
+      <c r="J771" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K771" s="6" t="s">
@@ -60226,7 +60298,7 @@
       <c r="I772" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J772" s="9" t="s">
+      <c r="J772" s="13" t="s">
         <v>662</v>
       </c>
       <c r="K772" s="6" t="s">
@@ -60287,7 +60359,7 @@
       <c r="I773" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J773" s="9" t="s">
+      <c r="J773" s="13" t="s">
         <v>3530</v>
       </c>
       <c r="K773" s="6" t="s">
@@ -60348,7 +60420,7 @@
       <c r="I774" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J774" s="9" t="s">
+      <c r="J774" s="13" t="s">
         <v>332</v>
       </c>
       <c r="K774" s="6" t="s">
@@ -60409,7 +60481,7 @@
       <c r="I775" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J775" s="9" t="s">
+      <c r="J775" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K775" s="6" t="s">
@@ -60470,7 +60542,7 @@
       <c r="I776" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J776" s="9" t="s">
+      <c r="J776" s="13" t="s">
         <v>332</v>
       </c>
       <c r="K776" s="6" t="s">
@@ -60531,7 +60603,7 @@
       <c r="I777" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J777" s="9" t="s">
+      <c r="J777" s="13" t="s">
         <v>2820</v>
       </c>
       <c r="K777" s="6" t="s">
@@ -60592,7 +60664,7 @@
       <c r="I778" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J778" s="9" t="s">
+      <c r="J778" s="13" t="s">
         <v>2072</v>
       </c>
       <c r="K778" s="6" t="s">
@@ -60653,7 +60725,7 @@
       <c r="I779" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J779" s="9" t="s">
+      <c r="J779" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K779" s="6" t="s">
@@ -60714,7 +60786,7 @@
       <c r="I780" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J780" s="9" t="s">
+      <c r="J780" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K780" s="6" t="s">
@@ -60775,7 +60847,7 @@
       <c r="I781" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J781" s="9" t="s">
+      <c r="J781" s="13" t="s">
         <v>3557</v>
       </c>
       <c r="K781" s="6" t="s">
@@ -60836,7 +60908,7 @@
       <c r="I782" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J782" s="9" t="s">
+      <c r="J782" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K782" s="6" t="s">
@@ -60897,7 +60969,7 @@
       <c r="I783" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J783" s="9" t="s">
+      <c r="J783" s="13" t="s">
         <v>2001</v>
       </c>
       <c r="K783" s="6" t="s">
@@ -60958,7 +61030,7 @@
       <c r="I784" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J784" s="9" t="s">
+      <c r="J784" s="13" t="s">
         <v>433</v>
       </c>
       <c r="K784" s="6" t="s">
@@ -61019,7 +61091,7 @@
       <c r="I785" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J785" s="9" t="s">
+      <c r="J785" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K785" s="6" t="s">
@@ -61080,7 +61152,7 @@
       <c r="I786" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J786" s="9" t="s">
+      <c r="J786" s="13" t="s">
         <v>1819</v>
       </c>
       <c r="K786" s="6" t="s">
@@ -61141,7 +61213,7 @@
       <c r="I787" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J787" s="9" t="s">
+      <c r="J787" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K787" s="6" t="s">
@@ -61202,7 +61274,7 @@
       <c r="I788" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J788" s="9" t="s">
+      <c r="J788" s="13" t="s">
         <v>3578</v>
       </c>
       <c r="K788" s="6" t="s">
@@ -61263,7 +61335,7 @@
       <c r="I789" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J789" s="9" t="s">
+      <c r="J789" s="13" t="s">
         <v>3578</v>
       </c>
       <c r="K789" s="6" t="s">
@@ -61324,7 +61396,7 @@
       <c r="I790" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J790" s="9" t="s">
+      <c r="J790" s="13" t="s">
         <v>3578</v>
       </c>
       <c r="K790" s="6" t="s">
@@ -61385,7 +61457,7 @@
       <c r="I791" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J791" s="9" t="s">
+      <c r="J791" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K791" s="6" t="s">
@@ -61446,7 +61518,7 @@
       <c r="I792" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="J792" s="9" t="s">
+      <c r="J792" s="13" t="s">
         <v>781</v>
       </c>
       <c r="K792" s="6" t="s">
@@ -61507,7 +61579,7 @@
       <c r="I793" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J793" s="9" t="s">
+      <c r="J793" s="13" t="s">
         <v>3598</v>
       </c>
       <c r="K793" s="6" t="s">
@@ -61568,7 +61640,7 @@
       <c r="I794" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J794" s="9" t="s">
+      <c r="J794" s="13" t="s">
         <v>332</v>
       </c>
       <c r="K794" s="6" t="s">
@@ -61629,7 +61701,7 @@
       <c r="I795" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J795" s="9" t="s">
+      <c r="J795" s="13" t="s">
         <v>332</v>
       </c>
       <c r="K795" s="6" t="s">
@@ -61690,7 +61762,7 @@
       <c r="I796" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J796" s="9" t="s">
+      <c r="J796" s="13" t="s">
         <v>257</v>
       </c>
       <c r="K796" s="6" t="s">
@@ -61751,7 +61823,7 @@
       <c r="I797" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J797" s="9" t="s">
+      <c r="J797" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K797" s="6" t="s">
@@ -61812,7 +61884,7 @@
       <c r="I798" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J798" s="9" t="s">
+      <c r="J798" s="13" t="s">
         <v>3322</v>
       </c>
       <c r="K798" s="6" t="s">
@@ -61873,7 +61945,7 @@
       <c r="I799" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J799" s="9" t="s">
+      <c r="J799" s="13" t="s">
         <v>3322</v>
       </c>
       <c r="K799" s="6" t="s">
@@ -61934,7 +62006,7 @@
       <c r="I800" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J800" s="9" t="s">
+      <c r="J800" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K800" s="6" t="s">
@@ -61995,7 +62067,7 @@
       <c r="I801" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J801" s="9" t="s">
+      <c r="J801" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K801" s="6" t="s">
@@ -62056,7 +62128,7 @@
       <c r="I802" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J802" s="9" t="s">
+      <c r="J802" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K802" s="6" t="s">
@@ -62117,7 +62189,7 @@
       <c r="I803" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J803" s="9" t="s">
+      <c r="J803" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K803" s="6" t="s">
@@ -62178,7 +62250,7 @@
       <c r="I804" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J804" s="9" t="s">
+      <c r="J804" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K804" s="6" t="s">
@@ -62239,7 +62311,7 @@
       <c r="I805" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J805" s="9" t="s">
+      <c r="J805" s="13" t="s">
         <v>2297</v>
       </c>
       <c r="K805" s="6" t="s">
@@ -62300,7 +62372,7 @@
       <c r="I806" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J806" s="9" t="s">
+      <c r="J806" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K806" s="6" t="s">
@@ -62361,7 +62433,7 @@
       <c r="I807" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J807" s="9" t="s">
+      <c r="J807" s="13" t="s">
         <v>2896</v>
       </c>
       <c r="K807" s="6" t="s">
@@ -62422,7 +62494,7 @@
       <c r="I808" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J808" s="9" t="s">
+      <c r="J808" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K808" s="6" t="s">
@@ -62483,7 +62555,7 @@
       <c r="I809" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J809" s="9" t="s">
+      <c r="J809" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K809" s="6" t="s">
@@ -62544,7 +62616,7 @@
       <c r="I810" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J810" s="9" t="s">
+      <c r="J810" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K810" s="6" t="s">
@@ -62605,7 +62677,7 @@
       <c r="I811" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J811" s="9" t="s">
+      <c r="J811" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K811" s="6" t="s">
@@ -62668,7 +62740,7 @@
       <c r="I812" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="J812" s="9" t="s">
+      <c r="J812" s="13" t="s">
         <v>376</v>
       </c>
       <c r="K812" s="6" t="s">
@@ -62729,7 +62801,7 @@
       <c r="I813" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="J813" s="9" t="s">
+      <c r="J813" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K813" s="6" t="s">
@@ -62790,7 +62862,7 @@
       <c r="I814" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J814" s="9" t="s">
+      <c r="J814" s="13" t="s">
         <v>2072</v>
       </c>
       <c r="K814" s="6" t="s">
@@ -62851,7 +62923,7 @@
       <c r="I815" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J815" s="9" t="s">
+      <c r="J815" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K815" s="6" t="s">
@@ -62912,7 +62984,7 @@
       <c r="I816" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J816" s="9" t="s">
+      <c r="J816" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K816" s="6" t="s">
@@ -62973,7 +63045,7 @@
       <c r="I817" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J817" s="9" t="s">
+      <c r="J817" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K817" s="6" t="s">
@@ -63034,7 +63106,7 @@
       <c r="I818" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J818" s="9" t="s">
+      <c r="J818" s="13" t="s">
         <v>181</v>
       </c>
       <c r="K818" s="6" t="s">
@@ -63095,7 +63167,7 @@
       <c r="I819" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J819" s="9" t="s">
+      <c r="J819" s="13" t="s">
         <v>89</v>
       </c>
       <c r="K819" s="6" t="s">
@@ -63156,7 +63228,7 @@
       <c r="I820" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J820" s="9" t="s">
+      <c r="J820" s="13" t="s">
         <v>147</v>
       </c>
       <c r="K820" s="6" t="s">
@@ -63217,7 +63289,7 @@
       <c r="I821" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J821" s="9" t="s">
+      <c r="J821" s="13" t="s">
         <v>421</v>
       </c>
       <c r="K821" s="6" t="s">
@@ -63278,7 +63350,7 @@
       <c r="I822" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J822" s="9" t="s">
+      <c r="J822" s="13" t="s">
         <v>28</v>
       </c>
       <c r="K822" s="6" t="s">
@@ -63339,7 +63411,7 @@
       <c r="I823" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J823" s="9" t="s">
+      <c r="J823" s="13" t="s">
         <v>701</v>
       </c>
       <c r="K823" s="6" t="s">
@@ -63400,7 +63472,7 @@
       <c r="I824" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J824" s="9" t="s">
+      <c r="J824" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K824" s="6" t="s">
@@ -63461,7 +63533,7 @@
       <c r="I825" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J825" s="9" t="s">
+      <c r="J825" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K825" s="6" t="s">
@@ -63498,8 +63570,130 @@
         <v>2463</v>
       </c>
     </row>
+    <row r="826" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A826" s="4">
+        <v>825</v>
+      </c>
+      <c r="B826" s="5"/>
+      <c r="C826" s="6" t="s">
+        <v>3691</v>
+      </c>
+      <c r="D826" s="5"/>
+      <c r="E826" s="6" t="s">
+        <v>3692</v>
+      </c>
+      <c r="F826" s="6" t="s">
+        <v>3693</v>
+      </c>
+      <c r="G826" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H826" s="6" t="s">
+        <v>3379</v>
+      </c>
+      <c r="I826" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="J826" s="13" t="s">
+        <v>3380</v>
+      </c>
+      <c r="K826" s="6" t="s">
+        <v>3694</v>
+      </c>
+      <c r="L826" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M826" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N826" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="O826" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P826" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q826" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="R826" s="6" t="s">
+        <v>3695</v>
+      </c>
+      <c r="S826" s="6" t="s">
+        <v>3696</v>
+      </c>
+      <c r="T826" s="6" t="s">
+        <v>2508</v>
+      </c>
+      <c r="U826" s="7" t="s">
+        <v>3697</v>
+      </c>
+    </row>
+    <row r="827" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A827" s="9">
+        <v>826</v>
+      </c>
+      <c r="B827" s="10"/>
+      <c r="C827" s="11" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D827" s="10"/>
+      <c r="E827" s="11" t="s">
+        <v>3698</v>
+      </c>
+      <c r="F827" s="11" t="s">
+        <v>3699</v>
+      </c>
+      <c r="G827" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="H827" s="11" t="s">
+        <v>2348</v>
+      </c>
+      <c r="I827" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J827" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="K827" s="11" t="s">
+        <v>848</v>
+      </c>
+      <c r="L827" s="11" t="s">
+        <v>690</v>
+      </c>
+      <c r="M827" s="11" t="s">
+        <v>691</v>
+      </c>
+      <c r="N827" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="O827" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="P827" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q827" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R827" s="11" t="s">
+        <v>2350</v>
+      </c>
+      <c r="S827" s="11" t="s">
+        <v>2378</v>
+      </c>
+      <c r="T827" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="U827" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="c287mowFeTIS07wWhE59G0zH1yAXkEt7xvUZ+zo8PKdSGatvWg2dWcEJtO3g34z9+h55GTMYeUpizHkQJ/fTjg==" saltValue="pMGTec4t5O5mZorez8gtKg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="rmDk/+Duo0VlMz4iQI/10AYawdUq1m27Qkxw/g/w3EiBwdFGr7hZHjVHXBB+L5MrX5h0f1UWav5NmgG9k8mKFQ==" saltValue="ne2U/XF9L9EXI/5CMIRDVg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D4E270-6228-4D80-A7FC-4E30A40ACE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF41F85-5CF6-4B23-B0E8-E92B912479C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15436" uniqueCount="3722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15448" uniqueCount="3732">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11235,6 +11235,36 @@
   </si>
   <si>
     <t>1130.00 ± 20.00</t>
+  </si>
+  <si>
+    <t>MP0444</t>
+  </si>
+  <si>
+    <t>MP0444.1</t>
+  </si>
+  <si>
+    <t>Pet 200gm Powder Clear 63mm 21gm Jar</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Pending Matrix</t>
+  </si>
+  <si>
+    <t>Powder</t>
+  </si>
+  <si>
+    <t>67.60 ± 1.00</t>
+  </si>
+  <si>
+    <t>71.00 ± 1.00</t>
+  </si>
+  <si>
+    <t>21.00 ± 1.00</t>
+  </si>
+  <si>
+    <t>215.00 ± 4.00</t>
   </si>
 </sst>
 </file>
@@ -12006,30 +12036,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DF7C3832-AD9C-4121-AE94-9BA9778E5030}" name="Table1" displayName="Table1" ref="A1:U831" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U831" xr:uid="{DF7C3832-AD9C-4121-AE94-9BA9778E5030}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C2682CF-92AB-42A1-84D4-C59E8F613F3E}" name="Table1" displayName="Table1" ref="A1:U832" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U832" xr:uid="{9C2682CF-92AB-42A1-84D4-C59E8F613F3E}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{582A659E-A4D5-473D-B782-2EB64ED379DC}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{7B1B7309-AF1F-47D4-91FA-7253A71C62F3}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{D2C3D562-1CAB-4E4C-A340-6977705D2BB1}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{42AFDBBD-BF01-4F26-99A5-8258CC569A58}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{08062A23-9DB2-46A4-B18A-1FB77C5C3456}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{D57AC6E7-3833-462A-9D1A-6EF7DCF659EC}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{177EAFDD-1DD7-4344-B0D0-3A27E1354151}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{72ED5A6B-33B1-4820-B7A0-55FF7AB54D90}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{13C61335-D010-4E99-933A-62740B21429C}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{702C8F8D-D03A-4AAB-B337-E2A6E366ED69}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{D2CC3266-5B13-44DD-A406-A4B6197C3E49}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{C520EAAE-9413-40A6-8AFA-9FEE60FE446E}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{7CFC7FCF-C9F7-4C35-AEDA-0B0A01E17923}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{3EA000C5-FFE5-4579-875F-9263F21577DF}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{748EC611-B92A-424D-A543-C14968E63FD8}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{3CBF460D-BE6B-424B-8005-9C7867EBD551}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{93BE5DD7-A354-441B-9B98-2131569E8070}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{A02E83B3-A9B1-4487-9BAF-53E7DF3E0B9A}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{C98521C2-B38C-4825-B0CD-44FF70FE9E8E}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{8D55F48C-0292-46F7-9FDE-23F97D59975F}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{E1EF64F2-A64D-4CF5-97E2-14489D854F1A}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{43C97DA3-1B59-4A36-B2B7-0A4790677E73}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{2D62E34D-8FDB-4B42-9C13-C612E4072F5D}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{BD2795C8-F730-446F-8860-E36260C1E51E}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{48DF161A-2128-408B-B456-8F286958A8A1}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{DB11CE50-D760-4E2D-89F1-A52D80467BFA}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{03984774-1159-419D-A52A-E8BEC206DD20}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{FCE6D73F-2804-46A8-9E9B-95D02259934C}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{B63BB7C2-AA18-41A5-B774-82CABC93E0FD}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{D3F3B83F-4A65-4FF1-BC5D-D2FB157168CF}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{626BC24E-905A-4FEB-9761-38E79590271E}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{DA40042E-5B17-45F0-9280-6F9840BCD76D}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{B4B62FDE-9535-4B55-80A0-BB19A5256B25}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{F0CD9247-BAED-4411-B425-549E9E1B9C22}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{357E3C10-DD71-4745-B022-95B48D4BDC66}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{A2E82671-714B-40FA-8881-258D4D9E7693}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{39555E72-C115-4348-8A76-0B7AD89B16CB}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{EDD041F5-E8F9-4163-BC11-3AFCD09635D3}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{E38C5659-4E9A-4A0A-A299-FE8FE2E91023}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{06F73866-6383-47F3-BC61-6936D828EF60}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{E86F4BC1-DDAA-48C0-B900-334AE9183D2F}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{899561EA-69D3-4A47-82FB-8BA79FAD76A6}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12332,7 +12362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U831"/>
+  <dimension ref="A1:U832"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -63943,68 +63973,117 @@
       </c>
     </row>
     <row r="831" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A831" s="9">
+      <c r="A831" s="4">
         <v>830</v>
       </c>
-      <c r="B831" s="10"/>
-      <c r="C831" s="11" t="s">
+      <c r="B831" s="5"/>
+      <c r="C831" s="6" t="s">
         <v>3718</v>
       </c>
-      <c r="D831" s="10"/>
-      <c r="E831" s="11" t="s">
+      <c r="D831" s="5"/>
+      <c r="E831" s="6" t="s">
         <v>3719</v>
       </c>
-      <c r="F831" s="11" t="s">
+      <c r="F831" s="6" t="s">
         <v>3720</v>
       </c>
-      <c r="G831" s="11" t="s">
+      <c r="G831" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H831" s="11" t="s">
+      <c r="H831" s="6" t="s">
         <v>3379</v>
       </c>
-      <c r="I831" s="11" t="s">
+      <c r="I831" s="6" t="s">
         <v>269</v>
       </c>
       <c r="J831" s="13" t="s">
         <v>3380</v>
       </c>
-      <c r="K831" s="11" t="s">
+      <c r="K831" s="6" t="s">
         <v>3694</v>
       </c>
-      <c r="L831" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="M831" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="N831" s="11" t="s">
+      <c r="L831" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M831" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N831" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="O831" s="11" t="s">
+      <c r="O831" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="P831" s="11" t="s">
+      <c r="P831" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="Q831" s="11" t="s">
+      <c r="Q831" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="R831" s="11" t="s">
+      <c r="R831" s="6" t="s">
         <v>3695</v>
       </c>
-      <c r="S831" s="11" t="s">
+      <c r="S831" s="6" t="s">
         <v>3696</v>
       </c>
-      <c r="T831" s="11" t="s">
+      <c r="T831" s="6" t="s">
         <v>3384</v>
       </c>
-      <c r="U831" s="12" t="s">
+      <c r="U831" s="7" t="s">
         <v>3721</v>
       </c>
     </row>
+    <row r="832" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A832" s="9">
+        <v>831</v>
+      </c>
+      <c r="B832" s="10"/>
+      <c r="C832" s="11" t="s">
+        <v>3722</v>
+      </c>
+      <c r="D832" s="10"/>
+      <c r="E832" s="11" t="s">
+        <v>3723</v>
+      </c>
+      <c r="F832" s="11" t="s">
+        <v>3724</v>
+      </c>
+      <c r="G832" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="H832" s="11" t="s">
+        <v>3725</v>
+      </c>
+      <c r="I832" s="11" t="s">
+        <v>3725</v>
+      </c>
+      <c r="J832" s="13" t="s">
+        <v>3726</v>
+      </c>
+      <c r="K832" s="11" t="s">
+        <v>3727</v>
+      </c>
+      <c r="L832" s="10"/>
+      <c r="M832" s="10"/>
+      <c r="N832" s="10"/>
+      <c r="O832" s="10"/>
+      <c r="P832" s="10"/>
+      <c r="Q832" s="10"/>
+      <c r="R832" s="11" t="s">
+        <v>3728</v>
+      </c>
+      <c r="S832" s="11" t="s">
+        <v>3729</v>
+      </c>
+      <c r="T832" s="11" t="s">
+        <v>3730</v>
+      </c>
+      <c r="U832" s="12" t="s">
+        <v>3731</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="oI7ui37T5suk1jfgZ1aJaQBRve5Q7dWnTYS5eseOGMNc8zOL4gQK90ei54qiytkWOGJkKbxqB339I8ZL2s5WnQ==" saltValue="S6oRrGrNzxs/6JbzKwj3jg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="gdIIFF2rZN//3aeEAM7bx+VNAcgS91ZSlZmejbAlpa/HKiiHmYib97KN1SIlrMqfM448vEw3sMYNdan1aV0WWg==" saltValue="nOJedxNYFfAQxtkgoHF34Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF41F85-5CF6-4B23-B0E8-E92B912479C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B4CF18-A6F1-4869-B4D7-BF114C19DEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15448" uniqueCount="3732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15486" uniqueCount="3737">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11265,6 +11265,21 @@
   </si>
   <si>
     <t>215.00 ± 4.00</t>
+  </si>
+  <si>
+    <t>MP0315.2</t>
+  </si>
+  <si>
+    <t>Pet 90ml Avon Yellow Long Neck 19mm 12.5gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0466</t>
+  </si>
+  <si>
+    <t>MP0466.1</t>
+  </si>
+  <si>
+    <t>Pet 90ml Avon Light Yellow Long Neck 19mm 11gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -12036,30 +12051,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C2682CF-92AB-42A1-84D4-C59E8F613F3E}" name="Table1" displayName="Table1" ref="A1:U832" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U832" xr:uid="{9C2682CF-92AB-42A1-84D4-C59E8F613F3E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E9A40003-BFBD-4173-A1EF-216266D31715}" name="Table1" displayName="Table1" ref="A1:U834" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U834" xr:uid="{E9A40003-BFBD-4173-A1EF-216266D31715}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{43C97DA3-1B59-4A36-B2B7-0A4790677E73}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{2D62E34D-8FDB-4B42-9C13-C612E4072F5D}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{BD2795C8-F730-446F-8860-E36260C1E51E}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{48DF161A-2128-408B-B456-8F286958A8A1}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{DB11CE50-D760-4E2D-89F1-A52D80467BFA}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{03984774-1159-419D-A52A-E8BEC206DD20}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{FCE6D73F-2804-46A8-9E9B-95D02259934C}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{B63BB7C2-AA18-41A5-B774-82CABC93E0FD}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{D3F3B83F-4A65-4FF1-BC5D-D2FB157168CF}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{626BC24E-905A-4FEB-9761-38E79590271E}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{DA40042E-5B17-45F0-9280-6F9840BCD76D}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{B4B62FDE-9535-4B55-80A0-BB19A5256B25}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{F0CD9247-BAED-4411-B425-549E9E1B9C22}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{357E3C10-DD71-4745-B022-95B48D4BDC66}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{A2E82671-714B-40FA-8881-258D4D9E7693}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{39555E72-C115-4348-8A76-0B7AD89B16CB}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{EDD041F5-E8F9-4163-BC11-3AFCD09635D3}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{E38C5659-4E9A-4A0A-A299-FE8FE2E91023}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{06F73866-6383-47F3-BC61-6936D828EF60}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{E86F4BC1-DDAA-48C0-B900-334AE9183D2F}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{899561EA-69D3-4A47-82FB-8BA79FAD76A6}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{167F97E5-93DE-4415-ABEB-9CDBDE5E95E2}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{FA3AD723-3CA3-478B-A464-80EEEDEDD46B}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{71A7CCA0-61E5-461A-B40F-FAAD67DB1199}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{FA52E6B9-C48E-4237-8966-A4BCAA6C752A}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{6CD63ED1-385D-4037-96B9-FABD3779F944}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{CC0F2CA0-CF32-4588-A5B8-4F20C2CED6E8}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{404AEF1E-08CD-4169-87FF-B9C182C04892}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{85264FD2-8C94-48D7-8E36-B77450EA1040}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{6A432CAF-17C5-4541-B093-F94260DFE085}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{0DA4C76E-F85D-4705-AE81-21C1A1C5DF38}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{B8ABADBD-AC93-4DD9-81EF-35C74C9A6BEB}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{92159696-E71F-4BB9-9E5D-DEF61EC9AF28}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{DE2E4AEF-C674-4E98-AD7E-5A33A1FFFF47}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{6B6D7EB2-D40B-49B9-AC26-1BEBD75CC18E}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{945CAB83-3F8C-48B0-9FC1-2B33954726AF}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{9645F2A1-37E9-4B00-82D0-345AA10906ED}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{0A4B9ECA-E4B0-43B9-9046-488697BE15E4}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{DF5F9B50-CC37-4BA8-BCFE-4EBE3CD5E938}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{3563AA30-ED16-4DF3-A513-B339922CB4A4}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{75EF55B3-B1E5-4231-9A28-6F7C08EFA1A4}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{C543C1BF-0A64-4D0C-8FA5-CDB7043F926B}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12362,7 +12377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U832"/>
+  <dimension ref="A1:U834"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -60802,7 +60817,9 @@
       <c r="A779" s="4">
         <v>778</v>
       </c>
-      <c r="B779" s="5"/>
+      <c r="B779" s="6" t="s">
+        <v>325</v>
+      </c>
       <c r="C779" s="6" t="s">
         <v>2111</v>
       </c>
@@ -64034,56 +64051,180 @@
       </c>
     </row>
     <row r="832" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A832" s="9">
+      <c r="A832" s="4">
         <v>831</v>
       </c>
-      <c r="B832" s="10"/>
-      <c r="C832" s="11" t="s">
+      <c r="B832" s="5"/>
+      <c r="C832" s="6" t="s">
         <v>3722</v>
       </c>
-      <c r="D832" s="10"/>
-      <c r="E832" s="11" t="s">
+      <c r="D832" s="5"/>
+      <c r="E832" s="6" t="s">
         <v>3723</v>
       </c>
-      <c r="F832" s="11" t="s">
+      <c r="F832" s="6" t="s">
         <v>3724</v>
       </c>
-      <c r="G832" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="H832" s="11" t="s">
+      <c r="G832" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H832" s="6" t="s">
         <v>3725</v>
       </c>
-      <c r="I832" s="11" t="s">
+      <c r="I832" s="6" t="s">
         <v>3725</v>
       </c>
       <c r="J832" s="13" t="s">
         <v>3726</v>
       </c>
-      <c r="K832" s="11" t="s">
+      <c r="K832" s="6" t="s">
         <v>3727</v>
       </c>
-      <c r="L832" s="10"/>
-      <c r="M832" s="10"/>
-      <c r="N832" s="10"/>
-      <c r="O832" s="10"/>
-      <c r="P832" s="10"/>
-      <c r="Q832" s="10"/>
-      <c r="R832" s="11" t="s">
+      <c r="L832" s="5"/>
+      <c r="M832" s="5"/>
+      <c r="N832" s="5"/>
+      <c r="O832" s="5"/>
+      <c r="P832" s="5"/>
+      <c r="Q832" s="5"/>
+      <c r="R832" s="6" t="s">
         <v>3728</v>
       </c>
-      <c r="S832" s="11" t="s">
+      <c r="S832" s="6" t="s">
         <v>3729</v>
       </c>
-      <c r="T832" s="11" t="s">
+      <c r="T832" s="6" t="s">
         <v>3730</v>
       </c>
-      <c r="U832" s="12" t="s">
+      <c r="U832" s="7" t="s">
         <v>3731</v>
       </c>
     </row>
+    <row r="833" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A833" s="4">
+        <v>832</v>
+      </c>
+      <c r="B833" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C833" s="6" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D833" s="5"/>
+      <c r="E833" s="6" t="s">
+        <v>3732</v>
+      </c>
+      <c r="F833" s="6" t="s">
+        <v>3733</v>
+      </c>
+      <c r="G833" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H833" s="6" t="s">
+        <v>2193</v>
+      </c>
+      <c r="I833" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J833" s="13" t="s">
+        <v>2194</v>
+      </c>
+      <c r="K833" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L833" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M833" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N833" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="O833" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="P833" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q833" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R833" s="6" t="s">
+        <v>2195</v>
+      </c>
+      <c r="S833" s="6" t="s">
+        <v>2196</v>
+      </c>
+      <c r="T833" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="U833" s="7" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="834" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A834" s="9">
+        <v>833</v>
+      </c>
+      <c r="B834" s="10"/>
+      <c r="C834" s="11" t="s">
+        <v>3734</v>
+      </c>
+      <c r="D834" s="10"/>
+      <c r="E834" s="11" t="s">
+        <v>3735</v>
+      </c>
+      <c r="F834" s="11" t="s">
+        <v>3736</v>
+      </c>
+      <c r="G834" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H834" s="11" t="s">
+        <v>2193</v>
+      </c>
+      <c r="I834" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J834" s="13" t="s">
+        <v>2194</v>
+      </c>
+      <c r="K834" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="L834" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="M834" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N834" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O834" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="P834" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q834" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R834" s="11" t="s">
+        <v>2195</v>
+      </c>
+      <c r="S834" s="11" t="s">
+        <v>2196</v>
+      </c>
+      <c r="T834" s="11" t="s">
+        <v>3648</v>
+      </c>
+      <c r="U834" s="12" t="s">
+        <v>2197</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="gdIIFF2rZN//3aeEAM7bx+VNAcgS91ZSlZmejbAlpa/HKiiHmYib97KN1SIlrMqfM448vEw3sMYNdan1aV0WWg==" saltValue="nOJedxNYFfAQxtkgoHF34Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7VT3RJmLIVOOtlo03dKxRDCHghQYVUprdJdAPGHRe+yp+QBZCoLU15BxamGiEM1cj///atm9hNdKrRNcmWji/g==" saltValue="DUmWGY84/vLdT2h1fVdAmw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B4CF18-A6F1-4869-B4D7-BF114C19DEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857E96CA-28F8-4679-BF4F-2159A19AE012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15486" uniqueCount="3737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15522" uniqueCount="3747">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11280,6 +11280,36 @@
   </si>
   <si>
     <t>Pet 90ml Avon Light Yellow Long Neck 19mm 11gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0461</t>
+  </si>
+  <si>
+    <t>MP0461.1</t>
+  </si>
+  <si>
+    <t>Pet 300ml Maha Bhringraj Clear 24mm 23gm Bottle</t>
+  </si>
+  <si>
+    <t>14 Pcs x 5 Rows = 70 Pcs</t>
+  </si>
+  <si>
+    <t>Maha Bhringraj</t>
+  </si>
+  <si>
+    <t>69.70 ± 1.50</t>
+  </si>
+  <si>
+    <t>182.00 ± 1.20</t>
+  </si>
+  <si>
+    <t>310.00 ± 5.00</t>
+  </si>
+  <si>
+    <t>MP0460.2</t>
+  </si>
+  <si>
+    <t>Pet 200ml Micro Brute Dark Milky White 25mm 18.5gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -12051,30 +12081,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E9A40003-BFBD-4173-A1EF-216266D31715}" name="Table1" displayName="Table1" ref="A1:U834" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U834" xr:uid="{E9A40003-BFBD-4173-A1EF-216266D31715}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{48DFFD69-1691-4ED0-83BD-89641CF78526}" name="Table1" displayName="Table1" ref="A1:U836" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U836" xr:uid="{48DFFD69-1691-4ED0-83BD-89641CF78526}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{167F97E5-93DE-4415-ABEB-9CDBDE5E95E2}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{FA3AD723-3CA3-478B-A464-80EEEDEDD46B}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{71A7CCA0-61E5-461A-B40F-FAAD67DB1199}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{FA52E6B9-C48E-4237-8966-A4BCAA6C752A}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{6CD63ED1-385D-4037-96B9-FABD3779F944}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{CC0F2CA0-CF32-4588-A5B8-4F20C2CED6E8}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{404AEF1E-08CD-4169-87FF-B9C182C04892}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{85264FD2-8C94-48D7-8E36-B77450EA1040}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{6A432CAF-17C5-4541-B093-F94260DFE085}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{0DA4C76E-F85D-4705-AE81-21C1A1C5DF38}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{B8ABADBD-AC93-4DD9-81EF-35C74C9A6BEB}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{92159696-E71F-4BB9-9E5D-DEF61EC9AF28}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{DE2E4AEF-C674-4E98-AD7E-5A33A1FFFF47}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{6B6D7EB2-D40B-49B9-AC26-1BEBD75CC18E}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{945CAB83-3F8C-48B0-9FC1-2B33954726AF}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{9645F2A1-37E9-4B00-82D0-345AA10906ED}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{0A4B9ECA-E4B0-43B9-9046-488697BE15E4}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{DF5F9B50-CC37-4BA8-BCFE-4EBE3CD5E938}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{3563AA30-ED16-4DF3-A513-B339922CB4A4}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{75EF55B3-B1E5-4231-9A28-6F7C08EFA1A4}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{C543C1BF-0A64-4D0C-8FA5-CDB7043F926B}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{9CB7C7A2-424F-43C9-B3F3-227B1BC29847}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{FEDD8B6B-B772-4008-B368-50767B2BF7D6}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{656010DD-9A5A-473F-A653-1AE191C12530}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{7B5ADFE1-2C5E-4722-99AE-2005E9DB71FA}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{6F234183-7B34-4F71-9B53-D86BAE78B7D1}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{E9BF3667-9E4B-40D0-948D-56179F218CAD}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{C0AA3DE4-F70F-4815-917B-97EDD0417490}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{05CDCEDE-4C55-4C72-8B3C-4F8712C68955}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{F349641A-F68F-4574-B158-49ACEFCEA3D8}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{CF4E1A06-D65B-4692-910B-905B776256A3}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{62FE4984-8AB0-4BAD-BA0A-548FE2089B14}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{8D404EA8-6EC0-4118-A41D-10524DB7DB9D}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{5BCE8CD2-85B9-4B69-B1C8-B80EBAF3F5BE}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{B5DFD32E-0559-41C0-ADE0-C5C0AD018DF4}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{1F8A38E7-29A9-4BC0-A3DC-B7B486922877}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{501C93B1-D18B-4005-A894-49D5AE150ED4}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{9A9275CC-AEA5-41A0-B92B-850212D1B315}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{A87ED61D-AFA7-45B7-83A7-EBE15715F69F}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{77D5F1D1-DE7F-4473-9A9A-A98FB10B1F2A}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{1CFD88F3-A961-43C2-9EE9-D32E0BAFEC79}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{A3B8D73F-5BE0-4791-9D1C-76B2254AAE1A}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12377,7 +12407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U834"/>
+  <dimension ref="A1:U836"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -64163,68 +64193,190 @@
       </c>
     </row>
     <row r="834" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A834" s="9">
+      <c r="A834" s="4">
         <v>833</v>
       </c>
-      <c r="B834" s="10"/>
-      <c r="C834" s="11" t="s">
+      <c r="B834" s="5"/>
+      <c r="C834" s="6" t="s">
         <v>3734</v>
       </c>
-      <c r="D834" s="10"/>
-      <c r="E834" s="11" t="s">
+      <c r="D834" s="5"/>
+      <c r="E834" s="6" t="s">
         <v>3735</v>
       </c>
-      <c r="F834" s="11" t="s">
+      <c r="F834" s="6" t="s">
         <v>3736</v>
       </c>
-      <c r="G834" s="11" t="s">
+      <c r="G834" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H834" s="11" t="s">
+      <c r="H834" s="6" t="s">
         <v>2193</v>
       </c>
-      <c r="I834" s="11" t="s">
+      <c r="I834" s="6" t="s">
         <v>27</v>
       </c>
       <c r="J834" s="13" t="s">
         <v>2194</v>
       </c>
-      <c r="K834" s="11" t="s">
+      <c r="K834" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L834" s="11" t="s">
+      <c r="L834" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="M834" s="11" t="s">
+      <c r="M834" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="N834" s="11" t="s">
+      <c r="N834" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="O834" s="11" t="s">
+      <c r="O834" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="P834" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q834" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R834" s="11" t="s">
+      <c r="P834" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q834" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R834" s="6" t="s">
         <v>2195</v>
       </c>
-      <c r="S834" s="11" t="s">
+      <c r="S834" s="6" t="s">
         <v>2196</v>
       </c>
-      <c r="T834" s="11" t="s">
+      <c r="T834" s="6" t="s">
         <v>3648</v>
       </c>
-      <c r="U834" s="12" t="s">
+      <c r="U834" s="7" t="s">
         <v>2197</v>
       </c>
     </row>
+    <row r="835" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A835" s="4">
+        <v>834</v>
+      </c>
+      <c r="B835" s="5"/>
+      <c r="C835" s="6" t="s">
+        <v>3737</v>
+      </c>
+      <c r="D835" s="5"/>
+      <c r="E835" s="6" t="s">
+        <v>3738</v>
+      </c>
+      <c r="F835" s="6" t="s">
+        <v>3739</v>
+      </c>
+      <c r="G835" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H835" s="6" t="s">
+        <v>2398</v>
+      </c>
+      <c r="I835" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J835" s="13" t="s">
+        <v>3740</v>
+      </c>
+      <c r="K835" s="6" t="s">
+        <v>3741</v>
+      </c>
+      <c r="L835" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="M835" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="N835" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="O835" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="P835" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q835" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R835" s="6" t="s">
+        <v>3742</v>
+      </c>
+      <c r="S835" s="6" t="s">
+        <v>3743</v>
+      </c>
+      <c r="T835" s="6" t="s">
+        <v>2316</v>
+      </c>
+      <c r="U835" s="7" t="s">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="836" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A836" s="9">
+        <v>835</v>
+      </c>
+      <c r="B836" s="10"/>
+      <c r="C836" s="11" t="s">
+        <v>3659</v>
+      </c>
+      <c r="D836" s="10"/>
+      <c r="E836" s="11" t="s">
+        <v>3745</v>
+      </c>
+      <c r="F836" s="11" t="s">
+        <v>3746</v>
+      </c>
+      <c r="G836" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="H836" s="11" t="s">
+        <v>2071</v>
+      </c>
+      <c r="I836" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="J836" s="13" t="s">
+        <v>2072</v>
+      </c>
+      <c r="K836" s="11" t="s">
+        <v>748</v>
+      </c>
+      <c r="L836" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="M836" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="N836" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="O836" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="P836" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q836" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R836" s="11" t="s">
+        <v>851</v>
+      </c>
+      <c r="S836" s="11" t="s">
+        <v>2073</v>
+      </c>
+      <c r="T836" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="U836" s="12" t="s">
+        <v>442</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7VT3RJmLIVOOtlo03dKxRDCHghQYVUprdJdAPGHRe+yp+QBZCoLU15BxamGiEM1cj///atm9hNdKrRNcmWji/g==" saltValue="DUmWGY84/vLdT2h1fVdAmw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8ZHrnmoDXFY7nEDgcTH9IhC3v7gvuM1yeJm9v7XOAygLNOah+RYnwvOcxHNoFvFwyMooLorIvNq3FDRmg3XdEw==" saltValue="khpruq9VnSuh68KuptnlVw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857E96CA-28F8-4679-BF4F-2159A19AE012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB34D5B3-10D3-40F2-925F-83530DB496D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15522" uniqueCount="3747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15540" uniqueCount="3755">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11310,6 +11310,30 @@
   </si>
   <si>
     <t>Pet 200ml Micro Brute Dark Milky White 25mm 18.5gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0467</t>
+  </si>
+  <si>
+    <t>MP0467.1</t>
+  </si>
+  <si>
+    <t>Pet 1Kg Avon Clear 83mm 40gm Jar</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>6 Pcs x 11 Rows = 66 Pcs</t>
+  </si>
+  <si>
+    <t>101.50 ± 1.20</t>
+  </si>
+  <si>
+    <t>159.10 ± 1.50</t>
+  </si>
+  <si>
+    <t>1120.00 ± 15.00</t>
   </si>
 </sst>
 </file>
@@ -12081,30 +12105,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{48DFFD69-1691-4ED0-83BD-89641CF78526}" name="Table1" displayName="Table1" ref="A1:U836" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U836" xr:uid="{48DFFD69-1691-4ED0-83BD-89641CF78526}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{198C2B32-E820-443F-8AA9-AA318F205628}" name="Table1" displayName="Table1" ref="A1:U837" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U837" xr:uid="{198C2B32-E820-443F-8AA9-AA318F205628}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{9CB7C7A2-424F-43C9-B3F3-227B1BC29847}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{FEDD8B6B-B772-4008-B368-50767B2BF7D6}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{656010DD-9A5A-473F-A653-1AE191C12530}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{7B5ADFE1-2C5E-4722-99AE-2005E9DB71FA}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{6F234183-7B34-4F71-9B53-D86BAE78B7D1}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{E9BF3667-9E4B-40D0-948D-56179F218CAD}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{C0AA3DE4-F70F-4815-917B-97EDD0417490}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{05CDCEDE-4C55-4C72-8B3C-4F8712C68955}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{F349641A-F68F-4574-B158-49ACEFCEA3D8}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{CF4E1A06-D65B-4692-910B-905B776256A3}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{62FE4984-8AB0-4BAD-BA0A-548FE2089B14}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{8D404EA8-6EC0-4118-A41D-10524DB7DB9D}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{5BCE8CD2-85B9-4B69-B1C8-B80EBAF3F5BE}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{B5DFD32E-0559-41C0-ADE0-C5C0AD018DF4}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{1F8A38E7-29A9-4BC0-A3DC-B7B486922877}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{501C93B1-D18B-4005-A894-49D5AE150ED4}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{9A9275CC-AEA5-41A0-B92B-850212D1B315}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{A87ED61D-AFA7-45B7-83A7-EBE15715F69F}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{77D5F1D1-DE7F-4473-9A9A-A98FB10B1F2A}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{1CFD88F3-A961-43C2-9EE9-D32E0BAFEC79}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{A3B8D73F-5BE0-4791-9D1C-76B2254AAE1A}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{F1DC9809-CD35-480D-B5CC-3CE0D838FB80}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{EF8A71B7-EA24-46B6-BA2E-B477B9282F99}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{5D72C29D-CCA2-45AE-8C82-4AE46442AA38}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{16B6B7A9-AB31-4C8B-9A73-99E3EB1EB533}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{2896E054-043D-471A-9538-CC8A17999947}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{C45CBF93-45D4-4571-8D1A-7AF1D70D879F}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{D31857AC-E4A0-4B4E-831C-2AC5E5BBC0B3}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{B5F24D44-FBBA-4A0C-8787-23D5A167EA0E}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{D75D56CF-F482-4F2F-AC38-DF4F26502E73}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{5A496F01-042E-4226-A3A5-8968528E67F0}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{ABCB9372-595B-496A-83F0-14BB9D41A1E3}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{AF1C8492-0C41-44F8-B339-09AAC646276E}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{1FF3CBFC-7BF6-46BE-8314-EB24F77ED933}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{B109982B-6F54-40AC-8EB6-A74F7E050B1C}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{68ED9F20-92E0-4370-84E6-B3331586E0A3}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{936B9A6B-9C77-4296-B941-E0FD5627B7FF}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{AE8192EB-6D58-42C9-90E4-BE1E98DFCED7}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{F12FB804-AAB3-49FB-A595-57CB60F5FE48}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{51CFC130-50C7-4EE6-85FC-3C985DD1F147}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{68F2812B-7A5F-4900-AB5B-AE42EEFE69BE}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{72BA84B4-9161-4D1D-9EC8-10E8F17C4902}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12407,7 +12431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U836"/>
+  <dimension ref="A1:U837"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -64315,68 +64339,129 @@
       </c>
     </row>
     <row r="836" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A836" s="9">
+      <c r="A836" s="4">
         <v>835</v>
       </c>
-      <c r="B836" s="10"/>
-      <c r="C836" s="11" t="s">
+      <c r="B836" s="5"/>
+      <c r="C836" s="6" t="s">
         <v>3659</v>
       </c>
-      <c r="D836" s="10"/>
-      <c r="E836" s="11" t="s">
+      <c r="D836" s="5"/>
+      <c r="E836" s="6" t="s">
         <v>3745</v>
       </c>
-      <c r="F836" s="11" t="s">
+      <c r="F836" s="6" t="s">
         <v>3746</v>
       </c>
-      <c r="G836" s="11" t="s">
+      <c r="G836" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="H836" s="11" t="s">
+      <c r="H836" s="6" t="s">
         <v>2071</v>
       </c>
-      <c r="I836" s="11" t="s">
+      <c r="I836" s="6" t="s">
         <v>99</v>
       </c>
       <c r="J836" s="13" t="s">
         <v>2072</v>
       </c>
-      <c r="K836" s="11" t="s">
+      <c r="K836" s="6" t="s">
         <v>748</v>
       </c>
-      <c r="L836" s="11" t="s">
+      <c r="L836" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="M836" s="11" t="s">
+      <c r="M836" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="N836" s="11" t="s">
+      <c r="N836" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="O836" s="11" t="s">
+      <c r="O836" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="P836" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q836" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R836" s="11" t="s">
+      <c r="P836" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q836" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R836" s="6" t="s">
         <v>851</v>
       </c>
-      <c r="S836" s="11" t="s">
+      <c r="S836" s="6" t="s">
         <v>2073</v>
       </c>
-      <c r="T836" s="11" t="s">
+      <c r="T836" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="U836" s="12" t="s">
+      <c r="U836" s="7" t="s">
         <v>442</v>
       </c>
     </row>
+    <row r="837" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A837" s="9">
+        <v>836</v>
+      </c>
+      <c r="B837" s="10"/>
+      <c r="C837" s="11" t="s">
+        <v>3747</v>
+      </c>
+      <c r="D837" s="10"/>
+      <c r="E837" s="11" t="s">
+        <v>3748</v>
+      </c>
+      <c r="F837" s="11" t="s">
+        <v>3749</v>
+      </c>
+      <c r="G837" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H837" s="11" t="s">
+        <v>3750</v>
+      </c>
+      <c r="I837" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="J837" s="13" t="s">
+        <v>3751</v>
+      </c>
+      <c r="K837" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="L837" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="M837" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="N837" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="O837" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="P837" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q837" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="R837" s="11" t="s">
+        <v>3752</v>
+      </c>
+      <c r="S837" s="11" t="s">
+        <v>3753</v>
+      </c>
+      <c r="T837" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="U837" s="12" t="s">
+        <v>3754</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8ZHrnmoDXFY7nEDgcTH9IhC3v7gvuM1yeJm9v7XOAygLNOah+RYnwvOcxHNoFvFwyMooLorIvNq3FDRmg3XdEw==" saltValue="khpruq9VnSuh68KuptnlVw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="+tXiiqUI5zqREd9ZMwS5ztFxbO2igNHiL9Vu0jmZ0c/dp/+ATyL/idfWkvDHlWRFFtsWrNdVy+y+7q/yNp1DLw==" saltValue="dOIYShilZHE/DmQ5UDda/g==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB34D5B3-10D3-40F2-925F-83530DB496D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE74429-746E-4142-8468-C5C47A4502BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15540" uniqueCount="3755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15558" uniqueCount="3757">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11334,6 +11334,12 @@
   </si>
   <si>
     <t>1120.00 ± 15.00</t>
+  </si>
+  <si>
+    <t>MP0014.17</t>
+  </si>
+  <si>
+    <t>Pet 60ml Round Dark Milky white 25mm 10.0gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -12105,30 +12111,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{198C2B32-E820-443F-8AA9-AA318F205628}" name="Table1" displayName="Table1" ref="A1:U837" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U837" xr:uid="{198C2B32-E820-443F-8AA9-AA318F205628}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D9B9BFD7-C55E-46DE-85EC-6B1622B321C2}" name="Table1" displayName="Table1" ref="A1:U838" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U838" xr:uid="{D9B9BFD7-C55E-46DE-85EC-6B1622B321C2}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{F1DC9809-CD35-480D-B5CC-3CE0D838FB80}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{EF8A71B7-EA24-46B6-BA2E-B477B9282F99}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{5D72C29D-CCA2-45AE-8C82-4AE46442AA38}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{16B6B7A9-AB31-4C8B-9A73-99E3EB1EB533}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{2896E054-043D-471A-9538-CC8A17999947}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{C45CBF93-45D4-4571-8D1A-7AF1D70D879F}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{D31857AC-E4A0-4B4E-831C-2AC5E5BBC0B3}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{B5F24D44-FBBA-4A0C-8787-23D5A167EA0E}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{D75D56CF-F482-4F2F-AC38-DF4F26502E73}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{5A496F01-042E-4226-A3A5-8968528E67F0}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{ABCB9372-595B-496A-83F0-14BB9D41A1E3}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{AF1C8492-0C41-44F8-B339-09AAC646276E}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{1FF3CBFC-7BF6-46BE-8314-EB24F77ED933}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{B109982B-6F54-40AC-8EB6-A74F7E050B1C}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{68ED9F20-92E0-4370-84E6-B3331586E0A3}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{936B9A6B-9C77-4296-B941-E0FD5627B7FF}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{AE8192EB-6D58-42C9-90E4-BE1E98DFCED7}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{F12FB804-AAB3-49FB-A595-57CB60F5FE48}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{51CFC130-50C7-4EE6-85FC-3C985DD1F147}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{68F2812B-7A5F-4900-AB5B-AE42EEFE69BE}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{72BA84B4-9161-4D1D-9EC8-10E8F17C4902}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{D34B1BBE-0AA4-41AF-846D-8F62CE7E4441}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{5772256A-B521-40CD-B3A8-139840CB89C7}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{7D29E0A0-3A3E-471A-88DE-859DA3019E27}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{759E212D-5D73-4DFA-A738-C66CE1A4AAAB}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{2D74E3BF-E3B4-427A-A770-85132BB8AB1E}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{E11247FA-6560-4A70-BA6A-4F33CE86EE4C}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{D36AA78B-1D24-43AA-BBB5-E1E3FC404D1C}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{398CB402-8BA6-4414-9D63-430D66B1F8A1}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{47661555-DCD3-48E1-BE13-DEE1366557A8}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{FFEA18A4-F4AC-4B2A-A14B-2F943FA96A5F}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{59152D15-85F4-41D7-8CAB-41905F2A8972}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{D992B8C8-A4D2-471C-8B99-22EA743112E2}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{45955C21-5D62-4D9A-A94D-A46D6F56C835}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{65AB64C0-9CFB-421E-B609-82E961B268BA}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{8EA04DAE-75A7-4215-8744-B4C8EE32A9D4}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{D0B836C6-901C-4C94-B6A5-DD0CB354D2DE}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{F2931A6C-2180-417A-BE60-A350E8600806}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{4FBC82EF-CF68-485D-A125-40337C315F45}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{B28F63F6-C61E-4E3D-BB97-299E095EA87E}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{8C4D1CDB-1E19-42C1-B447-815CC94E8F99}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{35F83CC5-1E37-421E-A100-CCA2D01EA9C0}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12431,7 +12437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U837"/>
+  <dimension ref="A1:U838"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -64400,68 +64406,129 @@
       </c>
     </row>
     <row r="837" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A837" s="9">
+      <c r="A837" s="4">
         <v>836</v>
       </c>
-      <c r="B837" s="10"/>
-      <c r="C837" s="11" t="s">
+      <c r="B837" s="5"/>
+      <c r="C837" s="6" t="s">
         <v>3747</v>
       </c>
-      <c r="D837" s="10"/>
-      <c r="E837" s="11" t="s">
+      <c r="D837" s="5"/>
+      <c r="E837" s="6" t="s">
         <v>3748</v>
       </c>
-      <c r="F837" s="11" t="s">
+      <c r="F837" s="6" t="s">
         <v>3749</v>
       </c>
-      <c r="G837" s="11" t="s">
+      <c r="G837" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H837" s="11" t="s">
+      <c r="H837" s="6" t="s">
         <v>3750</v>
       </c>
-      <c r="I837" s="11" t="s">
+      <c r="I837" s="6" t="s">
         <v>269</v>
       </c>
       <c r="J837" s="13" t="s">
         <v>3751</v>
       </c>
-      <c r="K837" s="11" t="s">
+      <c r="K837" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L837" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="M837" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="N837" s="11" t="s">
+      <c r="L837" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M837" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N837" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="O837" s="11" t="s">
+      <c r="O837" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="P837" s="11" t="s">
+      <c r="P837" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="Q837" s="11" t="s">
+      <c r="Q837" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="R837" s="11" t="s">
+      <c r="R837" s="6" t="s">
         <v>3752</v>
       </c>
-      <c r="S837" s="11" t="s">
+      <c r="S837" s="6" t="s">
         <v>3753</v>
       </c>
-      <c r="T837" s="11" t="s">
+      <c r="T837" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="U837" s="12" t="s">
+      <c r="U837" s="7" t="s">
         <v>3754</v>
       </c>
     </row>
+    <row r="838" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A838" s="9">
+        <v>837</v>
+      </c>
+      <c r="B838" s="10"/>
+      <c r="C838" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="D838" s="10"/>
+      <c r="E838" s="11" t="s">
+        <v>3755</v>
+      </c>
+      <c r="F838" s="11" t="s">
+        <v>3756</v>
+      </c>
+      <c r="G838" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H838" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I838" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="J838" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="K838" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="L838" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="M838" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="N838" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O838" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="P838" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q838" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R838" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="S838" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="T838" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="U838" s="12" t="s">
+        <v>389</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+tXiiqUI5zqREd9ZMwS5ztFxbO2igNHiL9Vu0jmZ0c/dp/+ATyL/idfWkvDHlWRFFtsWrNdVy+y+7q/yNp1DLw==" saltValue="dOIYShilZHE/DmQ5UDda/g==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="z0HWZPazZHHwTJBXKS9PcP/70vyj2n9Kx2c/V5XwaUYOeegdlquChduNo2raeFfNucRnZgNTfx5UaMhJSMDhQA==" saltValue="HRrCqjvNwSjHbyhmM0LICw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3342B3-DA90-4E05-A191-37A8D37545A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BAF9E4-CC3F-4D16-96EE-B1B2DA28472D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15612" uniqueCount="3763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15631" uniqueCount="3765">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11358,6 +11358,12 @@
   </si>
   <si>
     <t>6 Pcs x 13 Rows = 78 Pcs</t>
+  </si>
+  <si>
+    <t>MP0034.3</t>
+  </si>
+  <si>
+    <t>Pet 170ml Round Dark Milky White 25mm 16gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -12129,30 +12135,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FB9D2C48-27CD-4FB2-AC86-9C69EC1E6DA0}" name="Table1" displayName="Table1" ref="A1:U841" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U841" xr:uid="{FB9D2C48-27CD-4FB2-AC86-9C69EC1E6DA0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{221D04FD-581C-48B9-A36F-0B9D09C87678}" name="Table1" displayName="Table1" ref="A1:U842" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U842" xr:uid="{221D04FD-581C-48B9-A36F-0B9D09C87678}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{87CC1280-31F1-4A37-A360-0ACB0BCC946B}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{D4D38B69-491A-4CBD-8651-E57BFE53C8A9}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{9E6000D8-4EC0-4F59-883A-7B7F7A19B24C}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{C691FED6-E841-4AC4-BADB-B2585495E900}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{FFB8952C-85A1-47F8-8778-D2B2A4851E5F}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{A2E371A3-F277-4C7F-91F0-3B59340749C5}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{FC2D0718-186C-4DFA-BF32-F15267EE862E}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{E619BE14-AE1D-489A-8D8B-DB39800CFE2D}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{9C9F289D-3943-471D-A9E7-E344A641D48B}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{4DD3B9DF-2FEB-4CED-A1E2-C8202B206576}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{702242FE-B5A8-4434-8031-FB83674EF6E5}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{20A971F1-C5CC-428F-B0D5-FFB67E049111}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{E9870B63-A27C-44E1-9E60-318EAA77C4C1}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{4402AA13-A022-462A-9092-6D455C8144A9}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{733C35FF-BC9D-46F5-B93D-14A5CFE034C4}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{8AE82CC3-F577-4F8B-89CE-9F706F85C662}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{0B7B62AF-575C-47D7-946B-3190727CA9B6}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{F8660E1D-E013-46A0-AF00-4D130CC00C7B}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{DFA6F47F-6557-4ED6-A64C-7723C1E029B7}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{B49985F2-8238-4C00-ADC5-AA065BFC0FAE}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{CBB11E5D-43DA-49A3-85E6-7480D2E00269}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{78259187-5B23-412F-AFC7-1DAED901DA7F}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{298BB2CB-1570-4839-93B2-18C816D4CC37}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{C474BFE1-2191-4AF4-8649-67B4DE265FF2}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{43863B1D-F74B-452E-A20D-B5C84B04D549}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{ADC2B471-91E1-4749-8177-F70BF3AEAF57}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{2B56374E-C009-4724-82F7-8FD6722F90CE}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{DCB3DC62-B550-40D0-AD85-91DA4AFA1A0E}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{F9D2B2AC-99B3-43B6-B0FF-16655ACBF009}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{81588809-C944-4D6D-8BA1-20059086DF52}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{C7C12444-BFE7-4C77-97C6-D88CA2C3CCAA}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{0C4E1137-D326-4D24-8997-69DB63FA8DC9}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{9B443B6F-FA0D-430F-9F9D-F4AC2B60FA61}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{7F7B2E5C-C89D-482A-BF08-A568B79E191F}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{F8124F0D-BBC8-4064-B607-B2CB948ECF57}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{D2DAA85D-7AC6-497C-9517-5CD469224C6A}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{CFFD78D1-C6CC-4FF9-ADC1-B8D37E1C0D00}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{401E7782-10F9-47D9-8FFC-4F0DBEF28CDD}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{75E69BBA-6B06-42A7-AFFB-3F05C26B6D8B}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{0D2EE5A0-2114-40ED-8AD3-CA4336982665}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{2570CAC8-039A-4017-A70D-6CDF3E49AD6E}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{9DE19422-C448-41B7-87DB-935455179922}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12455,7 +12461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U841"/>
+  <dimension ref="A1:U842"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -14999,7 +15005,9 @@
       <c r="A41" s="4">
         <v>40</v>
       </c>
-      <c r="B41" s="5"/>
+      <c r="B41" s="6" t="s">
+        <v>325</v>
+      </c>
       <c r="C41" s="6" t="s">
         <v>443</v>
       </c>
@@ -64668,67 +64676,129 @@
       </c>
     </row>
     <row r="841" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A841" s="9">
+      <c r="A841" s="4">
         <v>840</v>
       </c>
-      <c r="B841" s="10"/>
-      <c r="C841" s="11" t="s">
+      <c r="B841" s="5"/>
+      <c r="C841" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="D841" s="10"/>
-      <c r="E841" s="11" t="s">
+      <c r="D841" s="5"/>
+      <c r="E841" s="6" t="s">
         <v>3760</v>
       </c>
-      <c r="F841" s="11" t="s">
+      <c r="F841" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="G841" s="11" t="s">
+      <c r="G841" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H841" s="11" t="s">
+      <c r="H841" s="6" t="s">
         <v>3761</v>
       </c>
-      <c r="I841" s="11" t="s">
+      <c r="I841" s="6" t="s">
         <v>269</v>
       </c>
       <c r="J841" s="13" t="s">
         <v>3762</v>
       </c>
-      <c r="K841" s="11" t="s">
+      <c r="K841" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="L841" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="M841" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="N841" s="11" t="s">
+      <c r="L841" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M841" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N841" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="O841" s="11" t="s">
+      <c r="O841" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="P841" s="11" t="s">
+      <c r="P841" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="Q841" s="11" t="s">
+      <c r="Q841" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="R841" s="11" t="s">
+      <c r="R841" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="S841" s="11" t="s">
+      <c r="S841" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="T841" s="11" t="s">
+      <c r="T841" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="U841" s="12" t="s">
+      <c r="U841" s="7" t="s">
         <v>453</v>
       </c>
     </row>
+    <row r="842" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A842" s="9">
+        <v>841</v>
+      </c>
+      <c r="B842" s="10"/>
+      <c r="C842" s="11" t="s">
+        <v>2748</v>
+      </c>
+      <c r="D842" s="10"/>
+      <c r="E842" s="11" t="s">
+        <v>3763</v>
+      </c>
+      <c r="F842" s="11" t="s">
+        <v>3764</v>
+      </c>
+      <c r="G842" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H842" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="I842" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J842" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="K842" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="L842" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="M842" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="N842" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="O842" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="P842" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q842" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R842" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="S842" s="11" t="s">
+        <v>2752</v>
+      </c>
+      <c r="T842" s="11" t="s">
+        <v>2753</v>
+      </c>
+      <c r="U842" s="12" t="s">
+        <v>427</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="8KiwyPdBmUFrfN6ZYTwX0KlZLt+Ri4X4dCDkg6waZpHW1l4dc3j0EgIaqAU+3QZ1bYhLyDvDHMH60RA69JWD1A==" saltValue="OvaU5NvBiXdwste4bsU4CQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BAF9E4-CC3F-4D16-96EE-B1B2DA28472D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1F0A55-8524-47DA-990B-F19B9EFB4FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15631" uniqueCount="3765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15631" uniqueCount="3766">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11352,6 +11352,9 @@
   </si>
   <si>
     <t>MP0208.2</t>
+  </si>
+  <si>
+    <t>Pet 1L Savlon Clear 28mm 48gm Bottle</t>
   </si>
   <si>
     <t>78</t>
@@ -12135,30 +12138,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{221D04FD-581C-48B9-A36F-0B9D09C87678}" name="Table1" displayName="Table1" ref="A1:U842" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U842" xr:uid="{221D04FD-581C-48B9-A36F-0B9D09C87678}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A80A0783-5559-4B48-ADE2-337889679307}" name="Table1" displayName="Table1" ref="A1:U842" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U842" xr:uid="{A80A0783-5559-4B48-ADE2-337889679307}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{78259187-5B23-412F-AFC7-1DAED901DA7F}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{298BB2CB-1570-4839-93B2-18C816D4CC37}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{C474BFE1-2191-4AF4-8649-67B4DE265FF2}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{43863B1D-F74B-452E-A20D-B5C84B04D549}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{ADC2B471-91E1-4749-8177-F70BF3AEAF57}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{2B56374E-C009-4724-82F7-8FD6722F90CE}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{DCB3DC62-B550-40D0-AD85-91DA4AFA1A0E}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{F9D2B2AC-99B3-43B6-B0FF-16655ACBF009}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{81588809-C944-4D6D-8BA1-20059086DF52}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{C7C12444-BFE7-4C77-97C6-D88CA2C3CCAA}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{0C4E1137-D326-4D24-8997-69DB63FA8DC9}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{9B443B6F-FA0D-430F-9F9D-F4AC2B60FA61}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{7F7B2E5C-C89D-482A-BF08-A568B79E191F}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{F8124F0D-BBC8-4064-B607-B2CB948ECF57}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{D2DAA85D-7AC6-497C-9517-5CD469224C6A}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{CFFD78D1-C6CC-4FF9-ADC1-B8D37E1C0D00}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{401E7782-10F9-47D9-8FFC-4F0DBEF28CDD}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{75E69BBA-6B06-42A7-AFFB-3F05C26B6D8B}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{0D2EE5A0-2114-40ED-8AD3-CA4336982665}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{2570CAC8-039A-4017-A70D-6CDF3E49AD6E}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{9DE19422-C448-41B7-87DB-935455179922}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{7D4D5764-AA21-431C-B9F8-DAE0A28E1BC0}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{3B1AC749-49F0-491C-B6DB-324BB61AB0D9}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{1C70C5EC-CE1B-4AD7-9A68-F274D382B7CB}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{9E55C6B0-CC57-4E09-B01C-9F4F16DD88F9}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{6AACACEB-6395-43A2-A8A3-D979FD28156A}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{0F8DFEC9-4272-4AB4-B997-10A6461E1AA0}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{9A810187-EB31-4471-B0B1-48DF31CDE55A}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{D5CFFD03-D512-43A1-8AD0-437B567EC520}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{12BEE41C-46E4-4C77-BA9E-0AB78A574229}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{6B94D9A7-1196-40C8-A834-70428C1BE7A9}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{3C83CF24-3A4E-47A9-8143-79FA1B3F881F}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{415520D6-1121-4558-B34C-0BA4769B41D4}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{3A727C0D-3A97-48FA-A25C-04D0ACFFE1BF}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{31A185A4-D498-4906-9137-4732EA0EE51B}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{9C6CBE3F-A62B-44BB-AB10-5126A8215485}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{FCD6BE19-9E1B-41A8-9CB4-3834F91CAEE3}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{BB6E2E96-65D3-4317-BBA5-2AF35FB64FCE}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{518D1CC4-DE15-45E6-B23C-79820099A27D}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{217E127B-8BF3-46EE-869B-803193BB10AF}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{69F8C39E-E597-4919-BF0E-17BB6006E6E4}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{9DEDBB42-7875-4550-91E3-E211BF99DDE5}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -64688,19 +64691,19 @@
         <v>3760</v>
       </c>
       <c r="F841" s="6" t="s">
-        <v>446</v>
+        <v>3761</v>
       </c>
       <c r="G841" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H841" s="6" t="s">
-        <v>3761</v>
+        <v>3762</v>
       </c>
       <c r="I841" s="6" t="s">
         <v>269</v>
       </c>
       <c r="J841" s="13" t="s">
-        <v>3762</v>
+        <v>3763</v>
       </c>
       <c r="K841" s="6" t="s">
         <v>449</v>
@@ -64746,10 +64749,10 @@
       </c>
       <c r="D842" s="10"/>
       <c r="E842" s="11" t="s">
-        <v>3763</v>
+        <v>3764</v>
       </c>
       <c r="F842" s="11" t="s">
-        <v>3764</v>
+        <v>3765</v>
       </c>
       <c r="G842" s="11" t="s">
         <v>25</v>
@@ -64798,7 +64801,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8KiwyPdBmUFrfN6ZYTwX0KlZLt+Ri4X4dCDkg6waZpHW1l4dc3j0EgIaqAU+3QZ1bYhLyDvDHMH60RA69JWD1A==" saltValue="OvaU5NvBiXdwste4bsU4CQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="W55NgEFNRC91yFRL3hMuVLLqETL1UD/RbGW5StpjXuJvxv24ZNdffzRldGWOLGAWlZbg0gAt3q9/horlLNjpcg==" saltValue="xC78r4LI/QYTXzPsv8UKzA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1F0A55-8524-47DA-990B-F19B9EFB4FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96EBC49-CE73-4EB0-A6FB-3D6C272EDD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15631" uniqueCount="3766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15667" uniqueCount="3774">
   <si>
     <t>PDS No.</t>
   </si>
@@ -9910,7 +9910,7 @@
     <t>MP0033.3</t>
   </si>
   <si>
-    <t>Pet 170ml Oval Milky White 25mm 16.2gm Bottle</t>
+    <t>Pet 170ml Oval Dark Milky White 25mm 16.2gm Bottle</t>
   </si>
   <si>
     <t>MP0039</t>
@@ -11367,6 +11367,30 @@
   </si>
   <si>
     <t>Pet 170ml Round Dark Milky White 25mm 16gm Bottle</t>
+  </si>
+  <si>
+    <t>MP0391.4</t>
+  </si>
+  <si>
+    <t>Pet 120CC ASB Tablet Dark Milky White 38mm 18gm Jar MPCI</t>
+  </si>
+  <si>
+    <t>MP0452</t>
+  </si>
+  <si>
+    <t>MP0452.1</t>
+  </si>
+  <si>
+    <t>Pet 200ml Round Syrup Dark Milky White 38mm 20gm Bottle</t>
+  </si>
+  <si>
+    <t>53.00 ± 0.80</t>
+  </si>
+  <si>
+    <t>135.5 ± 1.20</t>
+  </si>
+  <si>
+    <t>232.00 ± 5.00</t>
   </si>
 </sst>
 </file>
@@ -12138,30 +12162,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A80A0783-5559-4B48-ADE2-337889679307}" name="Table1" displayName="Table1" ref="A1:U842" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U842" xr:uid="{A80A0783-5559-4B48-ADE2-337889679307}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F478626-1541-42B2-AE40-5BEAAA243091}" name="Table1" displayName="Table1" ref="A1:U844" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U844" xr:uid="{1F478626-1541-42B2-AE40-5BEAAA243091}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{7D4D5764-AA21-431C-B9F8-DAE0A28E1BC0}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{3B1AC749-49F0-491C-B6DB-324BB61AB0D9}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{1C70C5EC-CE1B-4AD7-9A68-F274D382B7CB}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{9E55C6B0-CC57-4E09-B01C-9F4F16DD88F9}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{6AACACEB-6395-43A2-A8A3-D979FD28156A}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{0F8DFEC9-4272-4AB4-B997-10A6461E1AA0}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{9A810187-EB31-4471-B0B1-48DF31CDE55A}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{D5CFFD03-D512-43A1-8AD0-437B567EC520}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{12BEE41C-46E4-4C77-BA9E-0AB78A574229}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{6B94D9A7-1196-40C8-A834-70428C1BE7A9}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{3C83CF24-3A4E-47A9-8143-79FA1B3F881F}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{415520D6-1121-4558-B34C-0BA4769B41D4}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{3A727C0D-3A97-48FA-A25C-04D0ACFFE1BF}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{31A185A4-D498-4906-9137-4732EA0EE51B}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{9C6CBE3F-A62B-44BB-AB10-5126A8215485}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{FCD6BE19-9E1B-41A8-9CB4-3834F91CAEE3}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{BB6E2E96-65D3-4317-BBA5-2AF35FB64FCE}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{518D1CC4-DE15-45E6-B23C-79820099A27D}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{217E127B-8BF3-46EE-869B-803193BB10AF}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{69F8C39E-E597-4919-BF0E-17BB6006E6E4}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{9DEDBB42-7875-4550-91E3-E211BF99DDE5}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{3ADC5E77-7721-4148-94CB-8CE5E8F51697}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{5DB2CA48-A2E4-4F45-B9AA-FFEB341E3219}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{CF92D109-D260-4C07-B9F0-A8C84BBD73C1}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{88CFD17A-B2D1-468F-83DF-8FA0631BED4B}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{4AFD21B0-919F-47D8-A9C5-DD596902EE54}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{0B70B357-08DD-4876-9621-5A5AD54C0972}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{C5FA65AE-1053-4439-B26B-07077403B72A}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{718FECE1-1D74-4B0C-AEC9-9236248A4E97}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{B1DBFE2C-5859-451E-B906-C956D31DA552}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{91E23A17-8C2B-4322-9F40-B97740478105}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{D2FA24E7-AD69-46AF-B3AB-B6C36CE7F72C}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{97791775-4A69-4EF8-81B9-811339740273}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{FB72876F-6000-4CB9-AB11-D915E18A815D}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{9B4E51B2-F0C6-42BA-9063-46195F99A429}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{9F8203AD-6FBC-4265-9D7D-D06A8A5B8493}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{2947E91C-467C-414C-BA3E-83A46B0DA6EB}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{011A1B0E-8FB2-4138-9B4E-2788013ED95E}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{59B4844D-2A16-408A-9DF4-CDCC9CB80715}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{D42E53D0-9D41-4199-9F0C-7262C16A9EBA}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{6BB2C8D6-9669-4F0F-AE74-5B9753A44E7E}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{6E1530B5-6DFC-499A-8334-C13D198E54CB}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12464,7 +12488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U842"/>
+  <dimension ref="A1:U844"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -64740,68 +64764,190 @@
       </c>
     </row>
     <row r="842" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A842" s="9">
+      <c r="A842" s="4">
         <v>841</v>
       </c>
-      <c r="B842" s="10"/>
-      <c r="C842" s="11" t="s">
+      <c r="B842" s="5"/>
+      <c r="C842" s="6" t="s">
         <v>2748</v>
       </c>
-      <c r="D842" s="10"/>
-      <c r="E842" s="11" t="s">
+      <c r="D842" s="5"/>
+      <c r="E842" s="6" t="s">
         <v>3764</v>
       </c>
-      <c r="F842" s="11" t="s">
+      <c r="F842" s="6" t="s">
         <v>3765</v>
       </c>
-      <c r="G842" s="11" t="s">
+      <c r="G842" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H842" s="11" t="s">
+      <c r="H842" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="I842" s="11" t="s">
+      <c r="I842" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J842" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="K842" s="11" t="s">
+      <c r="K842" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="L842" s="11" t="s">
+      <c r="L842" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="M842" s="11" t="s">
+      <c r="M842" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="N842" s="11" t="s">
+      <c r="N842" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="O842" s="11" t="s">
+      <c r="O842" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="P842" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q842" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R842" s="11" t="s">
+      <c r="P842" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q842" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R842" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="S842" s="11" t="s">
+      <c r="S842" s="6" t="s">
         <v>2752</v>
       </c>
-      <c r="T842" s="11" t="s">
+      <c r="T842" s="6" t="s">
         <v>2753</v>
       </c>
-      <c r="U842" s="12" t="s">
+      <c r="U842" s="7" t="s">
         <v>427</v>
       </c>
     </row>
+    <row r="843" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A843" s="4">
+        <v>842</v>
+      </c>
+      <c r="B843" s="5"/>
+      <c r="C843" s="6" t="s">
+        <v>3261</v>
+      </c>
+      <c r="D843" s="5"/>
+      <c r="E843" s="6" t="s">
+        <v>3766</v>
+      </c>
+      <c r="F843" s="6" t="s">
+        <v>3767</v>
+      </c>
+      <c r="G843" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H843" s="6" t="s">
+        <v>3059</v>
+      </c>
+      <c r="I843" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J843" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="K843" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="L843" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M843" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N843" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="O843" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P843" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q843" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R843" s="6" t="s">
+        <v>3264</v>
+      </c>
+      <c r="S843" s="6" t="s">
+        <v>3265</v>
+      </c>
+      <c r="T843" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="U843" s="7" t="s">
+        <v>3266</v>
+      </c>
+    </row>
+    <row r="844" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A844" s="9">
+        <v>843</v>
+      </c>
+      <c r="B844" s="10"/>
+      <c r="C844" s="11" t="s">
+        <v>3768</v>
+      </c>
+      <c r="D844" s="10"/>
+      <c r="E844" s="11" t="s">
+        <v>3769</v>
+      </c>
+      <c r="F844" s="11" t="s">
+        <v>3770</v>
+      </c>
+      <c r="G844" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H844" s="11" t="s">
+        <v>674</v>
+      </c>
+      <c r="I844" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J844" s="13" t="s">
+        <v>2804</v>
+      </c>
+      <c r="K844" s="11" t="s">
+        <v>2805</v>
+      </c>
+      <c r="L844" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="M844" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="N844" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="O844" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="P844" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q844" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R844" s="11" t="s">
+        <v>3771</v>
+      </c>
+      <c r="S844" s="11" t="s">
+        <v>3772</v>
+      </c>
+      <c r="T844" s="11" t="s">
+        <v>2546</v>
+      </c>
+      <c r="U844" s="12" t="s">
+        <v>3773</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="W55NgEFNRC91yFRL3hMuVLLqETL1UD/RbGW5StpjXuJvxv24ZNdffzRldGWOLGAWlZbg0gAt3q9/horlLNjpcg==" saltValue="xC78r4LI/QYTXzPsv8UKzA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="s2rP42dTQE53C1eVQVdk7+lZMwEGQfiBYM9D+hFvTLLhwJPZSCaz79aUKRXnIYr9OSu8PeGekr1b4xF+XZVXKA==" saltValue="S2KG9+uJttSJ2A8ZPczvdQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96EBC49-CE73-4EB0-A6FB-3D6C272EDD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E86B30-C93A-4427-9163-9B86CFEF3152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15667" uniqueCount="3774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15685" uniqueCount="3781">
   <si>
     <t>PDS No.</t>
   </si>
@@ -7937,7 +7937,7 @@
     <t>MP0358.3</t>
   </si>
   <si>
-    <t>Pet 100ml Round Milky White 24mm 20gm CR16.5 Bottle</t>
+    <t>Pet 100ml Round Dark Milky White 24mm 20gm CR16.5 Bottle</t>
   </si>
   <si>
     <t>MP0368</t>
@@ -11391,6 +11391,28 @@
   </si>
   <si>
     <t>232.00 ± 5.00</t>
+  </si>
+  <si>
+    <t>MP0473</t>
+  </si>
+  <si>
+    <t>MP0473.1</t>
+  </si>
+  <si>
+    <t>Pet 160ml Supreme Oil Clear 25mm 14gm Bottle</t>
+  </si>
+  <si>
+    <t>488</t>
+  </si>
+  <si>
+    <t>14 Pcs x 5 Rows = 70 Pcs
+13 Pcs x 4 Rows = 52 Pcs</t>
+  </si>
+  <si>
+    <t>Supreme Oil</t>
+  </si>
+  <si>
+    <t>163.00 ± 5.00</t>
   </si>
 </sst>
 </file>
@@ -12162,30 +12184,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F478626-1541-42B2-AE40-5BEAAA243091}" name="Table1" displayName="Table1" ref="A1:U844" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U844" xr:uid="{1F478626-1541-42B2-AE40-5BEAAA243091}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FDA1552-4173-4B4C-9DEF-589E5CC9669D}" name="Table1" displayName="Table1" ref="A1:U845" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U845" xr:uid="{0FDA1552-4173-4B4C-9DEF-589E5CC9669D}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{3ADC5E77-7721-4148-94CB-8CE5E8F51697}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{5DB2CA48-A2E4-4F45-B9AA-FFEB341E3219}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{CF92D109-D260-4C07-B9F0-A8C84BBD73C1}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{88CFD17A-B2D1-468F-83DF-8FA0631BED4B}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{4AFD21B0-919F-47D8-A9C5-DD596902EE54}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{0B70B357-08DD-4876-9621-5A5AD54C0972}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{C5FA65AE-1053-4439-B26B-07077403B72A}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{718FECE1-1D74-4B0C-AEC9-9236248A4E97}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{B1DBFE2C-5859-451E-B906-C956D31DA552}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{91E23A17-8C2B-4322-9F40-B97740478105}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{D2FA24E7-AD69-46AF-B3AB-B6C36CE7F72C}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{97791775-4A69-4EF8-81B9-811339740273}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{FB72876F-6000-4CB9-AB11-D915E18A815D}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{9B4E51B2-F0C6-42BA-9063-46195F99A429}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{9F8203AD-6FBC-4265-9D7D-D06A8A5B8493}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{2947E91C-467C-414C-BA3E-83A46B0DA6EB}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{011A1B0E-8FB2-4138-9B4E-2788013ED95E}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{59B4844D-2A16-408A-9DF4-CDCC9CB80715}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{D42E53D0-9D41-4199-9F0C-7262C16A9EBA}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{6BB2C8D6-9669-4F0F-AE74-5B9753A44E7E}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{6E1530B5-6DFC-499A-8334-C13D198E54CB}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{BE5A1A7C-3079-4AF5-BF64-64655F6E8199}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{833704B6-759A-4269-978D-E4B8E7E565C6}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{90D57D07-93B9-4DBB-B911-9912DB79526A}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{EEE5BBC1-6778-4CB8-A0E2-7E63AFE805B6}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{0D4FC283-70C8-4C2E-ACE1-E3374C9CA68D}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{B3C4A19A-CC71-4717-BBF3-CBBF2084D7DD}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{467E308E-99F9-41B8-A794-E52E0D43E7E8}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{C4B610C7-6379-44C5-A0DC-DB68B9030276}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{3E9668FA-A512-4CA9-B5DA-5B6EF5868BC1}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{4FA19E32-E7F1-4868-9E73-B165AAF6513A}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{509BF61B-670B-4DEB-9428-0EC633F356B7}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{F09BAD67-F959-427D-A6BD-19B1C2E6C326}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{BE14833D-CE03-456C-A503-F02196761324}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{945FF6FC-419A-4079-AA7F-681A6E8C4C05}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{EDDE1D6F-C8F4-407D-B74D-775E25EABCA2}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{4ACBA527-15BB-4FA0-BE9A-D28B2F8CE85B}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{D54B2D06-B2A7-45DF-951A-80C8068A43AA}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{0E695CD4-B45C-41EB-A00D-C524DDC131E1}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{AD41E98E-0751-451D-BE18-EFD3FDDF99C9}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{003E904F-5C71-4E9A-8F59-85609D7B6DCC}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{CF15B706-85F7-4B47-91C9-30AAE51275D7}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12488,7 +12510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U844"/>
+  <dimension ref="A1:U845"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -64886,68 +64908,129 @@
       </c>
     </row>
     <row r="844" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A844" s="9">
+      <c r="A844" s="4">
         <v>843</v>
       </c>
-      <c r="B844" s="10"/>
-      <c r="C844" s="11" t="s">
+      <c r="B844" s="5"/>
+      <c r="C844" s="6" t="s">
         <v>3768</v>
       </c>
-      <c r="D844" s="10"/>
-      <c r="E844" s="11" t="s">
+      <c r="D844" s="5"/>
+      <c r="E844" s="6" t="s">
         <v>3769</v>
       </c>
-      <c r="F844" s="11" t="s">
+      <c r="F844" s="6" t="s">
         <v>3770</v>
       </c>
-      <c r="G844" s="11" t="s">
+      <c r="G844" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H844" s="11" t="s">
+      <c r="H844" s="6" t="s">
         <v>674</v>
       </c>
-      <c r="I844" s="11" t="s">
+      <c r="I844" s="6" t="s">
         <v>27</v>
       </c>
       <c r="J844" s="13" t="s">
         <v>2804</v>
       </c>
-      <c r="K844" s="11" t="s">
+      <c r="K844" s="6" t="s">
         <v>2805</v>
       </c>
-      <c r="L844" s="11" t="s">
+      <c r="L844" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="M844" s="11" t="s">
+      <c r="M844" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="N844" s="11" t="s">
+      <c r="N844" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="O844" s="11" t="s">
+      <c r="O844" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="P844" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q844" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R844" s="11" t="s">
+      <c r="P844" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q844" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R844" s="6" t="s">
         <v>3771</v>
       </c>
-      <c r="S844" s="11" t="s">
+      <c r="S844" s="6" t="s">
         <v>3772</v>
       </c>
-      <c r="T844" s="11" t="s">
+      <c r="T844" s="6" t="s">
         <v>2546</v>
       </c>
-      <c r="U844" s="12" t="s">
+      <c r="U844" s="7" t="s">
         <v>3773</v>
       </c>
     </row>
+    <row r="845" spans="1:21" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A845" s="9">
+        <v>844</v>
+      </c>
+      <c r="B845" s="10"/>
+      <c r="C845" s="11" t="s">
+        <v>3774</v>
+      </c>
+      <c r="D845" s="10"/>
+      <c r="E845" s="11" t="s">
+        <v>3775</v>
+      </c>
+      <c r="F845" s="11" t="s">
+        <v>3776</v>
+      </c>
+      <c r="G845" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="H845" s="11" t="s">
+        <v>3777</v>
+      </c>
+      <c r="I845" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="J845" s="13" t="s">
+        <v>3778</v>
+      </c>
+      <c r="K845" s="11" t="s">
+        <v>3779</v>
+      </c>
+      <c r="L845" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M845" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N845" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="O845" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="P845" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q845" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R845" s="11" t="s">
+        <v>2235</v>
+      </c>
+      <c r="S845" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="T845" s="11" t="s">
+        <v>906</v>
+      </c>
+      <c r="U845" s="12" t="s">
+        <v>3780</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="s2rP42dTQE53C1eVQVdk7+lZMwEGQfiBYM9D+hFvTLLhwJPZSCaz79aUKRXnIYr9OSu8PeGekr1b4xF+XZVXKA==" saltValue="S2KG9+uJttSJ2A8ZPczvdQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="s+SJrcbszldW/OS76TRMT1J/hyw1S5pcMRQagkpZ6JPuqZplt1d18pl9SZ8vVTZBFQRxszjbGvKf90hxGfDB1Q==" saltValue="8DPEUaaLqrWZkMdtOHZqMw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KANU\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D16E2BC-EBD8-4C9F-B721-516B8A4822A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8235"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15721" uniqueCount="3785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15817" uniqueCount="3818">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11242,10 +11243,7 @@
     <t>Pet 200gm Powder Clear 63mm 21gm Jar</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>Pending Matrix</t>
+    <t>405</t>
   </si>
   <si>
     <t>Powder</t>
@@ -11424,12 +11422,115 @@
   </si>
   <si>
     <t>Pet 120CC ASB Tablet Clear 38mm 18gm Jar MPCI</t>
+  </si>
+  <si>
+    <t>MP0447</t>
+  </si>
+  <si>
+    <t>MP0447.1</t>
+  </si>
+  <si>
+    <t>Pet 1.5L Square Goli Clear 83mm 39gm Jar</t>
+  </si>
+  <si>
+    <t>Square Goli</t>
+  </si>
+  <si>
+    <t>110.00 ± 1.50</t>
+  </si>
+  <si>
+    <t>193.00 ± 1.50</t>
+  </si>
+  <si>
+    <t>39.00 ± 2.00</t>
+  </si>
+  <si>
+    <t>1550.00 ± 20.00</t>
+  </si>
+  <si>
+    <t>MP0470</t>
+  </si>
+  <si>
+    <t>MP0470.1</t>
+  </si>
+  <si>
+    <t>Pet 30ml JLI Clear Short Neck 19mm 5.5gm Bottle</t>
+  </si>
+  <si>
+    <t>1995</t>
+  </si>
+  <si>
+    <t>19 Pcs x 15 Rows = 285 Pcs</t>
+  </si>
+  <si>
+    <t>26.80 ± 0.80</t>
+  </si>
+  <si>
+    <t>83.50 ± 0.80</t>
+  </si>
+  <si>
+    <t>5.50 ± 0.50</t>
+  </si>
+  <si>
+    <t>37.00 ± 3.00</t>
+  </si>
+  <si>
+    <t>MP0474</t>
+  </si>
+  <si>
+    <t>MP0474.1</t>
+  </si>
+  <si>
+    <t>Pet 1Kg Avon Clear 83mm 50gm Jar</t>
+  </si>
+  <si>
+    <t>MP0472</t>
+  </si>
+  <si>
+    <t>MP0472.1</t>
+  </si>
+  <si>
+    <t>Pet 30ml D Type Hair Oil Clear Short Neck 19mm 5.5gm Bottle</t>
+  </si>
+  <si>
+    <t>1967</t>
+  </si>
+  <si>
+    <t>26 Pcs x 6 Rows = 156 Pcs
+25 Pcs x 5 Rows = 125 Pcs</t>
+  </si>
+  <si>
+    <t>D Type Hair Oil</t>
+  </si>
+  <si>
+    <t>39.00 ± 0.80</t>
+  </si>
+  <si>
+    <t>86.30 ± 0.80</t>
+  </si>
+  <si>
+    <t>36.00 ± 3.00</t>
+  </si>
+  <si>
+    <t>MP0451</t>
+  </si>
+  <si>
+    <t>MP0451.1</t>
+  </si>
+  <si>
+    <t>Pet 150CC ASB Tablet Amber 38mm 20gm Jar MPCI</t>
+  </si>
+  <si>
+    <t>105.50 ± 1.20</t>
+  </si>
+  <si>
+    <t>170.00 ± 5.00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -11580,34 +11681,34 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -11629,9 +11730,9 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -11651,21 +11752,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11688,21 +11774,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11727,21 +11798,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11766,21 +11822,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11805,21 +11846,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11844,21 +11870,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11883,21 +11894,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11922,21 +11918,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -11961,21 +11942,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12000,21 +11966,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12039,21 +11990,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12078,21 +12014,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12117,21 +12038,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12156,21 +12062,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12195,21 +12086,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12234,21 +12110,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12273,21 +12134,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12334,21 +12180,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -12395,22 +12226,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -12462,21 +12277,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -12493,30 +12293,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:U847" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U847"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7ACAB3D-AC78-47D5-81AE-33BD08BE3494}" name="Table1" displayName="Table1" ref="A1:U852" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U852" xr:uid="{D7ACAB3D-AC78-47D5-81AE-33BD08BE3494}"/>
   <tableColumns count="21">
-    <tableColumn id="1" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{0E466952-5BCD-4DBD-B7E0-94B822111115}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{94CFF99D-BDC8-46BB-8611-2C58783F62D6}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{48812F9D-3F1D-4BB0-B488-442FBFCB643B}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{16F470E3-FF94-4826-B6AF-3D9096C54514}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{7F5CFA63-21FA-4D5A-A7DC-86D63DD06FC2}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{D04041CE-09A9-4AB8-9986-FD0B72D39061}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{B088E793-5D8E-47C3-B17E-8976FE184B2C}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{B96EF495-338D-4355-9634-0DF56864B888}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{C0FDA1BC-B48D-48F5-9AFC-D50E079A2E17}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{5CAC9926-9171-4E60-8CD4-0A90E97E9440}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{CBD6D1A9-3D03-4D22-BC07-341610ABD5D2}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{42301E5C-ACCE-4E7F-A954-C672328B140F}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{87E1B73B-2D74-46B2-96C4-D3FCAA80D516}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{DD2E8F3F-1FC5-4E33-AD54-96B1C0F4EEC9}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{2F3F91F5-A260-4EBE-B03C-A7A87C1E2426}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{9DAECD21-9A7C-471D-89C4-BE7110C2F7BE}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{BE9BBD67-6EB6-43A1-AD65-17EC8AAB6BCD}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{64F8EDE7-2095-40C0-A74E-9AE1A5A5E0FF}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{0B8903B1-A8D4-4690-BD66-E33246B810C8}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{A3215038-E5B2-4B76-BFCD-E2001696F644}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{2F65A95A-4221-48C5-BD00-1D63995D82FA}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12539,7 +12339,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -12551,7 +12351,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -12568,9 +12368,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -12598,14 +12398,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -12633,6 +12450,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -12784,8 +12618,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U847"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U852"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -64476,37 +64310,49 @@
         <v>3723</v>
       </c>
       <c r="G832" s="6" t="s">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="H832" s="6" t="s">
         <v>3724</v>
       </c>
       <c r="I832" s="6" t="s">
-        <v>3724</v>
+        <v>61</v>
       </c>
       <c r="J832" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="K832" s="6" t="s">
         <v>3725</v>
       </c>
-      <c r="K832" s="6" t="s">
+      <c r="L832" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="M832" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="N832" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O832" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P832" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q832" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R832" s="6" t="s">
         <v>3726</v>
       </c>
-      <c r="L832" s="5"/>
-      <c r="M832" s="5"/>
-      <c r="N832" s="5"/>
-      <c r="O832" s="5"/>
-      <c r="P832" s="5"/>
-      <c r="Q832" s="5"/>
-      <c r="R832" s="6" t="s">
+      <c r="S832" s="6" t="s">
         <v>3727</v>
       </c>
-      <c r="S832" s="6" t="s">
+      <c r="T832" s="6" t="s">
         <v>3728</v>
       </c>
-      <c r="T832" s="6" t="s">
+      <c r="U832" s="7" t="s">
         <v>3729</v>
-      </c>
-      <c r="U832" s="7" t="s">
-        <v>3730</v>
       </c>
     </row>
     <row r="833" spans="1:21" x14ac:dyDescent="0.2">
@@ -64521,10 +64367,10 @@
       </c>
       <c r="D833" s="5"/>
       <c r="E833" s="6" t="s">
+        <v>3730</v>
+      </c>
+      <c r="F833" s="6" t="s">
         <v>3731</v>
-      </c>
-      <c r="F833" s="6" t="s">
-        <v>3732</v>
       </c>
       <c r="G833" s="6" t="s">
         <v>25</v>
@@ -64578,14 +64424,14 @@
       </c>
       <c r="B834" s="5"/>
       <c r="C834" s="6" t="s">
-        <v>3733</v>
+        <v>3732</v>
       </c>
       <c r="D834" s="5"/>
       <c r="E834" s="6" t="s">
+        <v>3733</v>
+      </c>
+      <c r="F834" s="6" t="s">
         <v>3734</v>
-      </c>
-      <c r="F834" s="6" t="s">
-        <v>3735</v>
       </c>
       <c r="G834" s="6" t="s">
         <v>25</v>
@@ -64639,14 +64485,14 @@
       </c>
       <c r="B835" s="5"/>
       <c r="C835" s="6" t="s">
-        <v>3736</v>
+        <v>3735</v>
       </c>
       <c r="D835" s="5"/>
       <c r="E835" s="6" t="s">
+        <v>3736</v>
+      </c>
+      <c r="F835" s="6" t="s">
         <v>3737</v>
-      </c>
-      <c r="F835" s="6" t="s">
-        <v>3738</v>
       </c>
       <c r="G835" s="6" t="s">
         <v>25</v>
@@ -64658,10 +64504,10 @@
         <v>146</v>
       </c>
       <c r="J835" s="6" t="s">
+        <v>3738</v>
+      </c>
+      <c r="K835" s="6" t="s">
         <v>3739</v>
-      </c>
-      <c r="K835" s="6" t="s">
-        <v>3740</v>
       </c>
       <c r="L835" s="6" t="s">
         <v>258</v>
@@ -64682,16 +64528,16 @@
         <v>35</v>
       </c>
       <c r="R835" s="6" t="s">
+        <v>3740</v>
+      </c>
+      <c r="S835" s="6" t="s">
         <v>3741</v>
-      </c>
-      <c r="S835" s="6" t="s">
-        <v>3742</v>
       </c>
       <c r="T835" s="6" t="s">
         <v>2316</v>
       </c>
       <c r="U835" s="7" t="s">
-        <v>3743</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="836" spans="1:21" x14ac:dyDescent="0.2">
@@ -64704,10 +64550,10 @@
       </c>
       <c r="D836" s="5"/>
       <c r="E836" s="6" t="s">
+        <v>3743</v>
+      </c>
+      <c r="F836" s="6" t="s">
         <v>3744</v>
-      </c>
-      <c r="F836" s="6" t="s">
-        <v>3745</v>
       </c>
       <c r="G836" s="6" t="s">
         <v>239</v>
@@ -64761,26 +64607,26 @@
       </c>
       <c r="B837" s="5"/>
       <c r="C837" s="6" t="s">
-        <v>3746</v>
+        <v>3745</v>
       </c>
       <c r="D837" s="5"/>
       <c r="E837" s="6" t="s">
+        <v>3746</v>
+      </c>
+      <c r="F837" s="6" t="s">
         <v>3747</v>
-      </c>
-      <c r="F837" s="6" t="s">
-        <v>3748</v>
       </c>
       <c r="G837" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H837" s="6" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
       <c r="I837" s="6" t="s">
         <v>269</v>
       </c>
       <c r="J837" s="6" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
       <c r="K837" s="6" t="s">
         <v>29</v>
@@ -64804,16 +64650,16 @@
         <v>275</v>
       </c>
       <c r="R837" s="6" t="s">
+        <v>3750</v>
+      </c>
+      <c r="S837" s="6" t="s">
         <v>3751</v>
-      </c>
-      <c r="S837" s="6" t="s">
-        <v>3752</v>
       </c>
       <c r="T837" s="6" t="s">
         <v>251</v>
       </c>
       <c r="U837" s="7" t="s">
-        <v>3753</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="838" spans="1:21" x14ac:dyDescent="0.2">
@@ -64826,10 +64672,10 @@
       </c>
       <c r="D838" s="5"/>
       <c r="E838" s="6" t="s">
+        <v>3753</v>
+      </c>
+      <c r="F838" s="6" t="s">
         <v>3754</v>
-      </c>
-      <c r="F838" s="6" t="s">
-        <v>3755</v>
       </c>
       <c r="G838" s="6" t="s">
         <v>25</v>
@@ -64887,10 +64733,10 @@
       </c>
       <c r="D839" s="5"/>
       <c r="E839" s="6" t="s">
+        <v>3755</v>
+      </c>
+      <c r="F839" s="6" t="s">
         <v>3756</v>
-      </c>
-      <c r="F839" s="6" t="s">
-        <v>3757</v>
       </c>
       <c r="G839" s="6" t="s">
         <v>25</v>
@@ -64948,10 +64794,10 @@
       </c>
       <c r="D840" s="5"/>
       <c r="E840" s="6" t="s">
+        <v>3757</v>
+      </c>
+      <c r="F840" s="6" t="s">
         <v>3758</v>
-      </c>
-      <c r="F840" s="6" t="s">
-        <v>3759</v>
       </c>
       <c r="G840" s="6" t="s">
         <v>25</v>
@@ -65009,22 +64855,22 @@
       </c>
       <c r="D841" s="5"/>
       <c r="E841" s="6" t="s">
+        <v>3759</v>
+      </c>
+      <c r="F841" s="6" t="s">
         <v>3760</v>
-      </c>
-      <c r="F841" s="6" t="s">
-        <v>3761</v>
       </c>
       <c r="G841" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H841" s="6" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
       <c r="I841" s="6" t="s">
         <v>269</v>
       </c>
       <c r="J841" s="6" t="s">
-        <v>3763</v>
+        <v>3762</v>
       </c>
       <c r="K841" s="6" t="s">
         <v>449</v>
@@ -65070,10 +64916,10 @@
       </c>
       <c r="D842" s="5"/>
       <c r="E842" s="6" t="s">
+        <v>3763</v>
+      </c>
+      <c r="F842" s="6" t="s">
         <v>3764</v>
-      </c>
-      <c r="F842" s="6" t="s">
-        <v>3765</v>
       </c>
       <c r="G842" s="6" t="s">
         <v>25</v>
@@ -65131,10 +64977,10 @@
       </c>
       <c r="D843" s="5"/>
       <c r="E843" s="6" t="s">
+        <v>3765</v>
+      </c>
+      <c r="F843" s="6" t="s">
         <v>3766</v>
-      </c>
-      <c r="F843" s="6" t="s">
-        <v>3767</v>
       </c>
       <c r="G843" s="6" t="s">
         <v>25</v>
@@ -65188,14 +65034,14 @@
       </c>
       <c r="B844" s="5"/>
       <c r="C844" s="6" t="s">
-        <v>3768</v>
+        <v>3767</v>
       </c>
       <c r="D844" s="5"/>
       <c r="E844" s="6" t="s">
+        <v>3768</v>
+      </c>
+      <c r="F844" s="6" t="s">
         <v>3769</v>
-      </c>
-      <c r="F844" s="6" t="s">
-        <v>3770</v>
       </c>
       <c r="G844" s="6" t="s">
         <v>25</v>
@@ -65231,16 +65077,16 @@
         <v>35</v>
       </c>
       <c r="R844" s="6" t="s">
+        <v>3770</v>
+      </c>
+      <c r="S844" s="6" t="s">
         <v>3771</v>
-      </c>
-      <c r="S844" s="6" t="s">
-        <v>3772</v>
       </c>
       <c r="T844" s="6" t="s">
         <v>2546</v>
       </c>
       <c r="U844" s="7" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="845" spans="1:21" x14ac:dyDescent="0.2">
@@ -65249,29 +65095,29 @@
       </c>
       <c r="B845" s="5"/>
       <c r="C845" s="6" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="D845" s="5"/>
       <c r="E845" s="6" t="s">
+        <v>3774</v>
+      </c>
+      <c r="F845" s="6" t="s">
         <v>3775</v>
-      </c>
-      <c r="F845" s="6" t="s">
-        <v>3776</v>
       </c>
       <c r="G845" s="6" t="s">
         <v>239</v>
       </c>
       <c r="H845" s="6" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="I845" s="6" t="s">
         <v>99</v>
       </c>
       <c r="J845" s="6" t="s">
+        <v>3777</v>
+      </c>
+      <c r="K845" s="6" t="s">
         <v>3778</v>
-      </c>
-      <c r="K845" s="6" t="s">
-        <v>3779</v>
       </c>
       <c r="L845" s="6" t="s">
         <v>63</v>
@@ -65301,7 +65147,7 @@
         <v>906</v>
       </c>
       <c r="U845" s="7" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
     </row>
     <row r="846" spans="1:21" x14ac:dyDescent="0.2">
@@ -65314,10 +65160,10 @@
       </c>
       <c r="D846" s="5"/>
       <c r="E846" s="6" t="s">
+        <v>3780</v>
+      </c>
+      <c r="F846" s="6" t="s">
         <v>3781</v>
-      </c>
-      <c r="F846" s="6" t="s">
-        <v>3782</v>
       </c>
       <c r="G846" s="6" t="s">
         <v>136</v>
@@ -65366,68 +65212,373 @@
       </c>
     </row>
     <row r="847" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A847" s="9">
+      <c r="A847" s="4">
         <v>846</v>
       </c>
-      <c r="B847" s="10"/>
-      <c r="C847" s="11" t="s">
+      <c r="B847" s="5"/>
+      <c r="C847" s="6" t="s">
         <v>3261</v>
       </c>
-      <c r="D847" s="10"/>
-      <c r="E847" s="11" t="s">
+      <c r="D847" s="5"/>
+      <c r="E847" s="6" t="s">
+        <v>3782</v>
+      </c>
+      <c r="F847" s="6" t="s">
         <v>3783</v>
       </c>
-      <c r="F847" s="11" t="s">
+      <c r="G847" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H847" s="6" t="s">
+        <v>3059</v>
+      </c>
+      <c r="I847" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J847" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K847" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="L847" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M847" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N847" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="O847" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P847" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q847" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R847" s="6" t="s">
+        <v>3264</v>
+      </c>
+      <c r="S847" s="6" t="s">
+        <v>3265</v>
+      </c>
+      <c r="T847" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="U847" s="7" t="s">
+        <v>3266</v>
+      </c>
+    </row>
+    <row r="848" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A848" s="4">
+        <v>847</v>
+      </c>
+      <c r="B848" s="5"/>
+      <c r="C848" s="6" t="s">
         <v>3784</v>
       </c>
-      <c r="G847" s="11" t="s">
+      <c r="D848" s="5"/>
+      <c r="E848" s="6" t="s">
+        <v>3785</v>
+      </c>
+      <c r="F848" s="6" t="s">
+        <v>3786</v>
+      </c>
+      <c r="G848" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H847" s="11" t="s">
-        <v>3059</v>
-      </c>
-      <c r="I847" s="11" t="s">
+      <c r="H848" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="I848" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="J848" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="K848" s="6" t="s">
+        <v>3787</v>
+      </c>
+      <c r="L848" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M848" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N848" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="O848" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P848" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q848" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="R848" s="6" t="s">
+        <v>3788</v>
+      </c>
+      <c r="S848" s="6" t="s">
+        <v>3789</v>
+      </c>
+      <c r="T848" s="6" t="s">
+        <v>3790</v>
+      </c>
+      <c r="U848" s="7" t="s">
+        <v>3791</v>
+      </c>
+    </row>
+    <row r="849" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A849" s="4">
+        <v>848</v>
+      </c>
+      <c r="B849" s="5"/>
+      <c r="C849" s="6" t="s">
+        <v>3792</v>
+      </c>
+      <c r="D849" s="5"/>
+      <c r="E849" s="6" t="s">
+        <v>3793</v>
+      </c>
+      <c r="F849" s="6" t="s">
+        <v>3794</v>
+      </c>
+      <c r="G849" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H849" s="6" t="s">
+        <v>3795</v>
+      </c>
+      <c r="I849" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J847" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="K847" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="L847" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M847" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="N847" s="11" t="s">
+      <c r="J849" s="6" t="s">
+        <v>3796</v>
+      </c>
+      <c r="K849" s="6" t="s">
+        <v>2288</v>
+      </c>
+      <c r="L849" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M849" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N849" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O849" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P849" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q849" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R849" s="6" t="s">
+        <v>3797</v>
+      </c>
+      <c r="S849" s="6" t="s">
+        <v>3798</v>
+      </c>
+      <c r="T849" s="6" t="s">
+        <v>3799</v>
+      </c>
+      <c r="U849" s="7" t="s">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="850" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A850" s="4">
+        <v>849</v>
+      </c>
+      <c r="B850" s="5"/>
+      <c r="C850" s="6" t="s">
+        <v>3801</v>
+      </c>
+      <c r="D850" s="5"/>
+      <c r="E850" s="6" t="s">
+        <v>3802</v>
+      </c>
+      <c r="F850" s="6" t="s">
+        <v>3803</v>
+      </c>
+      <c r="G850" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H850" s="6" t="s">
+        <v>3748</v>
+      </c>
+      <c r="I850" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="J850" s="6" t="s">
+        <v>3749</v>
+      </c>
+      <c r="K850" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L850" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M850" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N850" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="O850" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P850" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q850" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="R850" s="6" t="s">
+        <v>3750</v>
+      </c>
+      <c r="S850" s="6" t="s">
+        <v>3751</v>
+      </c>
+      <c r="T850" s="6" t="s">
+        <v>2597</v>
+      </c>
+      <c r="U850" s="7" t="s">
+        <v>3752</v>
+      </c>
+    </row>
+    <row r="851" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A851" s="4">
+        <v>850</v>
+      </c>
+      <c r="B851" s="5"/>
+      <c r="C851" s="6" t="s">
+        <v>3804</v>
+      </c>
+      <c r="D851" s="5"/>
+      <c r="E851" s="6" t="s">
+        <v>3805</v>
+      </c>
+      <c r="F851" s="6" t="s">
+        <v>3806</v>
+      </c>
+      <c r="G851" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H851" s="6" t="s">
+        <v>3807</v>
+      </c>
+      <c r="I851" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J851" s="6" t="s">
+        <v>3808</v>
+      </c>
+      <c r="K851" s="6" t="s">
+        <v>3809</v>
+      </c>
+      <c r="L851" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M851" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N851" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O851" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P851" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q851" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R851" s="6" t="s">
+        <v>3810</v>
+      </c>
+      <c r="S851" s="6" t="s">
+        <v>3811</v>
+      </c>
+      <c r="T851" s="6" t="s">
+        <v>3799</v>
+      </c>
+      <c r="U851" s="7" t="s">
+        <v>3812</v>
+      </c>
+    </row>
+    <row r="852" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A852" s="9">
+        <v>851</v>
+      </c>
+      <c r="B852" s="10"/>
+      <c r="C852" s="11" t="s">
+        <v>3813</v>
+      </c>
+      <c r="D852" s="10"/>
+      <c r="E852" s="11" t="s">
+        <v>3814</v>
+      </c>
+      <c r="F852" s="11" t="s">
+        <v>3815</v>
+      </c>
+      <c r="G852" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H852" s="11" t="s">
+        <v>3208</v>
+      </c>
+      <c r="I852" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J852" s="11" t="s">
+        <v>903</v>
+      </c>
+      <c r="K852" s="11" t="s">
+        <v>3060</v>
+      </c>
+      <c r="L852" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M852" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N852" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="O847" s="11" t="s">
+      <c r="O852" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="P847" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q847" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R847" s="11" t="s">
-        <v>3264</v>
-      </c>
-      <c r="S847" s="11" t="s">
-        <v>3265</v>
-      </c>
-      <c r="T847" s="11" t="s">
-        <v>858</v>
-      </c>
-      <c r="U847" s="12" t="s">
-        <v>3266</v>
+      <c r="P852" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q852" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R852" s="11" t="s">
+        <v>3137</v>
+      </c>
+      <c r="S852" s="11" t="s">
+        <v>3816</v>
+      </c>
+      <c r="T852" s="11" t="s">
+        <v>2138</v>
+      </c>
+      <c r="U852" s="12" t="s">
+        <v>3817</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1gRCGAYD3rC0rM4U0u+pLfJKkMhz0LxQRdDpOY+8ZPvAf8r9RvFtE+FMNPxBwzBX+kuox6RlfdG+xwAiYavriw==" saltValue="ekwHNzdiAZ8PtNHeFV8DSA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="WJumHy/FOpcSnL1032aq585tvBXSHpQ9s8wsVznm5vPCGMqoZwHSdlEIE9JVknvLaD27Fot42/BwVLqZTQecQA==" saltValue="h7aTxNoDXeKM0wkTYhaOLA==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/FGVAULT.xlsx
+++ b/FGVAULT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D16E2BC-EBD8-4C9F-B721-516B8A4822A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BF0C64-4C16-40B4-8882-AB076906FDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15817" uniqueCount="3818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15835" uniqueCount="3820">
   <si>
     <t>PDS No.</t>
   </si>
@@ -11525,6 +11525,12 @@
   </si>
   <si>
     <t>170.00 ± 5.00</t>
+  </si>
+  <si>
+    <t>MP0277.3</t>
+  </si>
+  <si>
+    <t>Pet 120ml Round Green 25mm 12.5gm Bottle</t>
   </si>
 </sst>
 </file>
@@ -12293,30 +12299,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7ACAB3D-AC78-47D5-81AE-33BD08BE3494}" name="Table1" displayName="Table1" ref="A1:U852" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <autoFilter ref="A1:U852" xr:uid="{D7ACAB3D-AC78-47D5-81AE-33BD08BE3494}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{37E0A1A8-18AB-435A-8EA2-07384ABF1757}" name="Table1" displayName="Table1" ref="A1:U853" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+  <autoFilter ref="A1:U853" xr:uid="{37E0A1A8-18AB-435A-8EA2-07384ABF1757}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{0E466952-5BCD-4DBD-B7E0-94B822111115}" name="PDS No." dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{94CFF99D-BDC8-46BB-8611-2C58783F62D6}" name="STATUS" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{48812F9D-3F1D-4BB0-B488-442FBFCB643B}" name="Product Code" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{16F470E3-FF94-4826-B6AF-3D9096C54514}" name="Old Item Code" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{7F5CFA63-21FA-4D5A-A7DC-86D63DD06FC2}" name="Item Code" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{D04041CE-09A9-4AB8-9986-FD0B72D39061}" name="Item Name" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{B088E793-5D8E-47C3-B17E-8976FE184B2C}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{B96EF495-338D-4355-9634-0DF56864B888}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{C0FDA1BC-B48D-48F5-9AFC-D50E079A2E17}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{5CAC9926-9171-4E60-8CD4-0A90E97E9440}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{CBD6D1A9-3D03-4D22-BC07-341610ABD5D2}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{42301E5C-ACCE-4E7F-A954-C672328B140F}" name="Corrugated Box Code" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{87E1B73B-2D74-46B2-96C4-D3FCAA80D516}" name="Corrugated Box Size" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{DD2E8F3F-1FC5-4E33-AD54-96B1C0F4EEC9}" name="Pouch Product Code" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{2F3F91F5-A260-4EBE-B03C-A7A87C1E2426}" name="Pouch Size" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{9DAECD21-9A7C-471D-89C4-BE7110C2F7BE}" name="Tape Roll Product Code" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{BE9BBD67-6EB6-43A1-AD65-17EC8AAB6BCD}" name="Tape Roll Size" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{64F8EDE7-2095-40C0-A74E-9AE1A5A5E0FF}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{0B8903B1-A8D4-4690-BD66-E33246B810C8}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{A3215038-E5B2-4B76-BFCD-E2001696F644}" name="Technical DataSheet::Weight" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{2F65A95A-4221-48C5-BD00-1D63995D82FA}" name="Technical DataSheet::OFC" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{A8A5CA21-9D9B-4A69-82CF-5670BBE1C4F6}" name="PDS No." dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{18F82B40-077A-406D-ACA2-34E3108A8A1E}" name="STATUS" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{D773AADF-4D98-4FB5-B182-1565BBB4A13B}" name="Product Code" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{2D469E3C-9C5C-4A77-A9E0-B263CF2E3C8E}" name="Old Item Code" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{811FB727-3954-4B08-93B2-9122F0D8B168}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{81B60EDC-7AB9-4116-92EA-803C3F2EE48D}" name="Item Name" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{E1487E29-D932-41E8-928C-857813411778}" name="List of Matrix::Packing Direction of Bottles" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{4C5A81A1-27DF-49BC-9F24-231606B27897}" name="List of Matrix::Total Pcs" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{288F7526-A613-4016-97BF-BD09A89BADFC}" name="List of Matrix::Total Pouch Used" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{0182023F-807C-4D0F-AC35-6B1FBE521971}" name="List of Matrix::Packing Matrix per Tray" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{1604DB0F-BC21-4E8C-9E24-4EC9A9E39666}" name="Technical DataSheet::Product Shape" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{B71A96E2-1DA6-46D0-86E4-9DFABC33B648}" name="Corrugated Box Code" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{5DF08D22-33D2-4F47-A155-040700D92FE8}" name="Corrugated Box Size" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{0002B301-9790-4334-869D-DEB27874D3FC}" name="Pouch Product Code" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{E68AC660-108D-4AD9-A08E-D9EAD14F64A2}" name="Pouch Size" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{30FF466E-ACDA-40A7-8C33-503375DEA73D}" name="Tape Roll Product Code" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{B40FC791-BBBF-40D2-82B4-9E88C539F05C}" name="Tape Roll Size" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{DB721051-171B-4DFE-B196-B4E40235F76D}" name="Technical DataSheet::Body Dia Major" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{140BB9BD-6C71-4C9C-8901-3D5BAE841C25}" name="Technical DataSheet::Total Height" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{F76C7FA9-3514-447C-973D-B77FB45BDAAB}" name="Technical DataSheet::Weight" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{2E5B29B4-9C66-4353-A512-C496127B62E6}" name="Technical DataSheet::OFC" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12619,7 +12625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U852"/>
+  <dimension ref="A1:U853"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -65517,68 +65523,129 @@
       </c>
     </row>
     <row r="852" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A852" s="9">
+      <c r="A852" s="4">
         <v>851</v>
       </c>
-      <c r="B852" s="10"/>
-      <c r="C852" s="11" t="s">
+      <c r="B852" s="5"/>
+      <c r="C852" s="6" t="s">
         <v>3813</v>
       </c>
-      <c r="D852" s="10"/>
-      <c r="E852" s="11" t="s">
+      <c r="D852" s="5"/>
+      <c r="E852" s="6" t="s">
         <v>3814</v>
       </c>
-      <c r="F852" s="11" t="s">
+      <c r="F852" s="6" t="s">
         <v>3815</v>
       </c>
-      <c r="G852" s="11" t="s">
+      <c r="G852" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H852" s="11" t="s">
+      <c r="H852" s="6" t="s">
         <v>3208</v>
       </c>
-      <c r="I852" s="11" t="s">
+      <c r="I852" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J852" s="11" t="s">
+      <c r="J852" s="6" t="s">
         <v>903</v>
       </c>
-      <c r="K852" s="11" t="s">
+      <c r="K852" s="6" t="s">
         <v>3060</v>
       </c>
-      <c r="L852" s="11" t="s">
+      <c r="L852" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="M852" s="11" t="s">
+      <c r="M852" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="N852" s="11" t="s">
+      <c r="N852" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="O852" s="11" t="s">
+      <c r="O852" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="P852" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q852" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="R852" s="11" t="s">
+      <c r="P852" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q852" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R852" s="6" t="s">
         <v>3137</v>
       </c>
-      <c r="S852" s="11" t="s">
+      <c r="S852" s="6" t="s">
         <v>3816</v>
       </c>
-      <c r="T852" s="11" t="s">
+      <c r="T852" s="6" t="s">
         <v>2138</v>
       </c>
-      <c r="U852" s="12" t="s">
+      <c r="U852" s="7" t="s">
         <v>3817</v>
       </c>
     </row>
+    <row r="853" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A853" s="9">
+        <v>852</v>
+      </c>
+      <c r="B853" s="10"/>
+      <c r="C853" s="11" t="s">
+        <v>808</v>
+      </c>
+      <c r="D853" s="10"/>
+      <c r="E853" s="11" t="s">
+        <v>3818</v>
+      </c>
+      <c r="F853" s="11" t="s">
+        <v>3819</v>
+      </c>
+      <c r="G853" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H853" s="11" t="s">
+        <v>812</v>
+      </c>
+      <c r="I853" s="11" t="s">
+        <v>813</v>
+      </c>
+      <c r="J853" s="11" t="s">
+        <v>814</v>
+      </c>
+      <c r="K853" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="L853" s="11" t="s">
+        <v>815</v>
+      </c>
+      <c r="M853" s="11" t="s">
+        <v>816</v>
+      </c>
+      <c r="N853" s="11" t="s">
+        <v>764</v>
+      </c>
+      <c r="O853" s="11" t="s">
+        <v>765</v>
+      </c>
+      <c r="P853" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q853" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R853" s="11" t="s">
+        <v>817</v>
+      </c>
+      <c r="S853" s="11" t="s">
+        <v>818</v>
+      </c>
+      <c r="T853" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="U853" s="12" t="s">
+        <v>819</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="WJumHy/FOpcSnL1032aq585tvBXSHpQ9s8wsVznm5vPCGMqoZwHSdlEIE9JVknvLaD27Fot42/BwVLqZTQecQA==" saltValue="h7aTxNoDXeKM0wkTYhaOLA==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="XWr3e3OCjhw/cNU9yoEnc9Jl0ibl1gV3wRkP8DAHxeS9xVFHMGxvReRuHvlrAT/bk2TtuwnsN1pPEeMFcLmJFg==" saltValue="L7sAqzD7Sg9Yg9weUQtCaw==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
